--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-08</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>3:29</v>
+        <v>4:27</v>
       </c>
       <c r="H2" t="str">
-        <v>Michael Bolton</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-08</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:59</v>
+        <v>3:26</v>
       </c>
       <c r="H3" t="str">
-        <v>mgk</v>
+        <v>Netflix</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-08</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:51</v>
+        <v>3:29</v>
       </c>
       <c r="H4" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-08</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:13</v>
+        <v>2:59</v>
       </c>
       <c r="H5" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-08</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:41</v>
+        <v>2:51</v>
       </c>
       <c r="H6" t="str">
-        <v>NICK JONAS</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-08</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>7:03</v>
+        <v>4:13</v>
       </c>
       <c r="H7" t="str">
-        <v>Take That</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-08</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>4:37</v>
+        <v>4:41</v>
       </c>
       <c r="H8" t="str">
-        <v>Cliff Richard</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-08</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:54</v>
+        <v>7:03</v>
       </c>
       <c r="H9" t="str">
-        <v>Bryan Adams</v>
+        <v>Take That</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-08</v>
@@ -758,10 +758,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:06</v>
+        <v>4:37</v>
       </c>
       <c r="H10" t="str">
-        <v>Anna Graves</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B11" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-08</v>
@@ -796,10 +796,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:21</v>
+        <v>3:54</v>
       </c>
       <c r="H11" t="str">
-        <v>George Birge</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B12" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-08</v>
@@ -834,10 +834,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:09</v>
+        <v>3:06</v>
       </c>
       <c r="H12" t="str">
-        <v>Warner Records</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B13" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-08</v>
@@ -872,10 +872,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:18</v>
+        <v>3:21</v>
       </c>
       <c r="H13" t="str">
-        <v>NICK JONAS</v>
+        <v>George Birge</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
+        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-08</v>
@@ -910,10 +910,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:08</v>
+        <v>4:09</v>
       </c>
       <c r="H14" t="str">
-        <v>Charlie Puth</v>
+        <v>Warner Records</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
+        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-08</v>
@@ -948,10 +948,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:03</v>
+        <v>4:18</v>
       </c>
       <c r="H15" t="str">
-        <v>Olivia Newton-John</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
       </c>
       <c r="B16" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
+        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-08</v>
@@ -986,10 +986,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:01</v>
+        <v>3:08</v>
       </c>
       <c r="H16" t="str">
-        <v>The Warning and Carin Leon</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
       </c>
       <c r="B17" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
+        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-08</v>
@@ -1024,10 +1024,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:05</v>
+        <v>4:03</v>
       </c>
       <c r="H17" t="str">
-        <v>Iman Fandi</v>
+        <v>Olivia Newton-John</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
       </c>
       <c r="B18" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
+        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-08</v>
@@ -1062,10 +1062,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:34</v>
+        <v>3:01</v>
       </c>
       <c r="H18" t="str">
-        <v>Megan Moroney</v>
+        <v>The Warning and Carin Leon</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Dylan Davidson - Escape Artist</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
       </c>
       <c r="B19" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
+        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-08</v>
@@ -1100,10 +1100,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:15</v>
+        <v>3:05</v>
       </c>
       <c r="H19" t="str">
-        <v>Dylan Davidson</v>
+        <v>Iman Fandi</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
+        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-08</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:16</v>
+        <v>3:34</v>
       </c>
       <c r="H20" t="str">
-        <v>Lady Gaga</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video)</v>
+        <v>Dylan Davidson - Escape Artist</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
+        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-08</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:53</v>
+        <v>3:15</v>
       </c>
       <c r="H21" t="str">
-        <v>Carlos Vives</v>
+        <v>Dylan Davidson</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
+        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
+        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-08</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>2:25</v>
+        <v>4:16</v>
       </c>
       <c r="H22" t="str">
-        <v>Monsieur Periné</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio)</v>
+        <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
+        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-08</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:09</v>
+        <v>3:53</v>
       </c>
       <c r="H23" t="str">
-        <v>The Happy Fits</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
+        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>chase (lyric vid) - Michael Aldag</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
+        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-08</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:45</v>
+        <v>2:25</v>
       </c>
       <c r="H24" t="str">
-        <v>Michael Aldag</v>
+        <v>Monsieur Periné</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
+        <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
+        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-08</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>4:07</v>
+        <v>4:09</v>
       </c>
       <c r="H25" t="str">
-        <v>Dermot Kennedy</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
+        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
+        <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
+        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-08</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:34</v>
+        <v>2:45</v>
       </c>
       <c r="H26" t="str">
-        <v>Marc Anthony</v>
+        <v>Michael Aldag</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
+        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
+        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-08</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>5:14</v>
+        <v>4:07</v>
       </c>
       <c r="H27" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
+        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-08</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:11</v>
+        <v>4:34</v>
       </c>
       <c r="H28" t="str">
-        <v>Michael Bolton</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Lachie Gill - Last Drive</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
+        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-08</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:40</v>
+        <v>5:14</v>
       </c>
       <c r="H29" t="str">
-        <v>Lachie Gill</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Lachie Gill - Last Drive - Lachie Gill</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
+        <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
+        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-08</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:45</v>
+        <v>3:11</v>
       </c>
       <c r="H30" t="str">
-        <v>Eli &amp; Fur</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
+        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Freya Skye - why'd you have to call</v>
+        <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
+        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-08</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:19</v>
+        <v>3:40</v>
       </c>
       <c r="H31" t="str">
-        <v>Freya Skye</v>
+        <v>Lachie Gill</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Freya Skye - why'd you have to call - Freya Skye</v>
+        <v>Lachie Gill - Last Drive - Lachie Gill</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
+        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-08</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:30</v>
+        <v>3:45</v>
       </c>
       <c r="H32" t="str">
-        <v>Jessie J</v>
+        <v>Eli &amp; Fur</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer)</v>
+        <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B33" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
+        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-08</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:24</v>
+        <v>4:19</v>
       </c>
       <c r="H33" t="str">
-        <v>Marc Anthony</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
+        <v>Freya Skye - why'd you have to call - Freya Skye</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
+        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-08</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:33</v>
+        <v>2:30</v>
       </c>
       <c r="H34" t="str">
-        <v>Clara Mae</v>
+        <v>Jessie J</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Metric - Victim of Luck (Official Music Video)</v>
+        <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B35" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
+        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-08</v>
@@ -1708,10 +1708,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:25</v>
+        <v>4:24</v>
       </c>
       <c r="H35" t="str">
-        <v>metricmusic</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
+        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B36" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
+        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-08</v>
@@ -1746,10 +1746,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:41</v>
+        <v>2:33</v>
       </c>
       <c r="H36" t="str">
-        <v>kesha</v>
+        <v>Clara Mae</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
+        <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
+        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-08</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:19</v>
+        <v>3:25</v>
       </c>
       <c r="H37" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>metricmusic</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
+        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
+        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-08</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:37</v>
+        <v>3:41</v>
       </c>
       <c r="H38" t="str">
-        <v>Vera Blue</v>
+        <v>kesha</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B39" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
+        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-08</v>
@@ -1860,10 +1860,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:08</v>
+        <v>3:19</v>
       </c>
       <c r="H39" t="str">
-        <v>Bob Moses</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B40" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
+        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-08</v>
@@ -1898,10 +1898,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:28</v>
+        <v>3:37</v>
       </c>
       <c r="H40" t="str">
-        <v>Marc Anthony</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B41" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
+        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-08</v>
@@ -1936,10 +1936,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:05</v>
+        <v>3:08</v>
       </c>
       <c r="H41" t="str">
-        <v>Marc Anthony</v>
+        <v>Bob Moses</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Loreen - Feels Like Heaven</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B42" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
+        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-08</v>
@@ -1974,10 +1974,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:14</v>
+        <v>3:28</v>
       </c>
       <c r="H42" t="str">
-        <v>Loreen</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Loreen - Feels Like Heaven - Loreen</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B43" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
+        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-08</v>
@@ -2012,10 +2012,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:36</v>
+        <v>5:05</v>
       </c>
       <c r="H43" t="str">
-        <v>Take That</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
+        <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B44" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
+        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-08</v>
@@ -2050,10 +2050,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>5:31</v>
+        <v>3:14</v>
       </c>
       <c r="H44" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Loreen</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
+        <v>Loreen - Feels Like Heaven - Loreen</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio)</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B45" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
+        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-08</v>
@@ -2088,10 +2088,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:37</v>
+        <v>3:36</v>
       </c>
       <c r="H45" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Take That</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-08</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:58</v>
+        <v>5:31</v>
       </c>
       <c r="H46" t="str">
-        <v>The Warning</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
+        <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-08</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>5:08</v>
+        <v>3:37</v>
       </c>
       <c r="H47" t="str">
-        <v>The Offspring</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
+        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B48" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-08</v>
@@ -2202,10 +2202,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:38</v>
+        <v>4:58</v>
       </c>
       <c r="H48" t="str">
-        <v>Roxette</v>
+        <v>The Warning</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B49" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-08</v>
@@ -2240,10 +2240,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:50</v>
+        <v>5:08</v>
       </c>
       <c r="H49" t="str">
-        <v>Jessie Ware</v>
+        <v>The Offspring</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-08</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:10</v>
+        <v>4:38</v>
       </c>
       <c r="H50" t="str">
-        <v>Joseph</v>
+        <v>Roxette</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-08</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:44</v>
+        <v>3:50</v>
       </c>
       <c r="H51" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-08</v>
@@ -2354,10 +2354,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:57</v>
+        <v>3:10</v>
       </c>
       <c r="H52" t="str">
-        <v>Take That</v>
+        <v>Joseph</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-08</v>
@@ -2392,10 +2392,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:07</v>
+        <v>2:44</v>
       </c>
       <c r="H53" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-08</v>
@@ -2430,10 +2430,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:47</v>
+        <v>2:57</v>
       </c>
       <c r="H54" t="str">
-        <v>Paris Paloma</v>
+        <v>Take That</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-08</v>
@@ -2468,10 +2468,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:22</v>
+        <v>3:07</v>
       </c>
       <c r="H55" t="str">
-        <v>Zara Larsson</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-08</v>
@@ -2506,10 +2506,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:48</v>
+        <v>4:47</v>
       </c>
       <c r="H56" t="str">
-        <v>only the poets</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-08</v>
@@ -2544,10 +2544,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:52</v>
+        <v>3:22</v>
       </c>
       <c r="H57" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B58" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-08</v>
@@ -2582,10 +2582,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:33</v>
+        <v>2:48</v>
       </c>
       <c r="H58" t="str">
-        <v>David Guetta</v>
+        <v>only the poets</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B59" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-08</v>
@@ -2620,10 +2620,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:41</v>
+        <v>2:52</v>
       </c>
       <c r="H59" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B60" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-08</v>
@@ -2658,10 +2658,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:01</v>
+        <v>3:33</v>
       </c>
       <c r="H60" t="str">
-        <v>Ella Langley</v>
+        <v>David Guetta</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B61" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-08</v>
@@ -2696,10 +2696,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:16</v>
+        <v>2:41</v>
       </c>
       <c r="H61" t="str">
-        <v>Dogpark</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-08</v>
@@ -2734,10 +2734,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:03</v>
+        <v>4:01</v>
       </c>
       <c r="H62" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-08</v>
@@ -2772,10 +2772,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:41</v>
+        <v>3:16</v>
       </c>
       <c r="H63" t="str">
-        <v>ERNEST</v>
+        <v>Dogpark</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B64" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-08</v>
@@ -2810,10 +2810,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:05</v>
+        <v>3:03</v>
       </c>
       <c r="H64" t="str">
-        <v>Labrinth</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-08</v>
@@ -2848,10 +2848,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:46</v>
+        <v>2:41</v>
       </c>
       <c r="H65" t="str">
-        <v>Grace VanderWaal</v>
+        <v>ERNEST</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B66" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-08</v>
@@ -2886,10 +2886,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:32</v>
+        <v>3:05</v>
       </c>
       <c r="H66" t="str">
-        <v>VOILÀ</v>
+        <v>Labrinth</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-08</v>
@@ -2924,10 +2924,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:42</v>
+        <v>2:46</v>
       </c>
       <c r="H67" t="str">
-        <v>Cannons</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-08</v>
@@ -2962,10 +2962,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:38</v>
+        <v>3:32</v>
       </c>
       <c r="H68" t="str">
-        <v>Kylie Morgan</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B69" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-08</v>
@@ -3000,10 +3000,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:10</v>
+        <v>3:42</v>
       </c>
       <c r="H69" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Cannons</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B70" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-08</v>
@@ -3038,10 +3038,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:57</v>
+        <v>2:38</v>
       </c>
       <c r="H70" t="str">
-        <v>Willie Nelson</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B71" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-08</v>
@@ -3076,10 +3076,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:19</v>
+        <v>3:10</v>
       </c>
       <c r="H71" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-08</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:04</v>
+        <v>3:57</v>
       </c>
       <c r="H72" t="str">
-        <v>India Martínez</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-08</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:16</v>
+        <v>2:19</v>
       </c>
       <c r="H73" t="str">
-        <v>Chelsea Cutler</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-08</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>5:58</v>
+        <v>4:04</v>
       </c>
       <c r="H74" t="str">
-        <v>TINI</v>
+        <v>India Martínez</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-08</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:26</v>
+        <v>2:16</v>
       </c>
       <c r="H75" t="str">
-        <v>Charley</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-08</v>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:05</v>
+        <v>5:58</v>
       </c>
       <c r="H76" t="str">
-        <v>Demi Lovato</v>
+        <v>TINI</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-08</v>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:16</v>
+        <v>3:26</v>
       </c>
       <c r="H77" t="str">
-        <v>Teddy Swims</v>
+        <v>Charley</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-08</v>
@@ -3342,10 +3342,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:14</v>
+        <v>4:05</v>
       </c>
       <c r="H78" t="str">
-        <v>Beck</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-08</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:57</v>
+        <v>3:16</v>
       </c>
       <c r="H79" t="str">
-        <v>The Offspring</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B80" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-08</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:10</v>
+        <v>3:14</v>
       </c>
       <c r="H80" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Beck</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B81" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-08</v>
@@ -3456,10 +3456,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:10</v>
+        <v>2:57</v>
       </c>
       <c r="H81" t="str">
-        <v>Jason Derulo</v>
+        <v>The Offspring</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-08</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:52</v>
+        <v>4:10</v>
       </c>
       <c r="H82" t="str">
-        <v>lights</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-08</v>
@@ -3532,10 +3532,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:50</v>
+        <v>2:10</v>
       </c>
       <c r="H83" t="str">
-        <v>Telenova</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B84" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-08</v>
@@ -3570,10 +3570,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>5:32</v>
+        <v>3:52</v>
       </c>
       <c r="H84" t="str">
-        <v>Marcin</v>
+        <v>lights</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B85" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-08</v>
@@ -3608,10 +3608,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:27</v>
+        <v>3:50</v>
       </c>
       <c r="H85" t="str">
-        <v>We Three</v>
+        <v>Telenova</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B86" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-08</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:01</v>
+        <v>5:32</v>
       </c>
       <c r="H86" t="str">
-        <v>Timebelle Official</v>
+        <v>Marcin</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-08</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:20</v>
+        <v>4:27</v>
       </c>
       <c r="H87" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>We Three</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-08</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:34</v>
+        <v>3:01</v>
       </c>
       <c r="H88" t="str">
-        <v>Clinton Kane</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-08</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:01</v>
+        <v>3:20</v>
       </c>
       <c r="H89" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-08</v>
@@ -3798,10 +3798,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:24</v>
+        <v>3:34</v>
       </c>
       <c r="H90" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-08</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>5:52</v>
+        <v>4:01</v>
       </c>
       <c r="H91" t="str">
-        <v>Harry Styles</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-08</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>5:01</v>
+        <v>3:24</v>
       </c>
       <c r="H92" t="str">
-        <v>Neal Francis</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-08</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>4:12</v>
+        <v>5:52</v>
       </c>
       <c r="H93" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-08</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:59</v>
+        <v>5:01</v>
       </c>
       <c r="H94" t="str">
-        <v>Holly Humberstone</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-08</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:56</v>
+        <v>4:12</v>
       </c>
       <c r="H95" t="str">
-        <v>Cliff Richard</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-08</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:46</v>
+        <v>3:59</v>
       </c>
       <c r="H96" t="str">
-        <v>Jessie Ware</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-08</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:37</v>
+        <v>2:56</v>
       </c>
       <c r="H97" t="str">
-        <v>Bella White</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-08</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:06</v>
+        <v>3:46</v>
       </c>
       <c r="H98" t="str">
-        <v>Ryan Wright</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-08</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:54</v>
+        <v>4:37</v>
       </c>
       <c r="H99" t="str">
-        <v>Dove Cameron</v>
+        <v>Bella White</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=WGb8KVdqs6k</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-08</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:10</v>
+        <v>4:06</v>
       </c>
       <c r="H100" t="str">
-        <v>Parker McCollum</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Parker McCollum - Big Ole Fancy House (Studio Performance Video) - Parker McCollum</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=X1ZeY4Y3l1M</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-08</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:26</v>
+        <v>3:54</v>
       </c>
       <c r="H101" t="str">
-        <v>Matt Hansen</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Matt Hansen - SOMEWHERE IN BETWEEN (Official Lyric Video) - Matt Hansen</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="102">

--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>
@@ -477,7 +477,7 @@
         <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B3" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:26</v>
@@ -515,7 +515,7 @@
         <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:29</v>
@@ -819,7 +819,7 @@
         <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>3:06</v>
@@ -857,7 +857,7 @@
         <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>3:21</v>
@@ -895,7 +895,7 @@
         <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>4:09</v>
@@ -933,7 +933,7 @@
         <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>4:18</v>
@@ -971,7 +971,7 @@
         <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:08</v>
@@ -1009,7 +1009,7 @@
         <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:03</v>
@@ -1047,7 +1047,7 @@
         <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:01</v>
@@ -1085,7 +1085,7 @@
         <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:05</v>
@@ -1123,7 +1123,7 @@
         <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:34</v>
@@ -1161,7 +1161,7 @@
         <v>Dylan Davidson - Escape Artist</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>3:15</v>
@@ -2681,7 +2681,7 @@
         <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>2:41</v>
@@ -2719,7 +2719,7 @@
         <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>4:01</v>
@@ -2757,7 +2757,7 @@
         <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:16</v>
@@ -2795,7 +2795,7 @@
         <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>3:03</v>
@@ -2833,7 +2833,7 @@
         <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>2:41</v>
@@ -2871,7 +2871,7 @@
         <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>3:05</v>
@@ -2909,7 +2909,7 @@
         <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>2:46</v>
@@ -2947,7 +2947,7 @@
         <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>3:32</v>
@@ -2985,7 +2985,7 @@
         <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>3:42</v>
@@ -3023,7 +3023,7 @@
         <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>2:38</v>
@@ -3061,7 +3061,7 @@
         <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B71" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>3:10</v>
@@ -3099,7 +3099,7 @@
         <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B72" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>3:57</v>
@@ -3137,7 +3137,7 @@
         <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>2:19</v>

--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B4" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:29</v>

--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>
@@ -477,7 +477,7 @@
         <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:26</v>
@@ -515,7 +515,7 @@
         <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B4" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:29</v>
@@ -2605,7 +2605,7 @@
         <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>2:52</v>
@@ -2643,7 +2643,7 @@
         <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>3:33</v>

--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>
@@ -477,7 +477,7 @@
         <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:26</v>
@@ -515,7 +515,7 @@
         <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B4" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:29</v>
@@ -781,7 +781,7 @@
         <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:54</v>
@@ -2301,7 +2301,7 @@
         <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:50</v>
@@ -2529,7 +2529,7 @@
         <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>3:22</v>
@@ -2567,7 +2567,7 @@
         <v>Only The Poets - Monumental</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>2:48</v>
@@ -3669,7 +3669,7 @@
         <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
         <v>4:27</v>

--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>
@@ -477,7 +477,7 @@
         <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:26</v>
@@ -515,7 +515,7 @@
         <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B4" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:29</v>
@@ -743,7 +743,7 @@
         <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>4:37</v>
@@ -2491,7 +2491,7 @@
         <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>4:47</v>

--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>
@@ -477,7 +477,7 @@
         <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:26</v>
@@ -515,7 +515,7 @@
         <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B4" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>3:29</v>
@@ -1579,7 +1579,7 @@
         <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:45</v>

--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:L197"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>יובל בנשלום – ממשיך ליפול</v>
       </c>
       <c r="B2" t="str">
-        <v>14 hours ago</v>
+        <v>2026-02-08</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%91%d7%a0%d7%a9%d7%9c%d7%95%d7%9d-%d7%9e%d7%9e%d7%a9%d7%99%d7%9a-%d7%9c%d7%99%d7%a4%d7%95%d7%9c/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-08</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14 hours ago</v>
+        <v>יובל בנשלום שר שיר עדין קשה, שכוחו נובע דווקא מהעובדה שהוא לא מנסה לפתור את הדיכאון – אלא להיות לידו. זהו שיר על אהבה תחת דיכאון, נאמנות של אוהבת שלא יודעת איך לעזור, פער כואב בין רצון למציאות הבחירה לספר</v>
       </c>
       <c r="G2" t="str">
-        <v>4:27</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Mariah Carey</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>יובל בנשלום – ממשיך ליפול</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B3" t="str">
-        <v>20 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-08</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>20 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:26</v>
+        <v>4:27</v>
       </c>
       <c r="H3" t="str">
-        <v>Netflix</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B4" t="str">
-        <v>22 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-08</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>22 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:29</v>
+        <v>3:26</v>
       </c>
       <c r="H4" t="str">
-        <v>Michael Bolton</v>
+        <v>Netflix</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-08</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:59</v>
+        <v>3:29</v>
       </c>
       <c r="H5" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-08</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:51</v>
+        <v>2:59</v>
       </c>
       <c r="H6" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>mgk</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-08</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:13</v>
+        <v>2:51</v>
       </c>
       <c r="H7" t="str">
-        <v>Michael Bolton</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-08</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>4:41</v>
+        <v>4:13</v>
       </c>
       <c r="H8" t="str">
-        <v>NICK JONAS</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-08</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>7:03</v>
+        <v>4:41</v>
       </c>
       <c r="H9" t="str">
-        <v>Take That</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-08</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:37</v>
+        <v>7:03</v>
       </c>
       <c r="H10" t="str">
-        <v>Cliff Richard</v>
+        <v>Take That</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-08</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:54</v>
+        <v>4:37</v>
       </c>
       <c r="H11" t="str">
-        <v>Bryan Adams</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-08</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:06</v>
+        <v>3:54</v>
       </c>
       <c r="H12" t="str">
-        <v>Anna Graves</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-08</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H13" t="str">
-        <v>George Birge</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-08</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:09</v>
+        <v>3:21</v>
       </c>
       <c r="H14" t="str">
-        <v>Warner Records</v>
+        <v>George Birge</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
+        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-08</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:18</v>
+        <v>4:09</v>
       </c>
       <c r="H15" t="str">
-        <v>NICK JONAS</v>
+        <v>Warner Records</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
+        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-08</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:08</v>
+        <v>4:18</v>
       </c>
       <c r="H16" t="str">
-        <v>Charlie Puth</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
+        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-08</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:03</v>
+        <v>3:08</v>
       </c>
       <c r="H17" t="str">
-        <v>Olivia Newton-John</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
+        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-08</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:01</v>
+        <v>4:03</v>
       </c>
       <c r="H18" t="str">
-        <v>The Warning and Carin Leon</v>
+        <v>Olivia Newton-John</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
+        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-08</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:05</v>
+        <v>3:01</v>
       </c>
       <c r="H19" t="str">
-        <v>Iman Fandi</v>
+        <v>The Warning and Carin Leon</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
+        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-08</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:34</v>
+        <v>3:05</v>
       </c>
       <c r="H20" t="str">
-        <v>Megan Moroney</v>
+        <v>Iman Fandi</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Dylan Davidson - Escape Artist</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
+        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-08</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:15</v>
+        <v>3:34</v>
       </c>
       <c r="H21" t="str">
-        <v>Dylan Davidson</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
+        <v>Dylan Davidson - Escape Artist</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
+        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-08</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:16</v>
+        <v>3:15</v>
       </c>
       <c r="H22" t="str">
-        <v>Lady Gaga</v>
+        <v>Dylan Davidson</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
+        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video)</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
+        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-08</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:53</v>
+        <v>4:16</v>
       </c>
       <c r="H23" t="str">
-        <v>Carlos Vives</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
+        <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
+        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-08</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:25</v>
+        <v>3:53</v>
       </c>
       <c r="H24" t="str">
-        <v>Monsieur Periné</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
+        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio)</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
+        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-08</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>4:09</v>
+        <v>2:25</v>
       </c>
       <c r="H25" t="str">
-        <v>The Happy Fits</v>
+        <v>Monsieur Periné</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>chase (lyric vid) - Michael Aldag</v>
+        <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
+        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-08</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:45</v>
+        <v>4:09</v>
       </c>
       <c r="H26" t="str">
-        <v>Michael Aldag</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
+        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
+        <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
+        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-08</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:07</v>
+        <v>2:45</v>
       </c>
       <c r="H27" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Michael Aldag</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
+        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
+        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-08</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:34</v>
+        <v>4:07</v>
       </c>
       <c r="H28" t="str">
-        <v>Marc Anthony</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
+        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-08</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>5:14</v>
+        <v>4:34</v>
       </c>
       <c r="H29" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
+        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-08</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:11</v>
+        <v>5:14</v>
       </c>
       <c r="H30" t="str">
-        <v>Michael Bolton</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lachie Gill - Last Drive</v>
+        <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
+        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-08</v>
@@ -1556,10 +1556,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:40</v>
+        <v>3:11</v>
       </c>
       <c r="H31" t="str">
-        <v>Lachie Gill</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Lachie Gill - Last Drive - Lachie Gill</v>
+        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
+        <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
+        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-08</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:45</v>
+        <v>3:40</v>
       </c>
       <c r="H32" t="str">
-        <v>Eli &amp; Fur</v>
+        <v>Lachie Gill</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
+        <v>Lachie Gill - Last Drive - Lachie Gill</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Freya Skye - why'd you have to call</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
+        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-08</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:19</v>
+        <v>3:45</v>
       </c>
       <c r="H33" t="str">
-        <v>Freya Skye</v>
+        <v>Eli &amp; Fur</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Freya Skye - why'd you have to call - Freya Skye</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
+        <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
+        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-08</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:30</v>
+        <v>4:19</v>
       </c>
       <c r="H34" t="str">
-        <v>Jessie J</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
+        <v>Freya Skye - why'd you have to call - Freya Skye</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer)</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
+        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-08</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:24</v>
+        <v>2:30</v>
       </c>
       <c r="H35" t="str">
-        <v>Marc Anthony</v>
+        <v>Jessie J</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
+        <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B36" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
+        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-08</v>
@@ -1746,10 +1746,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:33</v>
+        <v>4:24</v>
       </c>
       <c r="H36" t="str">
-        <v>Clara Mae</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
+        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Metric - Victim of Luck (Official Music Video)</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B37" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
+        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-08</v>
@@ -1784,10 +1784,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:25</v>
+        <v>2:33</v>
       </c>
       <c r="H37" t="str">
-        <v>metricmusic</v>
+        <v>Clara Mae</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
+        <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B38" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
+        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-08</v>
@@ -1822,10 +1822,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:41</v>
+        <v>3:25</v>
       </c>
       <c r="H38" t="str">
-        <v>kesha</v>
+        <v>metricmusic</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
+        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
+        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-08</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:19</v>
+        <v>3:41</v>
       </c>
       <c r="H39" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>kesha</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B40" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
+        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-08</v>
@@ -1898,10 +1898,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:37</v>
+        <v>3:19</v>
       </c>
       <c r="H40" t="str">
-        <v>Vera Blue</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B41" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
+        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-08</v>
@@ -1936,10 +1936,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:08</v>
+        <v>3:37</v>
       </c>
       <c r="H41" t="str">
-        <v>Bob Moses</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B42" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
+        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-08</v>
@@ -1974,10 +1974,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:28</v>
+        <v>3:08</v>
       </c>
       <c r="H42" t="str">
-        <v>Marc Anthony</v>
+        <v>Bob Moses</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B43" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
+        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-08</v>
@@ -2012,7 +2012,7 @@
         <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>5:05</v>
+        <v>3:28</v>
       </c>
       <c r="H43" t="str">
         <v>Marc Anthony</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Loreen - Feels Like Heaven</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B44" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
+        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-08</v>
@@ -2050,10 +2050,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:14</v>
+        <v>5:05</v>
       </c>
       <c r="H44" t="str">
-        <v>Loreen</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Loreen - Feels Like Heaven - Loreen</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
+        <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B45" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
+        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-08</v>
@@ -2088,10 +2088,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:36</v>
+        <v>3:14</v>
       </c>
       <c r="H45" t="str">
-        <v>Take That</v>
+        <v>Loreen</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
+        <v>Loreen - Feels Like Heaven - Loreen</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B46" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
+        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-08</v>
@@ -2126,10 +2126,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>5:31</v>
+        <v>3:36</v>
       </c>
       <c r="H46" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Take That</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio)</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B47" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
+        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-08</v>
@@ -2164,10 +2164,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:37</v>
+        <v>5:31</v>
       </c>
       <c r="H47" t="str">
-        <v>Nothing But Thieves</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-08</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:58</v>
+        <v>3:37</v>
       </c>
       <c r="H48" t="str">
-        <v>The Warning</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B49" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-08</v>
@@ -2240,10 +2240,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>5:08</v>
+        <v>4:58</v>
       </c>
       <c r="H49" t="str">
-        <v>The Offspring</v>
+        <v>The Warning</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B50" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-08</v>
@@ -2278,10 +2278,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:38</v>
+        <v>5:08</v>
       </c>
       <c r="H50" t="str">
-        <v>Roxette</v>
+        <v>The Offspring</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-08</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:50</v>
+        <v>4:38</v>
       </c>
       <c r="H51" t="str">
-        <v>Jessie Ware</v>
+        <v>Roxette</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
       </c>
       <c r="B52" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-08</v>
@@ -2354,10 +2354,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:10</v>
+        <v>3:50</v>
       </c>
       <c r="H52" t="str">
-        <v>Joseph</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-08</v>
@@ -2392,10 +2392,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:44</v>
+        <v>3:10</v>
       </c>
       <c r="H53" t="str">
-        <v>Dean Lewis</v>
+        <v>Joseph</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-08</v>
@@ -2430,10 +2430,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:57</v>
+        <v>2:44</v>
       </c>
       <c r="H54" t="str">
-        <v>Take That</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-08</v>
@@ -2468,10 +2468,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:07</v>
+        <v>2:57</v>
       </c>
       <c r="H55" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>Take That</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B56" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-08</v>
@@ -2506,10 +2506,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:47</v>
+        <v>3:07</v>
       </c>
       <c r="H56" t="str">
-        <v>Paris Paloma</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-08</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:22</v>
+        <v>4:47</v>
       </c>
       <c r="H57" t="str">
-        <v>Zara Larsson</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-08</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:48</v>
+        <v>3:22</v>
       </c>
       <c r="H58" t="str">
-        <v>only the poets</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B59" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-08</v>
@@ -2620,10 +2620,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:52</v>
+        <v>2:48</v>
       </c>
       <c r="H59" t="str">
-        <v>Katelyn Tarver</v>
+        <v>only the poets</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-08</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:33</v>
+        <v>2:52</v>
       </c>
       <c r="H60" t="str">
-        <v>David Guetta</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-08</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:41</v>
+        <v>3:33</v>
       </c>
       <c r="H61" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>David Guetta</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-08</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:01</v>
+        <v>2:41</v>
       </c>
       <c r="H62" t="str">
-        <v>Ella Langley</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-08</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:16</v>
+        <v>4:01</v>
       </c>
       <c r="H63" t="str">
-        <v>Dogpark</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-08</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:03</v>
+        <v>3:16</v>
       </c>
       <c r="H64" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Dogpark</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-08</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:41</v>
+        <v>3:03</v>
       </c>
       <c r="H65" t="str">
-        <v>ERNEST</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-08</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:05</v>
+        <v>2:41</v>
       </c>
       <c r="H66" t="str">
-        <v>Labrinth</v>
+        <v>ERNEST</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-08</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:46</v>
+        <v>3:05</v>
       </c>
       <c r="H67" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Labrinth</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-08</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:32</v>
+        <v>2:46</v>
       </c>
       <c r="H68" t="str">
-        <v>VOILÀ</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-08</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:42</v>
+        <v>3:32</v>
       </c>
       <c r="H69" t="str">
-        <v>Cannons</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-08</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:38</v>
+        <v>3:42</v>
       </c>
       <c r="H70" t="str">
-        <v>Kylie Morgan</v>
+        <v>Cannons</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-08</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:10</v>
+        <v>2:38</v>
       </c>
       <c r="H71" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-08</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:57</v>
+        <v>3:10</v>
       </c>
       <c r="H72" t="str">
-        <v>Willie Nelson</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-08</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:19</v>
+        <v>3:57</v>
       </c>
       <c r="H73" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-08</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:04</v>
+        <v>2:19</v>
       </c>
       <c r="H74" t="str">
-        <v>India Martínez</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-08</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:16</v>
+        <v>4:04</v>
       </c>
       <c r="H75" t="str">
-        <v>Chelsea Cutler</v>
+        <v>India Martínez</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-08</v>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>5:58</v>
+        <v>2:16</v>
       </c>
       <c r="H76" t="str">
-        <v>TINI</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-08</v>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:26</v>
+        <v>5:58</v>
       </c>
       <c r="H77" t="str">
-        <v>Charley</v>
+        <v>TINI</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-08</v>
@@ -3342,10 +3342,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:05</v>
+        <v>3:26</v>
       </c>
       <c r="H78" t="str">
-        <v>Demi Lovato</v>
+        <v>Charley</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B79" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-08</v>
@@ -3380,10 +3380,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H79" t="str">
-        <v>Teddy Swims</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B80" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-08</v>
@@ -3418,10 +3418,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:14</v>
+        <v>3:16</v>
       </c>
       <c r="H80" t="str">
-        <v>Beck</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B81" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-08</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:57</v>
+        <v>3:14</v>
       </c>
       <c r="H81" t="str">
-        <v>The Offspring</v>
+        <v>Beck</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-08</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>4:10</v>
+        <v>2:57</v>
       </c>
       <c r="H82" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>The Offspring</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-08</v>
@@ -3532,10 +3532,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:10</v>
+        <v>4:10</v>
       </c>
       <c r="H83" t="str">
-        <v>Jason Derulo</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B84" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-08</v>
@@ -3570,10 +3570,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:52</v>
+        <v>2:10</v>
       </c>
       <c r="H84" t="str">
-        <v>lights</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B85" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-08</v>
@@ -3608,10 +3608,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:50</v>
+        <v>3:52</v>
       </c>
       <c r="H85" t="str">
-        <v>Telenova</v>
+        <v>lights</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-08</v>
@@ -3646,10 +3646,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>5:32</v>
+        <v>3:50</v>
       </c>
       <c r="H86" t="str">
-        <v>Marcin</v>
+        <v>Telenova</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B87" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-08</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:27</v>
+        <v>5:32</v>
       </c>
       <c r="H87" t="str">
-        <v>We Three</v>
+        <v>Marcin</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-08</v>
@@ -3722,10 +3722,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:01</v>
+        <v>4:27</v>
       </c>
       <c r="H88" t="str">
-        <v>Timebelle Official</v>
+        <v>We Three</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-08</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:20</v>
+        <v>3:01</v>
       </c>
       <c r="H89" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-08</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:34</v>
+        <v>3:20</v>
       </c>
       <c r="H90" t="str">
-        <v>Clinton Kane</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-08</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:01</v>
+        <v>3:34</v>
       </c>
       <c r="H91" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-08</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:24</v>
+        <v>4:01</v>
       </c>
       <c r="H92" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-08</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>5:52</v>
+        <v>3:24</v>
       </c>
       <c r="H93" t="str">
-        <v>Harry Styles</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-08</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>5:01</v>
+        <v>5:52</v>
       </c>
       <c r="H94" t="str">
-        <v>Neal Francis</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-08</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:12</v>
+        <v>5:01</v>
       </c>
       <c r="H95" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-08</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:59</v>
+        <v>4:12</v>
       </c>
       <c r="H96" t="str">
-        <v>Holly Humberstone</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-08</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:56</v>
+        <v>3:59</v>
       </c>
       <c r="H97" t="str">
-        <v>Cliff Richard</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-08</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:46</v>
+        <v>2:56</v>
       </c>
       <c r="H98" t="str">
-        <v>Jessie Ware</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-08</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:37</v>
+        <v>3:46</v>
       </c>
       <c r="H99" t="str">
-        <v>Bella White</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-08</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:06</v>
+        <v>4:37</v>
       </c>
       <c r="H100" t="str">
-        <v>Ryan Wright</v>
+        <v>Bella White</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-08</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:54</v>
+        <v>4:06</v>
       </c>
       <c r="H101" t="str">
-        <v>Dove Cameron</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Die For Me</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-08</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>KONNAKOL</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:00</v>
+        <v>3:54</v>
       </c>
       <c r="H102" t="str">
-        <v>ZAYN</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Die For Me - ZAYN</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Two Six</v>
+        <v>Die For Me</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/two-six/1875080974</v>
+        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-08</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Fall-Off</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G103" t="str">
-        <v>3:16</v>
+        <v>3:00</v>
       </c>
       <c r="H103" t="str">
-        <v>J. Cole</v>
+        <v>ZAYN</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/two-six/1875080726</v>
+        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
       </c>
       <c r="L103" t="str">
-        <v>Two Six - J. Cole</v>
+        <v>Die For Me - ZAYN</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Dracula (JENNIE Remix)</v>
+        <v>Two Six</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
+        <v>https://music.apple.com/us/song/two-six/1875080974</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-08</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Dracula (Remix) - Single</v>
+        <v>The Fall-Off</v>
       </c>
       <c r="G104" t="str">
-        <v>3:29</v>
+        <v>3:16</v>
       </c>
       <c r="H104" t="str">
-        <v>Tame Impala</v>
+        <v>J. Cole</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
+        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
+        <v>https://music.apple.com/us/album/two-six/1875080726</v>
       </c>
       <c r="L104" t="str">
-        <v>Dracula (JENNIE Remix) - Tame Impala</v>
+        <v>Two Six - J. Cole</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Hotel California</v>
+        <v>Dracula (JENNIE Remix)</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
+        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-08</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Piss In The Wind</v>
+        <v>Dracula (Remix) - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:08</v>
+        <v>3:29</v>
       </c>
       <c r="H105" t="str">
-        <v>Joji</v>
+        <v>Tame Impala</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
+        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
       </c>
       <c r="L105" t="str">
-        <v>Hotel California - Joji</v>
+        <v>Dracula (JENNIE Remix) - Tame Impala</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Homewrecker</v>
+        <v>Hotel California</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
+        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-08</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Homewrecker - Single</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G106" t="str">
-        <v>3:29</v>
+        <v>2:08</v>
       </c>
       <c r="H106" t="str">
-        <v>sombr</v>
+        <v>Joji</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
+        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
       </c>
       <c r="L106" t="str">
-        <v>Homewrecker - sombr</v>
+        <v>Hotel California - Joji</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Might Just</v>
+        <v>Homewrecker</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/might-just/1858755211</v>
+        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-08</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Do You Still Love Me?</v>
+        <v>Homewrecker - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:43</v>
+        <v>3:29</v>
       </c>
       <c r="H107" t="str">
-        <v>Ella Mai</v>
+        <v>sombr</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/might-just/1858754868</v>
+        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
       </c>
       <c r="L107" t="str">
-        <v>Might Just - Ella Mai</v>
+        <v>Homewrecker - sombr</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Cloud 9</v>
+        <v>Might Just</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
+        <v>https://music.apple.com/us/song/might-just/1858755211</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-08</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Cloud 9</v>
+        <v>Do You Still Love Me?</v>
       </c>
       <c r="G108" t="str">
-        <v>3:33</v>
+        <v>3:43</v>
       </c>
       <c r="H108" t="str">
-        <v>Megan Moroney</v>
+        <v>Ella Mai</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
+        <v>https://music.apple.com/us/album/might-just/1858754868</v>
       </c>
       <c r="L108" t="str">
-        <v>Cloud 9 - Megan Moroney</v>
+        <v>Might Just - Ella Mai</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Cry</v>
+        <v>Cloud 9</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/cry/1845189974</v>
+        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-08</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G109" t="str">
-        <v>3:07</v>
+        <v>3:33</v>
       </c>
       <c r="H109" t="str">
-        <v>Charlie Puth</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/cry/1845189970</v>
+        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
       </c>
       <c r="L109" t="str">
-        <v>Cry - Charlie Puth</v>
+        <v>Cloud 9 - Megan Moroney</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>I'll Change for You</v>
+        <v>Cry</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
+        <v>https://music.apple.com/us/song/cry/1845189974</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-08</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G110" t="str">
-        <v>3:16</v>
+        <v>3:07</v>
       </c>
       <c r="H110" t="str">
-        <v>Mitski</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
+        <v>https://music.apple.com/us/album/cry/1845189970</v>
       </c>
       <c r="L110" t="str">
-        <v>I'll Change for You - Mitski</v>
+        <v>Cry - Charlie Puth</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>ASSIGNMENT</v>
+        <v>I'll Change for You</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/assignment/1872764440</v>
+        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-08</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>ASSIGNMENT - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G111" t="str">
-        <v>2:23</v>
+        <v>3:16</v>
       </c>
       <c r="H111" t="str">
-        <v>Power Snatch</v>
+        <v>Mitski</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/assignment/1872764438</v>
+        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
       </c>
       <c r="L111" t="str">
-        <v>ASSIGNMENT - Power Snatch</v>
+        <v>I'll Change for You - Mitski</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Como en el Idilio</v>
+        <v>ASSIGNMENT</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
+        <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-08</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Como en el Idilio - Single</v>
+        <v>ASSIGNMENT - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>4:27</v>
+        <v>2:23</v>
       </c>
       <c r="H112" t="str">
-        <v>Marc Anthony</v>
+        <v>Power Snatch</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
+        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
+        <v>https://music.apple.com/us/album/assignment/1872764438</v>
       </c>
       <c r="L112" t="str">
-        <v>Como en el Idilio - Marc Anthony</v>
+        <v>ASSIGNMENT - Power Snatch</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>golden boy</v>
+        <v>Como en el Idilio</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
+        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-08</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>stardust - EP</v>
+        <v>Como en el Idilio - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:17</v>
+        <v>4:27</v>
       </c>
       <c r="H113" t="str">
-        <v>Freya Skye</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
+        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
       </c>
       <c r="L113" t="str">
-        <v>golden boy - Freya Skye</v>
+        <v>Como en el Idilio - Marc Anthony</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Penny in the Lake</v>
+        <v>golden boy</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
+        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-08</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Singin’ to an Empty Chair</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G114" t="str">
-        <v>3:51</v>
+        <v>3:17</v>
       </c>
       <c r="H114" t="str">
-        <v>Ratboys</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
+        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
       </c>
       <c r="L114" t="str">
-        <v>Penny in the Lake - Ratboys</v>
+        <v>golden boy - Freya Skye</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Heaven</v>
+        <v>Penny in the Lake</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/heaven/1862570892</v>
+        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-08</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Singin’ to an Empty Chair</v>
       </c>
       <c r="G115" t="str">
-        <v>4:26</v>
+        <v>3:51</v>
       </c>
       <c r="H115" t="str">
-        <v>Arlo Parks</v>
+        <v>Ratboys</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/heaven/1862570378</v>
+        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
       </c>
       <c r="L115" t="str">
-        <v>Heaven - Arlo Parks</v>
+        <v>Penny in the Lake - Ratboys</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Adrenaline</v>
+        <v>Heaven</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
+        <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-08</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>GOLDEN HOUR : Part.4 - EP</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G116" t="str">
-        <v>3:39</v>
+        <v>4:26</v>
       </c>
       <c r="H116" t="str">
-        <v>ATEEZ</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
+        <v>https://music.apple.com/us/album/heaven/1862570378</v>
       </c>
       <c r="L116" t="str">
-        <v>Adrenaline - ATEEZ</v>
+        <v>Heaven - Arlo Parks</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Sweet To Me</v>
+        <v>Adrenaline</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
+        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-08</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Sunday Best</v>
+        <v>GOLDEN HOUR : Part.4 - EP</v>
       </c>
       <c r="G117" t="str">
-        <v>4:17</v>
+        <v>3:39</v>
       </c>
       <c r="H117" t="str">
-        <v>Nick Jonas</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
+        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
       </c>
       <c r="L117" t="str">
-        <v>Sweet To Me - Nick Jonas</v>
+        <v>Adrenaline - ATEEZ</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Time Goes On</v>
+        <v>Sweet To Me</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
+        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-08</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Time Goes On - Single</v>
+        <v>Sunday Best</v>
       </c>
       <c r="G118" t="str">
-        <v>2:55</v>
+        <v>4:17</v>
       </c>
       <c r="H118" t="str">
-        <v>Koe Wetzel</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
+        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
       </c>
       <c r="L118" t="str">
-        <v>Time Goes On - Koe Wetzel</v>
+        <v>Sweet To Me - Nick Jonas</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Drive Safe</v>
+        <v>Time Goes On</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
+        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-08</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Drive Safe - Single</v>
+        <v>Time Goes On - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:21</v>
+        <v>2:55</v>
       </c>
       <c r="H119" t="str">
-        <v>Myles Smith</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
+        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
       </c>
       <c r="L119" t="str">
-        <v>Drive Safe - Myles Smith</v>
+        <v>Time Goes On - Koe Wetzel</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Love To Be Loved</v>
+        <v>Drive Safe</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
+        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-08</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Love To Be Loved - Single</v>
+        <v>Drive Safe - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:50</v>
+        <v>3:21</v>
       </c>
       <c r="H120" t="str">
-        <v>The Warning</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
+        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
       </c>
       <c r="L120" t="str">
-        <v>Love To Be Loved - The Warning</v>
+        <v>Drive Safe - Myles Smith</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Mi Yo de Antes</v>
+        <v>Love To Be Loved</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
+        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-08</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Mi Yo de Antes - Single</v>
+        <v>Love To Be Loved - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:02</v>
+        <v>2:50</v>
       </c>
       <c r="H121" t="str">
-        <v>Eden Muñoz</v>
+        <v>The Warning</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
+        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
       </c>
       <c r="L121" t="str">
-        <v>Mi Yo de Antes - Eden Muñoz</v>
+        <v>Love To Be Loved - The Warning</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Omens</v>
+        <v>Mi Yo de Antes</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/omens/1872546206</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-08</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Omens - Single</v>
+        <v>Mi Yo de Antes - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:00</v>
+        <v>3:02</v>
       </c>
       <c r="H122" t="str">
-        <v>EsDeeKid</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/omens/1872546204</v>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
       </c>
       <c r="L122" t="str">
-        <v>Omens - EsDeeKid</v>
+        <v>Mi Yo de Antes - Eden Muñoz</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>My Regards</v>
+        <v>Omens</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
+        <v>https://music.apple.com/us/song/omens/1872546206</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-08</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Florescence</v>
+        <v>Omens - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:11</v>
+        <v>2:00</v>
       </c>
       <c r="H123" t="str">
-        <v>Maisie Peters</v>
+        <v>EsDeeKid</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
+        <v>https://music.apple.com/us/album/omens/1872546204</v>
       </c>
       <c r="L123" t="str">
-        <v>My Regards - Maisie Peters</v>
+        <v>Omens - EsDeeKid</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Time After Time</v>
+        <v>My Regards</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
+        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-08</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Time After Time - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G124" t="str">
-        <v>2:48</v>
+        <v>3:11</v>
       </c>
       <c r="H124" t="str">
-        <v>EJAE</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
+        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
       </c>
       <c r="L124" t="str">
-        <v>Time After Time - EJAE</v>
+        <v>My Regards - Maisie Peters</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Don't Want Your Love</v>
+        <v>Time After Time</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
+        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-08</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>ODYSSEY</v>
+        <v>Time After Time - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:12</v>
+        <v>2:48</v>
       </c>
       <c r="H125" t="str">
-        <v>ILLENIUM</v>
+        <v>EJAE</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
+        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
       </c>
       <c r="L125" t="str">
-        <v>Don't Want Your Love - ILLENIUM</v>
+        <v>Time After Time - EJAE</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Pa' Los Envidiosos</v>
+        <v>Don't Want Your Love</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
+        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-08</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Pa' Los Envidiosos - Single</v>
+        <v>ODYSSEY</v>
       </c>
       <c r="G126" t="str">
-        <v>3:37</v>
+        <v>3:12</v>
       </c>
       <c r="H126" t="str">
-        <v>Pitbull</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
+        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
       </c>
       <c r="L126" t="str">
-        <v>Pa' Los Envidiosos - Pitbull</v>
+        <v>Don't Want Your Love - ILLENIUM</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Plei</v>
+        <v>Pa' Los Envidiosos</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/plei/1872137577</v>
+        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-08</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Plei - Single</v>
+        <v>Pa' Los Envidiosos - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:22</v>
+        <v>3:37</v>
       </c>
       <c r="H127" t="str">
-        <v>Chuwi</v>
+        <v>Pitbull</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/plei/1872137372</v>
+        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
       </c>
       <c r="L127" t="str">
-        <v>Plei - Chuwi</v>
+        <v>Pa' Los Envidiosos - Pitbull</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Flood (feat. Bon Iver)</v>
+        <v>Plei</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
+        <v>https://music.apple.com/us/song/plei/1872137577</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-08</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Plei - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:59</v>
+        <v>3:22</v>
       </c>
       <c r="H128" t="str">
-        <v>Dua Saleh</v>
+        <v>Chuwi</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
+        <v>https://music.apple.com/us/album/plei/1872137372</v>
       </c>
       <c r="L128" t="str">
-        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
+        <v>Plei - Chuwi</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Rain</v>
+        <v>Flood (feat. Bon Iver)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/rain/1867258289</v>
+        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-08</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Rain - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G129" t="str">
-        <v>3:28</v>
+        <v>2:59</v>
       </c>
       <c r="H129" t="str">
-        <v>FISHER</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/rain/1867258288</v>
+        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
       </c>
       <c r="L129" t="str">
-        <v>Rain - FISHER</v>
+        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Release The Pressure</v>
+        <v>Rain</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
+        <v>https://music.apple.com/us/song/rain/1867258289</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-08</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Release The Pressure - Single</v>
+        <v>Rain - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:23</v>
+        <v>3:28</v>
       </c>
       <c r="H130" t="str">
-        <v>Calvin Harris</v>
+        <v>FISHER</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
+        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
+        <v>https://music.apple.com/us/album/rain/1867258288</v>
       </c>
       <c r="L130" t="str">
-        <v>Release The Pressure - Calvin Harris</v>
+        <v>Rain - FISHER</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Sexistential (Arca’s Take)</v>
+        <v>Release The Pressure</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
+        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-08</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Sexistential (Arca’s Take) - Single</v>
+        <v>Release The Pressure - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:44</v>
+        <v>3:23</v>
       </c>
       <c r="H131" t="str">
-        <v>Robyn</v>
+        <v>Calvin Harris</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
+        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
       </c>
       <c r="L131" t="str">
-        <v>Sexistential (Arca’s Take) - Robyn</v>
+        <v>Release The Pressure - Calvin Harris</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>heal something</v>
+        <v>Sexistential (Arca’s Take)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
+        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-08</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>ACT II</v>
+        <v>Sexistential (Arca’s Take) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:01</v>
+        <v>3:44</v>
       </c>
       <c r="H132" t="str">
-        <v>Sasha Keable</v>
+        <v>Robyn</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
+        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
       </c>
       <c r="L132" t="str">
-        <v>heal something - Sasha Keable</v>
+        <v>Sexistential (Arca’s Take) - Robyn</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Buenos Días</v>
+        <v>heal something</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
+        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-08</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Buenos Días - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G133" t="str">
-        <v>2:39</v>
+        <v>3:01</v>
       </c>
       <c r="H133" t="str">
-        <v>Eladio Carrión</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
+        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
       </c>
       <c r="L133" t="str">
-        <v>Buenos Días - Eladio Carrión</v>
+        <v>heal something - Sasha Keable</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>COOK</v>
+        <v>Buenos Días</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/cook/1872816147</v>
+        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-08</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>COOK - Single</v>
+        <v>Buenos Días - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:50</v>
+        <v>2:39</v>
       </c>
       <c r="H134" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/cook/1872816146</v>
+        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
       </c>
       <c r="L134" t="str">
-        <v>COOK - SOFI TUKKER</v>
+        <v>Buenos Días - Eladio Carrión</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>You Got to Lose</v>
+        <v>COOK</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
+        <v>https://music.apple.com/us/song/cook/1872816147</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-08</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Peaches!</v>
+        <v>COOK - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:17</v>
+        <v>2:50</v>
       </c>
       <c r="H135" t="str">
-        <v>The Black Keys</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
+        <v>https://music.apple.com/us/album/cook/1872816146</v>
       </c>
       <c r="L135" t="str">
-        <v>You Got to Lose - The Black Keys</v>
+        <v>COOK - SOFI TUKKER</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Different Kind Of Love</v>
+        <v>You Got to Lose</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
+        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-08</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Victory Garden</v>
+        <v>Peaches!</v>
       </c>
       <c r="G136" t="str">
-        <v>3:39</v>
+        <v>3:17</v>
       </c>
       <c r="H136" t="str">
-        <v>Young the Giant</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
+        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
       </c>
       <c r="L136" t="str">
-        <v>Different Kind Of Love - Young the Giant</v>
+        <v>You Got to Lose - The Black Keys</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Living Water</v>
+        <v>Different Kind Of Love</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/living-water/1871565262</v>
+        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-08</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Reconstruction: Second Story</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G137" t="str">
-        <v>2:09</v>
+        <v>3:39</v>
       </c>
       <c r="H137" t="str">
-        <v>Lecrae</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/living-water/1871564892</v>
+        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
       </c>
       <c r="L137" t="str">
-        <v>Living Water - Lecrae</v>
+        <v>Different Kind Of Love - Young the Giant</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>What It Feels Like</v>
+        <v>Living Water</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
+        <v>https://music.apple.com/us/song/living-water/1871565262</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-08</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>What It Feels Like - Single</v>
+        <v>Reconstruction: Second Story</v>
       </c>
       <c r="G138" t="str">
-        <v>2:18</v>
+        <v>2:09</v>
       </c>
       <c r="H138" t="str">
-        <v>Dillon Francis</v>
+        <v>Lecrae</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
+        <v>https://music.apple.com/us/album/living-water/1871564892</v>
       </c>
       <c r="L138" t="str">
-        <v>What It Feels Like - Dillon Francis</v>
+        <v>Living Water - Lecrae</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>neck</v>
+        <v>What It Feels Like</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/neck/1866953832</v>
+        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-08</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>neck - Single</v>
+        <v>What It Feels Like - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:40</v>
+        <v>2:18</v>
       </c>
       <c r="H139" t="str">
-        <v>Mau P</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/neck/1866953831</v>
+        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
       </c>
       <c r="L139" t="str">
-        <v>neck - Mau P</v>
+        <v>What It Feels Like - Dillon Francis</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Colorblind</v>
+        <v>neck</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
+        <v>https://music.apple.com/us/song/neck/1866953832</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-08</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Colorblind - Single</v>
+        <v>neck - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:56</v>
+        <v>3:40</v>
       </c>
       <c r="H140" t="str">
-        <v>Gavin Adcock</v>
+        <v>Mau P</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
+        <v>https://music.apple.com/us/album/neck/1866953831</v>
       </c>
       <c r="L140" t="str">
-        <v>Colorblind - Gavin Adcock</v>
+        <v>neck - Mau P</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Au Revoir Reservoir</v>
+        <v>Colorblind</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
+        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-08</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Tenterhooks</v>
+        <v>Colorblind - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:21</v>
+        <v>2:56</v>
       </c>
       <c r="H141" t="str">
-        <v>Silversun Pickups</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
+        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
       </c>
       <c r="L141" t="str">
-        <v>Au Revoir Reservoir - Silversun Pickups</v>
+        <v>Colorblind - Gavin Adcock</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Flavorless</v>
+        <v>Au Revoir Reservoir</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
+        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-08</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Flavorless - Single</v>
+        <v>Tenterhooks</v>
       </c>
       <c r="G142" t="str">
-        <v>3:31</v>
+        <v>3:21</v>
       </c>
       <c r="H142" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Silversun Pickups</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
+        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
       </c>
       <c r="L142" t="str">
-        <v>Flavorless - Dexter and The Moonrocks</v>
+        <v>Au Revoir Reservoir - Silversun Pickups</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Nunca</v>
+        <v>Flavorless</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/nunca/1860691713</v>
+        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-08</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>ESCENAS</v>
+        <v>Flavorless - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:05</v>
+        <v>3:31</v>
       </c>
       <c r="H143" t="str">
-        <v>Sin Bandera</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/nunca/1860691704</v>
+        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
       </c>
       <c r="L143" t="str">
-        <v>Nunca - Sin Bandera</v>
+        <v>Flavorless - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Just In Case</v>
+        <v>Nunca</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
+        <v>https://music.apple.com/us/song/nunca/1860691713</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-08</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>NO HArD FEELINGS (Deluxe)</v>
+        <v>ESCENAS</v>
       </c>
       <c r="G144" t="str">
-        <v>1:45</v>
+        <v>3:05</v>
       </c>
       <c r="H144" t="str">
-        <v>Marc E. Bassy</v>
+        <v>Sin Bandera</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
+        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
+        <v>https://music.apple.com/us/album/nunca/1860691704</v>
       </c>
       <c r="L144" t="str">
-        <v>Just In Case - Marc E. Bassy</v>
+        <v>Nunca - Sin Bandera</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Thinking of You</v>
+        <v>Just In Case</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
+        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-08</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Thinking of You - Single</v>
+        <v>NO HArD FEELINGS (Deluxe)</v>
       </c>
       <c r="G145" t="str">
-        <v>3:00</v>
+        <v>1:45</v>
       </c>
       <c r="H145" t="str">
-        <v>AP Dhillon</v>
+        <v>Marc E. Bassy</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
+        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
+        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
       </c>
       <c r="L145" t="str">
-        <v>Thinking of You - AP Dhillon</v>
+        <v>Just In Case - Marc E. Bassy</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>House Of Cards</v>
+        <v>Thinking of You</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
+        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-08</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>House of Cards</v>
+        <v>Thinking of You - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:26</v>
+        <v>3:00</v>
       </c>
       <c r="H146" t="str">
-        <v>The Amity Affliction</v>
+        <v>AP Dhillon</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
+        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
+        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
       </c>
       <c r="L146" t="str">
-        <v>House Of Cards - The Amity Affliction</v>
+        <v>Thinking of You - AP Dhillon</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Stay With Me</v>
+        <v>House Of Cards</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
+        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-08</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Stay With Me - Single</v>
+        <v>House of Cards</v>
       </c>
       <c r="G147" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H147" t="str">
-        <v>Agents Of Time</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
+        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
       </c>
       <c r="L147" t="str">
-        <v>Stay With Me - Agents Of Time</v>
+        <v>House Of Cards - The Amity Affliction</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>I had a dream...</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-08</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Dream inside a dream…</v>
+        <v>Stay With Me - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:39</v>
+        <v>3:21</v>
       </c>
       <c r="H148" t="str">
-        <v>R3HAB</v>
+        <v>Agents Of Time</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
       </c>
       <c r="L148" t="str">
-        <v>I had a dream... - R3HAB</v>
+        <v>Stay With Me - Agents Of Time</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Back to You</v>
+        <v>I had a dream...</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-08</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Satellite</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G149" t="str">
-        <v>3:10</v>
+        <v>2:39</v>
       </c>
       <c r="H149" t="str">
-        <v>Charlotte Sands</v>
+        <v>R3HAB</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
       </c>
       <c r="L149" t="str">
-        <v>Back to You - Charlotte Sands</v>
+        <v>I had a dream... - R3HAB</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>rager</v>
+        <v>Back to You</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/rager/1872808801</v>
+        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-08</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>rager</v>
+        <v>Satellite</v>
       </c>
       <c r="G150" t="str">
-        <v>2:48</v>
+        <v>3:10</v>
       </c>
       <c r="H150" t="str">
-        <v>Blusher</v>
+        <v>Charlotte Sands</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/blusher/485578161</v>
+        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/rager/1872808800</v>
+        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
       </c>
       <c r="L150" t="str">
-        <v>rager - Blusher</v>
+        <v>Back to You - Charlotte Sands</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>If Only</v>
+        <v>rager</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/if-only/1870281318</v>
+        <v>https://music.apple.com/us/song/rager/1872808801</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-08</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Patchwork</v>
+        <v>rager</v>
       </c>
       <c r="G151" t="str">
-        <v>3:28</v>
+        <v>2:48</v>
       </c>
       <c r="H151" t="str">
-        <v>Charlotte Day Wilson</v>
+        <v>Blusher</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
+        <v>https://music.apple.com/us/artist/blusher/485578161</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/if-only/1870281314</v>
+        <v>https://music.apple.com/us/album/rager/1872808800</v>
       </c>
       <c r="L151" t="str">
-        <v>If Only - Charlotte Day Wilson</v>
+        <v>rager - Blusher</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>DON'T LOVE ME</v>
+        <v>If Only</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
+        <v>https://music.apple.com/us/song/if-only/1870281318</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-08</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>DON'T LOVE ME - Single</v>
+        <v>Patchwork</v>
       </c>
       <c r="G152" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H152" t="str">
-        <v>Omah Lay</v>
+        <v>Charlotte Day Wilson</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
+        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
+        <v>https://music.apple.com/us/album/if-only/1870281314</v>
       </c>
       <c r="L152" t="str">
-        <v>DON'T LOVE ME - Omah Lay</v>
+        <v>If Only - Charlotte Day Wilson</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>No Sikes, No Tradesies</v>
+        <v>DON'T LOVE ME</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
+        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-08</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Sweet Nothings</v>
+        <v>DON'T LOVE ME - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:32</v>
+        <v>3:01</v>
       </c>
       <c r="H153" t="str">
-        <v>Jaymin</v>
+        <v>Omah Lay</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
+        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
+        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
       </c>
       <c r="L153" t="str">
-        <v>No Sikes, No Tradesies - Jaymin</v>
+        <v>DON'T LOVE ME - Omah Lay</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>you woke me up</v>
+        <v>No Sikes, No Tradesies</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
+        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-08</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>you woke me up - Single</v>
+        <v>Sweet Nothings</v>
       </c>
       <c r="G154" t="str">
-        <v>3:14</v>
+        <v>2:32</v>
       </c>
       <c r="H154" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Jaymin</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
+        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
       </c>
       <c r="L154" t="str">
-        <v>you woke me up - Kevian Kraemer</v>
+        <v>No Sikes, No Tradesies - Jaymin</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>No One’s Business</v>
+        <v>you woke me up</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
+        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-08</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>No One’s Business - Single</v>
+        <v>you woke me up - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:00</v>
+        <v>3:14</v>
       </c>
       <c r="H155" t="str">
-        <v>Alicia Creti</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
+        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
       </c>
       <c r="L155" t="str">
-        <v>No One’s Business - Alicia Creti</v>
+        <v>you woke me up - Kevian Kraemer</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
+        <v>No One’s Business</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
+        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-08</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>No One’s Business - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:13</v>
+        <v>3:00</v>
       </c>
       <c r="H156" t="str">
-        <v>Bryant Barnes</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
       </c>
       <c r="L156" t="str">
-        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
+        <v>No One’s Business - Alicia Creti</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>TWICE</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/twice/1871578107</v>
+        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-08</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>KINDA HARD</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G157" t="str">
-        <v>3:44</v>
+        <v>3:13</v>
       </c>
       <c r="H157" t="str">
-        <v>Bilmuri</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/twice/1871578103</v>
+        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L157" t="str">
-        <v>TWICE - Bilmuri</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>ROOFTOP</v>
+        <v>TWICE</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
+        <v>https://music.apple.com/us/song/twice/1871578107</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-08</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>ROOFTOP - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G158" t="str">
-        <v>3:22</v>
+        <v>3:44</v>
       </c>
       <c r="H158" t="str">
-        <v>Hulvey</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
+        <v>https://music.apple.com/us/album/twice/1871578103</v>
       </c>
       <c r="L158" t="str">
-        <v>ROOFTOP - Hulvey</v>
+        <v>TWICE - Bilmuri</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Louisiana Rain</v>
+        <v>ROOFTOP</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
+        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-08</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Louisiana Rain - Single</v>
+        <v>ROOFTOP - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:41</v>
+        <v>3:22</v>
       </c>
       <c r="H159" t="str">
-        <v>Hunter Plake</v>
+        <v>Hulvey</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
+        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
       </c>
       <c r="L159" t="str">
-        <v>Louisiana Rain - Hunter Plake</v>
+        <v>ROOFTOP - Hulvey</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>sharing Jesus with an ex</v>
+        <v>Louisiana Rain</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
+        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-08</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>sharing Jesus with an ex - Single</v>
+        <v>Louisiana Rain - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>1:55</v>
+        <v>3:41</v>
       </c>
       <c r="H160" t="str">
-        <v>Zoe Levert</v>
+        <v>Hunter Plake</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
+        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
       </c>
       <c r="L160" t="str">
-        <v>sharing Jesus with an ex - Zoe Levert</v>
+        <v>Louisiana Rain - Hunter Plake</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Body Control (feat. CHILLS)</v>
+        <v>sharing Jesus with an ex</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
+        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-08</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Body Control (feat. CHILLS) - Single</v>
+        <v>sharing Jesus with an ex - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:21</v>
+        <v>1:55</v>
       </c>
       <c r="H161" t="str">
-        <v>Cole Knight</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
+        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
       </c>
       <c r="L161" t="str">
-        <v>Body Control (feat. CHILLS) - Cole Knight</v>
+        <v>sharing Jesus with an ex - Zoe Levert</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
+        <v>Body Control (feat. CHILLS)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
+        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-08</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>A Prayer for the Dancefloor - Single</v>
+        <v>Body Control (feat. CHILLS) - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>6:54</v>
+        <v>3:21</v>
       </c>
       <c r="H162" t="str">
-        <v>Charlotte de Witte</v>
+        <v>Cole Knight</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
+        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
+        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
       </c>
       <c r="L162" t="str">
-        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
+        <v>Body Control (feat. CHILLS) - Cole Knight</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Realm of Endless Misery</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
+        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-08</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Liturgy of Death</v>
+        <v>A Prayer for the Dancefloor - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>4:56</v>
+        <v>6:54</v>
       </c>
       <c r="H163" t="str">
-        <v>Mayhem</v>
+        <v>Charlotte de Witte</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
+        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
+        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
       </c>
       <c r="L163" t="str">
-        <v>Realm of Endless Misery - Mayhem</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>BLEACH</v>
+        <v>Realm of Endless Misery</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/bleach/1869795882</v>
+        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-08</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>BLEACH - Single</v>
+        <v>Liturgy of Death</v>
       </c>
       <c r="G164" t="str">
-        <v>2:28</v>
+        <v>4:56</v>
       </c>
       <c r="H164" t="str">
-        <v>Ecca Vandal</v>
+        <v>Mayhem</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/bleach/1869795874</v>
+        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
       </c>
       <c r="L164" t="str">
-        <v>BLEACH - Ecca Vandal</v>
+        <v>Realm of Endless Misery - Mayhem</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>pretty in pink</v>
+        <v>BLEACH</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
+        <v>https://music.apple.com/us/song/bleach/1869795882</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-08</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>AngelPink</v>
+        <v>BLEACH - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:13</v>
+        <v>2:28</v>
       </c>
       <c r="H165" t="str">
-        <v>Keni Titus</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
+        <v>https://music.apple.com/us/album/bleach/1869795874</v>
       </c>
       <c r="L165" t="str">
-        <v>pretty in pink - Keni Titus</v>
+        <v>BLEACH - Ecca Vandal</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Pickup Man</v>
+        <v>pretty in pink</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
+        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-08</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Pickup Man - Single</v>
+        <v>AngelPink</v>
       </c>
       <c r="G166" t="str">
-        <v>3:28</v>
+        <v>3:13</v>
       </c>
       <c r="H166" t="str">
-        <v>Bayker Blankenship</v>
+        <v>Keni Titus</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
+        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
+        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
       </c>
       <c r="L166" t="str">
-        <v>Pickup Man - Bayker Blankenship</v>
+        <v>pretty in pink - Keni Titus</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Get To Drinkin'</v>
+        <v>Pickup Man</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
+        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-08</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Get To Drinkin' - Single</v>
+        <v>Pickup Man - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:48</v>
+        <v>3:28</v>
       </c>
       <c r="H167" t="str">
-        <v>Zach John King</v>
+        <v>Bayker Blankenship</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
+        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
+        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
       </c>
       <c r="L167" t="str">
-        <v>Get To Drinkin' - Zach John King</v>
+        <v>Pickup Man - Bayker Blankenship</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>The Roses</v>
+        <v>Get To Drinkin'</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
+        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-08</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>The Roses - Single</v>
+        <v>Get To Drinkin' - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:02</v>
+        <v>2:48</v>
       </c>
       <c r="H168" t="str">
-        <v>Russell Dickerson</v>
+        <v>Zach John King</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
+        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
+        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
       </c>
       <c r="L168" t="str">
-        <v>The Roses - Russell Dickerson</v>
+        <v>Get To Drinkin' - Zach John King</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>I Should Know Better</v>
+        <v>The Roses</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
+        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-08</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Under The Streetlights</v>
+        <v>The Roses - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:33</v>
+        <v>3:02</v>
       </c>
       <c r="H169" t="str">
-        <v>Michael Marcagi</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
+        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
+        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
       </c>
       <c r="L169" t="str">
-        <v>I Should Know Better - Michael Marcagi</v>
+        <v>The Roses - Russell Dickerson</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Never Do</v>
+        <v>I Should Know Better</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/never-do/1872842226</v>
+        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-08</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Never Do - Single</v>
+        <v>Under The Streetlights</v>
       </c>
       <c r="G170" t="str">
-        <v>1:58</v>
+        <v>3:33</v>
       </c>
       <c r="H170" t="str">
-        <v>charlieonnafriday</v>
+        <v>Michael Marcagi</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
+        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/never-do/1872842225</v>
+        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
       </c>
       <c r="L170" t="str">
-        <v>Never Do - charlieonnafriday</v>
+        <v>I Should Know Better - Michael Marcagi</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Primary Colors</v>
+        <v>Never Do</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
+        <v>https://music.apple.com/us/song/never-do/1872842226</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-08</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Lost on You</v>
+        <v>Never Do - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:37</v>
+        <v>1:58</v>
       </c>
       <c r="H171" t="str">
-        <v>Tigers Jaw</v>
+        <v>charlieonnafriday</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
+        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
+        <v>https://music.apple.com/us/album/never-do/1872842225</v>
       </c>
       <c r="L171" t="str">
-        <v>Primary Colors - Tigers Jaw</v>
+        <v>Never Do - charlieonnafriday</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Rock Bottom</v>
+        <v>Primary Colors</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
+        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-08</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Rock Bottom / Octopus - Single</v>
+        <v>Lost on You</v>
       </c>
       <c r="G172" t="str">
-        <v>4:10</v>
+        <v>3:37</v>
       </c>
       <c r="H172" t="str">
-        <v>King Krule</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
+        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
       </c>
       <c r="L172" t="str">
-        <v>Rock Bottom - King Krule</v>
+        <v>Primary Colors - Tigers Jaw</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Te Dedico</v>
+        <v>Rock Bottom</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-08</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Te Dedico - Single</v>
+        <v>Rock Bottom / Octopus - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:45</v>
+        <v>4:10</v>
       </c>
       <c r="H173" t="str">
-        <v>Carlos Vives</v>
+        <v>King Krule</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
+        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
       </c>
       <c r="L173" t="str">
-        <v>Te Dedico - Carlos Vives</v>
+        <v>Rock Bottom - King Krule</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>AUNQUE SEA EN DOS</v>
+        <v>Te Dedico</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
+        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-08</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>18</v>
+        <v>Te Dedico - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:38</v>
+        <v>3:45</v>
       </c>
       <c r="H174" t="str">
-        <v>Conexión Divina</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
+        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
+        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
       </c>
       <c r="L174" t="str">
-        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
+        <v>Te Dedico - Carlos Vives</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>I Dare You</v>
+        <v>AUNQUE SEA EN DOS</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
+        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-08</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>I Dare You - Single</v>
+        <v>18</v>
       </c>
       <c r="G175" t="str">
-        <v>3:25</v>
+        <v>2:38</v>
       </c>
       <c r="H175" t="str">
-        <v>Dylan Dunlap</v>
+        <v>Conexión Divina</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
+        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
+        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
       </c>
       <c r="L175" t="str">
-        <v>I Dare You - Dylan Dunlap</v>
+        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>new irish boyfriend</v>
+        <v>I Dare You</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
+        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-08</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>long time caller, first time listener</v>
+        <v>I Dare You - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:50</v>
+        <v>3:25</v>
       </c>
       <c r="H176" t="str">
-        <v>vegas water taxi</v>
+        <v>Dylan Dunlap</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
+        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
+        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
       </c>
       <c r="L176" t="str">
-        <v>new irish boyfriend - vegas water taxi</v>
+        <v>I Dare You - Dylan Dunlap</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Everyone Around Me Dancing</v>
+        <v>new irish boyfriend</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
+        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-08</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Singing</v>
+        <v>long time caller, first time listener</v>
       </c>
       <c r="G177" t="str">
-        <v>3:05</v>
+        <v>3:50</v>
       </c>
       <c r="H177" t="str">
-        <v>Gia Margaret</v>
+        <v>vegas water taxi</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
+        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
       </c>
       <c r="L177" t="str">
-        <v>Everyone Around Me Dancing - Gia Margaret</v>
+        <v>new irish boyfriend - vegas water taxi</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Good Enough (feat. Julie Doiron)</v>
+        <v>Everyone Around Me Dancing</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
+        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-08</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Big Changes</v>
+        <v>Singing</v>
       </c>
       <c r="G178" t="str">
-        <v>6:05</v>
+        <v>3:05</v>
       </c>
       <c r="H178" t="str">
-        <v>Status/Non-Status</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
+        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
       </c>
       <c r="L178" t="str">
-        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
+        <v>Everyone Around Me Dancing - Gia Margaret</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
+        <v>Good Enough (feat. Julie Doiron)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
+        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-08</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
+        <v>Big Changes</v>
       </c>
       <c r="G179" t="str">
-        <v>4:09</v>
+        <v>6:05</v>
       </c>
       <c r="H179" t="str">
-        <v>Julian Lage</v>
+        <v>Status/Non-Status</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
+        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
+        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
       </c>
       <c r="L179" t="str">
-        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
+        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Big Deal</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
+        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-08</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Big Deal - Single</v>
+        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="G180" t="str">
-        <v>3:47</v>
+        <v>4:09</v>
       </c>
       <c r="H180" t="str">
-        <v>In Color</v>
+        <v>Julian Lage</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
+        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
       </c>
       <c r="L180" t="str">
-        <v>Big Deal - In Color</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Buy What U Want</v>
+        <v>Big Deal</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
+        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-08</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Road To Osshland III - EP</v>
+        <v>Big Deal - Single</v>
       </c>
       <c r="G181" t="str">
         <v>3:47</v>
       </c>
       <c r="H181" t="str">
-        <v>Black Fortune</v>
+        <v>In Color</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
+        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
       </c>
       <c r="L181" t="str">
-        <v>Buy What U Want - Black Fortune</v>
+        <v>Big Deal - In Color</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Common Ground</v>
+        <v>Buy What U Want</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
+        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-08</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Common Ground - Single</v>
+        <v>Road To Osshland III - EP</v>
       </c>
       <c r="G182" t="str">
-        <v>1:42</v>
+        <v>3:47</v>
       </c>
       <c r="H182" t="str">
-        <v>ELIO</v>
+        <v>Black Fortune</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/elio/1501417625</v>
+        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
+        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
       </c>
       <c r="L182" t="str">
-        <v>Common Ground - ELIO</v>
+        <v>Buy What U Want - Black Fortune</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Cellophane</v>
+        <v>Common Ground</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
+        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-08</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Cellophane - Single</v>
+        <v>Common Ground - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>4:21</v>
+        <v>1:42</v>
       </c>
       <c r="H183" t="str">
-        <v>Maddie Zahm</v>
+        <v>ELIO</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
+        <v>https://music.apple.com/us/artist/elio/1501417625</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
+        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
       </c>
       <c r="L183" t="str">
-        <v>Cellophane - Maddie Zahm</v>
+        <v>Common Ground - ELIO</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>96 Camry</v>
+        <v>Cellophane</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
+        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-08</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>PRAY FOR ME</v>
+        <v>Cellophane - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:15</v>
+        <v>4:21</v>
       </c>
       <c r="H184" t="str">
-        <v>RAAHiiM</v>
+        <v>Maddie Zahm</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
+        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
+        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
       </c>
       <c r="L184" t="str">
-        <v>96 Camry - RAAHiiM</v>
+        <v>Cellophane - Maddie Zahm</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>La Allstar</v>
+        <v>96 Camry</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
+        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-08</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>La Allstar - Single</v>
+        <v>PRAY FOR ME</v>
       </c>
       <c r="G185" t="str">
-        <v>2:49</v>
+        <v>3:15</v>
       </c>
       <c r="H185" t="str">
-        <v>ELIKAI</v>
+        <v>RAAHiiM</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
+        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
+        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
       </c>
       <c r="L185" t="str">
-        <v>La Allstar - ELIKAI</v>
+        <v>96 Camry - RAAHiiM</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Luka</v>
+        <v>La Allstar</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/luka/1869396162</v>
+        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-08</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Luka - Single</v>
+        <v>La Allstar - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:07</v>
+        <v>2:49</v>
       </c>
       <c r="H186" t="str">
-        <v>Fonta</v>
+        <v>ELIKAI</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
+        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/luka/1869396161</v>
+        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
       </c>
       <c r="L186" t="str">
-        <v>Luka - Fonta</v>
+        <v>La Allstar - ELIKAI</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Ganas De Tenerla</v>
+        <v>Luka</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
+        <v>https://music.apple.com/us/song/luka/1869396162</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-08</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Ganas De Tenerla - Single</v>
+        <v>Luka - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:06</v>
+        <v>2:07</v>
       </c>
       <c r="H187" t="str">
-        <v>Silvestre Dangond</v>
+        <v>Fonta</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
+        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
+        <v>https://music.apple.com/us/album/luka/1869396161</v>
       </c>
       <c r="L187" t="str">
-        <v>Ganas De Tenerla - Silvestre Dangond</v>
+        <v>Luka - Fonta</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>In My Blue</v>
+        <v>Ganas De Tenerla</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
+        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-08</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Doomsday...Don't Leave Me Here</v>
+        <v>Ganas De Tenerla - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:26</v>
+        <v>3:06</v>
       </c>
       <c r="H188" t="str">
-        <v>Rosie Carney</v>
+        <v>Silvestre Dangond</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
+        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
+        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
       </c>
       <c r="L188" t="str">
-        <v>In My Blue - Rosie Carney</v>
+        <v>Ganas De Tenerla - Silvestre Dangond</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Living With It (feat. Feist)</v>
+        <v>In My Blue</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
+        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-08</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Hurts Like Hell</v>
+        <v>Doomsday...Don't Leave Me Here</v>
       </c>
       <c r="G189" t="str">
-        <v>3:20</v>
+        <v>3:26</v>
       </c>
       <c r="H189" t="str">
-        <v>Charlotte Cornfield</v>
+        <v>Rosie Carney</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
+        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
+        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
       </c>
       <c r="L189" t="str">
-        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
+        <v>In My Blue - Rosie Carney</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Silently</v>
+        <v>Living With It (feat. Feist)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/silently/1841629898</v>
+        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-08</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Croak Dream</v>
+        <v>Hurts Like Hell</v>
       </c>
       <c r="G190" t="str">
-        <v>3:29</v>
+        <v>3:20</v>
       </c>
       <c r="H190" t="str">
-        <v>Puma Blue</v>
+        <v>Charlotte Cornfield</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
+        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/silently/1841629444</v>
+        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
       </c>
       <c r="L190" t="str">
-        <v>Silently - Puma Blue</v>
+        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Ashes &amp; Smoke</v>
+        <v>Silently</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
+        <v>https://music.apple.com/us/song/silently/1841629898</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-08</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Ashes &amp; Smoke - Single</v>
+        <v>Croak Dream</v>
       </c>
       <c r="G191" t="str">
-        <v>3:05</v>
+        <v>3:29</v>
       </c>
       <c r="H191" t="str">
-        <v>Anna Graves</v>
+        <v>Puma Blue</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
+        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
+        <v>https://music.apple.com/us/album/silently/1841629444</v>
       </c>
       <c r="L191" t="str">
-        <v>Ashes &amp; Smoke - Anna Graves</v>
+        <v>Silently - Puma Blue</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Tormentor</v>
+        <v>Ashes &amp; Smoke</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
+        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-08</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>The Flowers I See You In - EP</v>
+        <v>Ashes &amp; Smoke - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:40</v>
+        <v>3:05</v>
       </c>
       <c r="H192" t="str">
-        <v>Ninush</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
+        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
+        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
       </c>
       <c r="L192" t="str">
-        <v>Tormentor - Ninush</v>
+        <v>Ashes &amp; Smoke - Anna Graves</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Red Rocking Chair</v>
+        <v>Tormentor</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
+        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-08</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Red Rocking Chair - Single</v>
+        <v>The Flowers I See You In - EP</v>
       </c>
       <c r="G193" t="str">
-        <v>6:28</v>
+        <v>2:40</v>
       </c>
       <c r="H193" t="str">
-        <v>All Them Witches</v>
+        <v>Ninush</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
+        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
       </c>
       <c r="L193" t="str">
-        <v>Red Rocking Chair - All Them Witches</v>
+        <v>Tormentor - Ninush</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
+        <v>Red Rocking Chair</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
+        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-08</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>...of Death and Fire</v>
+        <v>Red Rocking Chair - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>7:07</v>
+        <v>6:28</v>
       </c>
       <c r="H194" t="str">
-        <v>In Aeternum</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
+        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
       </c>
       <c r="L194" t="str">
-        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
+        <v>Red Rocking Chair - All Them Witches</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Mizantrop</v>
+        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
+        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-08</v>
@@ -7785,68 +7785,106 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Mizantrop</v>
+        <v>...of Death and Fire</v>
       </c>
       <c r="G195" t="str">
-        <v>3:42</v>
+        <v>7:07</v>
       </c>
       <c r="H195" t="str">
-        <v>She Past Away</v>
+        <v>In Aeternum</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
+        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
+        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
       </c>
       <c r="L195" t="str">
-        <v>Mizantrop - She Past Away</v>
+        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
+        <v>Mizantrop</v>
+      </c>
+      <c r="B196" t="str">
+        <v/>
+      </c>
+      <c r="C196" t="str">
+        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
+      </c>
+      <c r="D196" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v>Mizantrop</v>
+      </c>
+      <c r="G196" t="str">
+        <v>3:42</v>
+      </c>
+      <c r="H196" t="str">
+        <v>She Past Away</v>
+      </c>
+      <c r="I196" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J196" t="str">
+        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
+      </c>
+      <c r="K196" t="str">
+        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
+      </c>
+      <c r="L196" t="str">
+        <v>Mizantrop - She Past Away</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
         <v>In the Name of the Moth</v>
       </c>
-      <c r="B196" t="str">
-        <v/>
-      </c>
-      <c r="C196" t="str">
+      <c r="B197" t="str">
+        <v/>
+      </c>
+      <c r="C197" t="str">
         <v>https://music.apple.com/us/song/in-the-name-of-the-moth/1866911203</v>
       </c>
-      <c r="D196" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E196" t="str">
-        <v/>
-      </c>
-      <c r="F196" t="str">
+      <c r="D197" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
         <v>Hidden Fires Burn Hottest</v>
       </c>
-      <c r="G196" t="str">
+      <c r="G197" t="str">
         <v>7:15</v>
       </c>
-      <c r="H196" t="str">
+      <c r="H197" t="str">
         <v>Bosse-de-Nage</v>
       </c>
-      <c r="I196" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J196" t="str">
+      <c r="I197" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J197" t="str">
         <v>https://music.apple.com/us/artist/bosse-de-nage/465123183</v>
       </c>
-      <c r="K196" t="str">
+      <c r="K197" t="str">
         <v>https://music.apple.com/us/album/in-the-name-of-the-moth/1866911198</v>
       </c>
-      <c r="L196" t="str">
+      <c r="L197" t="str">
         <v>In the Name of the Moth - Bosse-de-Nage</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:L196"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל בנשלום – ממשיך ליפול</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-08</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%91%d7%a0%d7%a9%d7%9c%d7%95%d7%9d-%d7%9e%d7%9e%d7%a9%d7%99%d7%9a-%d7%9c%d7%99%d7%a4%d7%95%d7%9c/</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-08</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יובל בנשלום שר שיר עדין קשה, שכוחו נובע דווקא מהעובדה שהוא לא מנסה לפתור את הדיכאון – אלא להיות לידו. זהו שיר על אהבה תחת דיכאון, נאמנות של אוהבת שלא יודעת איך לעזור, פער כואב בין רצון למציאות הבחירה לספר</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>4:27</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Mariah Carey</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל בנשלום – ממשיך ליפול</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-08</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:27</v>
+        <v>3:26</v>
       </c>
       <c r="H3" t="str">
-        <v>Mariah Carey</v>
+        <v>Netflix</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B4" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-08</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:26</v>
+        <v>3:29</v>
       </c>
       <c r="H4" t="str">
-        <v>Netflix</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-08</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:29</v>
+        <v>2:59</v>
       </c>
       <c r="H5" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-08</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:59</v>
+        <v>2:51</v>
       </c>
       <c r="H6" t="str">
-        <v>mgk</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-08</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:51</v>
+        <v>4:13</v>
       </c>
       <c r="H7" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-08</v>
@@ -682,10 +682,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>4:13</v>
+        <v>4:41</v>
       </c>
       <c r="H8" t="str">
-        <v>Michael Bolton</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-08</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>4:41</v>
+        <v>7:03</v>
       </c>
       <c r="H9" t="str">
-        <v>NICK JONAS</v>
+        <v>Take That</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-08</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>7:03</v>
+        <v>4:37</v>
       </c>
       <c r="H10" t="str">
-        <v>Take That</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-08</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:37</v>
+        <v>3:54</v>
       </c>
       <c r="H11" t="str">
-        <v>Cliff Richard</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-08</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:54</v>
+        <v>3:06</v>
       </c>
       <c r="H12" t="str">
-        <v>Bryan Adams</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-08</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H13" t="str">
-        <v>Anna Graves</v>
+        <v>George Birge</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-08</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:21</v>
+        <v>4:09</v>
       </c>
       <c r="H14" t="str">
-        <v>George Birge</v>
+        <v>Warner Records</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
+        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-08</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:09</v>
+        <v>4:18</v>
       </c>
       <c r="H15" t="str">
-        <v>Warner Records</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
+        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-08</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:18</v>
+        <v>3:08</v>
       </c>
       <c r="H16" t="str">
-        <v>NICK JONAS</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
+        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-08</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:08</v>
+        <v>4:03</v>
       </c>
       <c r="H17" t="str">
-        <v>Charlie Puth</v>
+        <v>Olivia Newton-John</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
+        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-08</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:03</v>
+        <v>3:01</v>
       </c>
       <c r="H18" t="str">
-        <v>Olivia Newton-John</v>
+        <v>The Warning and Carin Leon</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
+        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-08</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:01</v>
+        <v>3:05</v>
       </c>
       <c r="H19" t="str">
-        <v>The Warning and Carin Leon</v>
+        <v>Iman Fandi</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
+        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-08</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:05</v>
+        <v>3:34</v>
       </c>
       <c r="H20" t="str">
-        <v>Iman Fandi</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
+        <v>Dylan Davidson - Escape Artist</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
+        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-08</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:34</v>
+        <v>3:15</v>
       </c>
       <c r="H21" t="str">
-        <v>Megan Moroney</v>
+        <v>Dylan Davidson</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
+        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dylan Davidson - Escape Artist</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
+        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-08</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:15</v>
+        <v>4:16</v>
       </c>
       <c r="H22" t="str">
-        <v>Dylan Davidson</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
+        <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
+        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-08</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:16</v>
+        <v>3:53</v>
       </c>
       <c r="H23" t="str">
-        <v>Lady Gaga</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
+        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video)</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
+        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-08</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:53</v>
+        <v>2:25</v>
       </c>
       <c r="H24" t="str">
-        <v>Carlos Vives</v>
+        <v>Monsieur Periné</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
+        <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
+        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-08</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:25</v>
+        <v>4:09</v>
       </c>
       <c r="H25" t="str">
-        <v>Monsieur Periné</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
+        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio)</v>
+        <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
+        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-08</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:09</v>
+        <v>2:45</v>
       </c>
       <c r="H26" t="str">
-        <v>The Happy Fits</v>
+        <v>Michael Aldag</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
+        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>chase (lyric vid) - Michael Aldag</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
+        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-08</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:45</v>
+        <v>4:07</v>
       </c>
       <c r="H27" t="str">
-        <v>Michael Aldag</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
+        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-08</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:07</v>
+        <v>4:34</v>
       </c>
       <c r="H28" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
+        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-08</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:34</v>
+        <v>5:14</v>
       </c>
       <c r="H29" t="str">
-        <v>Marc Anthony</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
+        <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
+        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-08</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>5:14</v>
+        <v>3:11</v>
       </c>
       <c r="H30" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer)</v>
+        <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
+        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-08</v>
@@ -1556,10 +1556,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:11</v>
+        <v>3:40</v>
       </c>
       <c r="H31" t="str">
-        <v>Michael Bolton</v>
+        <v>Lachie Gill</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
+        <v>Lachie Gill - Last Drive - Lachie Gill</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lachie Gill - Last Drive</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
+        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-08</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:40</v>
+        <v>3:45</v>
       </c>
       <c r="H32" t="str">
-        <v>Lachie Gill</v>
+        <v>Eli &amp; Fur</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lachie Gill - Last Drive - Lachie Gill</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
+        <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
+        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-08</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:45</v>
+        <v>4:19</v>
       </c>
       <c r="H33" t="str">
-        <v>Eli &amp; Fur</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
+        <v>Freya Skye - why'd you have to call - Freya Skye</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Freya Skye - why'd you have to call</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
+        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-08</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:19</v>
+        <v>2:30</v>
       </c>
       <c r="H34" t="str">
-        <v>Freya Skye</v>
+        <v>Jessie J</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Freya Skye - why'd you have to call - Freya Skye</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
+        <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
+        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-08</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:30</v>
+        <v>4:24</v>
       </c>
       <c r="H35" t="str">
-        <v>Jessie J</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
+        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer)</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B36" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
+        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-08</v>
@@ -1746,10 +1746,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:24</v>
+        <v>2:33</v>
       </c>
       <c r="H36" t="str">
-        <v>Marc Anthony</v>
+        <v>Clara Mae</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
+        <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
+        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-08</v>
@@ -1784,10 +1784,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:33</v>
+        <v>3:25</v>
       </c>
       <c r="H37" t="str">
-        <v>Clara Mae</v>
+        <v>metricmusic</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
+        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Metric - Victim of Luck (Official Music Video)</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B38" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
+        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-08</v>
@@ -1822,10 +1822,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:25</v>
+        <v>3:41</v>
       </c>
       <c r="H38" t="str">
-        <v>metricmusic</v>
+        <v>kesha</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
+        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-08</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:41</v>
+        <v>3:19</v>
       </c>
       <c r="H39" t="str">
-        <v>kesha</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B40" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
+        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-08</v>
@@ -1898,10 +1898,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:19</v>
+        <v>3:37</v>
       </c>
       <c r="H40" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B41" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
+        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-08</v>
@@ -1936,10 +1936,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:37</v>
+        <v>3:08</v>
       </c>
       <c r="H41" t="str">
-        <v>Vera Blue</v>
+        <v>Bob Moses</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B42" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
+        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-08</v>
@@ -1974,10 +1974,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:08</v>
+        <v>3:28</v>
       </c>
       <c r="H42" t="str">
-        <v>Bob Moses</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B43" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
+        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-08</v>
@@ -2012,7 +2012,7 @@
         <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:28</v>
+        <v>5:05</v>
       </c>
       <c r="H43" t="str">
         <v>Marc Anthony</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
+        <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B44" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
+        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-08</v>
@@ -2050,10 +2050,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>5:05</v>
+        <v>3:14</v>
       </c>
       <c r="H44" t="str">
-        <v>Marc Anthony</v>
+        <v>Loreen</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
+        <v>Loreen - Feels Like Heaven - Loreen</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Loreen - Feels Like Heaven</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B45" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
+        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-08</v>
@@ -2088,10 +2088,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:14</v>
+        <v>3:36</v>
       </c>
       <c r="H45" t="str">
-        <v>Loreen</v>
+        <v>Take That</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Loreen - Feels Like Heaven - Loreen</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B46" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
+        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-08</v>
@@ -2126,10 +2126,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:36</v>
+        <v>5:31</v>
       </c>
       <c r="H46" t="str">
-        <v>Take That</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
+        <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B47" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
+        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-08</v>
@@ -2164,10 +2164,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>5:31</v>
+        <v>3:37</v>
       </c>
       <c r="H47" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
+        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio)</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B48" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-08</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:37</v>
+        <v>4:58</v>
       </c>
       <c r="H48" t="str">
-        <v>Nothing But Thieves</v>
+        <v>The Warning</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B49" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-08</v>
@@ -2240,10 +2240,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:58</v>
+        <v>5:08</v>
       </c>
       <c r="H49" t="str">
-        <v>The Warning</v>
+        <v>The Offspring</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B50" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-08</v>
@@ -2278,10 +2278,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>5:08</v>
+        <v>4:38</v>
       </c>
       <c r="H50" t="str">
-        <v>The Offspring</v>
+        <v>Roxette</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-08</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:38</v>
+        <v>3:50</v>
       </c>
       <c r="H51" t="str">
-        <v>Roxette</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-08</v>
@@ -2354,10 +2354,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:50</v>
+        <v>3:10</v>
       </c>
       <c r="H52" t="str">
-        <v>Jessie Ware</v>
+        <v>Joseph</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-08</v>
@@ -2392,10 +2392,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:10</v>
+        <v>2:44</v>
       </c>
       <c r="H53" t="str">
-        <v>Joseph</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-08</v>
@@ -2430,10 +2430,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:44</v>
+        <v>2:57</v>
       </c>
       <c r="H54" t="str">
-        <v>Dean Lewis</v>
+        <v>Take That</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-08</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:57</v>
+        <v>3:07</v>
       </c>
       <c r="H55" t="str">
-        <v>Take That</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B56" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-08</v>
@@ -2506,10 +2506,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:07</v>
+        <v>4:47</v>
       </c>
       <c r="H56" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-08</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:47</v>
+        <v>3:22</v>
       </c>
       <c r="H57" t="str">
-        <v>Paris Paloma</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-08</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:22</v>
+        <v>2:48</v>
       </c>
       <c r="H58" t="str">
-        <v>Zara Larsson</v>
+        <v>only the poets</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B59" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-08</v>
@@ -2620,10 +2620,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:48</v>
+        <v>2:52</v>
       </c>
       <c r="H59" t="str">
-        <v>only the poets</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-08</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:52</v>
+        <v>3:33</v>
       </c>
       <c r="H60" t="str">
-        <v>Katelyn Tarver</v>
+        <v>David Guetta</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-08</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:33</v>
+        <v>2:41</v>
       </c>
       <c r="H61" t="str">
-        <v>David Guetta</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-08</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>2:41</v>
+        <v>4:01</v>
       </c>
       <c r="H62" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-08</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>4:01</v>
+        <v>3:16</v>
       </c>
       <c r="H63" t="str">
-        <v>Ella Langley</v>
+        <v>Dogpark</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-08</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:16</v>
+        <v>3:03</v>
       </c>
       <c r="H64" t="str">
-        <v>Dogpark</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-08</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:03</v>
+        <v>2:41</v>
       </c>
       <c r="H65" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>ERNEST</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-08</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:41</v>
+        <v>3:05</v>
       </c>
       <c r="H66" t="str">
-        <v>ERNEST</v>
+        <v>Labrinth</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-08</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:05</v>
+        <v>2:46</v>
       </c>
       <c r="H67" t="str">
-        <v>Labrinth</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-08</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:46</v>
+        <v>3:32</v>
       </c>
       <c r="H68" t="str">
-        <v>Grace VanderWaal</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-08</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:32</v>
+        <v>3:42</v>
       </c>
       <c r="H69" t="str">
-        <v>VOILÀ</v>
+        <v>Cannons</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-08</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:42</v>
+        <v>2:38</v>
       </c>
       <c r="H70" t="str">
-        <v>Cannons</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-08</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:38</v>
+        <v>3:10</v>
       </c>
       <c r="H71" t="str">
-        <v>Kylie Morgan</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-08</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:10</v>
+        <v>3:57</v>
       </c>
       <c r="H72" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-08</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:57</v>
+        <v>2:19</v>
       </c>
       <c r="H73" t="str">
-        <v>Willie Nelson</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-08</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:19</v>
+        <v>4:04</v>
       </c>
       <c r="H74" t="str">
-        <v>JeremyCampMusic</v>
+        <v>India Martínez</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-08</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:04</v>
+        <v>2:16</v>
       </c>
       <c r="H75" t="str">
-        <v>India Martínez</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-08</v>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:16</v>
+        <v>5:58</v>
       </c>
       <c r="H76" t="str">
-        <v>Chelsea Cutler</v>
+        <v>TINI</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-08</v>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>5:58</v>
+        <v>3:26</v>
       </c>
       <c r="H77" t="str">
-        <v>TINI</v>
+        <v>Charley</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-08</v>
@@ -3342,10 +3342,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:26</v>
+        <v>4:05</v>
       </c>
       <c r="H78" t="str">
-        <v>Charley</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B79" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-08</v>
@@ -3380,10 +3380,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:05</v>
+        <v>3:16</v>
       </c>
       <c r="H79" t="str">
-        <v>Demi Lovato</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B80" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-08</v>
@@ -3418,10 +3418,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:16</v>
+        <v>3:14</v>
       </c>
       <c r="H80" t="str">
-        <v>Teddy Swims</v>
+        <v>Beck</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-08</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:14</v>
+        <v>2:57</v>
       </c>
       <c r="H81" t="str">
-        <v>Beck</v>
+        <v>The Offspring</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-08</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>2:57</v>
+        <v>4:10</v>
       </c>
       <c r="H82" t="str">
-        <v>The Offspring</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-08</v>
@@ -3532,10 +3532,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:10</v>
+        <v>2:10</v>
       </c>
       <c r="H83" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B84" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-08</v>
@@ -3570,10 +3570,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:10</v>
+        <v>3:52</v>
       </c>
       <c r="H84" t="str">
-        <v>Jason Derulo</v>
+        <v>lights</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B85" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-08</v>
@@ -3608,10 +3608,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:52</v>
+        <v>3:50</v>
       </c>
       <c r="H85" t="str">
-        <v>lights</v>
+        <v>Telenova</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B86" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-08</v>
@@ -3646,10 +3646,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:50</v>
+        <v>5:32</v>
       </c>
       <c r="H86" t="str">
-        <v>Telenova</v>
+        <v>Marcin</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-08</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>5:32</v>
+        <v>4:27</v>
       </c>
       <c r="H87" t="str">
-        <v>Marcin</v>
+        <v>We Three</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-08</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:27</v>
+        <v>3:01</v>
       </c>
       <c r="H88" t="str">
-        <v>We Three</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B89" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-08</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:01</v>
+        <v>3:20</v>
       </c>
       <c r="H89" t="str">
-        <v>Timebelle Official</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-08</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:20</v>
+        <v>3:34</v>
       </c>
       <c r="H90" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-08</v>
@@ -3836,10 +3836,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:34</v>
+        <v>4:01</v>
       </c>
       <c r="H91" t="str">
-        <v>Clinton Kane</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-08</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:01</v>
+        <v>3:24</v>
       </c>
       <c r="H92" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-08</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:24</v>
+        <v>5:52</v>
       </c>
       <c r="H93" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-08</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>5:52</v>
+        <v>5:01</v>
       </c>
       <c r="H94" t="str">
-        <v>Harry Styles</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-08</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>5:01</v>
+        <v>4:12</v>
       </c>
       <c r="H95" t="str">
-        <v>Neal Francis</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-08</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>4:12</v>
+        <v>3:59</v>
       </c>
       <c r="H96" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-08</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:59</v>
+        <v>2:56</v>
       </c>
       <c r="H97" t="str">
-        <v>Holly Humberstone</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-08</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:56</v>
+        <v>3:46</v>
       </c>
       <c r="H98" t="str">
-        <v>Cliff Richard</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-08</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:46</v>
+        <v>4:37</v>
       </c>
       <c r="H99" t="str">
-        <v>Jessie Ware</v>
+        <v>Bella White</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Ryan Wright - Film School Kids (Official Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-08</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:37</v>
+        <v>4:06</v>
       </c>
       <c r="H100" t="str">
-        <v>Bella White</v>
+        <v>Ryan Wright</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-08</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:06</v>
+        <v>3:54</v>
       </c>
       <c r="H101" t="str">
-        <v>Ryan Wright</v>
+        <v>Dove Cameron</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Die For Me</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-08</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G102" t="str">
-        <v>3:54</v>
+        <v>3:00</v>
       </c>
       <c r="H102" t="str">
-        <v>Dove Cameron</v>
+        <v>ZAYN</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
       </c>
       <c r="L102" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Die For Me - ZAYN</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Die For Me</v>
+        <v>Two Six</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
+        <v>https://music.apple.com/us/song/two-six/1875080974</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-08</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>KONNAKOL</v>
+        <v>The Fall-Off</v>
       </c>
       <c r="G103" t="str">
-        <v>3:00</v>
+        <v>3:16</v>
       </c>
       <c r="H103" t="str">
-        <v>ZAYN</v>
+        <v>J. Cole</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
+        <v>https://music.apple.com/us/album/two-six/1875080726</v>
       </c>
       <c r="L103" t="str">
-        <v>Die For Me - ZAYN</v>
+        <v>Two Six - J. Cole</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Two Six</v>
+        <v>Dracula (JENNIE Remix)</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/two-six/1875080974</v>
+        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-08</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Fall-Off</v>
+        <v>Dracula (Remix) - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:16</v>
+        <v>3:29</v>
       </c>
       <c r="H104" t="str">
-        <v>J. Cole</v>
+        <v>Tame Impala</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
+        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/two-six/1875080726</v>
+        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
       </c>
       <c r="L104" t="str">
-        <v>Two Six - J. Cole</v>
+        <v>Dracula (JENNIE Remix) - Tame Impala</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Dracula (JENNIE Remix)</v>
+        <v>Hotel California</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
+        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-08</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Dracula (Remix) - Single</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G105" t="str">
-        <v>3:29</v>
+        <v>2:08</v>
       </c>
       <c r="H105" t="str">
-        <v>Tame Impala</v>
+        <v>Joji</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
+        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
       </c>
       <c r="L105" t="str">
-        <v>Dracula (JENNIE Remix) - Tame Impala</v>
+        <v>Hotel California - Joji</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Hotel California</v>
+        <v>Homewrecker</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
+        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-08</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Piss In The Wind</v>
+        <v>Homewrecker - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>2:08</v>
+        <v>3:29</v>
       </c>
       <c r="H106" t="str">
-        <v>Joji</v>
+        <v>sombr</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
+        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
       </c>
       <c r="L106" t="str">
-        <v>Hotel California - Joji</v>
+        <v>Homewrecker - sombr</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Homewrecker</v>
+        <v>Might Just</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
+        <v>https://music.apple.com/us/song/might-just/1858755211</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-08</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Homewrecker - Single</v>
+        <v>Do You Still Love Me?</v>
       </c>
       <c r="G107" t="str">
-        <v>3:29</v>
+        <v>3:43</v>
       </c>
       <c r="H107" t="str">
-        <v>sombr</v>
+        <v>Ella Mai</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
+        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
+        <v>https://music.apple.com/us/album/might-just/1858754868</v>
       </c>
       <c r="L107" t="str">
-        <v>Homewrecker - sombr</v>
+        <v>Might Just - Ella Mai</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Might Just</v>
+        <v>Cloud 9</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/might-just/1858755211</v>
+        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-08</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Do You Still Love Me?</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G108" t="str">
-        <v>3:43</v>
+        <v>3:33</v>
       </c>
       <c r="H108" t="str">
-        <v>Ella Mai</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/might-just/1858754868</v>
+        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
       </c>
       <c r="L108" t="str">
-        <v>Might Just - Ella Mai</v>
+        <v>Cloud 9 - Megan Moroney</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Cloud 9</v>
+        <v>Cry</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
+        <v>https://music.apple.com/us/song/cry/1845189974</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-08</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Cloud 9</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G109" t="str">
-        <v>3:33</v>
+        <v>3:07</v>
       </c>
       <c r="H109" t="str">
-        <v>Megan Moroney</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
+        <v>https://music.apple.com/us/album/cry/1845189970</v>
       </c>
       <c r="L109" t="str">
-        <v>Cloud 9 - Megan Moroney</v>
+        <v>Cry - Charlie Puth</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Cry</v>
+        <v>I'll Change for You</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/cry/1845189974</v>
+        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-08</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G110" t="str">
-        <v>3:07</v>
+        <v>3:16</v>
       </c>
       <c r="H110" t="str">
-        <v>Charlie Puth</v>
+        <v>Mitski</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/cry/1845189970</v>
+        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
       </c>
       <c r="L110" t="str">
-        <v>Cry - Charlie Puth</v>
+        <v>I'll Change for You - Mitski</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>I'll Change for You</v>
+        <v>ASSIGNMENT</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
+        <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-08</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>ASSIGNMENT - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:16</v>
+        <v>2:23</v>
       </c>
       <c r="H111" t="str">
-        <v>Mitski</v>
+        <v>Power Snatch</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
+        <v>https://music.apple.com/us/album/assignment/1872764438</v>
       </c>
       <c r="L111" t="str">
-        <v>I'll Change for You - Mitski</v>
+        <v>ASSIGNMENT - Power Snatch</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ASSIGNMENT</v>
+        <v>Como en el Idilio</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/assignment/1872764440</v>
+        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-08</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>ASSIGNMENT - Single</v>
+        <v>Como en el Idilio - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>2:23</v>
+        <v>4:27</v>
       </c>
       <c r="H112" t="str">
-        <v>Power Snatch</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
+        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/assignment/1872764438</v>
+        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
       </c>
       <c r="L112" t="str">
-        <v>ASSIGNMENT - Power Snatch</v>
+        <v>Como en el Idilio - Marc Anthony</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Como en el Idilio</v>
+        <v>golden boy</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
+        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-08</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Como en el Idilio - Single</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G113" t="str">
-        <v>4:27</v>
+        <v>3:17</v>
       </c>
       <c r="H113" t="str">
-        <v>Marc Anthony</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
+        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
       </c>
       <c r="L113" t="str">
-        <v>Como en el Idilio - Marc Anthony</v>
+        <v>golden boy - Freya Skye</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>golden boy</v>
+        <v>Penny in the Lake</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
+        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-08</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>stardust - EP</v>
+        <v>Singin’ to an Empty Chair</v>
       </c>
       <c r="G114" t="str">
-        <v>3:17</v>
+        <v>3:51</v>
       </c>
       <c r="H114" t="str">
-        <v>Freya Skye</v>
+        <v>Ratboys</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
+        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
       </c>
       <c r="L114" t="str">
-        <v>golden boy - Freya Skye</v>
+        <v>Penny in the Lake - Ratboys</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Penny in the Lake</v>
+        <v>Heaven</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
+        <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-08</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Singin’ to an Empty Chair</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G115" t="str">
-        <v>3:51</v>
+        <v>4:26</v>
       </c>
       <c r="H115" t="str">
-        <v>Ratboys</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
+        <v>https://music.apple.com/us/album/heaven/1862570378</v>
       </c>
       <c r="L115" t="str">
-        <v>Penny in the Lake - Ratboys</v>
+        <v>Heaven - Arlo Parks</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Heaven</v>
+        <v>Adrenaline</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/heaven/1862570892</v>
+        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-08</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Ambiguous Desire</v>
+        <v>GOLDEN HOUR : Part.4 - EP</v>
       </c>
       <c r="G116" t="str">
-        <v>4:26</v>
+        <v>3:39</v>
       </c>
       <c r="H116" t="str">
-        <v>Arlo Parks</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/heaven/1862570378</v>
+        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
       </c>
       <c r="L116" t="str">
-        <v>Heaven - Arlo Parks</v>
+        <v>Adrenaline - ATEEZ</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Adrenaline</v>
+        <v>Sweet To Me</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
+        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-08</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>GOLDEN HOUR : Part.4 - EP</v>
+        <v>Sunday Best</v>
       </c>
       <c r="G117" t="str">
-        <v>3:39</v>
+        <v>4:17</v>
       </c>
       <c r="H117" t="str">
-        <v>ATEEZ</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
+        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
       </c>
       <c r="L117" t="str">
-        <v>Adrenaline - ATEEZ</v>
+        <v>Sweet To Me - Nick Jonas</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Sweet To Me</v>
+        <v>Time Goes On</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
+        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-08</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Sunday Best</v>
+        <v>Time Goes On - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>4:17</v>
+        <v>2:55</v>
       </c>
       <c r="H118" t="str">
-        <v>Nick Jonas</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
+        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
       </c>
       <c r="L118" t="str">
-        <v>Sweet To Me - Nick Jonas</v>
+        <v>Time Goes On - Koe Wetzel</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Time Goes On</v>
+        <v>Drive Safe</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
+        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-08</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Time Goes On - Single</v>
+        <v>Drive Safe - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:55</v>
+        <v>3:21</v>
       </c>
       <c r="H119" t="str">
-        <v>Koe Wetzel</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
+        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
       </c>
       <c r="L119" t="str">
-        <v>Time Goes On - Koe Wetzel</v>
+        <v>Drive Safe - Myles Smith</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drive Safe</v>
+        <v>Love To Be Loved</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
+        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-08</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Drive Safe - Single</v>
+        <v>Love To Be Loved - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:21</v>
+        <v>2:50</v>
       </c>
       <c r="H120" t="str">
-        <v>Myles Smith</v>
+        <v>The Warning</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
+        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
       </c>
       <c r="L120" t="str">
-        <v>Drive Safe - Myles Smith</v>
+        <v>Love To Be Loved - The Warning</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Love To Be Loved</v>
+        <v>Mi Yo de Antes</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-08</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Love To Be Loved - Single</v>
+        <v>Mi Yo de Antes - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:50</v>
+        <v>3:02</v>
       </c>
       <c r="H121" t="str">
-        <v>The Warning</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
       </c>
       <c r="L121" t="str">
-        <v>Love To Be Loved - The Warning</v>
+        <v>Mi Yo de Antes - Eden Muñoz</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Mi Yo de Antes</v>
+        <v>Omens</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
+        <v>https://music.apple.com/us/song/omens/1872546206</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-08</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Mi Yo de Antes - Single</v>
+        <v>Omens - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:02</v>
+        <v>2:00</v>
       </c>
       <c r="H122" t="str">
-        <v>Eden Muñoz</v>
+        <v>EsDeeKid</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
+        <v>https://music.apple.com/us/album/omens/1872546204</v>
       </c>
       <c r="L122" t="str">
-        <v>Mi Yo de Antes - Eden Muñoz</v>
+        <v>Omens - EsDeeKid</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Omens</v>
+        <v>My Regards</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/omens/1872546206</v>
+        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-08</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Omens - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G123" t="str">
-        <v>2:00</v>
+        <v>3:11</v>
       </c>
       <c r="H123" t="str">
-        <v>EsDeeKid</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/omens/1872546204</v>
+        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
       </c>
       <c r="L123" t="str">
-        <v>Omens - EsDeeKid</v>
+        <v>My Regards - Maisie Peters</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>My Regards</v>
+        <v>Time After Time</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
+        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-08</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Florescence</v>
+        <v>Time After Time - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:11</v>
+        <v>2:48</v>
       </c>
       <c r="H124" t="str">
-        <v>Maisie Peters</v>
+        <v>EJAE</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
+        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
       </c>
       <c r="L124" t="str">
-        <v>My Regards - Maisie Peters</v>
+        <v>Time After Time - EJAE</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Time After Time</v>
+        <v>Don't Want Your Love</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
+        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-08</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Time After Time - Single</v>
+        <v>ODYSSEY</v>
       </c>
       <c r="G125" t="str">
-        <v>2:48</v>
+        <v>3:12</v>
       </c>
       <c r="H125" t="str">
-        <v>EJAE</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
+        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
       </c>
       <c r="L125" t="str">
-        <v>Time After Time - EJAE</v>
+        <v>Don't Want Your Love - ILLENIUM</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Don't Want Your Love</v>
+        <v>Pa' Los Envidiosos</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
+        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-08</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>ODYSSEY</v>
+        <v>Pa' Los Envidiosos - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:12</v>
+        <v>3:37</v>
       </c>
       <c r="H126" t="str">
-        <v>ILLENIUM</v>
+        <v>Pitbull</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
+        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
       </c>
       <c r="L126" t="str">
-        <v>Don't Want Your Love - ILLENIUM</v>
+        <v>Pa' Los Envidiosos - Pitbull</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Pa' Los Envidiosos</v>
+        <v>Plei</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
+        <v>https://music.apple.com/us/song/plei/1872137577</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-08</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Pa' Los Envidiosos - Single</v>
+        <v>Plei - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:37</v>
+        <v>3:22</v>
       </c>
       <c r="H127" t="str">
-        <v>Pitbull</v>
+        <v>Chuwi</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
+        <v>https://music.apple.com/us/album/plei/1872137372</v>
       </c>
       <c r="L127" t="str">
-        <v>Pa' Los Envidiosos - Pitbull</v>
+        <v>Plei - Chuwi</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Plei</v>
+        <v>Flood (feat. Bon Iver)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/plei/1872137577</v>
+        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-08</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Plei - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G128" t="str">
-        <v>3:22</v>
+        <v>2:59</v>
       </c>
       <c r="H128" t="str">
-        <v>Chuwi</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/plei/1872137372</v>
+        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
       </c>
       <c r="L128" t="str">
-        <v>Plei - Chuwi</v>
+        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Flood (feat. Bon Iver)</v>
+        <v>Rain</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
+        <v>https://music.apple.com/us/song/rain/1867258289</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-08</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Rain - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:59</v>
+        <v>3:28</v>
       </c>
       <c r="H129" t="str">
-        <v>Dua Saleh</v>
+        <v>FISHER</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
+        <v>https://music.apple.com/us/album/rain/1867258288</v>
       </c>
       <c r="L129" t="str">
-        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
+        <v>Rain - FISHER</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Rain</v>
+        <v>Release The Pressure</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/rain/1867258289</v>
+        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-08</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Rain - Single</v>
+        <v>Release The Pressure - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:28</v>
+        <v>3:23</v>
       </c>
       <c r="H130" t="str">
-        <v>FISHER</v>
+        <v>Calvin Harris</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
+        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/rain/1867258288</v>
+        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
       </c>
       <c r="L130" t="str">
-        <v>Rain - FISHER</v>
+        <v>Release The Pressure - Calvin Harris</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Release The Pressure</v>
+        <v>Sexistential (Arca’s Take)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
+        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-08</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Release The Pressure - Single</v>
+        <v>Sexistential (Arca’s Take) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:23</v>
+        <v>3:44</v>
       </c>
       <c r="H131" t="str">
-        <v>Calvin Harris</v>
+        <v>Robyn</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
+        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
       </c>
       <c r="L131" t="str">
-        <v>Release The Pressure - Calvin Harris</v>
+        <v>Sexistential (Arca’s Take) - Robyn</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Sexistential (Arca’s Take)</v>
+        <v>heal something</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
+        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-08</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Sexistential (Arca’s Take) - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G132" t="str">
-        <v>3:44</v>
+        <v>3:01</v>
       </c>
       <c r="H132" t="str">
-        <v>Robyn</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
+        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
       </c>
       <c r="L132" t="str">
-        <v>Sexistential (Arca’s Take) - Robyn</v>
+        <v>heal something - Sasha Keable</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>heal something</v>
+        <v>Buenos Días</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
+        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-08</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>ACT II</v>
+        <v>Buenos Días - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:01</v>
+        <v>2:39</v>
       </c>
       <c r="H133" t="str">
-        <v>Sasha Keable</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
+        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
       </c>
       <c r="L133" t="str">
-        <v>heal something - Sasha Keable</v>
+        <v>Buenos Días - Eladio Carrión</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Buenos Días</v>
+        <v>COOK</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
+        <v>https://music.apple.com/us/song/cook/1872816147</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-08</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Buenos Días - Single</v>
+        <v>COOK - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:39</v>
+        <v>2:50</v>
       </c>
       <c r="H134" t="str">
-        <v>Eladio Carrión</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
+        <v>https://music.apple.com/us/album/cook/1872816146</v>
       </c>
       <c r="L134" t="str">
-        <v>Buenos Días - Eladio Carrión</v>
+        <v>COOK - SOFI TUKKER</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>COOK</v>
+        <v>You Got to Lose</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/cook/1872816147</v>
+        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-08</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>COOK - Single</v>
+        <v>Peaches!</v>
       </c>
       <c r="G135" t="str">
-        <v>2:50</v>
+        <v>3:17</v>
       </c>
       <c r="H135" t="str">
-        <v>SOFI TUKKER</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/cook/1872816146</v>
+        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
       </c>
       <c r="L135" t="str">
-        <v>COOK - SOFI TUKKER</v>
+        <v>You Got to Lose - The Black Keys</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>You Got to Lose</v>
+        <v>Different Kind Of Love</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
+        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-08</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Peaches!</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G136" t="str">
-        <v>3:17</v>
+        <v>3:39</v>
       </c>
       <c r="H136" t="str">
-        <v>The Black Keys</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
+        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
       </c>
       <c r="L136" t="str">
-        <v>You Got to Lose - The Black Keys</v>
+        <v>Different Kind Of Love - Young the Giant</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Different Kind Of Love</v>
+        <v>Living Water</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
+        <v>https://music.apple.com/us/song/living-water/1871565262</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-08</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Victory Garden</v>
+        <v>Reconstruction: Second Story</v>
       </c>
       <c r="G137" t="str">
-        <v>3:39</v>
+        <v>2:09</v>
       </c>
       <c r="H137" t="str">
-        <v>Young the Giant</v>
+        <v>Lecrae</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
+        <v>https://music.apple.com/us/album/living-water/1871564892</v>
       </c>
       <c r="L137" t="str">
-        <v>Different Kind Of Love - Young the Giant</v>
+        <v>Living Water - Lecrae</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Living Water</v>
+        <v>What It Feels Like</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/living-water/1871565262</v>
+        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-08</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Reconstruction: Second Story</v>
+        <v>What It Feels Like - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:09</v>
+        <v>2:18</v>
       </c>
       <c r="H138" t="str">
-        <v>Lecrae</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/living-water/1871564892</v>
+        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
       </c>
       <c r="L138" t="str">
-        <v>Living Water - Lecrae</v>
+        <v>What It Feels Like - Dillon Francis</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>What It Feels Like</v>
+        <v>neck</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
+        <v>https://music.apple.com/us/song/neck/1866953832</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-08</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>What It Feels Like - Single</v>
+        <v>neck - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:18</v>
+        <v>3:40</v>
       </c>
       <c r="H139" t="str">
-        <v>Dillon Francis</v>
+        <v>Mau P</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
+        <v>https://music.apple.com/us/album/neck/1866953831</v>
       </c>
       <c r="L139" t="str">
-        <v>What It Feels Like - Dillon Francis</v>
+        <v>neck - Mau P</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>neck</v>
+        <v>Colorblind</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/neck/1866953832</v>
+        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-08</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>neck - Single</v>
+        <v>Colorblind - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:40</v>
+        <v>2:56</v>
       </c>
       <c r="H140" t="str">
-        <v>Mau P</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/neck/1866953831</v>
+        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
       </c>
       <c r="L140" t="str">
-        <v>neck - Mau P</v>
+        <v>Colorblind - Gavin Adcock</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Colorblind</v>
+        <v>Au Revoir Reservoir</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
+        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-08</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Colorblind - Single</v>
+        <v>Tenterhooks</v>
       </c>
       <c r="G141" t="str">
-        <v>2:56</v>
+        <v>3:21</v>
       </c>
       <c r="H141" t="str">
-        <v>Gavin Adcock</v>
+        <v>Silversun Pickups</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
+        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
       </c>
       <c r="L141" t="str">
-        <v>Colorblind - Gavin Adcock</v>
+        <v>Au Revoir Reservoir - Silversun Pickups</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Au Revoir Reservoir</v>
+        <v>Flavorless</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
+        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-08</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Tenterhooks</v>
+        <v>Flavorless - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:21</v>
+        <v>3:31</v>
       </c>
       <c r="H142" t="str">
-        <v>Silversun Pickups</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
+        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
       </c>
       <c r="L142" t="str">
-        <v>Au Revoir Reservoir - Silversun Pickups</v>
+        <v>Flavorless - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Flavorless</v>
+        <v>Nunca</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
+        <v>https://music.apple.com/us/song/nunca/1860691713</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-08</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Flavorless - Single</v>
+        <v>ESCENAS</v>
       </c>
       <c r="G143" t="str">
-        <v>3:31</v>
+        <v>3:05</v>
       </c>
       <c r="H143" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Sin Bandera</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
+        <v>https://music.apple.com/us/album/nunca/1860691704</v>
       </c>
       <c r="L143" t="str">
-        <v>Flavorless - Dexter and The Moonrocks</v>
+        <v>Nunca - Sin Bandera</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Nunca</v>
+        <v>Just In Case</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/nunca/1860691713</v>
+        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-08</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>ESCENAS</v>
+        <v>NO HArD FEELINGS (Deluxe)</v>
       </c>
       <c r="G144" t="str">
-        <v>3:05</v>
+        <v>1:45</v>
       </c>
       <c r="H144" t="str">
-        <v>Sin Bandera</v>
+        <v>Marc E. Bassy</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
+        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/nunca/1860691704</v>
+        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
       </c>
       <c r="L144" t="str">
-        <v>Nunca - Sin Bandera</v>
+        <v>Just In Case - Marc E. Bassy</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Just In Case</v>
+        <v>Thinking of You</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
+        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-08</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>NO HArD FEELINGS (Deluxe)</v>
+        <v>Thinking of You - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>1:45</v>
+        <v>3:00</v>
       </c>
       <c r="H145" t="str">
-        <v>Marc E. Bassy</v>
+        <v>AP Dhillon</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
+        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
+        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
       </c>
       <c r="L145" t="str">
-        <v>Just In Case - Marc E. Bassy</v>
+        <v>Thinking of You - AP Dhillon</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Thinking of You</v>
+        <v>House Of Cards</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
+        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-08</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Thinking of You - Single</v>
+        <v>House of Cards</v>
       </c>
       <c r="G146" t="str">
-        <v>3:00</v>
+        <v>3:26</v>
       </c>
       <c r="H146" t="str">
-        <v>AP Dhillon</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
+        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
       </c>
       <c r="L146" t="str">
-        <v>Thinking of You - AP Dhillon</v>
+        <v>House Of Cards - The Amity Affliction</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>House Of Cards</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-08</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>House of Cards</v>
+        <v>Stay With Me - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:26</v>
+        <v>3:21</v>
       </c>
       <c r="H147" t="str">
-        <v>The Amity Affliction</v>
+        <v>Agents Of Time</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
+        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
       </c>
       <c r="L147" t="str">
-        <v>House Of Cards - The Amity Affliction</v>
+        <v>Stay With Me - Agents Of Time</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Stay With Me</v>
+        <v>I had a dream...</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-08</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Stay With Me - Single</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G148" t="str">
-        <v>3:21</v>
+        <v>2:39</v>
       </c>
       <c r="H148" t="str">
-        <v>Agents Of Time</v>
+        <v>R3HAB</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
       </c>
       <c r="L148" t="str">
-        <v>Stay With Me - Agents Of Time</v>
+        <v>I had a dream... - R3HAB</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>I had a dream...</v>
+        <v>Back to You</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
+        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-08</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Dream inside a dream…</v>
+        <v>Satellite</v>
       </c>
       <c r="G149" t="str">
-        <v>2:39</v>
+        <v>3:10</v>
       </c>
       <c r="H149" t="str">
-        <v>R3HAB</v>
+        <v>Charlotte Sands</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
+        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
       </c>
       <c r="L149" t="str">
-        <v>I had a dream... - R3HAB</v>
+        <v>Back to You - Charlotte Sands</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Back to You</v>
+        <v>rager</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
+        <v>https://music.apple.com/us/song/rager/1872808801</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-08</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Satellite</v>
+        <v>rager</v>
       </c>
       <c r="G150" t="str">
-        <v>3:10</v>
+        <v>2:48</v>
       </c>
       <c r="H150" t="str">
-        <v>Charlotte Sands</v>
+        <v>Blusher</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
+        <v>https://music.apple.com/us/artist/blusher/485578161</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
+        <v>https://music.apple.com/us/album/rager/1872808800</v>
       </c>
       <c r="L150" t="str">
-        <v>Back to You - Charlotte Sands</v>
+        <v>rager - Blusher</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>rager</v>
+        <v>If Only</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/rager/1872808801</v>
+        <v>https://music.apple.com/us/song/if-only/1870281318</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-08</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>rager</v>
+        <v>Patchwork</v>
       </c>
       <c r="G151" t="str">
-        <v>2:48</v>
+        <v>3:28</v>
       </c>
       <c r="H151" t="str">
-        <v>Blusher</v>
+        <v>Charlotte Day Wilson</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/blusher/485578161</v>
+        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/rager/1872808800</v>
+        <v>https://music.apple.com/us/album/if-only/1870281314</v>
       </c>
       <c r="L151" t="str">
-        <v>rager - Blusher</v>
+        <v>If Only - Charlotte Day Wilson</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>If Only</v>
+        <v>DON'T LOVE ME</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/if-only/1870281318</v>
+        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-08</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Patchwork</v>
+        <v>DON'T LOVE ME - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H152" t="str">
-        <v>Charlotte Day Wilson</v>
+        <v>Omah Lay</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
+        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/if-only/1870281314</v>
+        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
       </c>
       <c r="L152" t="str">
-        <v>If Only - Charlotte Day Wilson</v>
+        <v>DON'T LOVE ME - Omah Lay</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>DON'T LOVE ME</v>
+        <v>No Sikes, No Tradesies</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
+        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-08</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>DON'T LOVE ME - Single</v>
+        <v>Sweet Nothings</v>
       </c>
       <c r="G153" t="str">
-        <v>3:01</v>
+        <v>2:32</v>
       </c>
       <c r="H153" t="str">
-        <v>Omah Lay</v>
+        <v>Jaymin</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
+        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
+        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
       </c>
       <c r="L153" t="str">
-        <v>DON'T LOVE ME - Omah Lay</v>
+        <v>No Sikes, No Tradesies - Jaymin</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No Sikes, No Tradesies</v>
+        <v>you woke me up</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
+        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-08</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Sweet Nothings</v>
+        <v>you woke me up - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:32</v>
+        <v>3:14</v>
       </c>
       <c r="H154" t="str">
-        <v>Jaymin</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
+        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
       </c>
       <c r="L154" t="str">
-        <v>No Sikes, No Tradesies - Jaymin</v>
+        <v>you woke me up - Kevian Kraemer</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>you woke me up</v>
+        <v>No One’s Business</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
+        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-08</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>you woke me up - Single</v>
+        <v>No One’s Business - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:14</v>
+        <v>3:00</v>
       </c>
       <c r="H155" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
+        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
       </c>
       <c r="L155" t="str">
-        <v>you woke me up - Kevian Kraemer</v>
+        <v>No One’s Business - Alicia Creti</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>No One’s Business</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
+        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-08</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>No One’s Business - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G156" t="str">
-        <v>3:00</v>
+        <v>3:13</v>
       </c>
       <c r="H156" t="str">
-        <v>Alicia Creti</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
+        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L156" t="str">
-        <v>No One’s Business - Alicia Creti</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
+        <v>TWICE</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
+        <v>https://music.apple.com/us/song/twice/1871578107</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-08</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G157" t="str">
-        <v>3:13</v>
+        <v>3:44</v>
       </c>
       <c r="H157" t="str">
-        <v>Bryant Barnes</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/twice/1871578103</v>
       </c>
       <c r="L157" t="str">
-        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
+        <v>TWICE - Bilmuri</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>TWICE</v>
+        <v>ROOFTOP</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/twice/1871578107</v>
+        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-08</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>KINDA HARD</v>
+        <v>ROOFTOP - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:44</v>
+        <v>3:22</v>
       </c>
       <c r="H158" t="str">
-        <v>Bilmuri</v>
+        <v>Hulvey</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/twice/1871578103</v>
+        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
       </c>
       <c r="L158" t="str">
-        <v>TWICE - Bilmuri</v>
+        <v>ROOFTOP - Hulvey</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>ROOFTOP</v>
+        <v>Louisiana Rain</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
+        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-08</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>ROOFTOP - Single</v>
+        <v>Louisiana Rain - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:22</v>
+        <v>3:41</v>
       </c>
       <c r="H159" t="str">
-        <v>Hulvey</v>
+        <v>Hunter Plake</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
+        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
       </c>
       <c r="L159" t="str">
-        <v>ROOFTOP - Hulvey</v>
+        <v>Louisiana Rain - Hunter Plake</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Louisiana Rain</v>
+        <v>sharing Jesus with an ex</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
+        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-08</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Louisiana Rain - Single</v>
+        <v>sharing Jesus with an ex - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:41</v>
+        <v>1:55</v>
       </c>
       <c r="H160" t="str">
-        <v>Hunter Plake</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
+        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
       </c>
       <c r="L160" t="str">
-        <v>Louisiana Rain - Hunter Plake</v>
+        <v>sharing Jesus with an ex - Zoe Levert</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>sharing Jesus with an ex</v>
+        <v>Body Control (feat. CHILLS)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
+        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-08</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>sharing Jesus with an ex - Single</v>
+        <v>Body Control (feat. CHILLS) - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>1:55</v>
+        <v>3:21</v>
       </c>
       <c r="H161" t="str">
-        <v>Zoe Levert</v>
+        <v>Cole Knight</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
+        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
       </c>
       <c r="L161" t="str">
-        <v>sharing Jesus with an ex - Zoe Levert</v>
+        <v>Body Control (feat. CHILLS) - Cole Knight</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Body Control (feat. CHILLS)</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
+        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-08</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Body Control (feat. CHILLS) - Single</v>
+        <v>A Prayer for the Dancefloor - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:21</v>
+        <v>6:54</v>
       </c>
       <c r="H162" t="str">
-        <v>Cole Knight</v>
+        <v>Charlotte de Witte</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
+        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
+        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
       </c>
       <c r="L162" t="str">
-        <v>Body Control (feat. CHILLS) - Cole Knight</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
+        <v>Realm of Endless Misery</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
+        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-08</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>A Prayer for the Dancefloor - Single</v>
+        <v>Liturgy of Death</v>
       </c>
       <c r="G163" t="str">
-        <v>6:54</v>
+        <v>4:56</v>
       </c>
       <c r="H163" t="str">
-        <v>Charlotte de Witte</v>
+        <v>Mayhem</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
+        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
+        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
       </c>
       <c r="L163" t="str">
-        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
+        <v>Realm of Endless Misery - Mayhem</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Realm of Endless Misery</v>
+        <v>BLEACH</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
+        <v>https://music.apple.com/us/song/bleach/1869795882</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-08</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Liturgy of Death</v>
+        <v>BLEACH - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>4:56</v>
+        <v>2:28</v>
       </c>
       <c r="H164" t="str">
-        <v>Mayhem</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
+        <v>https://music.apple.com/us/album/bleach/1869795874</v>
       </c>
       <c r="L164" t="str">
-        <v>Realm of Endless Misery - Mayhem</v>
+        <v>BLEACH - Ecca Vandal</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>BLEACH</v>
+        <v>pretty in pink</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/bleach/1869795882</v>
+        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-08</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>BLEACH - Single</v>
+        <v>AngelPink</v>
       </c>
       <c r="G165" t="str">
-        <v>2:28</v>
+        <v>3:13</v>
       </c>
       <c r="H165" t="str">
-        <v>Ecca Vandal</v>
+        <v>Keni Titus</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/bleach/1869795874</v>
+        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
       </c>
       <c r="L165" t="str">
-        <v>BLEACH - Ecca Vandal</v>
+        <v>pretty in pink - Keni Titus</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>pretty in pink</v>
+        <v>Pickup Man</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
+        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-08</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>AngelPink</v>
+        <v>Pickup Man - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:13</v>
+        <v>3:28</v>
       </c>
       <c r="H166" t="str">
-        <v>Keni Titus</v>
+        <v>Bayker Blankenship</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
+        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
+        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
       </c>
       <c r="L166" t="str">
-        <v>pretty in pink - Keni Titus</v>
+        <v>Pickup Man - Bayker Blankenship</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Pickup Man</v>
+        <v>Get To Drinkin'</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
+        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-08</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Pickup Man - Single</v>
+        <v>Get To Drinkin' - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:28</v>
+        <v>2:48</v>
       </c>
       <c r="H167" t="str">
-        <v>Bayker Blankenship</v>
+        <v>Zach John King</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
+        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
+        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
       </c>
       <c r="L167" t="str">
-        <v>Pickup Man - Bayker Blankenship</v>
+        <v>Get To Drinkin' - Zach John King</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Get To Drinkin'</v>
+        <v>The Roses</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
+        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-08</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Get To Drinkin' - Single</v>
+        <v>The Roses - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:48</v>
+        <v>3:02</v>
       </c>
       <c r="H168" t="str">
-        <v>Zach John King</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
+        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
+        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
       </c>
       <c r="L168" t="str">
-        <v>Get To Drinkin' - Zach John King</v>
+        <v>The Roses - Russell Dickerson</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>The Roses</v>
+        <v>I Should Know Better</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
+        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-08</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>The Roses - Single</v>
+        <v>Under The Streetlights</v>
       </c>
       <c r="G169" t="str">
-        <v>3:02</v>
+        <v>3:33</v>
       </c>
       <c r="H169" t="str">
-        <v>Russell Dickerson</v>
+        <v>Michael Marcagi</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
+        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
+        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
       </c>
       <c r="L169" t="str">
-        <v>The Roses - Russell Dickerson</v>
+        <v>I Should Know Better - Michael Marcagi</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>I Should Know Better</v>
+        <v>Never Do</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
+        <v>https://music.apple.com/us/song/never-do/1872842226</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-08</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Under The Streetlights</v>
+        <v>Never Do - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:33</v>
+        <v>1:58</v>
       </c>
       <c r="H170" t="str">
-        <v>Michael Marcagi</v>
+        <v>charlieonnafriday</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
+        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
+        <v>https://music.apple.com/us/album/never-do/1872842225</v>
       </c>
       <c r="L170" t="str">
-        <v>I Should Know Better - Michael Marcagi</v>
+        <v>Never Do - charlieonnafriday</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Never Do</v>
+        <v>Primary Colors</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/never-do/1872842226</v>
+        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-08</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Never Do - Single</v>
+        <v>Lost on You</v>
       </c>
       <c r="G171" t="str">
-        <v>1:58</v>
+        <v>3:37</v>
       </c>
       <c r="H171" t="str">
-        <v>charlieonnafriday</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/never-do/1872842225</v>
+        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
       </c>
       <c r="L171" t="str">
-        <v>Never Do - charlieonnafriday</v>
+        <v>Primary Colors - Tigers Jaw</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Primary Colors</v>
+        <v>Rock Bottom</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-08</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Lost on You</v>
+        <v>Rock Bottom / Octopus - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:37</v>
+        <v>4:10</v>
       </c>
       <c r="H172" t="str">
-        <v>Tigers Jaw</v>
+        <v>King Krule</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
+        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
       </c>
       <c r="L172" t="str">
-        <v>Primary Colors - Tigers Jaw</v>
+        <v>Rock Bottom - King Krule</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Rock Bottom</v>
+        <v>Te Dedico</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
+        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-08</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Rock Bottom / Octopus - Single</v>
+        <v>Te Dedico - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>4:10</v>
+        <v>3:45</v>
       </c>
       <c r="H173" t="str">
-        <v>King Krule</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
+        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
+        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
       </c>
       <c r="L173" t="str">
-        <v>Rock Bottom - King Krule</v>
+        <v>Te Dedico - Carlos Vives</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Te Dedico</v>
+        <v>AUNQUE SEA EN DOS</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
+        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-08</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Te Dedico - Single</v>
+        <v>18</v>
       </c>
       <c r="G174" t="str">
-        <v>3:45</v>
+        <v>2:38</v>
       </c>
       <c r="H174" t="str">
-        <v>Carlos Vives</v>
+        <v>Conexión Divina</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
+        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
+        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
       </c>
       <c r="L174" t="str">
-        <v>Te Dedico - Carlos Vives</v>
+        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>AUNQUE SEA EN DOS</v>
+        <v>I Dare You</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
+        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-08</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>18</v>
+        <v>I Dare You - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:38</v>
+        <v>3:25</v>
       </c>
       <c r="H175" t="str">
-        <v>Conexión Divina</v>
+        <v>Dylan Dunlap</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
+        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
+        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
       </c>
       <c r="L175" t="str">
-        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
+        <v>I Dare You - Dylan Dunlap</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>I Dare You</v>
+        <v>new irish boyfriend</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
+        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-08</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>I Dare You - Single</v>
+        <v>long time caller, first time listener</v>
       </c>
       <c r="G176" t="str">
-        <v>3:25</v>
+        <v>3:50</v>
       </c>
       <c r="H176" t="str">
-        <v>Dylan Dunlap</v>
+        <v>vegas water taxi</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
+        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
+        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
       </c>
       <c r="L176" t="str">
-        <v>I Dare You - Dylan Dunlap</v>
+        <v>new irish boyfriend - vegas water taxi</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>new irish boyfriend</v>
+        <v>Everyone Around Me Dancing</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
+        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-08</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>long time caller, first time listener</v>
+        <v>Singing</v>
       </c>
       <c r="G177" t="str">
-        <v>3:50</v>
+        <v>3:05</v>
       </c>
       <c r="H177" t="str">
-        <v>vegas water taxi</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
+        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
       </c>
       <c r="L177" t="str">
-        <v>new irish boyfriend - vegas water taxi</v>
+        <v>Everyone Around Me Dancing - Gia Margaret</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Everyone Around Me Dancing</v>
+        <v>Good Enough (feat. Julie Doiron)</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
+        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-08</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Singing</v>
+        <v>Big Changes</v>
       </c>
       <c r="G178" t="str">
-        <v>3:05</v>
+        <v>6:05</v>
       </c>
       <c r="H178" t="str">
-        <v>Gia Margaret</v>
+        <v>Status/Non-Status</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
+        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
       </c>
       <c r="L178" t="str">
-        <v>Everyone Around Me Dancing - Gia Margaret</v>
+        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Good Enough (feat. Julie Doiron)</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
+        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-08</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Big Changes</v>
+        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="G179" t="str">
-        <v>6:05</v>
+        <v>4:09</v>
       </c>
       <c r="H179" t="str">
-        <v>Status/Non-Status</v>
+        <v>Julian Lage</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
+        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
+        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
       </c>
       <c r="L179" t="str">
-        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
+        <v>Big Deal</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
+        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-08</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
+        <v>Big Deal - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>4:09</v>
+        <v>3:47</v>
       </c>
       <c r="H180" t="str">
-        <v>Julian Lage</v>
+        <v>In Color</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
+        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
       </c>
       <c r="L180" t="str">
-        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
+        <v>Big Deal - In Color</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Big Deal</v>
+        <v>Buy What U Want</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
+        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-08</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Big Deal - Single</v>
+        <v>Road To Osshland III - EP</v>
       </c>
       <c r="G181" t="str">
         <v>3:47</v>
       </c>
       <c r="H181" t="str">
-        <v>In Color</v>
+        <v>Black Fortune</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
+        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
       </c>
       <c r="L181" t="str">
-        <v>Big Deal - In Color</v>
+        <v>Buy What U Want - Black Fortune</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Buy What U Want</v>
+        <v>Common Ground</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
+        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-08</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Road To Osshland III - EP</v>
+        <v>Common Ground - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:47</v>
+        <v>1:42</v>
       </c>
       <c r="H182" t="str">
-        <v>Black Fortune</v>
+        <v>ELIO</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
+        <v>https://music.apple.com/us/artist/elio/1501417625</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
+        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
       </c>
       <c r="L182" t="str">
-        <v>Buy What U Want - Black Fortune</v>
+        <v>Common Ground - ELIO</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Common Ground</v>
+        <v>Cellophane</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
+        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-08</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Common Ground - Single</v>
+        <v>Cellophane - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>1:42</v>
+        <v>4:21</v>
       </c>
       <c r="H183" t="str">
-        <v>ELIO</v>
+        <v>Maddie Zahm</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/elio/1501417625</v>
+        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
+        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
       </c>
       <c r="L183" t="str">
-        <v>Common Ground - ELIO</v>
+        <v>Cellophane - Maddie Zahm</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Cellophane</v>
+        <v>96 Camry</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
+        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-08</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Cellophane - Single</v>
+        <v>PRAY FOR ME</v>
       </c>
       <c r="G184" t="str">
-        <v>4:21</v>
+        <v>3:15</v>
       </c>
       <c r="H184" t="str">
-        <v>Maddie Zahm</v>
+        <v>RAAHiiM</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
+        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
+        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
       </c>
       <c r="L184" t="str">
-        <v>Cellophane - Maddie Zahm</v>
+        <v>96 Camry - RAAHiiM</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>96 Camry</v>
+        <v>La Allstar</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
+        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-08</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>PRAY FOR ME</v>
+        <v>La Allstar - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:15</v>
+        <v>2:49</v>
       </c>
       <c r="H185" t="str">
-        <v>RAAHiiM</v>
+        <v>ELIKAI</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
+        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
+        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
       </c>
       <c r="L185" t="str">
-        <v>96 Camry - RAAHiiM</v>
+        <v>La Allstar - ELIKAI</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>La Allstar</v>
+        <v>Luka</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
+        <v>https://music.apple.com/us/song/luka/1869396162</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-08</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>La Allstar - Single</v>
+        <v>Luka - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:49</v>
+        <v>2:07</v>
       </c>
       <c r="H186" t="str">
-        <v>ELIKAI</v>
+        <v>Fonta</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
+        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
+        <v>https://music.apple.com/us/album/luka/1869396161</v>
       </c>
       <c r="L186" t="str">
-        <v>La Allstar - ELIKAI</v>
+        <v>Luka - Fonta</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Luka</v>
+        <v>Ganas De Tenerla</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/luka/1869396162</v>
+        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-08</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Luka - Single</v>
+        <v>Ganas De Tenerla - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:07</v>
+        <v>3:06</v>
       </c>
       <c r="H187" t="str">
-        <v>Fonta</v>
+        <v>Silvestre Dangond</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
+        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/luka/1869396161</v>
+        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
       </c>
       <c r="L187" t="str">
-        <v>Luka - Fonta</v>
+        <v>Ganas De Tenerla - Silvestre Dangond</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Ganas De Tenerla</v>
+        <v>In My Blue</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
+        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-08</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Ganas De Tenerla - Single</v>
+        <v>Doomsday...Don't Leave Me Here</v>
       </c>
       <c r="G188" t="str">
-        <v>3:06</v>
+        <v>3:26</v>
       </c>
       <c r="H188" t="str">
-        <v>Silvestre Dangond</v>
+        <v>Rosie Carney</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
+        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
+        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
       </c>
       <c r="L188" t="str">
-        <v>Ganas De Tenerla - Silvestre Dangond</v>
+        <v>In My Blue - Rosie Carney</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>In My Blue</v>
+        <v>Living With It (feat. Feist)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
+        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-08</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Doomsday...Don't Leave Me Here</v>
+        <v>Hurts Like Hell</v>
       </c>
       <c r="G189" t="str">
-        <v>3:26</v>
+        <v>3:20</v>
       </c>
       <c r="H189" t="str">
-        <v>Rosie Carney</v>
+        <v>Charlotte Cornfield</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
+        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
+        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
       </c>
       <c r="L189" t="str">
-        <v>In My Blue - Rosie Carney</v>
+        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Living With It (feat. Feist)</v>
+        <v>Silently</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
+        <v>https://music.apple.com/us/song/silently/1841629898</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-08</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Hurts Like Hell</v>
+        <v>Croak Dream</v>
       </c>
       <c r="G190" t="str">
-        <v>3:20</v>
+        <v>3:29</v>
       </c>
       <c r="H190" t="str">
-        <v>Charlotte Cornfield</v>
+        <v>Puma Blue</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
+        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
+        <v>https://music.apple.com/us/album/silently/1841629444</v>
       </c>
       <c r="L190" t="str">
-        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
+        <v>Silently - Puma Blue</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Silently</v>
+        <v>Ashes &amp; Smoke</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/silently/1841629898</v>
+        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-08</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Croak Dream</v>
+        <v>Ashes &amp; Smoke - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:29</v>
+        <v>3:05</v>
       </c>
       <c r="H191" t="str">
-        <v>Puma Blue</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
+        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/silently/1841629444</v>
+        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
       </c>
       <c r="L191" t="str">
-        <v>Silently - Puma Blue</v>
+        <v>Ashes &amp; Smoke - Anna Graves</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Ashes &amp; Smoke</v>
+        <v>Tormentor</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
+        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-08</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Ashes &amp; Smoke - Single</v>
+        <v>The Flowers I See You In - EP</v>
       </c>
       <c r="G192" t="str">
-        <v>3:05</v>
+        <v>2:40</v>
       </c>
       <c r="H192" t="str">
-        <v>Anna Graves</v>
+        <v>Ninush</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
+        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
+        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
       </c>
       <c r="L192" t="str">
-        <v>Ashes &amp; Smoke - Anna Graves</v>
+        <v>Tormentor - Ninush</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Tormentor</v>
+        <v>Red Rocking Chair</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
+        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-08</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>The Flowers I See You In - EP</v>
+        <v>Red Rocking Chair - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:40</v>
+        <v>6:28</v>
       </c>
       <c r="H193" t="str">
-        <v>Ninush</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
+        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
       </c>
       <c r="L193" t="str">
-        <v>Tormentor - Ninush</v>
+        <v>Red Rocking Chair - All Them Witches</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Red Rocking Chair</v>
+        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
+        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-08</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Red Rocking Chair - Single</v>
+        <v>...of Death and Fire</v>
       </c>
       <c r="G194" t="str">
-        <v>6:28</v>
+        <v>7:07</v>
       </c>
       <c r="H194" t="str">
-        <v>All Them Witches</v>
+        <v>In Aeternum</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
+        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
       </c>
       <c r="L194" t="str">
-        <v>Red Rocking Chair - All Them Witches</v>
+        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
+        <v>Mizantrop</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
+        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-08</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>...of Death and Fire</v>
+        <v>Mizantrop</v>
       </c>
       <c r="G195" t="str">
-        <v>7:07</v>
+        <v>3:42</v>
       </c>
       <c r="H195" t="str">
-        <v>In Aeternum</v>
+        <v>She Past Away</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
+        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
+        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
       </c>
       <c r="L195" t="str">
-        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
+        <v>Mizantrop - She Past Away</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Mizantrop</v>
+        <v>In the Name of the Moth</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
+        <v>https://music.apple.com/us/song/in-the-name-of-the-moth/1866911203</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-08</v>
@@ -7823,68 +7823,30 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Mizantrop</v>
+        <v>Hidden Fires Burn Hottest</v>
       </c>
       <c r="G196" t="str">
-        <v>3:42</v>
+        <v>7:15</v>
       </c>
       <c r="H196" t="str">
-        <v>She Past Away</v>
+        <v>Bosse-de-Nage</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
+        <v>https://music.apple.com/us/artist/bosse-de-nage/465123183</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
+        <v>https://music.apple.com/us/album/in-the-name-of-the-moth/1866911198</v>
       </c>
       <c r="L196" t="str">
-        <v>Mizantrop - She Past Away</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>In the Name of the Moth</v>
-      </c>
-      <c r="B197" t="str">
-        <v/>
-      </c>
-      <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/in-the-name-of-the-moth/1866911203</v>
-      </c>
-      <c r="D197" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" t="str">
-        <v>Hidden Fires Burn Hottest</v>
-      </c>
-      <c r="G197" t="str">
-        <v>7:15</v>
-      </c>
-      <c r="H197" t="str">
-        <v>Bosse-de-Nage</v>
-      </c>
-      <c r="I197" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/bosse-de-nage/465123183</v>
-      </c>
-      <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/in-the-name-of-the-moth/1866911198</v>
-      </c>
-      <c r="L197" t="str">
         <v>In the Name of the Moth - Bosse-de-Nage</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B2" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>
@@ -477,7 +477,7 @@
         <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:26</v>
@@ -705,7 +705,7 @@
         <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>7:03</v>
@@ -1541,7 +1541,7 @@
         <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>3:40</v>
@@ -1807,7 +1807,7 @@
         <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>3:41</v>
@@ -2377,7 +2377,7 @@
         <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>2:44</v>
@@ -2415,7 +2415,7 @@
         <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>2:57</v>
@@ -3593,7 +3593,7 @@
         <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
         <v>3:50</v>
@@ -3631,7 +3631,7 @@
         <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B86" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>5:32</v>

--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>
@@ -477,7 +477,7 @@
         <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:26</v>
@@ -667,7 +667,7 @@
         <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>4:41</v>
@@ -2149,7 +2149,7 @@
         <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:37</v>
@@ -2339,7 +2339,7 @@
         <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:10</v>

--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:27</v>
@@ -629,7 +629,7 @@
         <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>4:13</v>
@@ -2263,7 +2263,7 @@
         <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:38</v>
@@ -3403,7 +3403,7 @@
         <v>Beck - Love (Audio)</v>
       </c>
       <c r="B80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>3:14</v>
@@ -3555,7 +3555,7 @@
         <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B84" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
         <v>3:52</v>

--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-08</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>4:27</v>
+        <v>6:00</v>
       </c>
       <c r="H2" t="str">
-        <v>Mariah Carey</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-08</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:26</v>
+        <v>4:20</v>
       </c>
       <c r="H3" t="str">
-        <v>Netflix</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-08</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:29</v>
+        <v>4:27</v>
       </c>
       <c r="H4" t="str">
-        <v>Michael Bolton</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-08</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:59</v>
+        <v>3:26</v>
       </c>
       <c r="H5" t="str">
-        <v>mgk</v>
+        <v>Netflix</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-08</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:51</v>
+        <v>3:29</v>
       </c>
       <c r="H6" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-08</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:13</v>
+        <v>2:59</v>
       </c>
       <c r="H7" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B8" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-08</v>
@@ -682,10 +682,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>4:41</v>
+        <v>2:51</v>
       </c>
       <c r="H8" t="str">
-        <v>NICK JONAS</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-08</v>
@@ -720,10 +720,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>7:03</v>
+        <v>4:13</v>
       </c>
       <c r="H9" t="str">
-        <v>Take That</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-08</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:37</v>
+        <v>4:41</v>
       </c>
       <c r="H10" t="str">
-        <v>Cliff Richard</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-08</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:54</v>
+        <v>7:03</v>
       </c>
       <c r="H11" t="str">
-        <v>Bryan Adams</v>
+        <v>Take That</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-08</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:06</v>
+        <v>4:37</v>
       </c>
       <c r="H12" t="str">
-        <v>Anna Graves</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-08</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:21</v>
+        <v>3:54</v>
       </c>
       <c r="H13" t="str">
-        <v>George Birge</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-08</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:09</v>
+        <v>3:06</v>
       </c>
       <c r="H14" t="str">
-        <v>Warner Records</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-08</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:18</v>
+        <v>3:21</v>
       </c>
       <c r="H15" t="str">
-        <v>NICK JONAS</v>
+        <v>George Birge</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
+        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-08</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:08</v>
+        <v>4:09</v>
       </c>
       <c r="H16" t="str">
-        <v>Charlie Puth</v>
+        <v>Warner Records</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
+        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-08</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:03</v>
+        <v>4:18</v>
       </c>
       <c r="H17" t="str">
-        <v>Olivia Newton-John</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
+        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-08</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:01</v>
+        <v>3:08</v>
       </c>
       <c r="H18" t="str">
-        <v>The Warning and Carin Leon</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
+        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-08</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:05</v>
+        <v>4:03</v>
       </c>
       <c r="H19" t="str">
-        <v>Iman Fandi</v>
+        <v>Olivia Newton-John</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
+        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-08</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:34</v>
+        <v>3:01</v>
       </c>
       <c r="H20" t="str">
-        <v>Megan Moroney</v>
+        <v>The Warning and Carin Leon</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Dylan Davidson - Escape Artist</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
+        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-08</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:15</v>
+        <v>3:05</v>
       </c>
       <c r="H21" t="str">
-        <v>Dylan Davidson</v>
+        <v>Iman Fandi</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
+        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-08</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:16</v>
+        <v>3:34</v>
       </c>
       <c r="H22" t="str">
-        <v>Lady Gaga</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video)</v>
+        <v>Dylan Davidson - Escape Artist</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
+        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-08</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:53</v>
+        <v>3:15</v>
       </c>
       <c r="H23" t="str">
-        <v>Carlos Vives</v>
+        <v>Dylan Davidson</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
+        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
+        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-08</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:25</v>
+        <v>4:16</v>
       </c>
       <c r="H24" t="str">
-        <v>Monsieur Periné</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio)</v>
+        <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
+        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-08</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>4:09</v>
+        <v>3:53</v>
       </c>
       <c r="H25" t="str">
-        <v>The Happy Fits</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
+        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>chase (lyric vid) - Michael Aldag</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
+        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-08</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:45</v>
+        <v>2:25</v>
       </c>
       <c r="H26" t="str">
-        <v>Michael Aldag</v>
+        <v>Monsieur Periné</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
+        <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
+        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-08</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:07</v>
+        <v>4:09</v>
       </c>
       <c r="H27" t="str">
-        <v>Dermot Kennedy</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
+        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
+        <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
+        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-08</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:34</v>
+        <v>2:45</v>
       </c>
       <c r="H28" t="str">
-        <v>Marc Anthony</v>
+        <v>Michael Aldag</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
+        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
+        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-08</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>5:14</v>
+        <v>4:07</v>
       </c>
       <c r="H29" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
+        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-08</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:11</v>
+        <v>4:34</v>
       </c>
       <c r="H30" t="str">
-        <v>Michael Bolton</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lachie Gill - Last Drive</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
+        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-08</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:40</v>
+        <v>5:14</v>
       </c>
       <c r="H31" t="str">
-        <v>Lachie Gill</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Lachie Gill - Last Drive - Lachie Gill</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
+        <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
+        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-08</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:45</v>
+        <v>3:11</v>
       </c>
       <c r="H32" t="str">
-        <v>Eli &amp; Fur</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
+        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Freya Skye - why'd you have to call</v>
+        <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
+        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-08</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:19</v>
+        <v>3:40</v>
       </c>
       <c r="H33" t="str">
-        <v>Freya Skye</v>
+        <v>Lachie Gill</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Freya Skye - why'd you have to call - Freya Skye</v>
+        <v>Lachie Gill - Last Drive - Lachie Gill</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
+        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-08</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:30</v>
+        <v>3:45</v>
       </c>
       <c r="H34" t="str">
-        <v>Jessie J</v>
+        <v>Eli &amp; Fur</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer)</v>
+        <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
+        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-08</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:24</v>
+        <v>4:19</v>
       </c>
       <c r="H35" t="str">
-        <v>Marc Anthony</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
+        <v>Freya Skye - why'd you have to call - Freya Skye</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
+        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-08</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:33</v>
+        <v>2:30</v>
       </c>
       <c r="H36" t="str">
-        <v>Clara Mae</v>
+        <v>Jessie J</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Metric - Victim of Luck (Official Music Video)</v>
+        <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B37" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
+        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-08</v>
@@ -1784,10 +1784,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:25</v>
+        <v>4:24</v>
       </c>
       <c r="H37" t="str">
-        <v>metricmusic</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
+        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
+        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-08</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:41</v>
+        <v>2:33</v>
       </c>
       <c r="H38" t="str">
-        <v>kesha</v>
+        <v>Clara Mae</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
+        <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
+        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-08</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:19</v>
+        <v>3:25</v>
       </c>
       <c r="H39" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>metricmusic</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
+        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B40" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
+        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-08</v>
@@ -1898,10 +1898,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:37</v>
+        <v>3:41</v>
       </c>
       <c r="H40" t="str">
-        <v>Vera Blue</v>
+        <v>kesha</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B41" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
+        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-08</v>
@@ -1936,10 +1936,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:08</v>
+        <v>3:19</v>
       </c>
       <c r="H41" t="str">
-        <v>Bob Moses</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B42" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
+        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-08</v>
@@ -1974,10 +1974,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:28</v>
+        <v>3:37</v>
       </c>
       <c r="H42" t="str">
-        <v>Marc Anthony</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B43" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
+        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-08</v>
@@ -2012,10 +2012,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>5:05</v>
+        <v>3:08</v>
       </c>
       <c r="H43" t="str">
-        <v>Marc Anthony</v>
+        <v>Bob Moses</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Loreen - Feels Like Heaven</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B44" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
+        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-08</v>
@@ -2050,10 +2050,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:14</v>
+        <v>3:28</v>
       </c>
       <c r="H44" t="str">
-        <v>Loreen</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Loreen - Feels Like Heaven - Loreen</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B45" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
+        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-08</v>
@@ -2088,10 +2088,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:36</v>
+        <v>5:05</v>
       </c>
       <c r="H45" t="str">
-        <v>Take That</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
+        <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B46" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
+        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-08</v>
@@ -2126,10 +2126,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>5:31</v>
+        <v>3:14</v>
       </c>
       <c r="H46" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Loreen</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
+        <v>Loreen - Feels Like Heaven - Loreen</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio)</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B47" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
+        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-08</v>
@@ -2164,10 +2164,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:37</v>
+        <v>3:36</v>
       </c>
       <c r="H47" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Take That</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-08</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:58</v>
+        <v>5:31</v>
       </c>
       <c r="H48" t="str">
-        <v>The Warning</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
+        <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-08</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>5:08</v>
+        <v>3:37</v>
       </c>
       <c r="H49" t="str">
-        <v>The Offspring</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
+        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-08</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:38</v>
+        <v>4:58</v>
       </c>
       <c r="H50" t="str">
-        <v>Roxette</v>
+        <v>The Warning</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-08</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:50</v>
+        <v>5:08</v>
       </c>
       <c r="H51" t="str">
-        <v>Jessie Ware</v>
+        <v>The Offspring</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-08</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:10</v>
+        <v>4:38</v>
       </c>
       <c r="H52" t="str">
-        <v>Joseph</v>
+        <v>Roxette</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-08</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:44</v>
+        <v>3:50</v>
       </c>
       <c r="H53" t="str">
-        <v>Dean Lewis</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-08</v>
@@ -2430,10 +2430,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:57</v>
+        <v>3:10</v>
       </c>
       <c r="H54" t="str">
-        <v>Take That</v>
+        <v>Joseph</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-08</v>
@@ -2468,10 +2468,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:07</v>
+        <v>2:44</v>
       </c>
       <c r="H55" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B56" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-08</v>
@@ -2506,10 +2506,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:47</v>
+        <v>2:57</v>
       </c>
       <c r="H56" t="str">
-        <v>Paris Paloma</v>
+        <v>Take That</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-08</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:22</v>
+        <v>3:07</v>
       </c>
       <c r="H57" t="str">
-        <v>Zara Larsson</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-08</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:48</v>
+        <v>4:47</v>
       </c>
       <c r="H58" t="str">
-        <v>only the poets</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B59" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-08</v>
@@ -2620,10 +2620,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:52</v>
+        <v>3:22</v>
       </c>
       <c r="H59" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-08</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:33</v>
+        <v>2:48</v>
       </c>
       <c r="H60" t="str">
-        <v>David Guetta</v>
+        <v>only the poets</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-08</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:41</v>
+        <v>2:52</v>
       </c>
       <c r="H61" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-08</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:01</v>
+        <v>3:33</v>
       </c>
       <c r="H62" t="str">
-        <v>Ella Langley</v>
+        <v>David Guetta</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-08</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:16</v>
+        <v>2:41</v>
       </c>
       <c r="H63" t="str">
-        <v>Dogpark</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-08</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:03</v>
+        <v>4:01</v>
       </c>
       <c r="H64" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-08</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:41</v>
+        <v>3:16</v>
       </c>
       <c r="H65" t="str">
-        <v>ERNEST</v>
+        <v>Dogpark</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-08</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:05</v>
+        <v>3:03</v>
       </c>
       <c r="H66" t="str">
-        <v>Labrinth</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-08</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:46</v>
+        <v>2:41</v>
       </c>
       <c r="H67" t="str">
-        <v>Grace VanderWaal</v>
+        <v>ERNEST</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-08</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:32</v>
+        <v>3:05</v>
       </c>
       <c r="H68" t="str">
-        <v>VOILÀ</v>
+        <v>Labrinth</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-08</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:42</v>
+        <v>2:46</v>
       </c>
       <c r="H69" t="str">
-        <v>Cannons</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-08</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:38</v>
+        <v>3:32</v>
       </c>
       <c r="H70" t="str">
-        <v>Kylie Morgan</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-08</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:10</v>
+        <v>3:42</v>
       </c>
       <c r="H71" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Cannons</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-08</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:57</v>
+        <v>2:38</v>
       </c>
       <c r="H72" t="str">
-        <v>Willie Nelson</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-08</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:19</v>
+        <v>3:10</v>
       </c>
       <c r="H73" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-08</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:04</v>
+        <v>3:57</v>
       </c>
       <c r="H74" t="str">
-        <v>India Martínez</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-08</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:16</v>
+        <v>2:19</v>
       </c>
       <c r="H75" t="str">
-        <v>Chelsea Cutler</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-08</v>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>5:58</v>
+        <v>4:04</v>
       </c>
       <c r="H76" t="str">
-        <v>TINI</v>
+        <v>India Martínez</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-08</v>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:26</v>
+        <v>2:16</v>
       </c>
       <c r="H77" t="str">
-        <v>Charley</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-08</v>
@@ -3342,10 +3342,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:05</v>
+        <v>5:58</v>
       </c>
       <c r="H78" t="str">
-        <v>Demi Lovato</v>
+        <v>TINI</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B79" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-08</v>
@@ -3380,10 +3380,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:16</v>
+        <v>3:26</v>
       </c>
       <c r="H79" t="str">
-        <v>Teddy Swims</v>
+        <v>Charley</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B80" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-08</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:14</v>
+        <v>4:05</v>
       </c>
       <c r="H80" t="str">
-        <v>Beck</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B81" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-08</v>
@@ -3456,10 +3456,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:57</v>
+        <v>3:16</v>
       </c>
       <c r="H81" t="str">
-        <v>The Offspring</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-08</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>4:10</v>
+        <v>3:14</v>
       </c>
       <c r="H82" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Beck</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-08</v>
@@ -3532,10 +3532,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:10</v>
+        <v>2:57</v>
       </c>
       <c r="H83" t="str">
-        <v>Jason Derulo</v>
+        <v>The Offspring</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B84" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-08</v>
@@ -3570,10 +3570,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:52</v>
+        <v>4:10</v>
       </c>
       <c r="H84" t="str">
-        <v>lights</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B85" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-08</v>
@@ -3608,10 +3608,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:50</v>
+        <v>2:10</v>
       </c>
       <c r="H85" t="str">
-        <v>Telenova</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B86" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-08</v>
@@ -3646,10 +3646,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>5:32</v>
+        <v>3:52</v>
       </c>
       <c r="H86" t="str">
-        <v>Marcin</v>
+        <v>lights</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B87" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-08</v>
@@ -3684,10 +3684,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:27</v>
+        <v>3:50</v>
       </c>
       <c r="H87" t="str">
-        <v>We Three</v>
+        <v>Telenova</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B88" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-08</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:01</v>
+        <v>5:32</v>
       </c>
       <c r="H88" t="str">
-        <v>Timebelle Official</v>
+        <v>Marcin</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-08</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:20</v>
+        <v>4:27</v>
       </c>
       <c r="H89" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>We Three</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-08</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:34</v>
+        <v>3:01</v>
       </c>
       <c r="H90" t="str">
-        <v>Clinton Kane</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-08</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:01</v>
+        <v>3:20</v>
       </c>
       <c r="H91" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-08</v>
@@ -3874,10 +3874,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:24</v>
+        <v>3:34</v>
       </c>
       <c r="H92" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-08</v>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>5:52</v>
+        <v>4:01</v>
       </c>
       <c r="H93" t="str">
-        <v>Harry Styles</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-08</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>5:01</v>
+        <v>3:24</v>
       </c>
       <c r="H94" t="str">
-        <v>Neal Francis</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-08</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:12</v>
+        <v>5:52</v>
       </c>
       <c r="H95" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-08</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:59</v>
+        <v>5:01</v>
       </c>
       <c r="H96" t="str">
-        <v>Holly Humberstone</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-08</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:56</v>
+        <v>4:12</v>
       </c>
       <c r="H97" t="str">
-        <v>Cliff Richard</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-08</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:46</v>
+        <v>3:59</v>
       </c>
       <c r="H98" t="str">
-        <v>Jessie Ware</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-08</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:37</v>
+        <v>2:56</v>
       </c>
       <c r="H99" t="str">
-        <v>Bella White</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=pnAz9RwGSek</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-08</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:06</v>
+        <v>3:46</v>
       </c>
       <c r="H100" t="str">
-        <v>Ryan Wright</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Ryan Wright - Film School Kids (Official Video) - Ryan Wright</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=u7aPv2saz_I</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-08</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:54</v>
+        <v>4:37</v>
       </c>
       <c r="H101" t="str">
-        <v>Dove Cameron</v>
+        <v>Bella White</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Dove Cameron - Do I Wanna Know? (Official Visualizer) - Dove Cameron</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="102">

--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>ליעד מאיר - חברים שלי</v>
       </c>
       <c r="B2" t="str">
-        <v>3 hours ago</v>
+        <v>2026-02-08</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409539&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-08</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 hours ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>6:00</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Taylor Swift</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>ליעד מאיר - חברים שלי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>ליאור עמדי - חן הבה</v>
       </c>
       <c r="B3" t="str">
-        <v>4 hours ago</v>
+        <v>2026-02-08</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409538&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-08</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 hours ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>4:20</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>Michael Bolton</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>ליאור עמדי - חן הבה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>יגל יובל שרעבי - אלופו של עולם</v>
       </c>
       <c r="B4" t="str">
-        <v>20 hours ago</v>
+        <v>2026-02-08</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409537&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-08</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>20 hours ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>4:27</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Mariah Carey</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>יגל יובל שרעבי - אלופו של עולם</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>טלי רבקה סימן טוב - אני עץ, אני אילן</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-08</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409536&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-08</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>3:26</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Netflix</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>טלי רבקה סימן טוב - אני עץ, אני אילן</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>חיים ישראל - מחרוזת השירים של זוהר 2026</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-08</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409535&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-08</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>3:29</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>Michael Bolton</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>חיים ישראל - מחרוזת השירים של זוהר 2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>האחים דוליס - הלילה עבר</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-08</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409534&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-08</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>2:59</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>mgk</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>האחים דוליס - הלילה עבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-08</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:51</v>
+        <v>6:00</v>
       </c>
       <c r="H8" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-08</v>
@@ -717,10 +717,10 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G9" t="str">
-        <v>4:13</v>
+        <v>4:20</v>
       </c>
       <c r="H9" t="str">
         <v>Michael Bolton</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-08</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:41</v>
+        <v>4:27</v>
       </c>
       <c r="H10" t="str">
-        <v>NICK JONAS</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-08</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>7:03</v>
+        <v>3:26</v>
       </c>
       <c r="H11" t="str">
-        <v>Take That</v>
+        <v>Netflix</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-08</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:37</v>
+        <v>3:29</v>
       </c>
       <c r="H12" t="str">
-        <v>Cliff Richard</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-08</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:54</v>
+        <v>2:59</v>
       </c>
       <c r="H13" t="str">
-        <v>Bryan Adams</v>
+        <v>mgk</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-08</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:06</v>
+        <v>2:51</v>
       </c>
       <c r="H14" t="str">
-        <v>Anna Graves</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-08</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:21</v>
+        <v>4:13</v>
       </c>
       <c r="H15" t="str">
-        <v>George Birge</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-08</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:09</v>
+        <v>4:41</v>
       </c>
       <c r="H16" t="str">
-        <v>Warner Records</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-08</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:18</v>
+        <v>7:03</v>
       </c>
       <c r="H17" t="str">
-        <v>NICK JONAS</v>
+        <v>Take That</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-08</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:08</v>
+        <v>4:37</v>
       </c>
       <c r="H18" t="str">
-        <v>Charlie Puth</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-08</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>4:03</v>
+        <v>3:54</v>
       </c>
       <c r="H19" t="str">
-        <v>Olivia Newton-John</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-08</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:01</v>
+        <v>3:06</v>
       </c>
       <c r="H20" t="str">
-        <v>The Warning and Carin Leon</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-08</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:05</v>
+        <v>3:21</v>
       </c>
       <c r="H21" t="str">
-        <v>Iman Fandi</v>
+        <v>George Birge</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
+        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-08</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:34</v>
+        <v>4:09</v>
       </c>
       <c r="H22" t="str">
-        <v>Megan Moroney</v>
+        <v>Warner Records</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dylan Davidson - Escape Artist</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
+        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-08</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:15</v>
+        <v>4:18</v>
       </c>
       <c r="H23" t="str">
-        <v>Dylan Davidson</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
+        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-08</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:16</v>
+        <v>3:08</v>
       </c>
       <c r="H24" t="str">
-        <v>Lady Gaga</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video)</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
+        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-08</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:53</v>
+        <v>4:03</v>
       </c>
       <c r="H25" t="str">
-        <v>Carlos Vives</v>
+        <v>Olivia Newton-John</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
+        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-08</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:25</v>
+        <v>3:01</v>
       </c>
       <c r="H26" t="str">
-        <v>Monsieur Periné</v>
+        <v>The Warning and Carin Leon</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio)</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
+        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-08</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:09</v>
+        <v>3:05</v>
       </c>
       <c r="H27" t="str">
-        <v>The Happy Fits</v>
+        <v>Iman Fandi</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>chase (lyric vid) - Michael Aldag</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
+        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-08</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:45</v>
+        <v>3:34</v>
       </c>
       <c r="H28" t="str">
-        <v>Michael Aldag</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
+        <v>Dylan Davidson - Escape Artist</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
+        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-08</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:07</v>
+        <v>3:15</v>
       </c>
       <c r="H29" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Dylan Davidson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
+        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
+        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-08</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:34</v>
+        <v>4:16</v>
       </c>
       <c r="H30" t="str">
-        <v>Marc Anthony</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
+        <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
+        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-08</v>
@@ -1556,10 +1556,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:14</v>
+        <v>3:53</v>
       </c>
       <c r="H31" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer)</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
+        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-08</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:11</v>
+        <v>2:25</v>
       </c>
       <c r="H32" t="str">
-        <v>Michael Bolton</v>
+        <v>Monsieur Periné</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Lachie Gill - Last Drive</v>
+        <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
+        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-08</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:40</v>
+        <v>4:09</v>
       </c>
       <c r="H33" t="str">
-        <v>Lachie Gill</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Lachie Gill - Last Drive - Lachie Gill</v>
+        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
+        <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
+        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-08</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:45</v>
+        <v>2:45</v>
       </c>
       <c r="H34" t="str">
-        <v>Eli &amp; Fur</v>
+        <v>Michael Aldag</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
+        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Freya Skye - why'd you have to call</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
+        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-08</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:19</v>
+        <v>4:07</v>
       </c>
       <c r="H35" t="str">
-        <v>Freya Skye</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Freya Skye - why'd you have to call - Freya Skye</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
+        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-08</v>
@@ -1746,10 +1746,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:30</v>
+        <v>4:34</v>
       </c>
       <c r="H36" t="str">
-        <v>Jessie J</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
+        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-08</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:24</v>
+        <v>5:14</v>
       </c>
       <c r="H37" t="str">
-        <v>Marc Anthony</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
+        <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
+        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-08</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:33</v>
+        <v>3:11</v>
       </c>
       <c r="H38" t="str">
-        <v>Clara Mae</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
+        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Metric - Victim of Luck (Official Music Video)</v>
+        <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
+        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-08</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:25</v>
+        <v>3:40</v>
       </c>
       <c r="H39" t="str">
-        <v>metricmusic</v>
+        <v>Lachie Gill</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
+        <v>Lachie Gill - Last Drive - Lachie Gill</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
+        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-08</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:41</v>
+        <v>3:45</v>
       </c>
       <c r="H40" t="str">
-        <v>kesha</v>
+        <v>Eli &amp; Fur</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
+        <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
+        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-08</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:19</v>
+        <v>4:19</v>
       </c>
       <c r="H41" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
+        <v>Freya Skye - why'd you have to call - Freya Skye</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
+        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-08</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:37</v>
+        <v>2:30</v>
       </c>
       <c r="H42" t="str">
-        <v>Vera Blue</v>
+        <v>Jessie J</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
+        <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
+        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-08</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:08</v>
+        <v>4:24</v>
       </c>
       <c r="H43" t="str">
-        <v>Bob Moses</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
+        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B44" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
+        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-08</v>
@@ -2050,10 +2050,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:28</v>
+        <v>2:33</v>
       </c>
       <c r="H44" t="str">
-        <v>Marc Anthony</v>
+        <v>Clara Mae</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
+        <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
+        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-08</v>
@@ -2088,10 +2088,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>5:05</v>
+        <v>3:25</v>
       </c>
       <c r="H45" t="str">
-        <v>Marc Anthony</v>
+        <v>metricmusic</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
+        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Loreen - Feels Like Heaven</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B46" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
+        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-08</v>
@@ -2126,10 +2126,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:14</v>
+        <v>3:41</v>
       </c>
       <c r="H46" t="str">
-        <v>Loreen</v>
+        <v>kesha</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Loreen - Feels Like Heaven - Loreen</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B47" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
+        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-08</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:36</v>
+        <v>3:19</v>
       </c>
       <c r="H47" t="str">
-        <v>Take That</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B48" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
+        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-08</v>
@@ -2202,10 +2202,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>5:31</v>
+        <v>3:37</v>
       </c>
       <c r="H48" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio)</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B49" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
+        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-08</v>
@@ -2240,10 +2240,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:37</v>
+        <v>3:08</v>
       </c>
       <c r="H49" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Bob Moses</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-08</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:58</v>
+        <v>3:28</v>
       </c>
       <c r="H50" t="str">
-        <v>The Warning</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-08</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>5:08</v>
+        <v>5:05</v>
       </c>
       <c r="H51" t="str">
-        <v>The Offspring</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-08</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:38</v>
+        <v>3:14</v>
       </c>
       <c r="H52" t="str">
-        <v>Roxette</v>
+        <v>Loreen</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Loreen - Feels Like Heaven - Loreen</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-08</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:50</v>
+        <v>3:36</v>
       </c>
       <c r="H53" t="str">
-        <v>Jessie Ware</v>
+        <v>Take That</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-08</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:10</v>
+        <v>5:31</v>
       </c>
       <c r="H54" t="str">
-        <v>Joseph</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-08</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:44</v>
+        <v>3:37</v>
       </c>
       <c r="H55" t="str">
-        <v>Dean Lewis</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-08</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:57</v>
+        <v>4:58</v>
       </c>
       <c r="H56" t="str">
-        <v>Take That</v>
+        <v>The Warning</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-08</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:07</v>
+        <v>5:08</v>
       </c>
       <c r="H57" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>The Offspring</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-08</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:47</v>
+        <v>4:38</v>
       </c>
       <c r="H58" t="str">
-        <v>Paris Paloma</v>
+        <v>Roxette</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-08</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:22</v>
+        <v>3:50</v>
       </c>
       <c r="H59" t="str">
-        <v>Zara Larsson</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-08</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:48</v>
+        <v>3:10</v>
       </c>
       <c r="H60" t="str">
-        <v>only the poets</v>
+        <v>Joseph</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-08</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:52</v>
+        <v>2:44</v>
       </c>
       <c r="H61" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-08</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:33</v>
+        <v>2:57</v>
       </c>
       <c r="H62" t="str">
-        <v>David Guetta</v>
+        <v>Take That</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-08</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:41</v>
+        <v>3:07</v>
       </c>
       <c r="H63" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-08</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:01</v>
+        <v>4:47</v>
       </c>
       <c r="H64" t="str">
-        <v>Ella Langley</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-08</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:16</v>
+        <v>3:22</v>
       </c>
       <c r="H65" t="str">
-        <v>Dogpark</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-08</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:03</v>
+        <v>2:48</v>
       </c>
       <c r="H66" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>only the poets</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-08</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:41</v>
+        <v>2:52</v>
       </c>
       <c r="H67" t="str">
-        <v>ERNEST</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-08</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:05</v>
+        <v>3:33</v>
       </c>
       <c r="H68" t="str">
-        <v>Labrinth</v>
+        <v>David Guetta</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-08</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:46</v>
+        <v>2:41</v>
       </c>
       <c r="H69" t="str">
-        <v>Grace VanderWaal</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-08</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:32</v>
+        <v>4:01</v>
       </c>
       <c r="H70" t="str">
-        <v>VOILÀ</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-08</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:42</v>
+        <v>3:16</v>
       </c>
       <c r="H71" t="str">
-        <v>Cannons</v>
+        <v>Dogpark</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-08</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:38</v>
+        <v>3:03</v>
       </c>
       <c r="H72" t="str">
-        <v>Kylie Morgan</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-08</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:10</v>
+        <v>2:41</v>
       </c>
       <c r="H73" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>ERNEST</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-08</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:57</v>
+        <v>3:05</v>
       </c>
       <c r="H74" t="str">
-        <v>Willie Nelson</v>
+        <v>Labrinth</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-08</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:19</v>
+        <v>2:46</v>
       </c>
       <c r="H75" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-08</v>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:04</v>
+        <v>3:32</v>
       </c>
       <c r="H76" t="str">
-        <v>India Martínez</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-08</v>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:16</v>
+        <v>3:42</v>
       </c>
       <c r="H77" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Cannons</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-08</v>
@@ -3342,10 +3342,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>5:58</v>
+        <v>2:38</v>
       </c>
       <c r="H78" t="str">
-        <v>TINI</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B79" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-08</v>
@@ -3380,10 +3380,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:26</v>
+        <v>3:10</v>
       </c>
       <c r="H79" t="str">
-        <v>Charley</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B80" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-08</v>
@@ -3418,10 +3418,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:05</v>
+        <v>3:57</v>
       </c>
       <c r="H80" t="str">
-        <v>Demi Lovato</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B81" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-08</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:16</v>
+        <v>2:19</v>
       </c>
       <c r="H81" t="str">
-        <v>Teddy Swims</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B82" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-08</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:14</v>
+        <v>4:04</v>
       </c>
       <c r="H82" t="str">
-        <v>Beck</v>
+        <v>India Martínez</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-08</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:57</v>
+        <v>2:16</v>
       </c>
       <c r="H83" t="str">
-        <v>The Offspring</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B84" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-08</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:10</v>
+        <v>5:58</v>
       </c>
       <c r="H84" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>TINI</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-08</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:10</v>
+        <v>3:26</v>
       </c>
       <c r="H85" t="str">
-        <v>Jason Derulo</v>
+        <v>Charley</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B86" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-08</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:52</v>
+        <v>4:05</v>
       </c>
       <c r="H86" t="str">
-        <v>lights</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B87" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-08</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:50</v>
+        <v>3:16</v>
       </c>
       <c r="H87" t="str">
-        <v>Telenova</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B88" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-08</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>5:32</v>
+        <v>3:14</v>
       </c>
       <c r="H88" t="str">
-        <v>Marcin</v>
+        <v>Beck</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B89" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-08</v>
@@ -3760,10 +3760,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:27</v>
+        <v>2:57</v>
       </c>
       <c r="H89" t="str">
-        <v>We Three</v>
+        <v>The Offspring</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B90" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-08</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:01</v>
+        <v>4:10</v>
       </c>
       <c r="H90" t="str">
-        <v>Timebelle Official</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B91" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-08</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:20</v>
+        <v>2:10</v>
       </c>
       <c r="H91" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-08</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:34</v>
+        <v>3:52</v>
       </c>
       <c r="H92" t="str">
-        <v>Clinton Kane</v>
+        <v>lights</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-08</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>4:01</v>
+        <v>3:50</v>
       </c>
       <c r="H93" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Telenova</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-08</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:24</v>
+        <v>5:32</v>
       </c>
       <c r="H94" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Marcin</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-08</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>5:52</v>
+        <v>4:27</v>
       </c>
       <c r="H95" t="str">
-        <v>Harry Styles</v>
+        <v>We Three</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-08</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>5:01</v>
+        <v>3:01</v>
       </c>
       <c r="H96" t="str">
-        <v>Neal Francis</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-08</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:12</v>
+        <v>3:20</v>
       </c>
       <c r="H97" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-08</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:59</v>
+        <v>3:34</v>
       </c>
       <c r="H98" t="str">
-        <v>Holly Humberstone</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-08</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:56</v>
+        <v>4:01</v>
       </c>
       <c r="H99" t="str">
-        <v>Cliff Richard</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-08</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:46</v>
+        <v>3:24</v>
       </c>
       <c r="H100" t="str">
-        <v>Jessie Ware</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-08</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:37</v>
+        <v>5:52</v>
       </c>
       <c r="H101" t="str">
-        <v>Bella White</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Die For Me</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-08</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>KONNAKOL</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:00</v>
+        <v>5:01</v>
       </c>
       <c r="H102" t="str">
-        <v>ZAYN</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Die For Me - ZAYN</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Two Six</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/two-six/1875080974</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-08</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Fall-Off</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:16</v>
+        <v>4:12</v>
       </c>
       <c r="H103" t="str">
-        <v>J. Cole</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/two-six/1875080726</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Two Six - J. Cole</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Dracula (JENNIE Remix)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-08</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Dracula (Remix) - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:29</v>
+        <v>3:59</v>
       </c>
       <c r="H104" t="str">
-        <v>Tame Impala</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Dracula (JENNIE Remix) - Tame Impala</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Hotel California</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-08</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Piss In The Wind</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>2:08</v>
+        <v>2:56</v>
       </c>
       <c r="H105" t="str">
-        <v>Joji</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>Hotel California - Joji</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Homewrecker</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-08</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Homewrecker - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:29</v>
+        <v>3:46</v>
       </c>
       <c r="H106" t="str">
-        <v>sombr</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Homewrecker - sombr</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Might Just</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/might-just/1858755211</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-08</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Do You Still Love Me?</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:43</v>
+        <v>4:37</v>
       </c>
       <c r="H107" t="str">
-        <v>Ella Mai</v>
+        <v>Bella White</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/might-just/1858754868</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Might Just - Ella Mai</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Cloud 9</v>
+        <v>Die For Me</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
+        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-08</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Cloud 9</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G108" t="str">
-        <v>3:33</v>
+        <v>3:00</v>
       </c>
       <c r="H108" t="str">
-        <v>Megan Moroney</v>
+        <v>ZAYN</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
+        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
       </c>
       <c r="L108" t="str">
-        <v>Cloud 9 - Megan Moroney</v>
+        <v>Die For Me - ZAYN</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Cry</v>
+        <v>Two Six</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/cry/1845189974</v>
+        <v>https://music.apple.com/us/song/two-six/1875080974</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-08</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Whatever's Clever!</v>
+        <v>The Fall-Off</v>
       </c>
       <c r="G109" t="str">
-        <v>3:07</v>
+        <v>3:16</v>
       </c>
       <c r="H109" t="str">
-        <v>Charlie Puth</v>
+        <v>J. Cole</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/cry/1845189970</v>
+        <v>https://music.apple.com/us/album/two-six/1875080726</v>
       </c>
       <c r="L109" t="str">
-        <v>Cry - Charlie Puth</v>
+        <v>Two Six - J. Cole</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>I'll Change for You</v>
+        <v>Dracula (JENNIE Remix)</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
+        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-08</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>Dracula (Remix) - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:16</v>
+        <v>3:29</v>
       </c>
       <c r="H110" t="str">
-        <v>Mitski</v>
+        <v>Tame Impala</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
+        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
       </c>
       <c r="L110" t="str">
-        <v>I'll Change for You - Mitski</v>
+        <v>Dracula (JENNIE Remix) - Tame Impala</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>ASSIGNMENT</v>
+        <v>Hotel California</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/assignment/1872764440</v>
+        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-08</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>ASSIGNMENT - Single</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G111" t="str">
-        <v>2:23</v>
+        <v>2:08</v>
       </c>
       <c r="H111" t="str">
-        <v>Power Snatch</v>
+        <v>Joji</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/assignment/1872764438</v>
+        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
       </c>
       <c r="L111" t="str">
-        <v>ASSIGNMENT - Power Snatch</v>
+        <v>Hotel California - Joji</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Como en el Idilio</v>
+        <v>Homewrecker</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
+        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-08</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Como en el Idilio - Single</v>
+        <v>Homewrecker - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>4:27</v>
+        <v>3:29</v>
       </c>
       <c r="H112" t="str">
-        <v>Marc Anthony</v>
+        <v>sombr</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
+        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
       </c>
       <c r="L112" t="str">
-        <v>Como en el Idilio - Marc Anthony</v>
+        <v>Homewrecker - sombr</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>golden boy</v>
+        <v>Might Just</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
+        <v>https://music.apple.com/us/song/might-just/1858755211</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-08</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>stardust - EP</v>
+        <v>Do You Still Love Me?</v>
       </c>
       <c r="G113" t="str">
-        <v>3:17</v>
+        <v>3:43</v>
       </c>
       <c r="H113" t="str">
-        <v>Freya Skye</v>
+        <v>Ella Mai</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
+        <v>https://music.apple.com/us/album/might-just/1858754868</v>
       </c>
       <c r="L113" t="str">
-        <v>golden boy - Freya Skye</v>
+        <v>Might Just - Ella Mai</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Penny in the Lake</v>
+        <v>Cloud 9</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
+        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-08</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Singin’ to an Empty Chair</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G114" t="str">
-        <v>3:51</v>
+        <v>3:33</v>
       </c>
       <c r="H114" t="str">
-        <v>Ratboys</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
+        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
       </c>
       <c r="L114" t="str">
-        <v>Penny in the Lake - Ratboys</v>
+        <v>Cloud 9 - Megan Moroney</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Heaven</v>
+        <v>Cry</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/heaven/1862570892</v>
+        <v>https://music.apple.com/us/song/cry/1845189974</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-08</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G115" t="str">
-        <v>4:26</v>
+        <v>3:07</v>
       </c>
       <c r="H115" t="str">
-        <v>Arlo Parks</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/heaven/1862570378</v>
+        <v>https://music.apple.com/us/album/cry/1845189970</v>
       </c>
       <c r="L115" t="str">
-        <v>Heaven - Arlo Parks</v>
+        <v>Cry - Charlie Puth</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Adrenaline</v>
+        <v>I'll Change for You</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
+        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-08</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>GOLDEN HOUR : Part.4 - EP</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G116" t="str">
-        <v>3:39</v>
+        <v>3:16</v>
       </c>
       <c r="H116" t="str">
-        <v>ATEEZ</v>
+        <v>Mitski</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
+        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
       </c>
       <c r="L116" t="str">
-        <v>Adrenaline - ATEEZ</v>
+        <v>I'll Change for You - Mitski</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Sweet To Me</v>
+        <v>ASSIGNMENT</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
+        <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-08</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Sunday Best</v>
+        <v>ASSIGNMENT - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>4:17</v>
+        <v>2:23</v>
       </c>
       <c r="H117" t="str">
-        <v>Nick Jonas</v>
+        <v>Power Snatch</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
+        <v>https://music.apple.com/us/album/assignment/1872764438</v>
       </c>
       <c r="L117" t="str">
-        <v>Sweet To Me - Nick Jonas</v>
+        <v>ASSIGNMENT - Power Snatch</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Time Goes On</v>
+        <v>Como en el Idilio</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
+        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-08</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Time Goes On - Single</v>
+        <v>Como en el Idilio - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:55</v>
+        <v>4:27</v>
       </c>
       <c r="H118" t="str">
-        <v>Koe Wetzel</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
+        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
       </c>
       <c r="L118" t="str">
-        <v>Time Goes On - Koe Wetzel</v>
+        <v>Como en el Idilio - Marc Anthony</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Drive Safe</v>
+        <v>golden boy</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
+        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-08</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Drive Safe - Single</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G119" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H119" t="str">
-        <v>Myles Smith</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
+        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
       </c>
       <c r="L119" t="str">
-        <v>Drive Safe - Myles Smith</v>
+        <v>golden boy - Freya Skye</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Love To Be Loved</v>
+        <v>Penny in the Lake</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
+        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-08</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Love To Be Loved - Single</v>
+        <v>Singin’ to an Empty Chair</v>
       </c>
       <c r="G120" t="str">
-        <v>2:50</v>
+        <v>3:51</v>
       </c>
       <c r="H120" t="str">
-        <v>The Warning</v>
+        <v>Ratboys</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
+        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
       </c>
       <c r="L120" t="str">
-        <v>Love To Be Loved - The Warning</v>
+        <v>Penny in the Lake - Ratboys</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Mi Yo de Antes</v>
+        <v>Heaven</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
+        <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-08</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Mi Yo de Antes - Single</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G121" t="str">
-        <v>3:02</v>
+        <v>4:26</v>
       </c>
       <c r="H121" t="str">
-        <v>Eden Muñoz</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
+        <v>https://music.apple.com/us/album/heaven/1862570378</v>
       </c>
       <c r="L121" t="str">
-        <v>Mi Yo de Antes - Eden Muñoz</v>
+        <v>Heaven - Arlo Parks</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Omens</v>
+        <v>Adrenaline</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/omens/1872546206</v>
+        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-08</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Omens - Single</v>
+        <v>GOLDEN HOUR : Part.4 - EP</v>
       </c>
       <c r="G122" t="str">
-        <v>2:00</v>
+        <v>3:39</v>
       </c>
       <c r="H122" t="str">
-        <v>EsDeeKid</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/omens/1872546204</v>
+        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
       </c>
       <c r="L122" t="str">
-        <v>Omens - EsDeeKid</v>
+        <v>Adrenaline - ATEEZ</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>My Regards</v>
+        <v>Sweet To Me</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
+        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-08</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Florescence</v>
+        <v>Sunday Best</v>
       </c>
       <c r="G123" t="str">
-        <v>3:11</v>
+        <v>4:17</v>
       </c>
       <c r="H123" t="str">
-        <v>Maisie Peters</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
+        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
       </c>
       <c r="L123" t="str">
-        <v>My Regards - Maisie Peters</v>
+        <v>Sweet To Me - Nick Jonas</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Time After Time</v>
+        <v>Time Goes On</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
+        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-08</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Time After Time - Single</v>
+        <v>Time Goes On - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:48</v>
+        <v>2:55</v>
       </c>
       <c r="H124" t="str">
-        <v>EJAE</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
+        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
       </c>
       <c r="L124" t="str">
-        <v>Time After Time - EJAE</v>
+        <v>Time Goes On - Koe Wetzel</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Don't Want Your Love</v>
+        <v>Drive Safe</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
+        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-08</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>ODYSSEY</v>
+        <v>Drive Safe - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:12</v>
+        <v>3:21</v>
       </c>
       <c r="H125" t="str">
-        <v>ILLENIUM</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
+        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
       </c>
       <c r="L125" t="str">
-        <v>Don't Want Your Love - ILLENIUM</v>
+        <v>Drive Safe - Myles Smith</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Pa' Los Envidiosos</v>
+        <v>Love To Be Loved</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
+        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-08</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Pa' Los Envidiosos - Single</v>
+        <v>Love To Be Loved - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:37</v>
+        <v>2:50</v>
       </c>
       <c r="H126" t="str">
-        <v>Pitbull</v>
+        <v>The Warning</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
+        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
       </c>
       <c r="L126" t="str">
-        <v>Pa' Los Envidiosos - Pitbull</v>
+        <v>Love To Be Loved - The Warning</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Plei</v>
+        <v>Mi Yo de Antes</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/plei/1872137577</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-08</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Plei - Single</v>
+        <v>Mi Yo de Antes - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:22</v>
+        <v>3:02</v>
       </c>
       <c r="H127" t="str">
-        <v>Chuwi</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/plei/1872137372</v>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
       </c>
       <c r="L127" t="str">
-        <v>Plei - Chuwi</v>
+        <v>Mi Yo de Antes - Eden Muñoz</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Flood (feat. Bon Iver)</v>
+        <v>Omens</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
+        <v>https://music.apple.com/us/song/omens/1872546206</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-08</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Omens - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:59</v>
+        <v>2:00</v>
       </c>
       <c r="H128" t="str">
-        <v>Dua Saleh</v>
+        <v>EsDeeKid</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
+        <v>https://music.apple.com/us/album/omens/1872546204</v>
       </c>
       <c r="L128" t="str">
-        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
+        <v>Omens - EsDeeKid</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Rain</v>
+        <v>My Regards</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/rain/1867258289</v>
+        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-08</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Rain - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G129" t="str">
-        <v>3:28</v>
+        <v>3:11</v>
       </c>
       <c r="H129" t="str">
-        <v>FISHER</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/rain/1867258288</v>
+        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
       </c>
       <c r="L129" t="str">
-        <v>Rain - FISHER</v>
+        <v>My Regards - Maisie Peters</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Release The Pressure</v>
+        <v>Time After Time</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
+        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-08</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Release The Pressure - Single</v>
+        <v>Time After Time - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:23</v>
+        <v>2:48</v>
       </c>
       <c r="H130" t="str">
-        <v>Calvin Harris</v>
+        <v>EJAE</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
+        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
+        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
       </c>
       <c r="L130" t="str">
-        <v>Release The Pressure - Calvin Harris</v>
+        <v>Time After Time - EJAE</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Sexistential (Arca’s Take)</v>
+        <v>Don't Want Your Love</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
+        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-08</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Sexistential (Arca’s Take) - Single</v>
+        <v>ODYSSEY</v>
       </c>
       <c r="G131" t="str">
-        <v>3:44</v>
+        <v>3:12</v>
       </c>
       <c r="H131" t="str">
-        <v>Robyn</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
+        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
       </c>
       <c r="L131" t="str">
-        <v>Sexistential (Arca’s Take) - Robyn</v>
+        <v>Don't Want Your Love - ILLENIUM</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>heal something</v>
+        <v>Pa' Los Envidiosos</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
+        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-08</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>ACT II</v>
+        <v>Pa' Los Envidiosos - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:01</v>
+        <v>3:37</v>
       </c>
       <c r="H132" t="str">
-        <v>Sasha Keable</v>
+        <v>Pitbull</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
+        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
       </c>
       <c r="L132" t="str">
-        <v>heal something - Sasha Keable</v>
+        <v>Pa' Los Envidiosos - Pitbull</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Buenos Días</v>
+        <v>Plei</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
+        <v>https://music.apple.com/us/song/plei/1872137577</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-08</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Buenos Días - Single</v>
+        <v>Plei - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:39</v>
+        <v>3:22</v>
       </c>
       <c r="H133" t="str">
-        <v>Eladio Carrión</v>
+        <v>Chuwi</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
+        <v>https://music.apple.com/us/album/plei/1872137372</v>
       </c>
       <c r="L133" t="str">
-        <v>Buenos Días - Eladio Carrión</v>
+        <v>Plei - Chuwi</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>COOK</v>
+        <v>Flood (feat. Bon Iver)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/cook/1872816147</v>
+        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-08</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>COOK - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G134" t="str">
-        <v>2:50</v>
+        <v>2:59</v>
       </c>
       <c r="H134" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/cook/1872816146</v>
+        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
       </c>
       <c r="L134" t="str">
-        <v>COOK - SOFI TUKKER</v>
+        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>You Got to Lose</v>
+        <v>Rain</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
+        <v>https://music.apple.com/us/song/rain/1867258289</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-08</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Peaches!</v>
+        <v>Rain - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:17</v>
+        <v>3:28</v>
       </c>
       <c r="H135" t="str">
-        <v>The Black Keys</v>
+        <v>FISHER</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
+        <v>https://music.apple.com/us/album/rain/1867258288</v>
       </c>
       <c r="L135" t="str">
-        <v>You Got to Lose - The Black Keys</v>
+        <v>Rain - FISHER</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Different Kind Of Love</v>
+        <v>Release The Pressure</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
+        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-08</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Victory Garden</v>
+        <v>Release The Pressure - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:39</v>
+        <v>3:23</v>
       </c>
       <c r="H136" t="str">
-        <v>Young the Giant</v>
+        <v>Calvin Harris</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
+        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
       </c>
       <c r="L136" t="str">
-        <v>Different Kind Of Love - Young the Giant</v>
+        <v>Release The Pressure - Calvin Harris</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Living Water</v>
+        <v>Sexistential (Arca’s Take)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/living-water/1871565262</v>
+        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-08</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Reconstruction: Second Story</v>
+        <v>Sexistential (Arca’s Take) - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:09</v>
+        <v>3:44</v>
       </c>
       <c r="H137" t="str">
-        <v>Lecrae</v>
+        <v>Robyn</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/living-water/1871564892</v>
+        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
       </c>
       <c r="L137" t="str">
-        <v>Living Water - Lecrae</v>
+        <v>Sexistential (Arca’s Take) - Robyn</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>What It Feels Like</v>
+        <v>heal something</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
+        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-08</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>What It Feels Like - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G138" t="str">
-        <v>2:18</v>
+        <v>3:01</v>
       </c>
       <c r="H138" t="str">
-        <v>Dillon Francis</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
+        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
       </c>
       <c r="L138" t="str">
-        <v>What It Feels Like - Dillon Francis</v>
+        <v>heal something - Sasha Keable</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>neck</v>
+        <v>Buenos Días</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/neck/1866953832</v>
+        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-08</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>neck - Single</v>
+        <v>Buenos Días - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:40</v>
+        <v>2:39</v>
       </c>
       <c r="H139" t="str">
-        <v>Mau P</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/neck/1866953831</v>
+        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
       </c>
       <c r="L139" t="str">
-        <v>neck - Mau P</v>
+        <v>Buenos Días - Eladio Carrión</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Colorblind</v>
+        <v>COOK</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
+        <v>https://music.apple.com/us/song/cook/1872816147</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-08</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Colorblind - Single</v>
+        <v>COOK - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:56</v>
+        <v>2:50</v>
       </c>
       <c r="H140" t="str">
-        <v>Gavin Adcock</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
+        <v>https://music.apple.com/us/album/cook/1872816146</v>
       </c>
       <c r="L140" t="str">
-        <v>Colorblind - Gavin Adcock</v>
+        <v>COOK - SOFI TUKKER</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Au Revoir Reservoir</v>
+        <v>You Got to Lose</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
+        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-08</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Tenterhooks</v>
+        <v>Peaches!</v>
       </c>
       <c r="G141" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H141" t="str">
-        <v>Silversun Pickups</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
+        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
       </c>
       <c r="L141" t="str">
-        <v>Au Revoir Reservoir - Silversun Pickups</v>
+        <v>You Got to Lose - The Black Keys</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Flavorless</v>
+        <v>Different Kind Of Love</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
+        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-08</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Flavorless - Single</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G142" t="str">
-        <v>3:31</v>
+        <v>3:39</v>
       </c>
       <c r="H142" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
+        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
       </c>
       <c r="L142" t="str">
-        <v>Flavorless - Dexter and The Moonrocks</v>
+        <v>Different Kind Of Love - Young the Giant</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Nunca</v>
+        <v>Living Water</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/nunca/1860691713</v>
+        <v>https://music.apple.com/us/song/living-water/1871565262</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-08</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>ESCENAS</v>
+        <v>Reconstruction: Second Story</v>
       </c>
       <c r="G143" t="str">
-        <v>3:05</v>
+        <v>2:09</v>
       </c>
       <c r="H143" t="str">
-        <v>Sin Bandera</v>
+        <v>Lecrae</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
+        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/nunca/1860691704</v>
+        <v>https://music.apple.com/us/album/living-water/1871564892</v>
       </c>
       <c r="L143" t="str">
-        <v>Nunca - Sin Bandera</v>
+        <v>Living Water - Lecrae</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Just In Case</v>
+        <v>What It Feels Like</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
+        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-08</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>NO HArD FEELINGS (Deluxe)</v>
+        <v>What It Feels Like - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>1:45</v>
+        <v>2:18</v>
       </c>
       <c r="H144" t="str">
-        <v>Marc E. Bassy</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
+        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
       </c>
       <c r="L144" t="str">
-        <v>Just In Case - Marc E. Bassy</v>
+        <v>What It Feels Like - Dillon Francis</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Thinking of You</v>
+        <v>neck</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
+        <v>https://music.apple.com/us/song/neck/1866953832</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-08</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Thinking of You - Single</v>
+        <v>neck - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:00</v>
+        <v>3:40</v>
       </c>
       <c r="H145" t="str">
-        <v>AP Dhillon</v>
+        <v>Mau P</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
+        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
+        <v>https://music.apple.com/us/album/neck/1866953831</v>
       </c>
       <c r="L145" t="str">
-        <v>Thinking of You - AP Dhillon</v>
+        <v>neck - Mau P</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>House Of Cards</v>
+        <v>Colorblind</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
+        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-08</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>House of Cards</v>
+        <v>Colorblind - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:26</v>
+        <v>2:56</v>
       </c>
       <c r="H146" t="str">
-        <v>The Amity Affliction</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
+        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
       </c>
       <c r="L146" t="str">
-        <v>House Of Cards - The Amity Affliction</v>
+        <v>Colorblind - Gavin Adcock</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Stay With Me</v>
+        <v>Au Revoir Reservoir</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
+        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-08</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Stay With Me - Single</v>
+        <v>Tenterhooks</v>
       </c>
       <c r="G147" t="str">
         <v>3:21</v>
       </c>
       <c r="H147" t="str">
-        <v>Agents Of Time</v>
+        <v>Silversun Pickups</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
+        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
+        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
       </c>
       <c r="L147" t="str">
-        <v>Stay With Me - Agents Of Time</v>
+        <v>Au Revoir Reservoir - Silversun Pickups</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>I had a dream...</v>
+        <v>Flavorless</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
+        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-08</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Dream inside a dream…</v>
+        <v>Flavorless - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:39</v>
+        <v>3:31</v>
       </c>
       <c r="H148" t="str">
-        <v>R3HAB</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
+        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
       </c>
       <c r="L148" t="str">
-        <v>I had a dream... - R3HAB</v>
+        <v>Flavorless - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Back to You</v>
+        <v>Nunca</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
+        <v>https://music.apple.com/us/song/nunca/1860691713</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-08</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Satellite</v>
+        <v>ESCENAS</v>
       </c>
       <c r="G149" t="str">
-        <v>3:10</v>
+        <v>3:05</v>
       </c>
       <c r="H149" t="str">
-        <v>Charlotte Sands</v>
+        <v>Sin Bandera</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
+        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
+        <v>https://music.apple.com/us/album/nunca/1860691704</v>
       </c>
       <c r="L149" t="str">
-        <v>Back to You - Charlotte Sands</v>
+        <v>Nunca - Sin Bandera</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>rager</v>
+        <v>Just In Case</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/rager/1872808801</v>
+        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-08</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>rager</v>
+        <v>NO HArD FEELINGS (Deluxe)</v>
       </c>
       <c r="G150" t="str">
-        <v>2:48</v>
+        <v>1:45</v>
       </c>
       <c r="H150" t="str">
-        <v>Blusher</v>
+        <v>Marc E. Bassy</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/blusher/485578161</v>
+        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/rager/1872808800</v>
+        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
       </c>
       <c r="L150" t="str">
-        <v>rager - Blusher</v>
+        <v>Just In Case - Marc E. Bassy</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>If Only</v>
+        <v>Thinking of You</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/if-only/1870281318</v>
+        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-08</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Patchwork</v>
+        <v>Thinking of You - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:28</v>
+        <v>3:00</v>
       </c>
       <c r="H151" t="str">
-        <v>Charlotte Day Wilson</v>
+        <v>AP Dhillon</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
+        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/if-only/1870281314</v>
+        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
       </c>
       <c r="L151" t="str">
-        <v>If Only - Charlotte Day Wilson</v>
+        <v>Thinking of You - AP Dhillon</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>DON'T LOVE ME</v>
+        <v>House Of Cards</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
+        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-08</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>DON'T LOVE ME - Single</v>
+        <v>House of Cards</v>
       </c>
       <c r="G152" t="str">
-        <v>3:01</v>
+        <v>3:26</v>
       </c>
       <c r="H152" t="str">
-        <v>Omah Lay</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
+        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
       </c>
       <c r="L152" t="str">
-        <v>DON'T LOVE ME - Omah Lay</v>
+        <v>House Of Cards - The Amity Affliction</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>No Sikes, No Tradesies</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-08</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Sweet Nothings</v>
+        <v>Stay With Me - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:32</v>
+        <v>3:21</v>
       </c>
       <c r="H153" t="str">
-        <v>Jaymin</v>
+        <v>Agents Of Time</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
+        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
       </c>
       <c r="L153" t="str">
-        <v>No Sikes, No Tradesies - Jaymin</v>
+        <v>Stay With Me - Agents Of Time</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>you woke me up</v>
+        <v>I had a dream...</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-08</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>you woke me up - Single</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G154" t="str">
-        <v>3:14</v>
+        <v>2:39</v>
       </c>
       <c r="H154" t="str">
-        <v>Kevian Kraemer</v>
+        <v>R3HAB</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
       </c>
       <c r="L154" t="str">
-        <v>you woke me up - Kevian Kraemer</v>
+        <v>I had a dream... - R3HAB</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>No One’s Business</v>
+        <v>Back to You</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
+        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-08</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>No One’s Business - Single</v>
+        <v>Satellite</v>
       </c>
       <c r="G155" t="str">
-        <v>3:00</v>
+        <v>3:10</v>
       </c>
       <c r="H155" t="str">
-        <v>Alicia Creti</v>
+        <v>Charlotte Sands</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
+        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
+        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
       </c>
       <c r="L155" t="str">
-        <v>No One’s Business - Alicia Creti</v>
+        <v>Back to You - Charlotte Sands</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
+        <v>rager</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
+        <v>https://music.apple.com/us/song/rager/1872808801</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-08</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>rager</v>
       </c>
       <c r="G156" t="str">
-        <v>3:13</v>
+        <v>2:48</v>
       </c>
       <c r="H156" t="str">
-        <v>Bryant Barnes</v>
+        <v>Blusher</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
+        <v>https://music.apple.com/us/artist/blusher/485578161</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/rager/1872808800</v>
       </c>
       <c r="L156" t="str">
-        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
+        <v>rager - Blusher</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>TWICE</v>
+        <v>If Only</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/twice/1871578107</v>
+        <v>https://music.apple.com/us/song/if-only/1870281318</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-08</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>KINDA HARD</v>
+        <v>Patchwork</v>
       </c>
       <c r="G157" t="str">
-        <v>3:44</v>
+        <v>3:28</v>
       </c>
       <c r="H157" t="str">
-        <v>Bilmuri</v>
+        <v>Charlotte Day Wilson</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/twice/1871578103</v>
+        <v>https://music.apple.com/us/album/if-only/1870281314</v>
       </c>
       <c r="L157" t="str">
-        <v>TWICE - Bilmuri</v>
+        <v>If Only - Charlotte Day Wilson</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>ROOFTOP</v>
+        <v>DON'T LOVE ME</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
+        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-08</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>ROOFTOP - Single</v>
+        <v>DON'T LOVE ME - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:22</v>
+        <v>3:01</v>
       </c>
       <c r="H158" t="str">
-        <v>Hulvey</v>
+        <v>Omah Lay</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
+        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
       </c>
       <c r="L158" t="str">
-        <v>ROOFTOP - Hulvey</v>
+        <v>DON'T LOVE ME - Omah Lay</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Louisiana Rain</v>
+        <v>No Sikes, No Tradesies</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
+        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-08</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Louisiana Rain - Single</v>
+        <v>Sweet Nothings</v>
       </c>
       <c r="G159" t="str">
-        <v>3:41</v>
+        <v>2:32</v>
       </c>
       <c r="H159" t="str">
-        <v>Hunter Plake</v>
+        <v>Jaymin</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
+        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
+        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
       </c>
       <c r="L159" t="str">
-        <v>Louisiana Rain - Hunter Plake</v>
+        <v>No Sikes, No Tradesies - Jaymin</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>sharing Jesus with an ex</v>
+        <v>you woke me up</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
+        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-08</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>sharing Jesus with an ex - Single</v>
+        <v>you woke me up - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>1:55</v>
+        <v>3:14</v>
       </c>
       <c r="H160" t="str">
-        <v>Zoe Levert</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
+        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
       </c>
       <c r="L160" t="str">
-        <v>sharing Jesus with an ex - Zoe Levert</v>
+        <v>you woke me up - Kevian Kraemer</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Body Control (feat. CHILLS)</v>
+        <v>No One’s Business</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
+        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-08</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Body Control (feat. CHILLS) - Single</v>
+        <v>No One’s Business - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:21</v>
+        <v>3:00</v>
       </c>
       <c r="H161" t="str">
-        <v>Cole Knight</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
+        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
       </c>
       <c r="L161" t="str">
-        <v>Body Control (feat. CHILLS) - Cole Knight</v>
+        <v>No One’s Business - Alicia Creti</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
+        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-08</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>A Prayer for the Dancefloor - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G162" t="str">
-        <v>6:54</v>
+        <v>3:13</v>
       </c>
       <c r="H162" t="str">
-        <v>Charlotte de Witte</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
+        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L162" t="str">
-        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Realm of Endless Misery</v>
+        <v>TWICE</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
+        <v>https://music.apple.com/us/song/twice/1871578107</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-08</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Liturgy of Death</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G163" t="str">
-        <v>4:56</v>
+        <v>3:44</v>
       </c>
       <c r="H163" t="str">
-        <v>Mayhem</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
+        <v>https://music.apple.com/us/album/twice/1871578103</v>
       </c>
       <c r="L163" t="str">
-        <v>Realm of Endless Misery - Mayhem</v>
+        <v>TWICE - Bilmuri</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>BLEACH</v>
+        <v>ROOFTOP</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/bleach/1869795882</v>
+        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-08</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>BLEACH - Single</v>
+        <v>ROOFTOP - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:28</v>
+        <v>3:22</v>
       </c>
       <c r="H164" t="str">
-        <v>Ecca Vandal</v>
+        <v>Hulvey</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/bleach/1869795874</v>
+        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
       </c>
       <c r="L164" t="str">
-        <v>BLEACH - Ecca Vandal</v>
+        <v>ROOFTOP - Hulvey</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>pretty in pink</v>
+        <v>Louisiana Rain</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
+        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-08</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>AngelPink</v>
+        <v>Louisiana Rain - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:13</v>
+        <v>3:41</v>
       </c>
       <c r="H165" t="str">
-        <v>Keni Titus</v>
+        <v>Hunter Plake</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
+        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
+        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
       </c>
       <c r="L165" t="str">
-        <v>pretty in pink - Keni Titus</v>
+        <v>Louisiana Rain - Hunter Plake</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Pickup Man</v>
+        <v>sharing Jesus with an ex</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
+        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-08</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Pickup Man - Single</v>
+        <v>sharing Jesus with an ex - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:28</v>
+        <v>1:55</v>
       </c>
       <c r="H166" t="str">
-        <v>Bayker Blankenship</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
+        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
       </c>
       <c r="L166" t="str">
-        <v>Pickup Man - Bayker Blankenship</v>
+        <v>sharing Jesus with an ex - Zoe Levert</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Get To Drinkin'</v>
+        <v>Body Control (feat. CHILLS)</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
+        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-08</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Get To Drinkin' - Single</v>
+        <v>Body Control (feat. CHILLS) - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:48</v>
+        <v>3:21</v>
       </c>
       <c r="H167" t="str">
-        <v>Zach John King</v>
+        <v>Cole Knight</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
+        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
+        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
       </c>
       <c r="L167" t="str">
-        <v>Get To Drinkin' - Zach John King</v>
+        <v>Body Control (feat. CHILLS) - Cole Knight</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>The Roses</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
+        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-08</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>The Roses - Single</v>
+        <v>A Prayer for the Dancefloor - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:02</v>
+        <v>6:54</v>
       </c>
       <c r="H168" t="str">
-        <v>Russell Dickerson</v>
+        <v>Charlotte de Witte</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
+        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
+        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
       </c>
       <c r="L168" t="str">
-        <v>The Roses - Russell Dickerson</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>I Should Know Better</v>
+        <v>Realm of Endless Misery</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
+        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-08</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Under The Streetlights</v>
+        <v>Liturgy of Death</v>
       </c>
       <c r="G169" t="str">
-        <v>3:33</v>
+        <v>4:56</v>
       </c>
       <c r="H169" t="str">
-        <v>Michael Marcagi</v>
+        <v>Mayhem</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
+        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
+        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
       </c>
       <c r="L169" t="str">
-        <v>I Should Know Better - Michael Marcagi</v>
+        <v>Realm of Endless Misery - Mayhem</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Never Do</v>
+        <v>BLEACH</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/never-do/1872842226</v>
+        <v>https://music.apple.com/us/song/bleach/1869795882</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-08</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Never Do - Single</v>
+        <v>BLEACH - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>1:58</v>
+        <v>2:28</v>
       </c>
       <c r="H170" t="str">
-        <v>charlieonnafriday</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/never-do/1872842225</v>
+        <v>https://music.apple.com/us/album/bleach/1869795874</v>
       </c>
       <c r="L170" t="str">
-        <v>Never Do - charlieonnafriday</v>
+        <v>BLEACH - Ecca Vandal</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Primary Colors</v>
+        <v>pretty in pink</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
+        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-08</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Lost on You</v>
+        <v>AngelPink</v>
       </c>
       <c r="G171" t="str">
-        <v>3:37</v>
+        <v>3:13</v>
       </c>
       <c r="H171" t="str">
-        <v>Tigers Jaw</v>
+        <v>Keni Titus</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
+        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
+        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
       </c>
       <c r="L171" t="str">
-        <v>Primary Colors - Tigers Jaw</v>
+        <v>pretty in pink - Keni Titus</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Rock Bottom</v>
+        <v>Pickup Man</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
+        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-08</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Rock Bottom / Octopus - Single</v>
+        <v>Pickup Man - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:10</v>
+        <v>3:28</v>
       </c>
       <c r="H172" t="str">
-        <v>King Krule</v>
+        <v>Bayker Blankenship</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
+        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
+        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
       </c>
       <c r="L172" t="str">
-        <v>Rock Bottom - King Krule</v>
+        <v>Pickup Man - Bayker Blankenship</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Te Dedico</v>
+        <v>Get To Drinkin'</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
+        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-08</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Te Dedico - Single</v>
+        <v>Get To Drinkin' - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:45</v>
+        <v>2:48</v>
       </c>
       <c r="H173" t="str">
-        <v>Carlos Vives</v>
+        <v>Zach John King</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
+        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
+        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
       </c>
       <c r="L173" t="str">
-        <v>Te Dedico - Carlos Vives</v>
+        <v>Get To Drinkin' - Zach John King</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>AUNQUE SEA EN DOS</v>
+        <v>The Roses</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
+        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-08</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>18</v>
+        <v>The Roses - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:38</v>
+        <v>3:02</v>
       </c>
       <c r="H174" t="str">
-        <v>Conexión Divina</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
+        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
+        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
       </c>
       <c r="L174" t="str">
-        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
+        <v>The Roses - Russell Dickerson</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>I Dare You</v>
+        <v>I Should Know Better</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
+        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-08</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>I Dare You - Single</v>
+        <v>Under The Streetlights</v>
       </c>
       <c r="G175" t="str">
-        <v>3:25</v>
+        <v>3:33</v>
       </c>
       <c r="H175" t="str">
-        <v>Dylan Dunlap</v>
+        <v>Michael Marcagi</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
+        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
+        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
       </c>
       <c r="L175" t="str">
-        <v>I Dare You - Dylan Dunlap</v>
+        <v>I Should Know Better - Michael Marcagi</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>new irish boyfriend</v>
+        <v>Never Do</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
+        <v>https://music.apple.com/us/song/never-do/1872842226</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-08</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>long time caller, first time listener</v>
+        <v>Never Do - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:50</v>
+        <v>1:58</v>
       </c>
       <c r="H176" t="str">
-        <v>vegas water taxi</v>
+        <v>charlieonnafriday</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
+        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
+        <v>https://music.apple.com/us/album/never-do/1872842225</v>
       </c>
       <c r="L176" t="str">
-        <v>new irish boyfriend - vegas water taxi</v>
+        <v>Never Do - charlieonnafriday</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Everyone Around Me Dancing</v>
+        <v>Primary Colors</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
+        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-08</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Singing</v>
+        <v>Lost on You</v>
       </c>
       <c r="G177" t="str">
-        <v>3:05</v>
+        <v>3:37</v>
       </c>
       <c r="H177" t="str">
-        <v>Gia Margaret</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
+        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
       </c>
       <c r="L177" t="str">
-        <v>Everyone Around Me Dancing - Gia Margaret</v>
+        <v>Primary Colors - Tigers Jaw</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Good Enough (feat. Julie Doiron)</v>
+        <v>Rock Bottom</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-08</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Big Changes</v>
+        <v>Rock Bottom / Octopus - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>6:05</v>
+        <v>4:10</v>
       </c>
       <c r="H178" t="str">
-        <v>Status/Non-Status</v>
+        <v>King Krule</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
+        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
       </c>
       <c r="L178" t="str">
-        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
+        <v>Rock Bottom - King Krule</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
+        <v>Te Dedico</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
+        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-08</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
+        <v>Te Dedico - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>4:09</v>
+        <v>3:45</v>
       </c>
       <c r="H179" t="str">
-        <v>Julian Lage</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
+        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
+        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
       </c>
       <c r="L179" t="str">
-        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
+        <v>Te Dedico - Carlos Vives</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Big Deal</v>
+        <v>AUNQUE SEA EN DOS</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
+        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-08</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Big Deal - Single</v>
+        <v>18</v>
       </c>
       <c r="G180" t="str">
-        <v>3:47</v>
+        <v>2:38</v>
       </c>
       <c r="H180" t="str">
-        <v>In Color</v>
+        <v>Conexión Divina</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
+        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
       </c>
       <c r="L180" t="str">
-        <v>Big Deal - In Color</v>
+        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Buy What U Want</v>
+        <v>I Dare You</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
+        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-08</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Road To Osshland III - EP</v>
+        <v>I Dare You - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:47</v>
+        <v>3:25</v>
       </c>
       <c r="H181" t="str">
-        <v>Black Fortune</v>
+        <v>Dylan Dunlap</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
+        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
+        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
       </c>
       <c r="L181" t="str">
-        <v>Buy What U Want - Black Fortune</v>
+        <v>I Dare You - Dylan Dunlap</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Common Ground</v>
+        <v>new irish boyfriend</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
+        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-08</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Common Ground - Single</v>
+        <v>long time caller, first time listener</v>
       </c>
       <c r="G182" t="str">
-        <v>1:42</v>
+        <v>3:50</v>
       </c>
       <c r="H182" t="str">
-        <v>ELIO</v>
+        <v>vegas water taxi</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/elio/1501417625</v>
+        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
+        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
       </c>
       <c r="L182" t="str">
-        <v>Common Ground - ELIO</v>
+        <v>new irish boyfriend - vegas water taxi</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Cellophane</v>
+        <v>Everyone Around Me Dancing</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
+        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-08</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Cellophane - Single</v>
+        <v>Singing</v>
       </c>
       <c r="G183" t="str">
-        <v>4:21</v>
+        <v>3:05</v>
       </c>
       <c r="H183" t="str">
-        <v>Maddie Zahm</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
+        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
       </c>
       <c r="L183" t="str">
-        <v>Cellophane - Maddie Zahm</v>
+        <v>Everyone Around Me Dancing - Gia Margaret</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>96 Camry</v>
+        <v>Good Enough (feat. Julie Doiron)</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
+        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-08</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>PRAY FOR ME</v>
+        <v>Big Changes</v>
       </c>
       <c r="G184" t="str">
-        <v>3:15</v>
+        <v>6:05</v>
       </c>
       <c r="H184" t="str">
-        <v>RAAHiiM</v>
+        <v>Status/Non-Status</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
+        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
+        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
       </c>
       <c r="L184" t="str">
-        <v>96 Camry - RAAHiiM</v>
+        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>La Allstar</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
+        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-08</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>La Allstar - Single</v>
+        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="G185" t="str">
-        <v>2:49</v>
+        <v>4:09</v>
       </c>
       <c r="H185" t="str">
-        <v>ELIKAI</v>
+        <v>Julian Lage</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
+        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
+        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
       </c>
       <c r="L185" t="str">
-        <v>La Allstar - ELIKAI</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Luka</v>
+        <v>Big Deal</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/luka/1869396162</v>
+        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-08</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Luka - Single</v>
+        <v>Big Deal - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:07</v>
+        <v>3:47</v>
       </c>
       <c r="H186" t="str">
-        <v>Fonta</v>
+        <v>In Color</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/luka/1869396161</v>
+        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
       </c>
       <c r="L186" t="str">
-        <v>Luka - Fonta</v>
+        <v>Big Deal - In Color</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Ganas De Tenerla</v>
+        <v>Buy What U Want</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
+        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-08</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Ganas De Tenerla - Single</v>
+        <v>Road To Osshland III - EP</v>
       </c>
       <c r="G187" t="str">
-        <v>3:06</v>
+        <v>3:47</v>
       </c>
       <c r="H187" t="str">
-        <v>Silvestre Dangond</v>
+        <v>Black Fortune</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
+        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
+        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
       </c>
       <c r="L187" t="str">
-        <v>Ganas De Tenerla - Silvestre Dangond</v>
+        <v>Buy What U Want - Black Fortune</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>In My Blue</v>
+        <v>Common Ground</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
+        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-08</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Doomsday...Don't Leave Me Here</v>
+        <v>Common Ground - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:26</v>
+        <v>1:42</v>
       </c>
       <c r="H188" t="str">
-        <v>Rosie Carney</v>
+        <v>ELIO</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
+        <v>https://music.apple.com/us/artist/elio/1501417625</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
+        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
       </c>
       <c r="L188" t="str">
-        <v>In My Blue - Rosie Carney</v>
+        <v>Common Ground - ELIO</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Living With It (feat. Feist)</v>
+        <v>Cellophane</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
+        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-08</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Hurts Like Hell</v>
+        <v>Cellophane - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:20</v>
+        <v>4:21</v>
       </c>
       <c r="H189" t="str">
-        <v>Charlotte Cornfield</v>
+        <v>Maddie Zahm</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
+        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
+        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
       </c>
       <c r="L189" t="str">
-        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
+        <v>Cellophane - Maddie Zahm</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Silently</v>
+        <v>96 Camry</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/silently/1841629898</v>
+        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-08</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Croak Dream</v>
+        <v>PRAY FOR ME</v>
       </c>
       <c r="G190" t="str">
-        <v>3:29</v>
+        <v>3:15</v>
       </c>
       <c r="H190" t="str">
-        <v>Puma Blue</v>
+        <v>RAAHiiM</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
+        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/silently/1841629444</v>
+        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
       </c>
       <c r="L190" t="str">
-        <v>Silently - Puma Blue</v>
+        <v>96 Camry - RAAHiiM</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Ashes &amp; Smoke</v>
+        <v>La Allstar</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
+        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-08</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Ashes &amp; Smoke - Single</v>
+        <v>La Allstar - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:05</v>
+        <v>2:49</v>
       </c>
       <c r="H191" t="str">
-        <v>Anna Graves</v>
+        <v>ELIKAI</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
+        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
+        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
       </c>
       <c r="L191" t="str">
-        <v>Ashes &amp; Smoke - Anna Graves</v>
+        <v>La Allstar - ELIKAI</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Tormentor</v>
+        <v>Luka</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
+        <v>https://music.apple.com/us/song/luka/1869396162</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-08</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>The Flowers I See You In - EP</v>
+        <v>Luka - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:40</v>
+        <v>2:07</v>
       </c>
       <c r="H192" t="str">
-        <v>Ninush</v>
+        <v>Fonta</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
+        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
+        <v>https://music.apple.com/us/album/luka/1869396161</v>
       </c>
       <c r="L192" t="str">
-        <v>Tormentor - Ninush</v>
+        <v>Luka - Fonta</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Red Rocking Chair</v>
+        <v>Ganas De Tenerla</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
+        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-08</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Red Rocking Chair - Single</v>
+        <v>Ganas De Tenerla - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>6:28</v>
+        <v>3:06</v>
       </c>
       <c r="H193" t="str">
-        <v>All Them Witches</v>
+        <v>Silvestre Dangond</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
+        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
       </c>
       <c r="L193" t="str">
-        <v>Red Rocking Chair - All Them Witches</v>
+        <v>Ganas De Tenerla - Silvestre Dangond</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
+        <v>In My Blue</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
+        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-08</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>...of Death and Fire</v>
+        <v>Doomsday...Don't Leave Me Here</v>
       </c>
       <c r="G194" t="str">
-        <v>7:07</v>
+        <v>3:26</v>
       </c>
       <c r="H194" t="str">
-        <v>In Aeternum</v>
+        <v>Rosie Carney</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
+        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
+        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
       </c>
       <c r="L194" t="str">
-        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
+        <v>In My Blue - Rosie Carney</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Mizantrop</v>
+        <v>Living With It (feat. Feist)</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
+        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-08</v>
@@ -7785,68 +7785,296 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Mizantrop</v>
+        <v>Hurts Like Hell</v>
       </c>
       <c r="G195" t="str">
-        <v>3:42</v>
+        <v>3:20</v>
       </c>
       <c r="H195" t="str">
-        <v>She Past Away</v>
+        <v>Charlotte Cornfield</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
+        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
+        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
       </c>
       <c r="L195" t="str">
-        <v>Mizantrop - She Past Away</v>
+        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
+        <v>Silently</v>
+      </c>
+      <c r="B196" t="str">
+        <v/>
+      </c>
+      <c r="C196" t="str">
+        <v>https://music.apple.com/us/song/silently/1841629898</v>
+      </c>
+      <c r="D196" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v>Croak Dream</v>
+      </c>
+      <c r="G196" t="str">
+        <v>3:29</v>
+      </c>
+      <c r="H196" t="str">
+        <v>Puma Blue</v>
+      </c>
+      <c r="I196" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J196" t="str">
+        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
+      </c>
+      <c r="K196" t="str">
+        <v>https://music.apple.com/us/album/silently/1841629444</v>
+      </c>
+      <c r="L196" t="str">
+        <v>Silently - Puma Blue</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Ashes &amp; Smoke</v>
+      </c>
+      <c r="B197" t="str">
+        <v/>
+      </c>
+      <c r="C197" t="str">
+        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
+      </c>
+      <c r="D197" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
+        <v>Ashes &amp; Smoke - Single</v>
+      </c>
+      <c r="G197" t="str">
+        <v>3:05</v>
+      </c>
+      <c r="H197" t="str">
+        <v>Anna Graves</v>
+      </c>
+      <c r="I197" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J197" t="str">
+        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
+      </c>
+      <c r="K197" t="str">
+        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
+      </c>
+      <c r="L197" t="str">
+        <v>Ashes &amp; Smoke - Anna Graves</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Tormentor</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>The Flowers I See You In - EP</v>
+      </c>
+      <c r="G198" t="str">
+        <v>2:40</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Ninush</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
+      </c>
+      <c r="L198" t="str">
+        <v>Tormentor - Ninush</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Red Rocking Chair</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>Red Rocking Chair - Single</v>
+      </c>
+      <c r="G199" t="str">
+        <v>6:28</v>
+      </c>
+      <c r="H199" t="str">
+        <v>All Them Witches</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Red Rocking Chair - All Them Witches</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>...of Death and Fire</v>
+      </c>
+      <c r="G200" t="str">
+        <v>7:07</v>
+      </c>
+      <c r="H200" t="str">
+        <v>In Aeternum</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
+      </c>
+      <c r="L200" t="str">
+        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Mizantrop</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>Mizantrop</v>
+      </c>
+      <c r="G201" t="str">
+        <v>3:42</v>
+      </c>
+      <c r="H201" t="str">
+        <v>She Past Away</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Mizantrop - She Past Away</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
         <v>In the Name of the Moth</v>
       </c>
-      <c r="B196" t="str">
-        <v/>
-      </c>
-      <c r="C196" t="str">
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
         <v>https://music.apple.com/us/song/in-the-name-of-the-moth/1866911203</v>
       </c>
-      <c r="D196" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E196" t="str">
-        <v/>
-      </c>
-      <c r="F196" t="str">
+      <c r="D202" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
         <v>Hidden Fires Burn Hottest</v>
       </c>
-      <c r="G196" t="str">
+      <c r="G202" t="str">
         <v>7:15</v>
       </c>
-      <c r="H196" t="str">
+      <c r="H202" t="str">
         <v>Bosse-de-Nage</v>
       </c>
-      <c r="I196" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J196" t="str">
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
         <v>https://music.apple.com/us/artist/bosse-de-nage/465123183</v>
       </c>
-      <c r="K196" t="str">
+      <c r="K202" t="str">
         <v>https://music.apple.com/us/album/in-the-name-of-the-moth/1866911198</v>
       </c>
-      <c r="L196" t="str">
+      <c r="L202" t="str">
         <v>In the Name of the Moth - Bosse-de-Nage</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L196"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליעד מאיר - חברים שלי</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-08</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409539&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-08</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>6 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>6:00</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Taylor Swift</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליעד מאיר - חברים שלי</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ליאור עמדי - חן הבה</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-08</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409538&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-08</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>7 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>4:20</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Michael Bolton</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ליאור עמדי - חן הבה</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יגל יובל שרעבי - אלופו של עולם</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-08</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409537&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-08</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>23 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>4:27</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Mariah Carey</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יגל יובל שרעבי - אלופו של עולם</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>טלי רבקה סימן טוב - אני עץ, אני אילן</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-08</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409536&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-08</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>3:26</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Netflix</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>טלי רבקה סימן טוב - אני עץ, אני אילן</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>חיים ישראל - מחרוזת השירים של זוהר 2026</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-08</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409535&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-08</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>3:29</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Michael Bolton</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>חיים ישראל - מחרוזת השירים של זוהר 2026</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>האחים דוליס - הלילה עבר</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-08</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409534&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-08</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>2:59</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>mgk</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>האחים דוליס - הלילה עבר</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B8" t="str">
-        <v>5 hours ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-08</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5 hours ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>6:00</v>
+        <v>2:51</v>
       </c>
       <c r="H8" t="str">
-        <v>Taylor Swift</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B9" t="str">
-        <v>6 hours ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-08</v>
@@ -717,10 +717,10 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6 hours ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>4:20</v>
+        <v>4:13</v>
       </c>
       <c r="H9" t="str">
         <v>Michael Bolton</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B10" t="str">
-        <v>22 hours ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-08</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>22 hours ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:27</v>
+        <v>4:41</v>
       </c>
       <c r="H10" t="str">
-        <v>Mariah Carey</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-08</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:26</v>
+        <v>7:03</v>
       </c>
       <c r="H11" t="str">
-        <v>Netflix</v>
+        <v>Take That</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-08</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:29</v>
+        <v>4:37</v>
       </c>
       <c r="H12" t="str">
-        <v>Michael Bolton</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-08</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>2:59</v>
+        <v>3:54</v>
       </c>
       <c r="H13" t="str">
-        <v>mgk</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-08</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:51</v>
+        <v>3:06</v>
       </c>
       <c r="H14" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-08</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:13</v>
+        <v>3:21</v>
       </c>
       <c r="H15" t="str">
-        <v>Michael Bolton</v>
+        <v>George Birge</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-08</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:41</v>
+        <v>4:09</v>
       </c>
       <c r="H16" t="str">
-        <v>NICK JONAS</v>
+        <v>Warner Records</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-08</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>7:03</v>
+        <v>4:18</v>
       </c>
       <c r="H17" t="str">
-        <v>Take That</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-08</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:37</v>
+        <v>3:08</v>
       </c>
       <c r="H18" t="str">
-        <v>Cliff Richard</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-08</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:54</v>
+        <v>4:03</v>
       </c>
       <c r="H19" t="str">
-        <v>Bryan Adams</v>
+        <v>Olivia Newton-John</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-08</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:06</v>
+        <v>3:01</v>
       </c>
       <c r="H20" t="str">
-        <v>Anna Graves</v>
+        <v>The Warning and Carin Leon</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-08</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:21</v>
+        <v>3:05</v>
       </c>
       <c r="H21" t="str">
-        <v>George Birge</v>
+        <v>Iman Fandi</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
+        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-08</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:09</v>
+        <v>3:34</v>
       </c>
       <c r="H22" t="str">
-        <v>Warner Records</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
+        <v>Dylan Davidson - Escape Artist</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
+        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-08</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:18</v>
+        <v>3:15</v>
       </c>
       <c r="H23" t="str">
-        <v>NICK JONAS</v>
+        <v>Dylan Davidson</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
+        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
+        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-08</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:08</v>
+        <v>4:16</v>
       </c>
       <c r="H24" t="str">
-        <v>Charlie Puth</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
+        <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
+        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-08</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>4:03</v>
+        <v>3:53</v>
       </c>
       <c r="H25" t="str">
-        <v>Olivia Newton-John</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
+        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
+        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-08</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:01</v>
+        <v>2:25</v>
       </c>
       <c r="H26" t="str">
-        <v>The Warning and Carin Leon</v>
+        <v>Monsieur Periné</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
+        <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
+        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-08</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:05</v>
+        <v>4:09</v>
       </c>
       <c r="H27" t="str">
-        <v>Iman Fandi</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
+        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
+        <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
+        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-08</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:34</v>
+        <v>2:45</v>
       </c>
       <c r="H28" t="str">
-        <v>Megan Moroney</v>
+        <v>Michael Aldag</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
+        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Dylan Davidson - Escape Artist</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
+        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-08</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:15</v>
+        <v>4:07</v>
       </c>
       <c r="H29" t="str">
-        <v>Dylan Davidson</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
+        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-08</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:16</v>
+        <v>4:34</v>
       </c>
       <c r="H30" t="str">
-        <v>Lady Gaga</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
+        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-08</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:53</v>
+        <v>5:14</v>
       </c>
       <c r="H31" t="str">
-        <v>Carlos Vives</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
+        <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
+        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-08</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:25</v>
+        <v>3:11</v>
       </c>
       <c r="H32" t="str">
-        <v>Monsieur Periné</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
+        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio)</v>
+        <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
+        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-08</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:09</v>
+        <v>3:40</v>
       </c>
       <c r="H33" t="str">
-        <v>The Happy Fits</v>
+        <v>Lachie Gill</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
+        <v>Lachie Gill - Last Drive - Lachie Gill</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>chase (lyric vid) - Michael Aldag</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
+        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-08</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:45</v>
+        <v>3:45</v>
       </c>
       <c r="H34" t="str">
-        <v>Michael Aldag</v>
+        <v>Eli &amp; Fur</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
+        <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
+        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-08</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:07</v>
+        <v>4:19</v>
       </c>
       <c r="H35" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
+        <v>Freya Skye - why'd you have to call - Freya Skye</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
+        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-08</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:34</v>
+        <v>2:30</v>
       </c>
       <c r="H36" t="str">
-        <v>Marc Anthony</v>
+        <v>Jessie J</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
+        <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
+        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-08</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>5:14</v>
+        <v>4:24</v>
       </c>
       <c r="H37" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer)</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
+        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-08</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:11</v>
+        <v>2:33</v>
       </c>
       <c r="H38" t="str">
-        <v>Michael Bolton</v>
+        <v>Clara Mae</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lachie Gill - Last Drive</v>
+        <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
+        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-08</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:40</v>
+        <v>3:25</v>
       </c>
       <c r="H39" t="str">
-        <v>Lachie Gill</v>
+        <v>metricmusic</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lachie Gill - Last Drive - Lachie Gill</v>
+        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B40" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
+        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-08</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:45</v>
+        <v>3:41</v>
       </c>
       <c r="H40" t="str">
-        <v>Eli &amp; Fur</v>
+        <v>kesha</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Freya Skye - why'd you have to call</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
+        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-08</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:19</v>
+        <v>3:19</v>
       </c>
       <c r="H41" t="str">
-        <v>Freya Skye</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Freya Skye - why'd you have to call - Freya Skye</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
+        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-08</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:30</v>
+        <v>3:37</v>
       </c>
       <c r="H42" t="str">
-        <v>Jessie J</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer)</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
+        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-08</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:24</v>
+        <v>3:08</v>
       </c>
       <c r="H43" t="str">
-        <v>Marc Anthony</v>
+        <v>Bob Moses</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
+        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-08</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:33</v>
+        <v>3:28</v>
       </c>
       <c r="H44" t="str">
-        <v>Clara Mae</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Metric - Victim of Luck (Official Music Video)</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
+        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-08</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:25</v>
+        <v>5:05</v>
       </c>
       <c r="H45" t="str">
-        <v>metricmusic</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
+        <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
+        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-08</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:41</v>
+        <v>3:14</v>
       </c>
       <c r="H46" t="str">
-        <v>kesha</v>
+        <v>Loreen</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
+        <v>Loreen - Feels Like Heaven - Loreen</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
+        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-08</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:19</v>
+        <v>3:36</v>
       </c>
       <c r="H47" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Take That</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
+        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-08</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:37</v>
+        <v>5:31</v>
       </c>
       <c r="H48" t="str">
-        <v>Vera Blue</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
+        <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B49" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
+        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-08</v>
@@ -2240,10 +2240,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:08</v>
+        <v>3:37</v>
       </c>
       <c r="H49" t="str">
-        <v>Bob Moses</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
+        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-08</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:28</v>
+        <v>4:58</v>
       </c>
       <c r="H50" t="str">
-        <v>Marc Anthony</v>
+        <v>The Warning</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B51" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-08</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>5:05</v>
+        <v>5:08</v>
       </c>
       <c r="H51" t="str">
-        <v>Marc Anthony</v>
+        <v>The Offspring</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Loreen - Feels Like Heaven</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B52" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-08</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:14</v>
+        <v>4:38</v>
       </c>
       <c r="H52" t="str">
-        <v>Loreen</v>
+        <v>Roxette</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Loreen - Feels Like Heaven - Loreen</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
       </c>
       <c r="B53" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-08</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:36</v>
+        <v>3:50</v>
       </c>
       <c r="H53" t="str">
-        <v>Take That</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-08</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>5:31</v>
+        <v>3:10</v>
       </c>
       <c r="H54" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Joseph</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-08</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:37</v>
+        <v>2:44</v>
       </c>
       <c r="H55" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-08</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:58</v>
+        <v>2:57</v>
       </c>
       <c r="H56" t="str">
-        <v>The Warning</v>
+        <v>Take That</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-08</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>5:08</v>
+        <v>3:07</v>
       </c>
       <c r="H57" t="str">
-        <v>The Offspring</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-08</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:38</v>
+        <v>4:47</v>
       </c>
       <c r="H58" t="str">
-        <v>Roxette</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-08</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:50</v>
+        <v>3:22</v>
       </c>
       <c r="H59" t="str">
-        <v>Jessie Ware</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-08</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:10</v>
+        <v>2:48</v>
       </c>
       <c r="H60" t="str">
-        <v>Joseph</v>
+        <v>only the poets</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-08</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:44</v>
+        <v>2:52</v>
       </c>
       <c r="H61" t="str">
-        <v>Dean Lewis</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-08</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>2:57</v>
+        <v>3:33</v>
       </c>
       <c r="H62" t="str">
-        <v>Take That</v>
+        <v>David Guetta</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-08</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:07</v>
+        <v>2:41</v>
       </c>
       <c r="H63" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-08</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:47</v>
+        <v>4:01</v>
       </c>
       <c r="H64" t="str">
-        <v>Paris Paloma</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-08</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:22</v>
+        <v>3:16</v>
       </c>
       <c r="H65" t="str">
-        <v>Zara Larsson</v>
+        <v>Dogpark</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-08</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:48</v>
+        <v>3:03</v>
       </c>
       <c r="H66" t="str">
-        <v>only the poets</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-08</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:52</v>
+        <v>2:41</v>
       </c>
       <c r="H67" t="str">
-        <v>Katelyn Tarver</v>
+        <v>ERNEST</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-08</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:33</v>
+        <v>3:05</v>
       </c>
       <c r="H68" t="str">
-        <v>David Guetta</v>
+        <v>Labrinth</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-08</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:41</v>
+        <v>2:46</v>
       </c>
       <c r="H69" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-08</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:01</v>
+        <v>3:32</v>
       </c>
       <c r="H70" t="str">
-        <v>Ella Langley</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-08</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:16</v>
+        <v>3:42</v>
       </c>
       <c r="H71" t="str">
-        <v>Dogpark</v>
+        <v>Cannons</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-08</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:03</v>
+        <v>2:38</v>
       </c>
       <c r="H72" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-08</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:41</v>
+        <v>3:10</v>
       </c>
       <c r="H73" t="str">
-        <v>ERNEST</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-08</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:05</v>
+        <v>3:57</v>
       </c>
       <c r="H74" t="str">
-        <v>Labrinth</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-08</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:46</v>
+        <v>2:19</v>
       </c>
       <c r="H75" t="str">
-        <v>Grace VanderWaal</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-08</v>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:32</v>
+        <v>4:04</v>
       </c>
       <c r="H76" t="str">
-        <v>VOILÀ</v>
+        <v>India Martínez</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-08</v>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:42</v>
+        <v>2:16</v>
       </c>
       <c r="H77" t="str">
-        <v>Cannons</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-08</v>
@@ -3342,10 +3342,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:38</v>
+        <v>5:58</v>
       </c>
       <c r="H78" t="str">
-        <v>Kylie Morgan</v>
+        <v>TINI</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B79" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-08</v>
@@ -3380,10 +3380,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:10</v>
+        <v>3:26</v>
       </c>
       <c r="H79" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Charley</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-08</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:57</v>
+        <v>4:05</v>
       </c>
       <c r="H80" t="str">
-        <v>Willie Nelson</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-08</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:19</v>
+        <v>3:16</v>
       </c>
       <c r="H81" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-08</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>4:04</v>
+        <v>3:14</v>
       </c>
       <c r="H82" t="str">
-        <v>India Martínez</v>
+        <v>Beck</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B83" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-08</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:16</v>
+        <v>2:57</v>
       </c>
       <c r="H83" t="str">
-        <v>Chelsea Cutler</v>
+        <v>The Offspring</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B84" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-08</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>5:58</v>
+        <v>4:10</v>
       </c>
       <c r="H84" t="str">
-        <v>TINI</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B85" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-08</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:26</v>
+        <v>2:10</v>
       </c>
       <c r="H85" t="str">
-        <v>Charley</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B86" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-08</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:05</v>
+        <v>3:52</v>
       </c>
       <c r="H86" t="str">
-        <v>Demi Lovato</v>
+        <v>lights</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-08</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:16</v>
+        <v>3:50</v>
       </c>
       <c r="H87" t="str">
-        <v>Teddy Swims</v>
+        <v>Telenova</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B88" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-08</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:14</v>
+        <v>5:32</v>
       </c>
       <c r="H88" t="str">
-        <v>Beck</v>
+        <v>Marcin</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-08</v>
@@ -3760,10 +3760,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:57</v>
+        <v>4:27</v>
       </c>
       <c r="H89" t="str">
-        <v>The Offspring</v>
+        <v>We Three</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-08</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:10</v>
+        <v>3:01</v>
       </c>
       <c r="H90" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B91" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-08</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:10</v>
+        <v>3:20</v>
       </c>
       <c r="H91" t="str">
-        <v>Jason Derulo</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-08</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:52</v>
+        <v>3:34</v>
       </c>
       <c r="H92" t="str">
-        <v>lights</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-08</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:50</v>
+        <v>4:01</v>
       </c>
       <c r="H93" t="str">
-        <v>Telenova</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B94" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-08</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>5:32</v>
+        <v>3:24</v>
       </c>
       <c r="H94" t="str">
-        <v>Marcin</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-08</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:27</v>
+        <v>5:52</v>
       </c>
       <c r="H95" t="str">
-        <v>We Three</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B96" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-08</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:01</v>
+        <v>5:01</v>
       </c>
       <c r="H96" t="str">
-        <v>Timebelle Official</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B97" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-08</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:20</v>
+        <v>4:12</v>
       </c>
       <c r="H97" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-08</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:34</v>
+        <v>3:59</v>
       </c>
       <c r="H98" t="str">
-        <v>Clinton Kane</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-08</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:01</v>
+        <v>2:56</v>
       </c>
       <c r="H99" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-08</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:24</v>
+        <v>3:46</v>
       </c>
       <c r="H100" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-08</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>5:52</v>
+        <v>4:37</v>
       </c>
       <c r="H101" t="str">
-        <v>Harry Styles</v>
+        <v>Bella White</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Die For Me</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-08</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G102" t="str">
-        <v>5:01</v>
+        <v>3:00</v>
       </c>
       <c r="H102" t="str">
-        <v>Neal Francis</v>
+        <v>ZAYN</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
       </c>
       <c r="L102" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Die For Me - ZAYN</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Two Six</v>
       </c>
       <c r="B103" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://music.apple.com/us/song/two-six/1875080974</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-08</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2 weeks ago</v>
+        <v>The Fall-Off</v>
       </c>
       <c r="G103" t="str">
-        <v>4:12</v>
+        <v>3:16</v>
       </c>
       <c r="H103" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>J. Cole</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/two-six/1875080726</v>
       </c>
       <c r="L103" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Two Six - J. Cole</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Dracula (JENNIE Remix)</v>
       </c>
       <c r="B104" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-08</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>2 weeks ago</v>
+        <v>Dracula (Remix) - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:59</v>
+        <v>3:29</v>
       </c>
       <c r="H104" t="str">
-        <v>Holly Humberstone</v>
+        <v>Tame Impala</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
       </c>
       <c r="L104" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Dracula (JENNIE Remix) - Tame Impala</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Hotel California</v>
       </c>
       <c r="B105" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-08</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>2 weeks ago</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G105" t="str">
-        <v>2:56</v>
+        <v>2:08</v>
       </c>
       <c r="H105" t="str">
-        <v>Cliff Richard</v>
+        <v>Joji</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
       </c>
       <c r="L105" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Hotel California - Joji</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Homewrecker</v>
       </c>
       <c r="B106" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-08</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>2 weeks ago</v>
+        <v>Homewrecker - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:46</v>
+        <v>3:29</v>
       </c>
       <c r="H106" t="str">
-        <v>Jessie Ware</v>
+        <v>sombr</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
       </c>
       <c r="L106" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Homewrecker - sombr</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Might Just</v>
       </c>
       <c r="B107" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://music.apple.com/us/song/might-just/1858755211</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-08</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>2 weeks ago</v>
+        <v>Do You Still Love Me?</v>
       </c>
       <c r="G107" t="str">
-        <v>4:37</v>
+        <v>3:43</v>
       </c>
       <c r="H107" t="str">
-        <v>Bella White</v>
+        <v>Ella Mai</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/might-just/1858754868</v>
       </c>
       <c r="L107" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Might Just - Ella Mai</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Die For Me</v>
+        <v>Cloud 9</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
+        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-08</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>KONNAKOL</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G108" t="str">
-        <v>3:00</v>
+        <v>3:33</v>
       </c>
       <c r="H108" t="str">
-        <v>ZAYN</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
+        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
       </c>
       <c r="L108" t="str">
-        <v>Die For Me - ZAYN</v>
+        <v>Cloud 9 - Megan Moroney</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Two Six</v>
+        <v>Cry</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/two-six/1875080974</v>
+        <v>https://music.apple.com/us/song/cry/1845189974</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-08</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>The Fall-Off</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G109" t="str">
-        <v>3:16</v>
+        <v>3:07</v>
       </c>
       <c r="H109" t="str">
-        <v>J. Cole</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/two-six/1875080726</v>
+        <v>https://music.apple.com/us/album/cry/1845189970</v>
       </c>
       <c r="L109" t="str">
-        <v>Two Six - J. Cole</v>
+        <v>Cry - Charlie Puth</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Dracula (JENNIE Remix)</v>
+        <v>I'll Change for You</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
+        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-08</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Dracula (Remix) - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G110" t="str">
-        <v>3:29</v>
+        <v>3:16</v>
       </c>
       <c r="H110" t="str">
-        <v>Tame Impala</v>
+        <v>Mitski</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
+        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
       </c>
       <c r="L110" t="str">
-        <v>Dracula (JENNIE Remix) - Tame Impala</v>
+        <v>I'll Change for You - Mitski</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Hotel California</v>
+        <v>ASSIGNMENT</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
+        <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-08</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Piss In The Wind</v>
+        <v>ASSIGNMENT - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>2:08</v>
+        <v>2:23</v>
       </c>
       <c r="H111" t="str">
-        <v>Joji</v>
+        <v>Power Snatch</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
+        <v>https://music.apple.com/us/album/assignment/1872764438</v>
       </c>
       <c r="L111" t="str">
-        <v>Hotel California - Joji</v>
+        <v>ASSIGNMENT - Power Snatch</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Homewrecker</v>
+        <v>Como en el Idilio</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
+        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-08</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Homewrecker - Single</v>
+        <v>Como en el Idilio - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:29</v>
+        <v>4:27</v>
       </c>
       <c r="H112" t="str">
-        <v>sombr</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
+        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
+        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
       </c>
       <c r="L112" t="str">
-        <v>Homewrecker - sombr</v>
+        <v>Como en el Idilio - Marc Anthony</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Might Just</v>
+        <v>golden boy</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/might-just/1858755211</v>
+        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-08</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Do You Still Love Me?</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G113" t="str">
-        <v>3:43</v>
+        <v>3:17</v>
       </c>
       <c r="H113" t="str">
-        <v>Ella Mai</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/might-just/1858754868</v>
+        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
       </c>
       <c r="L113" t="str">
-        <v>Might Just - Ella Mai</v>
+        <v>golden boy - Freya Skye</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Cloud 9</v>
+        <v>Penny in the Lake</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
+        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-08</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Cloud 9</v>
+        <v>Singin’ to an Empty Chair</v>
       </c>
       <c r="G114" t="str">
-        <v>3:33</v>
+        <v>3:51</v>
       </c>
       <c r="H114" t="str">
-        <v>Megan Moroney</v>
+        <v>Ratboys</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
+        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
       </c>
       <c r="L114" t="str">
-        <v>Cloud 9 - Megan Moroney</v>
+        <v>Penny in the Lake - Ratboys</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Cry</v>
+        <v>Heaven</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/cry/1845189974</v>
+        <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-08</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G115" t="str">
-        <v>3:07</v>
+        <v>4:26</v>
       </c>
       <c r="H115" t="str">
-        <v>Charlie Puth</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/cry/1845189970</v>
+        <v>https://music.apple.com/us/album/heaven/1862570378</v>
       </c>
       <c r="L115" t="str">
-        <v>Cry - Charlie Puth</v>
+        <v>Heaven - Arlo Parks</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>I'll Change for You</v>
+        <v>Adrenaline</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
+        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-08</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>GOLDEN HOUR : Part.4 - EP</v>
       </c>
       <c r="G116" t="str">
-        <v>3:16</v>
+        <v>3:39</v>
       </c>
       <c r="H116" t="str">
-        <v>Mitski</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
+        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
       </c>
       <c r="L116" t="str">
-        <v>I'll Change for You - Mitski</v>
+        <v>Adrenaline - ATEEZ</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ASSIGNMENT</v>
+        <v>Sweet To Me</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/assignment/1872764440</v>
+        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-08</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>ASSIGNMENT - Single</v>
+        <v>Sunday Best</v>
       </c>
       <c r="G117" t="str">
-        <v>2:23</v>
+        <v>4:17</v>
       </c>
       <c r="H117" t="str">
-        <v>Power Snatch</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/assignment/1872764438</v>
+        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
       </c>
       <c r="L117" t="str">
-        <v>ASSIGNMENT - Power Snatch</v>
+        <v>Sweet To Me - Nick Jonas</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Como en el Idilio</v>
+        <v>Time Goes On</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
+        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-08</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Como en el Idilio - Single</v>
+        <v>Time Goes On - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>4:27</v>
+        <v>2:55</v>
       </c>
       <c r="H118" t="str">
-        <v>Marc Anthony</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
+        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
       </c>
       <c r="L118" t="str">
-        <v>Como en el Idilio - Marc Anthony</v>
+        <v>Time Goes On - Koe Wetzel</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>golden boy</v>
+        <v>Drive Safe</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
+        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-08</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>stardust - EP</v>
+        <v>Drive Safe - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H119" t="str">
-        <v>Freya Skye</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
+        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
       </c>
       <c r="L119" t="str">
-        <v>golden boy - Freya Skye</v>
+        <v>Drive Safe - Myles Smith</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Penny in the Lake</v>
+        <v>Love To Be Loved</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
+        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-08</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Singin’ to an Empty Chair</v>
+        <v>Love To Be Loved - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:51</v>
+        <v>2:50</v>
       </c>
       <c r="H120" t="str">
-        <v>Ratboys</v>
+        <v>The Warning</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
+        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
       </c>
       <c r="L120" t="str">
-        <v>Penny in the Lake - Ratboys</v>
+        <v>Love To Be Loved - The Warning</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Heaven</v>
+        <v>Mi Yo de Antes</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/heaven/1862570892</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-08</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Mi Yo de Antes - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:26</v>
+        <v>3:02</v>
       </c>
       <c r="H121" t="str">
-        <v>Arlo Parks</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/heaven/1862570378</v>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
       </c>
       <c r="L121" t="str">
-        <v>Heaven - Arlo Parks</v>
+        <v>Mi Yo de Antes - Eden Muñoz</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Adrenaline</v>
+        <v>Omens</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
+        <v>https://music.apple.com/us/song/omens/1872546206</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-08</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>GOLDEN HOUR : Part.4 - EP</v>
+        <v>Omens - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:39</v>
+        <v>2:00</v>
       </c>
       <c r="H122" t="str">
-        <v>ATEEZ</v>
+        <v>EsDeeKid</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
+        <v>https://music.apple.com/us/album/omens/1872546204</v>
       </c>
       <c r="L122" t="str">
-        <v>Adrenaline - ATEEZ</v>
+        <v>Omens - EsDeeKid</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Sweet To Me</v>
+        <v>My Regards</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
+        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-08</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Sunday Best</v>
+        <v>Florescence</v>
       </c>
       <c r="G123" t="str">
-        <v>4:17</v>
+        <v>3:11</v>
       </c>
       <c r="H123" t="str">
-        <v>Nick Jonas</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
+        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
       </c>
       <c r="L123" t="str">
-        <v>Sweet To Me - Nick Jonas</v>
+        <v>My Regards - Maisie Peters</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Time Goes On</v>
+        <v>Time After Time</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
+        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-08</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Time Goes On - Single</v>
+        <v>Time After Time - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:55</v>
+        <v>2:48</v>
       </c>
       <c r="H124" t="str">
-        <v>Koe Wetzel</v>
+        <v>EJAE</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
+        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
       </c>
       <c r="L124" t="str">
-        <v>Time Goes On - Koe Wetzel</v>
+        <v>Time After Time - EJAE</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Drive Safe</v>
+        <v>Don't Want Your Love</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
+        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-08</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Drive Safe - Single</v>
+        <v>ODYSSEY</v>
       </c>
       <c r="G125" t="str">
-        <v>3:21</v>
+        <v>3:12</v>
       </c>
       <c r="H125" t="str">
-        <v>Myles Smith</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
+        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
       </c>
       <c r="L125" t="str">
-        <v>Drive Safe - Myles Smith</v>
+        <v>Don't Want Your Love - ILLENIUM</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Love To Be Loved</v>
+        <v>Pa' Los Envidiosos</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
+        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-08</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Love To Be Loved - Single</v>
+        <v>Pa' Los Envidiosos - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:50</v>
+        <v>3:37</v>
       </c>
       <c r="H126" t="str">
-        <v>The Warning</v>
+        <v>Pitbull</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
+        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
       </c>
       <c r="L126" t="str">
-        <v>Love To Be Loved - The Warning</v>
+        <v>Pa' Los Envidiosos - Pitbull</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Mi Yo de Antes</v>
+        <v>Plei</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
+        <v>https://music.apple.com/us/song/plei/1872137577</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-08</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Mi Yo de Antes - Single</v>
+        <v>Plei - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:02</v>
+        <v>3:22</v>
       </c>
       <c r="H127" t="str">
-        <v>Eden Muñoz</v>
+        <v>Chuwi</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
+        <v>https://music.apple.com/us/album/plei/1872137372</v>
       </c>
       <c r="L127" t="str">
-        <v>Mi Yo de Antes - Eden Muñoz</v>
+        <v>Plei - Chuwi</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Omens</v>
+        <v>Flood (feat. Bon Iver)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/omens/1872546206</v>
+        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-08</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Omens - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G128" t="str">
-        <v>2:00</v>
+        <v>2:59</v>
       </c>
       <c r="H128" t="str">
-        <v>EsDeeKid</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/omens/1872546204</v>
+        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
       </c>
       <c r="L128" t="str">
-        <v>Omens - EsDeeKid</v>
+        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>My Regards</v>
+        <v>Rain</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
+        <v>https://music.apple.com/us/song/rain/1867258289</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-08</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Florescence</v>
+        <v>Rain - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:11</v>
+        <v>3:28</v>
       </c>
       <c r="H129" t="str">
-        <v>Maisie Peters</v>
+        <v>FISHER</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
+        <v>https://music.apple.com/us/album/rain/1867258288</v>
       </c>
       <c r="L129" t="str">
-        <v>My Regards - Maisie Peters</v>
+        <v>Rain - FISHER</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Time After Time</v>
+        <v>Release The Pressure</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
+        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-08</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Time After Time - Single</v>
+        <v>Release The Pressure - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:48</v>
+        <v>3:23</v>
       </c>
       <c r="H130" t="str">
-        <v>EJAE</v>
+        <v>Calvin Harris</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
+        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
+        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
       </c>
       <c r="L130" t="str">
-        <v>Time After Time - EJAE</v>
+        <v>Release The Pressure - Calvin Harris</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Don't Want Your Love</v>
+        <v>Sexistential (Arca’s Take)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
+        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-08</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>ODYSSEY</v>
+        <v>Sexistential (Arca’s Take) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:12</v>
+        <v>3:44</v>
       </c>
       <c r="H131" t="str">
-        <v>ILLENIUM</v>
+        <v>Robyn</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
+        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
       </c>
       <c r="L131" t="str">
-        <v>Don't Want Your Love - ILLENIUM</v>
+        <v>Sexistential (Arca’s Take) - Robyn</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Pa' Los Envidiosos</v>
+        <v>heal something</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
+        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-08</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Pa' Los Envidiosos - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G132" t="str">
-        <v>3:37</v>
+        <v>3:01</v>
       </c>
       <c r="H132" t="str">
-        <v>Pitbull</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
+        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
       </c>
       <c r="L132" t="str">
-        <v>Pa' Los Envidiosos - Pitbull</v>
+        <v>heal something - Sasha Keable</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Plei</v>
+        <v>Buenos Días</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/plei/1872137577</v>
+        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-08</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Plei - Single</v>
+        <v>Buenos Días - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:22</v>
+        <v>2:39</v>
       </c>
       <c r="H133" t="str">
-        <v>Chuwi</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/plei/1872137372</v>
+        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
       </c>
       <c r="L133" t="str">
-        <v>Plei - Chuwi</v>
+        <v>Buenos Días - Eladio Carrión</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Flood (feat. Bon Iver)</v>
+        <v>COOK</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
+        <v>https://music.apple.com/us/song/cook/1872816147</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-08</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>COOK - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:59</v>
+        <v>2:50</v>
       </c>
       <c r="H134" t="str">
-        <v>Dua Saleh</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
+        <v>https://music.apple.com/us/album/cook/1872816146</v>
       </c>
       <c r="L134" t="str">
-        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
+        <v>COOK - SOFI TUKKER</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Rain</v>
+        <v>You Got to Lose</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/rain/1867258289</v>
+        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-08</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Rain - Single</v>
+        <v>Peaches!</v>
       </c>
       <c r="G135" t="str">
-        <v>3:28</v>
+        <v>3:17</v>
       </c>
       <c r="H135" t="str">
-        <v>FISHER</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/rain/1867258288</v>
+        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
       </c>
       <c r="L135" t="str">
-        <v>Rain - FISHER</v>
+        <v>You Got to Lose - The Black Keys</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Release The Pressure</v>
+        <v>Different Kind Of Love</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
+        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-08</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Release The Pressure - Single</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G136" t="str">
-        <v>3:23</v>
+        <v>3:39</v>
       </c>
       <c r="H136" t="str">
-        <v>Calvin Harris</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
+        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
       </c>
       <c r="L136" t="str">
-        <v>Release The Pressure - Calvin Harris</v>
+        <v>Different Kind Of Love - Young the Giant</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Sexistential (Arca’s Take)</v>
+        <v>Living Water</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
+        <v>https://music.apple.com/us/song/living-water/1871565262</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-08</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Sexistential (Arca’s Take) - Single</v>
+        <v>Reconstruction: Second Story</v>
       </c>
       <c r="G137" t="str">
-        <v>3:44</v>
+        <v>2:09</v>
       </c>
       <c r="H137" t="str">
-        <v>Robyn</v>
+        <v>Lecrae</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
+        <v>https://music.apple.com/us/album/living-water/1871564892</v>
       </c>
       <c r="L137" t="str">
-        <v>Sexistential (Arca’s Take) - Robyn</v>
+        <v>Living Water - Lecrae</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>heal something</v>
+        <v>What It Feels Like</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
+        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-08</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>ACT II</v>
+        <v>What It Feels Like - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:01</v>
+        <v>2:18</v>
       </c>
       <c r="H138" t="str">
-        <v>Sasha Keable</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
+        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
       </c>
       <c r="L138" t="str">
-        <v>heal something - Sasha Keable</v>
+        <v>What It Feels Like - Dillon Francis</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Buenos Días</v>
+        <v>neck</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
+        <v>https://music.apple.com/us/song/neck/1866953832</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-08</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Buenos Días - Single</v>
+        <v>neck - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:39</v>
+        <v>3:40</v>
       </c>
       <c r="H139" t="str">
-        <v>Eladio Carrión</v>
+        <v>Mau P</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
+        <v>https://music.apple.com/us/album/neck/1866953831</v>
       </c>
       <c r="L139" t="str">
-        <v>Buenos Días - Eladio Carrión</v>
+        <v>neck - Mau P</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>COOK</v>
+        <v>Colorblind</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/cook/1872816147</v>
+        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-08</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>COOK - Single</v>
+        <v>Colorblind - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:50</v>
+        <v>2:56</v>
       </c>
       <c r="H140" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/cook/1872816146</v>
+        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
       </c>
       <c r="L140" t="str">
-        <v>COOK - SOFI TUKKER</v>
+        <v>Colorblind - Gavin Adcock</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>You Got to Lose</v>
+        <v>Au Revoir Reservoir</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
+        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-08</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Peaches!</v>
+        <v>Tenterhooks</v>
       </c>
       <c r="G141" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H141" t="str">
-        <v>The Black Keys</v>
+        <v>Silversun Pickups</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
+        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
       </c>
       <c r="L141" t="str">
-        <v>You Got to Lose - The Black Keys</v>
+        <v>Au Revoir Reservoir - Silversun Pickups</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Different Kind Of Love</v>
+        <v>Flavorless</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
+        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-08</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Victory Garden</v>
+        <v>Flavorless - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:39</v>
+        <v>3:31</v>
       </c>
       <c r="H142" t="str">
-        <v>Young the Giant</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
+        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
       </c>
       <c r="L142" t="str">
-        <v>Different Kind Of Love - Young the Giant</v>
+        <v>Flavorless - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Living Water</v>
+        <v>Nunca</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/living-water/1871565262</v>
+        <v>https://music.apple.com/us/song/nunca/1860691713</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-08</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Reconstruction: Second Story</v>
+        <v>ESCENAS</v>
       </c>
       <c r="G143" t="str">
-        <v>2:09</v>
+        <v>3:05</v>
       </c>
       <c r="H143" t="str">
-        <v>Lecrae</v>
+        <v>Sin Bandera</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
+        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/living-water/1871564892</v>
+        <v>https://music.apple.com/us/album/nunca/1860691704</v>
       </c>
       <c r="L143" t="str">
-        <v>Living Water - Lecrae</v>
+        <v>Nunca - Sin Bandera</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>What It Feels Like</v>
+        <v>Just In Case</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
+        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-08</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>What It Feels Like - Single</v>
+        <v>NO HArD FEELINGS (Deluxe)</v>
       </c>
       <c r="G144" t="str">
-        <v>2:18</v>
+        <v>1:45</v>
       </c>
       <c r="H144" t="str">
-        <v>Dillon Francis</v>
+        <v>Marc E. Bassy</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
+        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
       </c>
       <c r="L144" t="str">
-        <v>What It Feels Like - Dillon Francis</v>
+        <v>Just In Case - Marc E. Bassy</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>neck</v>
+        <v>Thinking of You</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/neck/1866953832</v>
+        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-08</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>neck - Single</v>
+        <v>Thinking of You - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:40</v>
+        <v>3:00</v>
       </c>
       <c r="H145" t="str">
-        <v>Mau P</v>
+        <v>AP Dhillon</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
+        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/neck/1866953831</v>
+        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
       </c>
       <c r="L145" t="str">
-        <v>neck - Mau P</v>
+        <v>Thinking of You - AP Dhillon</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Colorblind</v>
+        <v>House Of Cards</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
+        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-08</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Colorblind - Single</v>
+        <v>House of Cards</v>
       </c>
       <c r="G146" t="str">
-        <v>2:56</v>
+        <v>3:26</v>
       </c>
       <c r="H146" t="str">
-        <v>Gavin Adcock</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
+        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
       </c>
       <c r="L146" t="str">
-        <v>Colorblind - Gavin Adcock</v>
+        <v>House Of Cards - The Amity Affliction</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Au Revoir Reservoir</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-08</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Tenterhooks</v>
+        <v>Stay With Me - Single</v>
       </c>
       <c r="G147" t="str">
         <v>3:21</v>
       </c>
       <c r="H147" t="str">
-        <v>Silversun Pickups</v>
+        <v>Agents Of Time</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
+        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
       </c>
       <c r="L147" t="str">
-        <v>Au Revoir Reservoir - Silversun Pickups</v>
+        <v>Stay With Me - Agents Of Time</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Flavorless</v>
+        <v>I had a dream...</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-08</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Flavorless - Single</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G148" t="str">
-        <v>3:31</v>
+        <v>2:39</v>
       </c>
       <c r="H148" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>R3HAB</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
       </c>
       <c r="L148" t="str">
-        <v>Flavorless - Dexter and The Moonrocks</v>
+        <v>I had a dream... - R3HAB</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Nunca</v>
+        <v>Back to You</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/nunca/1860691713</v>
+        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-08</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>ESCENAS</v>
+        <v>Satellite</v>
       </c>
       <c r="G149" t="str">
-        <v>3:05</v>
+        <v>3:10</v>
       </c>
       <c r="H149" t="str">
-        <v>Sin Bandera</v>
+        <v>Charlotte Sands</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
+        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/nunca/1860691704</v>
+        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
       </c>
       <c r="L149" t="str">
-        <v>Nunca - Sin Bandera</v>
+        <v>Back to You - Charlotte Sands</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Just In Case</v>
+        <v>rager</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
+        <v>https://music.apple.com/us/song/rager/1872808801</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-08</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>NO HArD FEELINGS (Deluxe)</v>
+        <v>rager</v>
       </c>
       <c r="G150" t="str">
-        <v>1:45</v>
+        <v>2:48</v>
       </c>
       <c r="H150" t="str">
-        <v>Marc E. Bassy</v>
+        <v>Blusher</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
+        <v>https://music.apple.com/us/artist/blusher/485578161</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
+        <v>https://music.apple.com/us/album/rager/1872808800</v>
       </c>
       <c r="L150" t="str">
-        <v>Just In Case - Marc E. Bassy</v>
+        <v>rager - Blusher</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Thinking of You</v>
+        <v>If Only</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
+        <v>https://music.apple.com/us/song/if-only/1870281318</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-08</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Thinking of You - Single</v>
+        <v>Patchwork</v>
       </c>
       <c r="G151" t="str">
-        <v>3:00</v>
+        <v>3:28</v>
       </c>
       <c r="H151" t="str">
-        <v>AP Dhillon</v>
+        <v>Charlotte Day Wilson</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
+        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
+        <v>https://music.apple.com/us/album/if-only/1870281314</v>
       </c>
       <c r="L151" t="str">
-        <v>Thinking of You - AP Dhillon</v>
+        <v>If Only - Charlotte Day Wilson</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>House Of Cards</v>
+        <v>DON'T LOVE ME</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
+        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-08</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>House of Cards</v>
+        <v>DON'T LOVE ME - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:26</v>
+        <v>3:01</v>
       </c>
       <c r="H152" t="str">
-        <v>The Amity Affliction</v>
+        <v>Omah Lay</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
+        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
+        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
       </c>
       <c r="L152" t="str">
-        <v>House Of Cards - The Amity Affliction</v>
+        <v>DON'T LOVE ME - Omah Lay</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Stay With Me</v>
+        <v>No Sikes, No Tradesies</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
+        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-08</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Stay With Me - Single</v>
+        <v>Sweet Nothings</v>
       </c>
       <c r="G153" t="str">
-        <v>3:21</v>
+        <v>2:32</v>
       </c>
       <c r="H153" t="str">
-        <v>Agents Of Time</v>
+        <v>Jaymin</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
+        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
+        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
       </c>
       <c r="L153" t="str">
-        <v>Stay With Me - Agents Of Time</v>
+        <v>No Sikes, No Tradesies - Jaymin</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>I had a dream...</v>
+        <v>you woke me up</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
+        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-08</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Dream inside a dream…</v>
+        <v>you woke me up - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:39</v>
+        <v>3:14</v>
       </c>
       <c r="H154" t="str">
-        <v>R3HAB</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
+        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
       </c>
       <c r="L154" t="str">
-        <v>I had a dream... - R3HAB</v>
+        <v>you woke me up - Kevian Kraemer</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Back to You</v>
+        <v>No One’s Business</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
+        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-08</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Satellite</v>
+        <v>No One’s Business - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:10</v>
+        <v>3:00</v>
       </c>
       <c r="H155" t="str">
-        <v>Charlotte Sands</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
+        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
       </c>
       <c r="L155" t="str">
-        <v>Back to You - Charlotte Sands</v>
+        <v>No One’s Business - Alicia Creti</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>rager</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/rager/1872808801</v>
+        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-08</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>rager</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G156" t="str">
-        <v>2:48</v>
+        <v>3:13</v>
       </c>
       <c r="H156" t="str">
-        <v>Blusher</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/blusher/485578161</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/rager/1872808800</v>
+        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L156" t="str">
-        <v>rager - Blusher</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>If Only</v>
+        <v>TWICE</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/if-only/1870281318</v>
+        <v>https://music.apple.com/us/song/twice/1871578107</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-08</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Patchwork</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G157" t="str">
-        <v>3:28</v>
+        <v>3:44</v>
       </c>
       <c r="H157" t="str">
-        <v>Charlotte Day Wilson</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/if-only/1870281314</v>
+        <v>https://music.apple.com/us/album/twice/1871578103</v>
       </c>
       <c r="L157" t="str">
-        <v>If Only - Charlotte Day Wilson</v>
+        <v>TWICE - Bilmuri</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>DON'T LOVE ME</v>
+        <v>ROOFTOP</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
+        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-08</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>DON'T LOVE ME - Single</v>
+        <v>ROOFTOP - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:01</v>
+        <v>3:22</v>
       </c>
       <c r="H158" t="str">
-        <v>Omah Lay</v>
+        <v>Hulvey</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
+        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
       </c>
       <c r="L158" t="str">
-        <v>DON'T LOVE ME - Omah Lay</v>
+        <v>ROOFTOP - Hulvey</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>No Sikes, No Tradesies</v>
+        <v>Louisiana Rain</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
+        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-08</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Sweet Nothings</v>
+        <v>Louisiana Rain - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:32</v>
+        <v>3:41</v>
       </c>
       <c r="H159" t="str">
-        <v>Jaymin</v>
+        <v>Hunter Plake</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
+        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
+        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
       </c>
       <c r="L159" t="str">
-        <v>No Sikes, No Tradesies - Jaymin</v>
+        <v>Louisiana Rain - Hunter Plake</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>you woke me up</v>
+        <v>sharing Jesus with an ex</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
+        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-08</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>you woke me up - Single</v>
+        <v>sharing Jesus with an ex - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:14</v>
+        <v>1:55</v>
       </c>
       <c r="H160" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
+        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
       </c>
       <c r="L160" t="str">
-        <v>you woke me up - Kevian Kraemer</v>
+        <v>sharing Jesus with an ex - Zoe Levert</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>No One’s Business</v>
+        <v>Body Control (feat. CHILLS)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
+        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-08</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>No One’s Business - Single</v>
+        <v>Body Control (feat. CHILLS) - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:00</v>
+        <v>3:21</v>
       </c>
       <c r="H161" t="str">
-        <v>Alicia Creti</v>
+        <v>Cole Knight</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
+        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
+        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
       </c>
       <c r="L161" t="str">
-        <v>No One’s Business - Alicia Creti</v>
+        <v>Body Control (feat. CHILLS) - Cole Knight</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
+        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-08</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>A Prayer for the Dancefloor - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:13</v>
+        <v>6:54</v>
       </c>
       <c r="H162" t="str">
-        <v>Bryant Barnes</v>
+        <v>Charlotte de Witte</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
+        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
       </c>
       <c r="L162" t="str">
-        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>TWICE</v>
+        <v>Realm of Endless Misery</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/twice/1871578107</v>
+        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-08</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>KINDA HARD</v>
+        <v>Liturgy of Death</v>
       </c>
       <c r="G163" t="str">
-        <v>3:44</v>
+        <v>4:56</v>
       </c>
       <c r="H163" t="str">
-        <v>Bilmuri</v>
+        <v>Mayhem</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/twice/1871578103</v>
+        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
       </c>
       <c r="L163" t="str">
-        <v>TWICE - Bilmuri</v>
+        <v>Realm of Endless Misery - Mayhem</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>ROOFTOP</v>
+        <v>BLEACH</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
+        <v>https://music.apple.com/us/song/bleach/1869795882</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-08</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>ROOFTOP - Single</v>
+        <v>BLEACH - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:22</v>
+        <v>2:28</v>
       </c>
       <c r="H164" t="str">
-        <v>Hulvey</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
+        <v>https://music.apple.com/us/album/bleach/1869795874</v>
       </c>
       <c r="L164" t="str">
-        <v>ROOFTOP - Hulvey</v>
+        <v>BLEACH - Ecca Vandal</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Louisiana Rain</v>
+        <v>pretty in pink</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
+        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-08</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Louisiana Rain - Single</v>
+        <v>AngelPink</v>
       </c>
       <c r="G165" t="str">
-        <v>3:41</v>
+        <v>3:13</v>
       </c>
       <c r="H165" t="str">
-        <v>Hunter Plake</v>
+        <v>Keni Titus</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
+        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
+        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
       </c>
       <c r="L165" t="str">
-        <v>Louisiana Rain - Hunter Plake</v>
+        <v>pretty in pink - Keni Titus</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>sharing Jesus with an ex</v>
+        <v>Pickup Man</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
+        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-08</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>sharing Jesus with an ex - Single</v>
+        <v>Pickup Man - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>1:55</v>
+        <v>3:28</v>
       </c>
       <c r="H166" t="str">
-        <v>Zoe Levert</v>
+        <v>Bayker Blankenship</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
+        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
       </c>
       <c r="L166" t="str">
-        <v>sharing Jesus with an ex - Zoe Levert</v>
+        <v>Pickup Man - Bayker Blankenship</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Body Control (feat. CHILLS)</v>
+        <v>Get To Drinkin'</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
+        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-08</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Body Control (feat. CHILLS) - Single</v>
+        <v>Get To Drinkin' - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:21</v>
+        <v>2:48</v>
       </c>
       <c r="H167" t="str">
-        <v>Cole Knight</v>
+        <v>Zach John King</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
+        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
+        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
       </c>
       <c r="L167" t="str">
-        <v>Body Control (feat. CHILLS) - Cole Knight</v>
+        <v>Get To Drinkin' - Zach John King</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
+        <v>The Roses</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
+        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-08</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>A Prayer for the Dancefloor - Single</v>
+        <v>The Roses - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>6:54</v>
+        <v>3:02</v>
       </c>
       <c r="H168" t="str">
-        <v>Charlotte de Witte</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
+        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
+        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
       </c>
       <c r="L168" t="str">
-        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
+        <v>The Roses - Russell Dickerson</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Realm of Endless Misery</v>
+        <v>I Should Know Better</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
+        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-08</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Liturgy of Death</v>
+        <v>Under The Streetlights</v>
       </c>
       <c r="G169" t="str">
-        <v>4:56</v>
+        <v>3:33</v>
       </c>
       <c r="H169" t="str">
-        <v>Mayhem</v>
+        <v>Michael Marcagi</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
+        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
+        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
       </c>
       <c r="L169" t="str">
-        <v>Realm of Endless Misery - Mayhem</v>
+        <v>I Should Know Better - Michael Marcagi</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>BLEACH</v>
+        <v>Never Do</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/bleach/1869795882</v>
+        <v>https://music.apple.com/us/song/never-do/1872842226</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-08</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>BLEACH - Single</v>
+        <v>Never Do - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:28</v>
+        <v>1:58</v>
       </c>
       <c r="H170" t="str">
-        <v>Ecca Vandal</v>
+        <v>charlieonnafriday</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/bleach/1869795874</v>
+        <v>https://music.apple.com/us/album/never-do/1872842225</v>
       </c>
       <c r="L170" t="str">
-        <v>BLEACH - Ecca Vandal</v>
+        <v>Never Do - charlieonnafriday</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>pretty in pink</v>
+        <v>Primary Colors</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
+        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-08</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>AngelPink</v>
+        <v>Lost on You</v>
       </c>
       <c r="G171" t="str">
-        <v>3:13</v>
+        <v>3:37</v>
       </c>
       <c r="H171" t="str">
-        <v>Keni Titus</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
+        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
       </c>
       <c r="L171" t="str">
-        <v>pretty in pink - Keni Titus</v>
+        <v>Primary Colors - Tigers Jaw</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Pickup Man</v>
+        <v>Rock Bottom</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-08</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Pickup Man - Single</v>
+        <v>Rock Bottom / Octopus - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:28</v>
+        <v>4:10</v>
       </c>
       <c r="H172" t="str">
-        <v>Bayker Blankenship</v>
+        <v>King Krule</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
+        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
       </c>
       <c r="L172" t="str">
-        <v>Pickup Man - Bayker Blankenship</v>
+        <v>Rock Bottom - King Krule</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Get To Drinkin'</v>
+        <v>Te Dedico</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
+        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-08</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Get To Drinkin' - Single</v>
+        <v>Te Dedico - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:48</v>
+        <v>3:45</v>
       </c>
       <c r="H173" t="str">
-        <v>Zach John King</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
+        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
+        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
       </c>
       <c r="L173" t="str">
-        <v>Get To Drinkin' - Zach John King</v>
+        <v>Te Dedico - Carlos Vives</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>The Roses</v>
+        <v>AUNQUE SEA EN DOS</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
+        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-08</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>The Roses - Single</v>
+        <v>18</v>
       </c>
       <c r="G174" t="str">
-        <v>3:02</v>
+        <v>2:38</v>
       </c>
       <c r="H174" t="str">
-        <v>Russell Dickerson</v>
+        <v>Conexión Divina</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
+        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
+        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
       </c>
       <c r="L174" t="str">
-        <v>The Roses - Russell Dickerson</v>
+        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>I Should Know Better</v>
+        <v>I Dare You</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
+        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-08</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Under The Streetlights</v>
+        <v>I Dare You - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:33</v>
+        <v>3:25</v>
       </c>
       <c r="H175" t="str">
-        <v>Michael Marcagi</v>
+        <v>Dylan Dunlap</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
+        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
+        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
       </c>
       <c r="L175" t="str">
-        <v>I Should Know Better - Michael Marcagi</v>
+        <v>I Dare You - Dylan Dunlap</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Never Do</v>
+        <v>new irish boyfriend</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/never-do/1872842226</v>
+        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-08</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Never Do - Single</v>
+        <v>long time caller, first time listener</v>
       </c>
       <c r="G176" t="str">
-        <v>1:58</v>
+        <v>3:50</v>
       </c>
       <c r="H176" t="str">
-        <v>charlieonnafriday</v>
+        <v>vegas water taxi</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
+        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/never-do/1872842225</v>
+        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
       </c>
       <c r="L176" t="str">
-        <v>Never Do - charlieonnafriday</v>
+        <v>new irish boyfriend - vegas water taxi</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Primary Colors</v>
+        <v>Everyone Around Me Dancing</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
+        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-08</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Lost on You</v>
+        <v>Singing</v>
       </c>
       <c r="G177" t="str">
-        <v>3:37</v>
+        <v>3:05</v>
       </c>
       <c r="H177" t="str">
-        <v>Tigers Jaw</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
+        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
       </c>
       <c r="L177" t="str">
-        <v>Primary Colors - Tigers Jaw</v>
+        <v>Everyone Around Me Dancing - Gia Margaret</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rock Bottom</v>
+        <v>Good Enough (feat. Julie Doiron)</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
+        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-08</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Rock Bottom / Octopus - Single</v>
+        <v>Big Changes</v>
       </c>
       <c r="G178" t="str">
-        <v>4:10</v>
+        <v>6:05</v>
       </c>
       <c r="H178" t="str">
-        <v>King Krule</v>
+        <v>Status/Non-Status</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
+        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
+        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
       </c>
       <c r="L178" t="str">
-        <v>Rock Bottom - King Krule</v>
+        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Te Dedico</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
+        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-08</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Te Dedico - Single</v>
+        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="G179" t="str">
-        <v>3:45</v>
+        <v>4:09</v>
       </c>
       <c r="H179" t="str">
-        <v>Carlos Vives</v>
+        <v>Julian Lage</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
+        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
+        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
       </c>
       <c r="L179" t="str">
-        <v>Te Dedico - Carlos Vives</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>AUNQUE SEA EN DOS</v>
+        <v>Big Deal</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
+        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-08</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>18</v>
+        <v>Big Deal - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:38</v>
+        <v>3:47</v>
       </c>
       <c r="H180" t="str">
-        <v>Conexión Divina</v>
+        <v>In Color</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
+        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
       </c>
       <c r="L180" t="str">
-        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
+        <v>Big Deal - In Color</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>I Dare You</v>
+        <v>Buy What U Want</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
+        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-08</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>I Dare You - Single</v>
+        <v>Road To Osshland III - EP</v>
       </c>
       <c r="G181" t="str">
-        <v>3:25</v>
+        <v>3:47</v>
       </c>
       <c r="H181" t="str">
-        <v>Dylan Dunlap</v>
+        <v>Black Fortune</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
+        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
+        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
       </c>
       <c r="L181" t="str">
-        <v>I Dare You - Dylan Dunlap</v>
+        <v>Buy What U Want - Black Fortune</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>new irish boyfriend</v>
+        <v>Common Ground</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
+        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-08</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>long time caller, first time listener</v>
+        <v>Common Ground - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:50</v>
+        <v>1:42</v>
       </c>
       <c r="H182" t="str">
-        <v>vegas water taxi</v>
+        <v>ELIO</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
+        <v>https://music.apple.com/us/artist/elio/1501417625</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
+        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
       </c>
       <c r="L182" t="str">
-        <v>new irish boyfriend - vegas water taxi</v>
+        <v>Common Ground - ELIO</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Everyone Around Me Dancing</v>
+        <v>Cellophane</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
+        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-08</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Singing</v>
+        <v>Cellophane - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:05</v>
+        <v>4:21</v>
       </c>
       <c r="H183" t="str">
-        <v>Gia Margaret</v>
+        <v>Maddie Zahm</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
+        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
       </c>
       <c r="L183" t="str">
-        <v>Everyone Around Me Dancing - Gia Margaret</v>
+        <v>Cellophane - Maddie Zahm</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Good Enough (feat. Julie Doiron)</v>
+        <v>96 Camry</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
+        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-08</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Big Changes</v>
+        <v>PRAY FOR ME</v>
       </c>
       <c r="G184" t="str">
-        <v>6:05</v>
+        <v>3:15</v>
       </c>
       <c r="H184" t="str">
-        <v>Status/Non-Status</v>
+        <v>RAAHiiM</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
+        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
+        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
       </c>
       <c r="L184" t="str">
-        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
+        <v>96 Camry - RAAHiiM</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
+        <v>La Allstar</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
+        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-08</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
+        <v>La Allstar - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>4:09</v>
+        <v>2:49</v>
       </c>
       <c r="H185" t="str">
-        <v>Julian Lage</v>
+        <v>ELIKAI</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
+        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
+        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
       </c>
       <c r="L185" t="str">
-        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
+        <v>La Allstar - ELIKAI</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Big Deal</v>
+        <v>Luka</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
+        <v>https://music.apple.com/us/song/luka/1869396162</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-08</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Big Deal - Single</v>
+        <v>Luka - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:47</v>
+        <v>2:07</v>
       </c>
       <c r="H186" t="str">
-        <v>In Color</v>
+        <v>Fonta</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
+        <v>https://music.apple.com/us/album/luka/1869396161</v>
       </c>
       <c r="L186" t="str">
-        <v>Big Deal - In Color</v>
+        <v>Luka - Fonta</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Buy What U Want</v>
+        <v>Ganas De Tenerla</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
+        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-08</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Road To Osshland III - EP</v>
+        <v>Ganas De Tenerla - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:47</v>
+        <v>3:06</v>
       </c>
       <c r="H187" t="str">
-        <v>Black Fortune</v>
+        <v>Silvestre Dangond</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
+        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
+        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
       </c>
       <c r="L187" t="str">
-        <v>Buy What U Want - Black Fortune</v>
+        <v>Ganas De Tenerla - Silvestre Dangond</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Common Ground</v>
+        <v>In My Blue</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
+        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-08</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Common Ground - Single</v>
+        <v>Doomsday...Don't Leave Me Here</v>
       </c>
       <c r="G188" t="str">
-        <v>1:42</v>
+        <v>3:26</v>
       </c>
       <c r="H188" t="str">
-        <v>ELIO</v>
+        <v>Rosie Carney</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/elio/1501417625</v>
+        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
+        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
       </c>
       <c r="L188" t="str">
-        <v>Common Ground - ELIO</v>
+        <v>In My Blue - Rosie Carney</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Cellophane</v>
+        <v>Living With It (feat. Feist)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
+        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-08</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Cellophane - Single</v>
+        <v>Hurts Like Hell</v>
       </c>
       <c r="G189" t="str">
-        <v>4:21</v>
+        <v>3:20</v>
       </c>
       <c r="H189" t="str">
-        <v>Maddie Zahm</v>
+        <v>Charlotte Cornfield</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
+        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
+        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
       </c>
       <c r="L189" t="str">
-        <v>Cellophane - Maddie Zahm</v>
+        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>96 Camry</v>
+        <v>Silently</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
+        <v>https://music.apple.com/us/song/silently/1841629898</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-08</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>PRAY FOR ME</v>
+        <v>Croak Dream</v>
       </c>
       <c r="G190" t="str">
-        <v>3:15</v>
+        <v>3:29</v>
       </c>
       <c r="H190" t="str">
-        <v>RAAHiiM</v>
+        <v>Puma Blue</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
+        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
+        <v>https://music.apple.com/us/album/silently/1841629444</v>
       </c>
       <c r="L190" t="str">
-        <v>96 Camry - RAAHiiM</v>
+        <v>Silently - Puma Blue</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>La Allstar</v>
+        <v>Ashes &amp; Smoke</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
+        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-08</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>La Allstar - Single</v>
+        <v>Ashes &amp; Smoke - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:49</v>
+        <v>3:05</v>
       </c>
       <c r="H191" t="str">
-        <v>ELIKAI</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
+        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
+        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
       </c>
       <c r="L191" t="str">
-        <v>La Allstar - ELIKAI</v>
+        <v>Ashes &amp; Smoke - Anna Graves</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Luka</v>
+        <v>Tormentor</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/luka/1869396162</v>
+        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-08</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Luka - Single</v>
+        <v>The Flowers I See You In - EP</v>
       </c>
       <c r="G192" t="str">
-        <v>2:07</v>
+        <v>2:40</v>
       </c>
       <c r="H192" t="str">
-        <v>Fonta</v>
+        <v>Ninush</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
+        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/luka/1869396161</v>
+        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
       </c>
       <c r="L192" t="str">
-        <v>Luka - Fonta</v>
+        <v>Tormentor - Ninush</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Ganas De Tenerla</v>
+        <v>Red Rocking Chair</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
+        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-08</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Ganas De Tenerla - Single</v>
+        <v>Red Rocking Chair - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:06</v>
+        <v>6:28</v>
       </c>
       <c r="H193" t="str">
-        <v>Silvestre Dangond</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
+        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
       </c>
       <c r="L193" t="str">
-        <v>Ganas De Tenerla - Silvestre Dangond</v>
+        <v>Red Rocking Chair - All Them Witches</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>In My Blue</v>
+        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
+        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-08</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Doomsday...Don't Leave Me Here</v>
+        <v>...of Death and Fire</v>
       </c>
       <c r="G194" t="str">
-        <v>3:26</v>
+        <v>7:07</v>
       </c>
       <c r="H194" t="str">
-        <v>Rosie Carney</v>
+        <v>In Aeternum</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
+        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
+        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
       </c>
       <c r="L194" t="str">
-        <v>In My Blue - Rosie Carney</v>
+        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Living With It (feat. Feist)</v>
+        <v>Mizantrop</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
+        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-08</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Hurts Like Hell</v>
+        <v>Mizantrop</v>
       </c>
       <c r="G195" t="str">
-        <v>3:20</v>
+        <v>3:42</v>
       </c>
       <c r="H195" t="str">
-        <v>Charlotte Cornfield</v>
+        <v>She Past Away</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
+        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
+        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
       </c>
       <c r="L195" t="str">
-        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
+        <v>Mizantrop - She Past Away</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Silently</v>
+        <v>In the Name of the Moth</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/silently/1841629898</v>
+        <v>https://music.apple.com/us/song/in-the-name-of-the-moth/1866911203</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-08</v>
@@ -7823,258 +7823,30 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Croak Dream</v>
+        <v>Hidden Fires Burn Hottest</v>
       </c>
       <c r="G196" t="str">
-        <v>3:29</v>
+        <v>7:15</v>
       </c>
       <c r="H196" t="str">
-        <v>Puma Blue</v>
+        <v>Bosse-de-Nage</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
+        <v>https://music.apple.com/us/artist/bosse-de-nage/465123183</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/silently/1841629444</v>
+        <v>https://music.apple.com/us/album/in-the-name-of-the-moth/1866911198</v>
       </c>
       <c r="L196" t="str">
-        <v>Silently - Puma Blue</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Ashes &amp; Smoke</v>
-      </c>
-      <c r="B197" t="str">
-        <v/>
-      </c>
-      <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
-      </c>
-      <c r="D197" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" t="str">
-        <v>Ashes &amp; Smoke - Single</v>
-      </c>
-      <c r="G197" t="str">
-        <v>3:05</v>
-      </c>
-      <c r="H197" t="str">
-        <v>Anna Graves</v>
-      </c>
-      <c r="I197" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
-      </c>
-      <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
-      </c>
-      <c r="L197" t="str">
-        <v>Ashes &amp; Smoke - Anna Graves</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>Tormentor</v>
-      </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
-      </c>
-      <c r="D198" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
-        <v>The Flowers I See You In - EP</v>
-      </c>
-      <c r="G198" t="str">
-        <v>2:40</v>
-      </c>
-      <c r="H198" t="str">
-        <v>Ninush</v>
-      </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
-      </c>
-      <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
-      </c>
-      <c r="L198" t="str">
-        <v>Tormentor - Ninush</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Red Rocking Chair</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Red Rocking Chair - Single</v>
-      </c>
-      <c r="G199" t="str">
-        <v>6:28</v>
-      </c>
-      <c r="H199" t="str">
-        <v>All Them Witches</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
-      </c>
-      <c r="L199" t="str">
-        <v>Red Rocking Chair - All Them Witches</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>...of Death and Fire</v>
-      </c>
-      <c r="G200" t="str">
-        <v>7:07</v>
-      </c>
-      <c r="H200" t="str">
-        <v>In Aeternum</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
-      </c>
-      <c r="L200" t="str">
-        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>Mizantrop</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>Mizantrop</v>
-      </c>
-      <c r="G201" t="str">
-        <v>3:42</v>
-      </c>
-      <c r="H201" t="str">
-        <v>She Past Away</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
-      </c>
-      <c r="L201" t="str">
-        <v>Mizantrop - She Past Away</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>In the Name of the Moth</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/in-the-name-of-the-moth/1866911203</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Hidden Fires Burn Hottest</v>
-      </c>
-      <c r="G202" t="str">
-        <v>7:15</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Bosse-de-Nage</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/bosse-de-nage/465123183</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/in-the-name-of-the-moth/1866911198</v>
-      </c>
-      <c r="L202" t="str">
         <v>In the Name of the Moth - Bosse-de-Nage</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>6:00</v>
@@ -477,7 +477,7 @@
         <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B3" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:20</v>
@@ -515,7 +515,7 @@
         <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:27</v>
@@ -1389,7 +1389,7 @@
         <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>4:09</v>
@@ -1959,7 +1959,7 @@
         <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>3:37</v>

--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:L200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>צח חכים &amp; להקת רגעים - מחרוזת שבת 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>7 hours ago</v>
+        <v>2026-02-08</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409543&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-08</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 hours ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>6:00</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Taylor Swift</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>צח חכים &amp; להקת רגעים - מחרוזת שבת 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>סדיאל בכר - אי אפשר להסביר</v>
       </c>
       <c r="B3" t="str">
-        <v>8 hours ago</v>
+        <v>2026-02-08</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409542&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-08</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 hours ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>4:20</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>Michael Bolton</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>סדיאל בכר - אי אפשר להסביר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>ניר קלברס - סיגריה בסלון</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-08</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409541&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-08</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>4:27</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Mariah Carey</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>ניר קלברס - סיגריה בסלון</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>מאור יפרח - אין עוד מלבדך</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-08</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409540&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-08</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>3:26</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Netflix</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>מאור יפרח - אין עוד מלבדך</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-08</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:29</v>
+        <v>6:00</v>
       </c>
       <c r="H6" t="str">
-        <v>Michael Bolton</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-08</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:59</v>
+        <v>4:20</v>
       </c>
       <c r="H7" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-08</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:51</v>
+        <v>4:27</v>
       </c>
       <c r="H8" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-08</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>4:13</v>
+        <v>3:26</v>
       </c>
       <c r="H9" t="str">
-        <v>Michael Bolton</v>
+        <v>Netflix</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-08</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:41</v>
+        <v>3:29</v>
       </c>
       <c r="H10" t="str">
-        <v>NICK JONAS</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-08</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>7:03</v>
+        <v>2:59</v>
       </c>
       <c r="H11" t="str">
-        <v>Take That</v>
+        <v>mgk</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-08</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:37</v>
+        <v>2:51</v>
       </c>
       <c r="H12" t="str">
-        <v>Cliff Richard</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-08</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:54</v>
+        <v>4:13</v>
       </c>
       <c r="H13" t="str">
-        <v>Bryan Adams</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-08</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:06</v>
+        <v>4:41</v>
       </c>
       <c r="H14" t="str">
-        <v>Anna Graves</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-08</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:21</v>
+        <v>7:03</v>
       </c>
       <c r="H15" t="str">
-        <v>George Birge</v>
+        <v>Take That</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-08</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:09</v>
+        <v>4:37</v>
       </c>
       <c r="H16" t="str">
-        <v>Warner Records</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-08</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:18</v>
+        <v>3:54</v>
       </c>
       <c r="H17" t="str">
-        <v>NICK JONAS</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-08</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:08</v>
+        <v>3:06</v>
       </c>
       <c r="H18" t="str">
-        <v>Charlie Puth</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-08</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>4:03</v>
+        <v>3:21</v>
       </c>
       <c r="H19" t="str">
-        <v>Olivia Newton-John</v>
+        <v>George Birge</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
+        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-08</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:01</v>
+        <v>4:09</v>
       </c>
       <c r="H20" t="str">
-        <v>The Warning and Carin Leon</v>
+        <v>Warner Records</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
+        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-08</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:05</v>
+        <v>4:18</v>
       </c>
       <c r="H21" t="str">
-        <v>Iman Fandi</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
+        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-08</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:34</v>
+        <v>3:08</v>
       </c>
       <c r="H22" t="str">
-        <v>Megan Moroney</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dylan Davidson - Escape Artist</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
+        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-08</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:15</v>
+        <v>4:03</v>
       </c>
       <c r="H23" t="str">
-        <v>Dylan Davidson</v>
+        <v>Olivia Newton-John</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
+        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-08</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:16</v>
+        <v>3:01</v>
       </c>
       <c r="H24" t="str">
-        <v>Lady Gaga</v>
+        <v>The Warning and Carin Leon</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video)</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
+        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-08</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:53</v>
+        <v>3:05</v>
       </c>
       <c r="H25" t="str">
-        <v>Carlos Vives</v>
+        <v>Iman Fandi</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
+        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-08</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:25</v>
+        <v>3:34</v>
       </c>
       <c r="H26" t="str">
-        <v>Monsieur Periné</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio)</v>
+        <v>Dylan Davidson - Escape Artist</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
+        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-08</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:09</v>
+        <v>3:15</v>
       </c>
       <c r="H27" t="str">
-        <v>The Happy Fits</v>
+        <v>Dylan Davidson</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
+        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>chase (lyric vid) - Michael Aldag</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
+        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-08</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:45</v>
+        <v>4:16</v>
       </c>
       <c r="H28" t="str">
-        <v>Michael Aldag</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
+        <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
+        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-08</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:07</v>
+        <v>3:53</v>
       </c>
       <c r="H29" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
+        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
+        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-08</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:34</v>
+        <v>2:25</v>
       </c>
       <c r="H30" t="str">
-        <v>Marc Anthony</v>
+        <v>Monsieur Periné</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
+        <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
+        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-08</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:14</v>
+        <v>4:09</v>
       </c>
       <c r="H31" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer)</v>
+        <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
+        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-08</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:11</v>
+        <v>2:45</v>
       </c>
       <c r="H32" t="str">
-        <v>Michael Bolton</v>
+        <v>Michael Aldag</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
+        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Lachie Gill - Last Drive</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
+        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-08</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:40</v>
+        <v>4:07</v>
       </c>
       <c r="H33" t="str">
-        <v>Lachie Gill</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Lachie Gill - Last Drive - Lachie Gill</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
+        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-08</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:45</v>
+        <v>4:34</v>
       </c>
       <c r="H34" t="str">
-        <v>Eli &amp; Fur</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Freya Skye - why'd you have to call</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
+        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-08</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:19</v>
+        <v>5:14</v>
       </c>
       <c r="H35" t="str">
-        <v>Freya Skye</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Freya Skye - why'd you have to call - Freya Skye</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
+        <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
+        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-08</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:30</v>
+        <v>3:11</v>
       </c>
       <c r="H36" t="str">
-        <v>Jessie J</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
+        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer)</v>
+        <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
+        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-08</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:24</v>
+        <v>3:40</v>
       </c>
       <c r="H37" t="str">
-        <v>Marc Anthony</v>
+        <v>Lachie Gill</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
+        <v>Lachie Gill - Last Drive - Lachie Gill</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
+        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-08</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:33</v>
+        <v>3:45</v>
       </c>
       <c r="H38" t="str">
-        <v>Clara Mae</v>
+        <v>Eli &amp; Fur</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Metric - Victim of Luck (Official Music Video)</v>
+        <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
+        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-08</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:25</v>
+        <v>4:19</v>
       </c>
       <c r="H39" t="str">
-        <v>metricmusic</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
+        <v>Freya Skye - why'd you have to call - Freya Skye</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
+        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-08</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:41</v>
+        <v>2:30</v>
       </c>
       <c r="H40" t="str">
-        <v>kesha</v>
+        <v>Jessie J</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
+        <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
+        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-08</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:19</v>
+        <v>4:24</v>
       </c>
       <c r="H41" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
+        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
+        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-08</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:37</v>
+        <v>2:33</v>
       </c>
       <c r="H42" t="str">
-        <v>Vera Blue</v>
+        <v>Clara Mae</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
+        <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
+        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-08</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:08</v>
+        <v>3:25</v>
       </c>
       <c r="H43" t="str">
-        <v>Bob Moses</v>
+        <v>metricmusic</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
+        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
+        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-08</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:28</v>
+        <v>3:41</v>
       </c>
       <c r="H44" t="str">
-        <v>Marc Anthony</v>
+        <v>kesha</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
+        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-08</v>
@@ -2088,10 +2088,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>5:05</v>
+        <v>3:19</v>
       </c>
       <c r="H45" t="str">
-        <v>Marc Anthony</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Loreen - Feels Like Heaven</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B46" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
+        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-08</v>
@@ -2126,10 +2126,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:14</v>
+        <v>3:37</v>
       </c>
       <c r="H46" t="str">
-        <v>Loreen</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Loreen - Feels Like Heaven - Loreen</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B47" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
+        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-08</v>
@@ -2164,10 +2164,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:36</v>
+        <v>3:08</v>
       </c>
       <c r="H47" t="str">
-        <v>Take That</v>
+        <v>Bob Moses</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B48" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
+        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-08</v>
@@ -2202,10 +2202,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>5:31</v>
+        <v>3:28</v>
       </c>
       <c r="H48" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio)</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B49" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
+        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-08</v>
@@ -2240,10 +2240,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:37</v>
+        <v>5:05</v>
       </c>
       <c r="H49" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-08</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:58</v>
+        <v>3:14</v>
       </c>
       <c r="H50" t="str">
-        <v>The Warning</v>
+        <v>Loreen</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>Loreen - Feels Like Heaven - Loreen</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-08</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>5:08</v>
+        <v>3:36</v>
       </c>
       <c r="H51" t="str">
-        <v>The Offspring</v>
+        <v>Take That</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-08</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:38</v>
+        <v>5:31</v>
       </c>
       <c r="H52" t="str">
-        <v>Roxette</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
+        <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-08</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:50</v>
+        <v>3:37</v>
       </c>
       <c r="H53" t="str">
-        <v>Jessie Ware</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
+        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-08</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:10</v>
+        <v>4:58</v>
       </c>
       <c r="H54" t="str">
-        <v>Joseph</v>
+        <v>The Warning</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-08</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:44</v>
+        <v>5:08</v>
       </c>
       <c r="H55" t="str">
-        <v>Dean Lewis</v>
+        <v>The Offspring</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-08</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:57</v>
+        <v>4:38</v>
       </c>
       <c r="H56" t="str">
-        <v>Take That</v>
+        <v>Roxette</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-08</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:07</v>
+        <v>3:50</v>
       </c>
       <c r="H57" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-08</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:47</v>
+        <v>3:10</v>
       </c>
       <c r="H58" t="str">
-        <v>Paris Paloma</v>
+        <v>Joseph</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-08</v>
@@ -2620,10 +2620,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:22</v>
+        <v>2:44</v>
       </c>
       <c r="H59" t="str">
-        <v>Zara Larsson</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-08</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:48</v>
+        <v>2:57</v>
       </c>
       <c r="H60" t="str">
-        <v>only the poets</v>
+        <v>Take That</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-08</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:52</v>
+        <v>3:07</v>
       </c>
       <c r="H61" t="str">
-        <v>Katelyn Tarver</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-08</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:33</v>
+        <v>4:47</v>
       </c>
       <c r="H62" t="str">
-        <v>David Guetta</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-08</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:41</v>
+        <v>3:22</v>
       </c>
       <c r="H63" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-08</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:01</v>
+        <v>2:48</v>
       </c>
       <c r="H64" t="str">
-        <v>Ella Langley</v>
+        <v>only the poets</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-08</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:16</v>
+        <v>2:52</v>
       </c>
       <c r="H65" t="str">
-        <v>Dogpark</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-08</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:03</v>
+        <v>3:33</v>
       </c>
       <c r="H66" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>David Guetta</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-08</v>
@@ -2927,7 +2927,7 @@
         <v>2:41</v>
       </c>
       <c r="H67" t="str">
-        <v>ERNEST</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-08</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:05</v>
+        <v>4:01</v>
       </c>
       <c r="H68" t="str">
-        <v>Labrinth</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-08</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:46</v>
+        <v>3:16</v>
       </c>
       <c r="H69" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Dogpark</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-08</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:32</v>
+        <v>3:03</v>
       </c>
       <c r="H70" t="str">
-        <v>VOILÀ</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-08</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:42</v>
+        <v>2:41</v>
       </c>
       <c r="H71" t="str">
-        <v>Cannons</v>
+        <v>ERNEST</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-08</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:38</v>
+        <v>3:05</v>
       </c>
       <c r="H72" t="str">
-        <v>Kylie Morgan</v>
+        <v>Labrinth</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-08</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:10</v>
+        <v>2:46</v>
       </c>
       <c r="H73" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-08</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:57</v>
+        <v>3:32</v>
       </c>
       <c r="H74" t="str">
-        <v>Willie Nelson</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-08</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:19</v>
+        <v>3:42</v>
       </c>
       <c r="H75" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Cannons</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-08</v>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:04</v>
+        <v>2:38</v>
       </c>
       <c r="H76" t="str">
-        <v>India Martínez</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-08</v>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:16</v>
+        <v>3:10</v>
       </c>
       <c r="H77" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-08</v>
@@ -3342,10 +3342,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>5:58</v>
+        <v>3:57</v>
       </c>
       <c r="H78" t="str">
-        <v>TINI</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B79" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-08</v>
@@ -3380,10 +3380,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:26</v>
+        <v>2:19</v>
       </c>
       <c r="H79" t="str">
-        <v>Charley</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B80" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-08</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:05</v>
+        <v>4:04</v>
       </c>
       <c r="H80" t="str">
-        <v>Demi Lovato</v>
+        <v>India Martínez</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-08</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:16</v>
+        <v>2:16</v>
       </c>
       <c r="H81" t="str">
-        <v>Teddy Swims</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-08</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:14</v>
+        <v>5:58</v>
       </c>
       <c r="H82" t="str">
-        <v>Beck</v>
+        <v>TINI</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-08</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:57</v>
+        <v>3:26</v>
       </c>
       <c r="H83" t="str">
-        <v>The Offspring</v>
+        <v>Charley</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B84" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-08</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:10</v>
+        <v>4:05</v>
       </c>
       <c r="H84" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B85" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-08</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:10</v>
+        <v>3:16</v>
       </c>
       <c r="H85" t="str">
-        <v>Jason Derulo</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B86" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-08</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:52</v>
+        <v>3:14</v>
       </c>
       <c r="H86" t="str">
-        <v>lights</v>
+        <v>Beck</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B87" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-08</v>
@@ -3684,10 +3684,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:50</v>
+        <v>2:57</v>
       </c>
       <c r="H87" t="str">
-        <v>Telenova</v>
+        <v>The Offspring</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B88" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-08</v>
@@ -3722,10 +3722,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>5:32</v>
+        <v>4:10</v>
       </c>
       <c r="H88" t="str">
-        <v>Marcin</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B89" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-08</v>
@@ -3760,10 +3760,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:27</v>
+        <v>2:10</v>
       </c>
       <c r="H89" t="str">
-        <v>We Three</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B90" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-08</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:01</v>
+        <v>3:52</v>
       </c>
       <c r="H90" t="str">
-        <v>Timebelle Official</v>
+        <v>lights</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-08</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:20</v>
+        <v>3:50</v>
       </c>
       <c r="H91" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Telenova</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-08</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:34</v>
+        <v>5:32</v>
       </c>
       <c r="H92" t="str">
-        <v>Clinton Kane</v>
+        <v>Marcin</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-08</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>4:01</v>
+        <v>4:27</v>
       </c>
       <c r="H93" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>We Three</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-08</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:24</v>
+        <v>3:01</v>
       </c>
       <c r="H94" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-08</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>5:52</v>
+        <v>3:20</v>
       </c>
       <c r="H95" t="str">
-        <v>Harry Styles</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-08</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>5:01</v>
+        <v>3:34</v>
       </c>
       <c r="H96" t="str">
-        <v>Neal Francis</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-08</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:12</v>
+        <v>4:01</v>
       </c>
       <c r="H97" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-08</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:59</v>
+        <v>3:24</v>
       </c>
       <c r="H98" t="str">
-        <v>Holly Humberstone</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-08</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:56</v>
+        <v>5:52</v>
       </c>
       <c r="H99" t="str">
-        <v>Cliff Richard</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-08</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:46</v>
+        <v>5:01</v>
       </c>
       <c r="H100" t="str">
-        <v>Jessie Ware</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-08</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:37</v>
+        <v>4:12</v>
       </c>
       <c r="H101" t="str">
-        <v>Bella White</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Die For Me</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-08</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>KONNAKOL</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:00</v>
+        <v>3:59</v>
       </c>
       <c r="H102" t="str">
-        <v>ZAYN</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Die For Me - ZAYN</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Two Six</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/two-six/1875080974</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-08</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Fall-Off</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:16</v>
+        <v>2:56</v>
       </c>
       <c r="H103" t="str">
-        <v>J. Cole</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/two-six/1875080726</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Two Six - J. Cole</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Dracula (JENNIE Remix)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-08</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Dracula (Remix) - Single</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:29</v>
+        <v>3:46</v>
       </c>
       <c r="H104" t="str">
-        <v>Tame Impala</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Dracula (JENNIE Remix) - Tame Impala</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Hotel California</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-08</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Piss In The Wind</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G105" t="str">
-        <v>2:08</v>
+        <v>4:37</v>
       </c>
       <c r="H105" t="str">
-        <v>Joji</v>
+        <v>Bella White</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>Hotel California - Joji</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Homewrecker</v>
+        <v>Die For Me</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
+        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-08</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Homewrecker - Single</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G106" t="str">
-        <v>3:29</v>
+        <v>3:00</v>
       </c>
       <c r="H106" t="str">
-        <v>sombr</v>
+        <v>ZAYN</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
+        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
       </c>
       <c r="L106" t="str">
-        <v>Homewrecker - sombr</v>
+        <v>Die For Me - ZAYN</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Might Just</v>
+        <v>Two Six</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/might-just/1858755211</v>
+        <v>https://music.apple.com/us/song/two-six/1875080974</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-08</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Do You Still Love Me?</v>
+        <v>The Fall-Off</v>
       </c>
       <c r="G107" t="str">
-        <v>3:43</v>
+        <v>3:16</v>
       </c>
       <c r="H107" t="str">
-        <v>Ella Mai</v>
+        <v>J. Cole</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
+        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/might-just/1858754868</v>
+        <v>https://music.apple.com/us/album/two-six/1875080726</v>
       </c>
       <c r="L107" t="str">
-        <v>Might Just - Ella Mai</v>
+        <v>Two Six - J. Cole</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Cloud 9</v>
+        <v>Dracula (JENNIE Remix)</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
+        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-08</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Cloud 9</v>
+        <v>Dracula (Remix) - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:33</v>
+        <v>3:29</v>
       </c>
       <c r="H108" t="str">
-        <v>Megan Moroney</v>
+        <v>Tame Impala</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
+        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
       </c>
       <c r="L108" t="str">
-        <v>Cloud 9 - Megan Moroney</v>
+        <v>Dracula (JENNIE Remix) - Tame Impala</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Cry</v>
+        <v>Hotel California</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/cry/1845189974</v>
+        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-08</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G109" t="str">
-        <v>3:07</v>
+        <v>2:08</v>
       </c>
       <c r="H109" t="str">
-        <v>Charlie Puth</v>
+        <v>Joji</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/cry/1845189970</v>
+        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
       </c>
       <c r="L109" t="str">
-        <v>Cry - Charlie Puth</v>
+        <v>Hotel California - Joji</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>I'll Change for You</v>
+        <v>Homewrecker</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
+        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-08</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>Homewrecker - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:16</v>
+        <v>3:29</v>
       </c>
       <c r="H110" t="str">
-        <v>Mitski</v>
+        <v>sombr</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
+        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
       </c>
       <c r="L110" t="str">
-        <v>I'll Change for You - Mitski</v>
+        <v>Homewrecker - sombr</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>ASSIGNMENT</v>
+        <v>Might Just</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/assignment/1872764440</v>
+        <v>https://music.apple.com/us/song/might-just/1858755211</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-08</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>ASSIGNMENT - Single</v>
+        <v>Do You Still Love Me?</v>
       </c>
       <c r="G111" t="str">
-        <v>2:23</v>
+        <v>3:43</v>
       </c>
       <c r="H111" t="str">
-        <v>Power Snatch</v>
+        <v>Ella Mai</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
+        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/assignment/1872764438</v>
+        <v>https://music.apple.com/us/album/might-just/1858754868</v>
       </c>
       <c r="L111" t="str">
-        <v>ASSIGNMENT - Power Snatch</v>
+        <v>Might Just - Ella Mai</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Como en el Idilio</v>
+        <v>Cloud 9</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
+        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-08</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Como en el Idilio - Single</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G112" t="str">
-        <v>4:27</v>
+        <v>3:33</v>
       </c>
       <c r="H112" t="str">
-        <v>Marc Anthony</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
+        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
       </c>
       <c r="L112" t="str">
-        <v>Como en el Idilio - Marc Anthony</v>
+        <v>Cloud 9 - Megan Moroney</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>golden boy</v>
+        <v>Cry</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
+        <v>https://music.apple.com/us/song/cry/1845189974</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-08</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>stardust - EP</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G113" t="str">
-        <v>3:17</v>
+        <v>3:07</v>
       </c>
       <c r="H113" t="str">
-        <v>Freya Skye</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
+        <v>https://music.apple.com/us/album/cry/1845189970</v>
       </c>
       <c r="L113" t="str">
-        <v>golden boy - Freya Skye</v>
+        <v>Cry - Charlie Puth</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Penny in the Lake</v>
+        <v>I'll Change for You</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
+        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-08</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Singin’ to an Empty Chair</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G114" t="str">
-        <v>3:51</v>
+        <v>3:16</v>
       </c>
       <c r="H114" t="str">
-        <v>Ratboys</v>
+        <v>Mitski</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
+        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
       </c>
       <c r="L114" t="str">
-        <v>Penny in the Lake - Ratboys</v>
+        <v>I'll Change for You - Mitski</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Heaven</v>
+        <v>ASSIGNMENT</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/heaven/1862570892</v>
+        <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-08</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Ambiguous Desire</v>
+        <v>ASSIGNMENT - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>4:26</v>
+        <v>2:23</v>
       </c>
       <c r="H115" t="str">
-        <v>Arlo Parks</v>
+        <v>Power Snatch</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/heaven/1862570378</v>
+        <v>https://music.apple.com/us/album/assignment/1872764438</v>
       </c>
       <c r="L115" t="str">
-        <v>Heaven - Arlo Parks</v>
+        <v>ASSIGNMENT - Power Snatch</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Adrenaline</v>
+        <v>Como en el Idilio</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
+        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-08</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>GOLDEN HOUR : Part.4 - EP</v>
+        <v>Como en el Idilio - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:39</v>
+        <v>4:27</v>
       </c>
       <c r="H116" t="str">
-        <v>ATEEZ</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
+        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
       </c>
       <c r="L116" t="str">
-        <v>Adrenaline - ATEEZ</v>
+        <v>Como en el Idilio - Marc Anthony</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Sweet To Me</v>
+        <v>golden boy</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
+        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-08</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Sunday Best</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G117" t="str">
-        <v>4:17</v>
+        <v>3:17</v>
       </c>
       <c r="H117" t="str">
-        <v>Nick Jonas</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
+        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
       </c>
       <c r="L117" t="str">
-        <v>Sweet To Me - Nick Jonas</v>
+        <v>golden boy - Freya Skye</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Time Goes On</v>
+        <v>Penny in the Lake</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
+        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-08</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Time Goes On - Single</v>
+        <v>Singin’ to an Empty Chair</v>
       </c>
       <c r="G118" t="str">
-        <v>2:55</v>
+        <v>3:51</v>
       </c>
       <c r="H118" t="str">
-        <v>Koe Wetzel</v>
+        <v>Ratboys</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
+        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
       </c>
       <c r="L118" t="str">
-        <v>Time Goes On - Koe Wetzel</v>
+        <v>Penny in the Lake - Ratboys</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Drive Safe</v>
+        <v>Heaven</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
+        <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-08</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Drive Safe - Single</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G119" t="str">
-        <v>3:21</v>
+        <v>4:26</v>
       </c>
       <c r="H119" t="str">
-        <v>Myles Smith</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
+        <v>https://music.apple.com/us/album/heaven/1862570378</v>
       </c>
       <c r="L119" t="str">
-        <v>Drive Safe - Myles Smith</v>
+        <v>Heaven - Arlo Parks</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Love To Be Loved</v>
+        <v>Adrenaline</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
+        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-08</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Love To Be Loved - Single</v>
+        <v>GOLDEN HOUR : Part.4 - EP</v>
       </c>
       <c r="G120" t="str">
-        <v>2:50</v>
+        <v>3:39</v>
       </c>
       <c r="H120" t="str">
-        <v>The Warning</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
+        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
       </c>
       <c r="L120" t="str">
-        <v>Love To Be Loved - The Warning</v>
+        <v>Adrenaline - ATEEZ</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Mi Yo de Antes</v>
+        <v>Sweet To Me</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
+        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-08</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Mi Yo de Antes - Single</v>
+        <v>Sunday Best</v>
       </c>
       <c r="G121" t="str">
-        <v>3:02</v>
+        <v>4:17</v>
       </c>
       <c r="H121" t="str">
-        <v>Eden Muñoz</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
+        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
       </c>
       <c r="L121" t="str">
-        <v>Mi Yo de Antes - Eden Muñoz</v>
+        <v>Sweet To Me - Nick Jonas</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Omens</v>
+        <v>Time Goes On</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/omens/1872546206</v>
+        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-08</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Omens - Single</v>
+        <v>Time Goes On - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:00</v>
+        <v>2:55</v>
       </c>
       <c r="H122" t="str">
-        <v>EsDeeKid</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/omens/1872546204</v>
+        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
       </c>
       <c r="L122" t="str">
-        <v>Omens - EsDeeKid</v>
+        <v>Time Goes On - Koe Wetzel</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>My Regards</v>
+        <v>Drive Safe</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
+        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-08</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Florescence</v>
+        <v>Drive Safe - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:11</v>
+        <v>3:21</v>
       </c>
       <c r="H123" t="str">
-        <v>Maisie Peters</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
+        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
       </c>
       <c r="L123" t="str">
-        <v>My Regards - Maisie Peters</v>
+        <v>Drive Safe - Myles Smith</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Time After Time</v>
+        <v>Love To Be Loved</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
+        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-08</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Time After Time - Single</v>
+        <v>Love To Be Loved - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:48</v>
+        <v>2:50</v>
       </c>
       <c r="H124" t="str">
-        <v>EJAE</v>
+        <v>The Warning</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
+        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
       </c>
       <c r="L124" t="str">
-        <v>Time After Time - EJAE</v>
+        <v>Love To Be Loved - The Warning</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Don't Want Your Love</v>
+        <v>Mi Yo de Antes</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-08</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>ODYSSEY</v>
+        <v>Mi Yo de Antes - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:12</v>
+        <v>3:02</v>
       </c>
       <c r="H125" t="str">
-        <v>ILLENIUM</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
       </c>
       <c r="L125" t="str">
-        <v>Don't Want Your Love - ILLENIUM</v>
+        <v>Mi Yo de Antes - Eden Muñoz</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Pa' Los Envidiosos</v>
+        <v>Omens</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
+        <v>https://music.apple.com/us/song/omens/1872546206</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-08</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Pa' Los Envidiosos - Single</v>
+        <v>Omens - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:37</v>
+        <v>2:00</v>
       </c>
       <c r="H126" t="str">
-        <v>Pitbull</v>
+        <v>EsDeeKid</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
+        <v>https://music.apple.com/us/album/omens/1872546204</v>
       </c>
       <c r="L126" t="str">
-        <v>Pa' Los Envidiosos - Pitbull</v>
+        <v>Omens - EsDeeKid</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Plei</v>
+        <v>My Regards</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/plei/1872137577</v>
+        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-08</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Plei - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G127" t="str">
-        <v>3:22</v>
+        <v>3:11</v>
       </c>
       <c r="H127" t="str">
-        <v>Chuwi</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/plei/1872137372</v>
+        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
       </c>
       <c r="L127" t="str">
-        <v>Plei - Chuwi</v>
+        <v>My Regards - Maisie Peters</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Flood (feat. Bon Iver)</v>
+        <v>Time After Time</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
+        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-08</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Time After Time - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:59</v>
+        <v>2:48</v>
       </c>
       <c r="H128" t="str">
-        <v>Dua Saleh</v>
+        <v>EJAE</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
+        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
       </c>
       <c r="L128" t="str">
-        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
+        <v>Time After Time - EJAE</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Rain</v>
+        <v>Don't Want Your Love</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/rain/1867258289</v>
+        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-08</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Rain - Single</v>
+        <v>ODYSSEY</v>
       </c>
       <c r="G129" t="str">
-        <v>3:28</v>
+        <v>3:12</v>
       </c>
       <c r="H129" t="str">
-        <v>FISHER</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/rain/1867258288</v>
+        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
       </c>
       <c r="L129" t="str">
-        <v>Rain - FISHER</v>
+        <v>Don't Want Your Love - ILLENIUM</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Release The Pressure</v>
+        <v>Pa' Los Envidiosos</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
+        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-08</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Release The Pressure - Single</v>
+        <v>Pa' Los Envidiosos - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:23</v>
+        <v>3:37</v>
       </c>
       <c r="H130" t="str">
-        <v>Calvin Harris</v>
+        <v>Pitbull</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
+        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
       </c>
       <c r="L130" t="str">
-        <v>Release The Pressure - Calvin Harris</v>
+        <v>Pa' Los Envidiosos - Pitbull</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Sexistential (Arca’s Take)</v>
+        <v>Plei</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
+        <v>https://music.apple.com/us/song/plei/1872137577</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-08</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Sexistential (Arca’s Take) - Single</v>
+        <v>Plei - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:44</v>
+        <v>3:22</v>
       </c>
       <c r="H131" t="str">
-        <v>Robyn</v>
+        <v>Chuwi</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
+        <v>https://music.apple.com/us/album/plei/1872137372</v>
       </c>
       <c r="L131" t="str">
-        <v>Sexistential (Arca’s Take) - Robyn</v>
+        <v>Plei - Chuwi</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>heal something</v>
+        <v>Flood (feat. Bon Iver)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
+        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-08</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>ACT II</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G132" t="str">
-        <v>3:01</v>
+        <v>2:59</v>
       </c>
       <c r="H132" t="str">
-        <v>Sasha Keable</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
+        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
       </c>
       <c r="L132" t="str">
-        <v>heal something - Sasha Keable</v>
+        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Buenos Días</v>
+        <v>Rain</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
+        <v>https://music.apple.com/us/song/rain/1867258289</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-08</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Buenos Días - Single</v>
+        <v>Rain - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:39</v>
+        <v>3:28</v>
       </c>
       <c r="H133" t="str">
-        <v>Eladio Carrión</v>
+        <v>FISHER</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
+        <v>https://music.apple.com/us/album/rain/1867258288</v>
       </c>
       <c r="L133" t="str">
-        <v>Buenos Días - Eladio Carrión</v>
+        <v>Rain - FISHER</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>COOK</v>
+        <v>Release The Pressure</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/cook/1872816147</v>
+        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-08</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>COOK - Single</v>
+        <v>Release The Pressure - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:50</v>
+        <v>3:23</v>
       </c>
       <c r="H134" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Calvin Harris</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/cook/1872816146</v>
+        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
       </c>
       <c r="L134" t="str">
-        <v>COOK - SOFI TUKKER</v>
+        <v>Release The Pressure - Calvin Harris</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>You Got to Lose</v>
+        <v>Sexistential (Arca’s Take)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
+        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-08</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Peaches!</v>
+        <v>Sexistential (Arca’s Take) - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:17</v>
+        <v>3:44</v>
       </c>
       <c r="H135" t="str">
-        <v>The Black Keys</v>
+        <v>Robyn</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
+        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
       </c>
       <c r="L135" t="str">
-        <v>You Got to Lose - The Black Keys</v>
+        <v>Sexistential (Arca’s Take) - Robyn</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Different Kind Of Love</v>
+        <v>heal something</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
+        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-08</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Victory Garden</v>
+        <v>ACT II</v>
       </c>
       <c r="G136" t="str">
-        <v>3:39</v>
+        <v>3:01</v>
       </c>
       <c r="H136" t="str">
-        <v>Young the Giant</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
+        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
       </c>
       <c r="L136" t="str">
-        <v>Different Kind Of Love - Young the Giant</v>
+        <v>heal something - Sasha Keable</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Living Water</v>
+        <v>Buenos Días</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/living-water/1871565262</v>
+        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-08</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Reconstruction: Second Story</v>
+        <v>Buenos Días - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:09</v>
+        <v>2:39</v>
       </c>
       <c r="H137" t="str">
-        <v>Lecrae</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/living-water/1871564892</v>
+        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
       </c>
       <c r="L137" t="str">
-        <v>Living Water - Lecrae</v>
+        <v>Buenos Días - Eladio Carrión</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>What It Feels Like</v>
+        <v>COOK</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
+        <v>https://music.apple.com/us/song/cook/1872816147</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-08</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>What It Feels Like - Single</v>
+        <v>COOK - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:18</v>
+        <v>2:50</v>
       </c>
       <c r="H138" t="str">
-        <v>Dillon Francis</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
+        <v>https://music.apple.com/us/album/cook/1872816146</v>
       </c>
       <c r="L138" t="str">
-        <v>What It Feels Like - Dillon Francis</v>
+        <v>COOK - SOFI TUKKER</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>neck</v>
+        <v>You Got to Lose</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/neck/1866953832</v>
+        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-08</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>neck - Single</v>
+        <v>Peaches!</v>
       </c>
       <c r="G139" t="str">
-        <v>3:40</v>
+        <v>3:17</v>
       </c>
       <c r="H139" t="str">
-        <v>Mau P</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/neck/1866953831</v>
+        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
       </c>
       <c r="L139" t="str">
-        <v>neck - Mau P</v>
+        <v>You Got to Lose - The Black Keys</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Colorblind</v>
+        <v>Different Kind Of Love</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
+        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-08</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Colorblind - Single</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G140" t="str">
-        <v>2:56</v>
+        <v>3:39</v>
       </c>
       <c r="H140" t="str">
-        <v>Gavin Adcock</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
+        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
       </c>
       <c r="L140" t="str">
-        <v>Colorblind - Gavin Adcock</v>
+        <v>Different Kind Of Love - Young the Giant</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Au Revoir Reservoir</v>
+        <v>Living Water</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
+        <v>https://music.apple.com/us/song/living-water/1871565262</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-08</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Tenterhooks</v>
+        <v>Reconstruction: Second Story</v>
       </c>
       <c r="G141" t="str">
-        <v>3:21</v>
+        <v>2:09</v>
       </c>
       <c r="H141" t="str">
-        <v>Silversun Pickups</v>
+        <v>Lecrae</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
+        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
+        <v>https://music.apple.com/us/album/living-water/1871564892</v>
       </c>
       <c r="L141" t="str">
-        <v>Au Revoir Reservoir - Silversun Pickups</v>
+        <v>Living Water - Lecrae</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Flavorless</v>
+        <v>What It Feels Like</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
+        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-08</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Flavorless - Single</v>
+        <v>What It Feels Like - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:31</v>
+        <v>2:18</v>
       </c>
       <c r="H142" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
+        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
       </c>
       <c r="L142" t="str">
-        <v>Flavorless - Dexter and The Moonrocks</v>
+        <v>What It Feels Like - Dillon Francis</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Nunca</v>
+        <v>neck</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/nunca/1860691713</v>
+        <v>https://music.apple.com/us/song/neck/1866953832</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-08</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>ESCENAS</v>
+        <v>neck - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:05</v>
+        <v>3:40</v>
       </c>
       <c r="H143" t="str">
-        <v>Sin Bandera</v>
+        <v>Mau P</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
+        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/nunca/1860691704</v>
+        <v>https://music.apple.com/us/album/neck/1866953831</v>
       </c>
       <c r="L143" t="str">
-        <v>Nunca - Sin Bandera</v>
+        <v>neck - Mau P</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Just In Case</v>
+        <v>Colorblind</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
+        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-08</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>NO HArD FEELINGS (Deluxe)</v>
+        <v>Colorblind - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>1:45</v>
+        <v>2:56</v>
       </c>
       <c r="H144" t="str">
-        <v>Marc E. Bassy</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
+        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
       </c>
       <c r="L144" t="str">
-        <v>Just In Case - Marc E. Bassy</v>
+        <v>Colorblind - Gavin Adcock</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Thinking of You</v>
+        <v>Au Revoir Reservoir</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
+        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-08</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Thinking of You - Single</v>
+        <v>Tenterhooks</v>
       </c>
       <c r="G145" t="str">
-        <v>3:00</v>
+        <v>3:21</v>
       </c>
       <c r="H145" t="str">
-        <v>AP Dhillon</v>
+        <v>Silversun Pickups</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
+        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
+        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
       </c>
       <c r="L145" t="str">
-        <v>Thinking of You - AP Dhillon</v>
+        <v>Au Revoir Reservoir - Silversun Pickups</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>House Of Cards</v>
+        <v>Flavorless</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
+        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-08</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>House of Cards</v>
+        <v>Flavorless - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:26</v>
+        <v>3:31</v>
       </c>
       <c r="H146" t="str">
-        <v>The Amity Affliction</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
+        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
       </c>
       <c r="L146" t="str">
-        <v>House Of Cards - The Amity Affliction</v>
+        <v>Flavorless - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Stay With Me</v>
+        <v>Nunca</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
+        <v>https://music.apple.com/us/song/nunca/1860691713</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-08</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Stay With Me - Single</v>
+        <v>ESCENAS</v>
       </c>
       <c r="G147" t="str">
-        <v>3:21</v>
+        <v>3:05</v>
       </c>
       <c r="H147" t="str">
-        <v>Agents Of Time</v>
+        <v>Sin Bandera</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
+        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
+        <v>https://music.apple.com/us/album/nunca/1860691704</v>
       </c>
       <c r="L147" t="str">
-        <v>Stay With Me - Agents Of Time</v>
+        <v>Nunca - Sin Bandera</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>I had a dream...</v>
+        <v>Just In Case</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
+        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-08</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Dream inside a dream…</v>
+        <v>NO HArD FEELINGS (Deluxe)</v>
       </c>
       <c r="G148" t="str">
-        <v>2:39</v>
+        <v>1:45</v>
       </c>
       <c r="H148" t="str">
-        <v>R3HAB</v>
+        <v>Marc E. Bassy</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
+        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
       </c>
       <c r="L148" t="str">
-        <v>I had a dream... - R3HAB</v>
+        <v>Just In Case - Marc E. Bassy</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Back to You</v>
+        <v>Thinking of You</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
+        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-08</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Satellite</v>
+        <v>Thinking of You - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:10</v>
+        <v>3:00</v>
       </c>
       <c r="H149" t="str">
-        <v>Charlotte Sands</v>
+        <v>AP Dhillon</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
+        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
+        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
       </c>
       <c r="L149" t="str">
-        <v>Back to You - Charlotte Sands</v>
+        <v>Thinking of You - AP Dhillon</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>rager</v>
+        <v>House Of Cards</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/rager/1872808801</v>
+        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-08</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>rager</v>
+        <v>House of Cards</v>
       </c>
       <c r="G150" t="str">
-        <v>2:48</v>
+        <v>3:26</v>
       </c>
       <c r="H150" t="str">
-        <v>Blusher</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/blusher/485578161</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/rager/1872808800</v>
+        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
       </c>
       <c r="L150" t="str">
-        <v>rager - Blusher</v>
+        <v>House Of Cards - The Amity Affliction</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>If Only</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/if-only/1870281318</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-08</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Patchwork</v>
+        <v>Stay With Me - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:28</v>
+        <v>3:21</v>
       </c>
       <c r="H151" t="str">
-        <v>Charlotte Day Wilson</v>
+        <v>Agents Of Time</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
+        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/if-only/1870281314</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
       </c>
       <c r="L151" t="str">
-        <v>If Only - Charlotte Day Wilson</v>
+        <v>Stay With Me - Agents Of Time</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>DON'T LOVE ME</v>
+        <v>I had a dream...</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-08</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>DON'T LOVE ME - Single</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G152" t="str">
-        <v>3:01</v>
+        <v>2:39</v>
       </c>
       <c r="H152" t="str">
-        <v>Omah Lay</v>
+        <v>R3HAB</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
       </c>
       <c r="L152" t="str">
-        <v>DON'T LOVE ME - Omah Lay</v>
+        <v>I had a dream... - R3HAB</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>No Sikes, No Tradesies</v>
+        <v>Back to You</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
+        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-08</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Sweet Nothings</v>
+        <v>Satellite</v>
       </c>
       <c r="G153" t="str">
-        <v>2:32</v>
+        <v>3:10</v>
       </c>
       <c r="H153" t="str">
-        <v>Jaymin</v>
+        <v>Charlotte Sands</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
+        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
+        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
       </c>
       <c r="L153" t="str">
-        <v>No Sikes, No Tradesies - Jaymin</v>
+        <v>Back to You - Charlotte Sands</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>you woke me up</v>
+        <v>rager</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
+        <v>https://music.apple.com/us/song/rager/1872808801</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-08</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>you woke me up - Single</v>
+        <v>rager</v>
       </c>
       <c r="G154" t="str">
-        <v>3:14</v>
+        <v>2:48</v>
       </c>
       <c r="H154" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Blusher</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/blusher/485578161</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
+        <v>https://music.apple.com/us/album/rager/1872808800</v>
       </c>
       <c r="L154" t="str">
-        <v>you woke me up - Kevian Kraemer</v>
+        <v>rager - Blusher</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>No One’s Business</v>
+        <v>If Only</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
+        <v>https://music.apple.com/us/song/if-only/1870281318</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-08</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>No One’s Business - Single</v>
+        <v>Patchwork</v>
       </c>
       <c r="G155" t="str">
-        <v>3:00</v>
+        <v>3:28</v>
       </c>
       <c r="H155" t="str">
-        <v>Alicia Creti</v>
+        <v>Charlotte Day Wilson</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
+        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
+        <v>https://music.apple.com/us/album/if-only/1870281314</v>
       </c>
       <c r="L155" t="str">
-        <v>No One’s Business - Alicia Creti</v>
+        <v>If Only - Charlotte Day Wilson</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
+        <v>DON'T LOVE ME</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
+        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-08</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>DON'T LOVE ME - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:13</v>
+        <v>3:01</v>
       </c>
       <c r="H156" t="str">
-        <v>Bryant Barnes</v>
+        <v>Omah Lay</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
+        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
       </c>
       <c r="L156" t="str">
-        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
+        <v>DON'T LOVE ME - Omah Lay</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>TWICE</v>
+        <v>No Sikes, No Tradesies</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/twice/1871578107</v>
+        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-08</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>KINDA HARD</v>
+        <v>Sweet Nothings</v>
       </c>
       <c r="G157" t="str">
-        <v>3:44</v>
+        <v>2:32</v>
       </c>
       <c r="H157" t="str">
-        <v>Bilmuri</v>
+        <v>Jaymin</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/twice/1871578103</v>
+        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
       </c>
       <c r="L157" t="str">
-        <v>TWICE - Bilmuri</v>
+        <v>No Sikes, No Tradesies - Jaymin</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>ROOFTOP</v>
+        <v>you woke me up</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
+        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-08</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>ROOFTOP - Single</v>
+        <v>you woke me up - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:22</v>
+        <v>3:14</v>
       </c>
       <c r="H158" t="str">
-        <v>Hulvey</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
+        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
       </c>
       <c r="L158" t="str">
-        <v>ROOFTOP - Hulvey</v>
+        <v>you woke me up - Kevian Kraemer</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Louisiana Rain</v>
+        <v>No One’s Business</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
+        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-08</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Louisiana Rain - Single</v>
+        <v>No One’s Business - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:41</v>
+        <v>3:00</v>
       </c>
       <c r="H159" t="str">
-        <v>Hunter Plake</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
+        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
       </c>
       <c r="L159" t="str">
-        <v>Louisiana Rain - Hunter Plake</v>
+        <v>No One’s Business - Alicia Creti</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>sharing Jesus with an ex</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
+        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-08</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>sharing Jesus with an ex - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G160" t="str">
-        <v>1:55</v>
+        <v>3:13</v>
       </c>
       <c r="H160" t="str">
-        <v>Zoe Levert</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
+        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L160" t="str">
-        <v>sharing Jesus with an ex - Zoe Levert</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Body Control (feat. CHILLS)</v>
+        <v>TWICE</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
+        <v>https://music.apple.com/us/song/twice/1871578107</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-08</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Body Control (feat. CHILLS) - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G161" t="str">
-        <v>3:21</v>
+        <v>3:44</v>
       </c>
       <c r="H161" t="str">
-        <v>Cole Knight</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
+        <v>https://music.apple.com/us/album/twice/1871578103</v>
       </c>
       <c r="L161" t="str">
-        <v>Body Control (feat. CHILLS) - Cole Knight</v>
+        <v>TWICE - Bilmuri</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
+        <v>ROOFTOP</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
+        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-08</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>A Prayer for the Dancefloor - Single</v>
+        <v>ROOFTOP - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>6:54</v>
+        <v>3:22</v>
       </c>
       <c r="H162" t="str">
-        <v>Charlotte de Witte</v>
+        <v>Hulvey</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
+        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
       </c>
       <c r="L162" t="str">
-        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
+        <v>ROOFTOP - Hulvey</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Realm of Endless Misery</v>
+        <v>Louisiana Rain</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
+        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-08</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Liturgy of Death</v>
+        <v>Louisiana Rain - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>4:56</v>
+        <v>3:41</v>
       </c>
       <c r="H163" t="str">
-        <v>Mayhem</v>
+        <v>Hunter Plake</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
+        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
+        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
       </c>
       <c r="L163" t="str">
-        <v>Realm of Endless Misery - Mayhem</v>
+        <v>Louisiana Rain - Hunter Plake</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>BLEACH</v>
+        <v>sharing Jesus with an ex</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/bleach/1869795882</v>
+        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-08</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>BLEACH - Single</v>
+        <v>sharing Jesus with an ex - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:28</v>
+        <v>1:55</v>
       </c>
       <c r="H164" t="str">
-        <v>Ecca Vandal</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/bleach/1869795874</v>
+        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
       </c>
       <c r="L164" t="str">
-        <v>BLEACH - Ecca Vandal</v>
+        <v>sharing Jesus with an ex - Zoe Levert</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>pretty in pink</v>
+        <v>Body Control (feat. CHILLS)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
+        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-08</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>AngelPink</v>
+        <v>Body Control (feat. CHILLS) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:13</v>
+        <v>3:21</v>
       </c>
       <c r="H165" t="str">
-        <v>Keni Titus</v>
+        <v>Cole Knight</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
+        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
+        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
       </c>
       <c r="L165" t="str">
-        <v>pretty in pink - Keni Titus</v>
+        <v>Body Control (feat. CHILLS) - Cole Knight</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Pickup Man</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
+        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-08</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Pickup Man - Single</v>
+        <v>A Prayer for the Dancefloor - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:28</v>
+        <v>6:54</v>
       </c>
       <c r="H166" t="str">
-        <v>Bayker Blankenship</v>
+        <v>Charlotte de Witte</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
+        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
+        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
       </c>
       <c r="L166" t="str">
-        <v>Pickup Man - Bayker Blankenship</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Get To Drinkin'</v>
+        <v>Realm of Endless Misery</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
+        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-08</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Get To Drinkin' - Single</v>
+        <v>Liturgy of Death</v>
       </c>
       <c r="G167" t="str">
-        <v>2:48</v>
+        <v>4:56</v>
       </c>
       <c r="H167" t="str">
-        <v>Zach John King</v>
+        <v>Mayhem</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
+        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
+        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
       </c>
       <c r="L167" t="str">
-        <v>Get To Drinkin' - Zach John King</v>
+        <v>Realm of Endless Misery - Mayhem</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>The Roses</v>
+        <v>BLEACH</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
+        <v>https://music.apple.com/us/song/bleach/1869795882</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-08</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>The Roses - Single</v>
+        <v>BLEACH - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:02</v>
+        <v>2:28</v>
       </c>
       <c r="H168" t="str">
-        <v>Russell Dickerson</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
+        <v>https://music.apple.com/us/album/bleach/1869795874</v>
       </c>
       <c r="L168" t="str">
-        <v>The Roses - Russell Dickerson</v>
+        <v>BLEACH - Ecca Vandal</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>I Should Know Better</v>
+        <v>pretty in pink</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
+        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-08</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Under The Streetlights</v>
+        <v>AngelPink</v>
       </c>
       <c r="G169" t="str">
-        <v>3:33</v>
+        <v>3:13</v>
       </c>
       <c r="H169" t="str">
-        <v>Michael Marcagi</v>
+        <v>Keni Titus</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
+        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
+        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
       </c>
       <c r="L169" t="str">
-        <v>I Should Know Better - Michael Marcagi</v>
+        <v>pretty in pink - Keni Titus</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Never Do</v>
+        <v>Pickup Man</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/never-do/1872842226</v>
+        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-08</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Never Do - Single</v>
+        <v>Pickup Man - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>1:58</v>
+        <v>3:28</v>
       </c>
       <c r="H170" t="str">
-        <v>charlieonnafriday</v>
+        <v>Bayker Blankenship</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
+        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/never-do/1872842225</v>
+        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
       </c>
       <c r="L170" t="str">
-        <v>Never Do - charlieonnafriday</v>
+        <v>Pickup Man - Bayker Blankenship</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Primary Colors</v>
+        <v>Get To Drinkin'</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
+        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-08</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Lost on You</v>
+        <v>Get To Drinkin' - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:37</v>
+        <v>2:48</v>
       </c>
       <c r="H171" t="str">
-        <v>Tigers Jaw</v>
+        <v>Zach John King</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
+        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
+        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
       </c>
       <c r="L171" t="str">
-        <v>Primary Colors - Tigers Jaw</v>
+        <v>Get To Drinkin' - Zach John King</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Rock Bottom</v>
+        <v>The Roses</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
+        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-08</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Rock Bottom / Octopus - Single</v>
+        <v>The Roses - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>4:10</v>
+        <v>3:02</v>
       </c>
       <c r="H172" t="str">
-        <v>King Krule</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
+        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
+        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
       </c>
       <c r="L172" t="str">
-        <v>Rock Bottom - King Krule</v>
+        <v>The Roses - Russell Dickerson</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Te Dedico</v>
+        <v>I Should Know Better</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
+        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-08</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Te Dedico - Single</v>
+        <v>Under The Streetlights</v>
       </c>
       <c r="G173" t="str">
-        <v>3:45</v>
+        <v>3:33</v>
       </c>
       <c r="H173" t="str">
-        <v>Carlos Vives</v>
+        <v>Michael Marcagi</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
+        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
+        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
       </c>
       <c r="L173" t="str">
-        <v>Te Dedico - Carlos Vives</v>
+        <v>I Should Know Better - Michael Marcagi</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>AUNQUE SEA EN DOS</v>
+        <v>Never Do</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
+        <v>https://music.apple.com/us/song/never-do/1872842226</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-08</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>18</v>
+        <v>Never Do - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:38</v>
+        <v>1:58</v>
       </c>
       <c r="H174" t="str">
-        <v>Conexión Divina</v>
+        <v>charlieonnafriday</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
+        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
+        <v>https://music.apple.com/us/album/never-do/1872842225</v>
       </c>
       <c r="L174" t="str">
-        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
+        <v>Never Do - charlieonnafriday</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>I Dare You</v>
+        <v>Primary Colors</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
+        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-08</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>I Dare You - Single</v>
+        <v>Lost on You</v>
       </c>
       <c r="G175" t="str">
-        <v>3:25</v>
+        <v>3:37</v>
       </c>
       <c r="H175" t="str">
-        <v>Dylan Dunlap</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
+        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
       </c>
       <c r="L175" t="str">
-        <v>I Dare You - Dylan Dunlap</v>
+        <v>Primary Colors - Tigers Jaw</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>new irish boyfriend</v>
+        <v>Rock Bottom</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-08</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>long time caller, first time listener</v>
+        <v>Rock Bottom / Octopus - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:50</v>
+        <v>4:10</v>
       </c>
       <c r="H176" t="str">
-        <v>vegas water taxi</v>
+        <v>King Krule</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
+        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
       </c>
       <c r="L176" t="str">
-        <v>new irish boyfriend - vegas water taxi</v>
+        <v>Rock Bottom - King Krule</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Everyone Around Me Dancing</v>
+        <v>Te Dedico</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
+        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-08</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Singing</v>
+        <v>Te Dedico - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:05</v>
+        <v>3:45</v>
       </c>
       <c r="H177" t="str">
-        <v>Gia Margaret</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
+        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
       </c>
       <c r="L177" t="str">
-        <v>Everyone Around Me Dancing - Gia Margaret</v>
+        <v>Te Dedico - Carlos Vives</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Good Enough (feat. Julie Doiron)</v>
+        <v>AUNQUE SEA EN DOS</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
+        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-08</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Big Changes</v>
+        <v>18</v>
       </c>
       <c r="G178" t="str">
-        <v>6:05</v>
+        <v>2:38</v>
       </c>
       <c r="H178" t="str">
-        <v>Status/Non-Status</v>
+        <v>Conexión Divina</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
+        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
+        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
       </c>
       <c r="L178" t="str">
-        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
+        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
+        <v>I Dare You</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
+        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-08</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
+        <v>I Dare You - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>4:09</v>
+        <v>3:25</v>
       </c>
       <c r="H179" t="str">
-        <v>Julian Lage</v>
+        <v>Dylan Dunlap</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
+        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
+        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
       </c>
       <c r="L179" t="str">
-        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
+        <v>I Dare You - Dylan Dunlap</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Big Deal</v>
+        <v>new irish boyfriend</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
+        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-08</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Big Deal - Single</v>
+        <v>long time caller, first time listener</v>
       </c>
       <c r="G180" t="str">
-        <v>3:47</v>
+        <v>3:50</v>
       </c>
       <c r="H180" t="str">
-        <v>In Color</v>
+        <v>vegas water taxi</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
+        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
       </c>
       <c r="L180" t="str">
-        <v>Big Deal - In Color</v>
+        <v>new irish boyfriend - vegas water taxi</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Buy What U Want</v>
+        <v>Everyone Around Me Dancing</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
+        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-08</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Road To Osshland III - EP</v>
+        <v>Singing</v>
       </c>
       <c r="G181" t="str">
-        <v>3:47</v>
+        <v>3:05</v>
       </c>
       <c r="H181" t="str">
-        <v>Black Fortune</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
+        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
       </c>
       <c r="L181" t="str">
-        <v>Buy What U Want - Black Fortune</v>
+        <v>Everyone Around Me Dancing - Gia Margaret</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Common Ground</v>
+        <v>Good Enough (feat. Julie Doiron)</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
+        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-08</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Common Ground - Single</v>
+        <v>Big Changes</v>
       </c>
       <c r="G182" t="str">
-        <v>1:42</v>
+        <v>6:05</v>
       </c>
       <c r="H182" t="str">
-        <v>ELIO</v>
+        <v>Status/Non-Status</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/elio/1501417625</v>
+        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
+        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
       </c>
       <c r="L182" t="str">
-        <v>Common Ground - ELIO</v>
+        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Cellophane</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
+        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-08</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Cellophane - Single</v>
+        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="G183" t="str">
-        <v>4:21</v>
+        <v>4:09</v>
       </c>
       <c r="H183" t="str">
-        <v>Maddie Zahm</v>
+        <v>Julian Lage</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
+        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
+        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
       </c>
       <c r="L183" t="str">
-        <v>Cellophane - Maddie Zahm</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>96 Camry</v>
+        <v>Big Deal</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
+        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-08</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>PRAY FOR ME</v>
+        <v>Big Deal - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:15</v>
+        <v>3:47</v>
       </c>
       <c r="H184" t="str">
-        <v>RAAHiiM</v>
+        <v>In Color</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
+        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
       </c>
       <c r="L184" t="str">
-        <v>96 Camry - RAAHiiM</v>
+        <v>Big Deal - In Color</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>La Allstar</v>
+        <v>Buy What U Want</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
+        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-08</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>La Allstar - Single</v>
+        <v>Road To Osshland III - EP</v>
       </c>
       <c r="G185" t="str">
-        <v>2:49</v>
+        <v>3:47</v>
       </c>
       <c r="H185" t="str">
-        <v>ELIKAI</v>
+        <v>Black Fortune</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
+        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
+        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
       </c>
       <c r="L185" t="str">
-        <v>La Allstar - ELIKAI</v>
+        <v>Buy What U Want - Black Fortune</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Luka</v>
+        <v>Common Ground</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/luka/1869396162</v>
+        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-08</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Luka - Single</v>
+        <v>Common Ground - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:07</v>
+        <v>1:42</v>
       </c>
       <c r="H186" t="str">
-        <v>Fonta</v>
+        <v>ELIO</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
+        <v>https://music.apple.com/us/artist/elio/1501417625</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/luka/1869396161</v>
+        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
       </c>
       <c r="L186" t="str">
-        <v>Luka - Fonta</v>
+        <v>Common Ground - ELIO</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Ganas De Tenerla</v>
+        <v>Cellophane</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
+        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-08</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Ganas De Tenerla - Single</v>
+        <v>Cellophane - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:06</v>
+        <v>4:21</v>
       </c>
       <c r="H187" t="str">
-        <v>Silvestre Dangond</v>
+        <v>Maddie Zahm</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
+        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
+        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
       </c>
       <c r="L187" t="str">
-        <v>Ganas De Tenerla - Silvestre Dangond</v>
+        <v>Cellophane - Maddie Zahm</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>In My Blue</v>
+        <v>96 Camry</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
+        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-08</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Doomsday...Don't Leave Me Here</v>
+        <v>PRAY FOR ME</v>
       </c>
       <c r="G188" t="str">
-        <v>3:26</v>
+        <v>3:15</v>
       </c>
       <c r="H188" t="str">
-        <v>Rosie Carney</v>
+        <v>RAAHiiM</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
+        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
+        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
       </c>
       <c r="L188" t="str">
-        <v>In My Blue - Rosie Carney</v>
+        <v>96 Camry - RAAHiiM</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Living With It (feat. Feist)</v>
+        <v>La Allstar</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
+        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-08</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Hurts Like Hell</v>
+        <v>La Allstar - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:20</v>
+        <v>2:49</v>
       </c>
       <c r="H189" t="str">
-        <v>Charlotte Cornfield</v>
+        <v>ELIKAI</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
+        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
+        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
       </c>
       <c r="L189" t="str">
-        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
+        <v>La Allstar - ELIKAI</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Silently</v>
+        <v>Luka</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/silently/1841629898</v>
+        <v>https://music.apple.com/us/song/luka/1869396162</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-08</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Croak Dream</v>
+        <v>Luka - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:29</v>
+        <v>2:07</v>
       </c>
       <c r="H190" t="str">
-        <v>Puma Blue</v>
+        <v>Fonta</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
+        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/silently/1841629444</v>
+        <v>https://music.apple.com/us/album/luka/1869396161</v>
       </c>
       <c r="L190" t="str">
-        <v>Silently - Puma Blue</v>
+        <v>Luka - Fonta</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Ashes &amp; Smoke</v>
+        <v>Ganas De Tenerla</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
+        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-08</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Ashes &amp; Smoke - Single</v>
+        <v>Ganas De Tenerla - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:05</v>
+        <v>3:06</v>
       </c>
       <c r="H191" t="str">
-        <v>Anna Graves</v>
+        <v>Silvestre Dangond</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
+        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
+        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
       </c>
       <c r="L191" t="str">
-        <v>Ashes &amp; Smoke - Anna Graves</v>
+        <v>Ganas De Tenerla - Silvestre Dangond</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Tormentor</v>
+        <v>In My Blue</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
+        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-08</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>The Flowers I See You In - EP</v>
+        <v>Doomsday...Don't Leave Me Here</v>
       </c>
       <c r="G192" t="str">
-        <v>2:40</v>
+        <v>3:26</v>
       </c>
       <c r="H192" t="str">
-        <v>Ninush</v>
+        <v>Rosie Carney</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
+        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
+        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
       </c>
       <c r="L192" t="str">
-        <v>Tormentor - Ninush</v>
+        <v>In My Blue - Rosie Carney</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Red Rocking Chair</v>
+        <v>Living With It (feat. Feist)</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
+        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-08</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Red Rocking Chair - Single</v>
+        <v>Hurts Like Hell</v>
       </c>
       <c r="G193" t="str">
-        <v>6:28</v>
+        <v>3:20</v>
       </c>
       <c r="H193" t="str">
-        <v>All Them Witches</v>
+        <v>Charlotte Cornfield</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
+        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
       </c>
       <c r="L193" t="str">
-        <v>Red Rocking Chair - All Them Witches</v>
+        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
+        <v>Silently</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
+        <v>https://music.apple.com/us/song/silently/1841629898</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-08</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>...of Death and Fire</v>
+        <v>Croak Dream</v>
       </c>
       <c r="G194" t="str">
-        <v>7:07</v>
+        <v>3:29</v>
       </c>
       <c r="H194" t="str">
-        <v>In Aeternum</v>
+        <v>Puma Blue</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
+        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
+        <v>https://music.apple.com/us/album/silently/1841629444</v>
       </c>
       <c r="L194" t="str">
-        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
+        <v>Silently - Puma Blue</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Mizantrop</v>
+        <v>Ashes &amp; Smoke</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
+        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-08</v>
@@ -7785,68 +7785,220 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Mizantrop</v>
+        <v>Ashes &amp; Smoke - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:42</v>
+        <v>3:05</v>
       </c>
       <c r="H195" t="str">
-        <v>She Past Away</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
+        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
+        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
       </c>
       <c r="L195" t="str">
-        <v>Mizantrop - She Past Away</v>
+        <v>Ashes &amp; Smoke - Anna Graves</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
+        <v>Tormentor</v>
+      </c>
+      <c r="B196" t="str">
+        <v/>
+      </c>
+      <c r="C196" t="str">
+        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
+      </c>
+      <c r="D196" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v>The Flowers I See You In - EP</v>
+      </c>
+      <c r="G196" t="str">
+        <v>2:40</v>
+      </c>
+      <c r="H196" t="str">
+        <v>Ninush</v>
+      </c>
+      <c r="I196" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J196" t="str">
+        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
+      </c>
+      <c r="K196" t="str">
+        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
+      </c>
+      <c r="L196" t="str">
+        <v>Tormentor - Ninush</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Red Rocking Chair</v>
+      </c>
+      <c r="B197" t="str">
+        <v/>
+      </c>
+      <c r="C197" t="str">
+        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
+      </c>
+      <c r="D197" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
+        <v>Red Rocking Chair - Single</v>
+      </c>
+      <c r="G197" t="str">
+        <v>6:28</v>
+      </c>
+      <c r="H197" t="str">
+        <v>All Them Witches</v>
+      </c>
+      <c r="I197" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J197" t="str">
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
+      </c>
+      <c r="K197" t="str">
+        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
+      </c>
+      <c r="L197" t="str">
+        <v>Red Rocking Chair - All Them Witches</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>...of Death and Fire</v>
+      </c>
+      <c r="G198" t="str">
+        <v>7:07</v>
+      </c>
+      <c r="H198" t="str">
+        <v>In Aeternum</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
+      </c>
+      <c r="L198" t="str">
+        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Mizantrop</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>Mizantrop</v>
+      </c>
+      <c r="G199" t="str">
+        <v>3:42</v>
+      </c>
+      <c r="H199" t="str">
+        <v>She Past Away</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Mizantrop - She Past Away</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>In the Name of the Moth</v>
       </c>
-      <c r="B196" t="str">
-        <v/>
-      </c>
-      <c r="C196" t="str">
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
         <v>https://music.apple.com/us/song/in-the-name-of-the-moth/1866911203</v>
       </c>
-      <c r="D196" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E196" t="str">
-        <v/>
-      </c>
-      <c r="F196" t="str">
+      <c r="D200" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
         <v>Hidden Fires Burn Hottest</v>
       </c>
-      <c r="G196" t="str">
+      <c r="G200" t="str">
         <v>7:15</v>
       </c>
-      <c r="H196" t="str">
+      <c r="H200" t="str">
         <v>Bosse-de-Nage</v>
       </c>
-      <c r="I196" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J196" t="str">
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
         <v>https://music.apple.com/us/artist/bosse-de-nage/465123183</v>
       </c>
-      <c r="K196" t="str">
+      <c r="K200" t="str">
         <v>https://music.apple.com/us/album/in-the-name-of-the-moth/1866911198</v>
       </c>
-      <c r="L196" t="str">
+      <c r="L200" t="str">
         <v>In the Name of the Moth - Bosse-de-Nage</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L196"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>צח חכים &amp; להקת רגעים - מחרוזת שבת 2026</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-08</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409543&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-08</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>6:00</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Taylor Swift</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>צח חכים &amp; להקת רגעים - מחרוזת שבת 2026</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>סדיאל בכר - אי אפשר להסביר</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-08</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409542&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-08</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>10 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>4:20</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Michael Bolton</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>סדיאל בכר - אי אפשר להסביר</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ניר קלברס - סיגריה בסלון</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-08</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409541&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-08</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>4:27</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Mariah Carey</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ניר קלברס - סיגריה בסלון</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מאור יפרח - אין עוד מלבדך</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-08</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409540&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-08</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>3:26</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Netflix</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מאור יפרח - אין עוד מלבדך</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B6" t="str">
-        <v>8 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-08</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>8 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>6:00</v>
+        <v>3:29</v>
       </c>
       <c r="H6" t="str">
-        <v>Taylor Swift</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>9 hours ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-08</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>9 hours ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:20</v>
+        <v>2:59</v>
       </c>
       <c r="H7" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-08</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>4:27</v>
+        <v>2:51</v>
       </c>
       <c r="H8" t="str">
-        <v>Mariah Carey</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-08</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:26</v>
+        <v>4:13</v>
       </c>
       <c r="H9" t="str">
-        <v>Netflix</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-08</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:29</v>
+        <v>4:41</v>
       </c>
       <c r="H10" t="str">
-        <v>Michael Bolton</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-08</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:59</v>
+        <v>7:03</v>
       </c>
       <c r="H11" t="str">
-        <v>mgk</v>
+        <v>Take That</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-08</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>2:51</v>
+        <v>4:37</v>
       </c>
       <c r="H12" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-08</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:13</v>
+        <v>3:54</v>
       </c>
       <c r="H13" t="str">
-        <v>Michael Bolton</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-08</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:41</v>
+        <v>3:06</v>
       </c>
       <c r="H14" t="str">
-        <v>NICK JONAS</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-08</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>7:03</v>
+        <v>3:21</v>
       </c>
       <c r="H15" t="str">
-        <v>Take That</v>
+        <v>George Birge</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-08</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:37</v>
+        <v>4:09</v>
       </c>
       <c r="H16" t="str">
-        <v>Cliff Richard</v>
+        <v>Warner Records</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-08</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:54</v>
+        <v>4:18</v>
       </c>
       <c r="H17" t="str">
-        <v>Bryan Adams</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-08</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:06</v>
+        <v>3:08</v>
       </c>
       <c r="H18" t="str">
-        <v>Anna Graves</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-08</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:21</v>
+        <v>4:03</v>
       </c>
       <c r="H19" t="str">
-        <v>George Birge</v>
+        <v>Olivia Newton-John</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
+        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-08</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:09</v>
+        <v>3:01</v>
       </c>
       <c r="H20" t="str">
-        <v>Warner Records</v>
+        <v>The Warning and Carin Leon</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
+        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-08</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:18</v>
+        <v>3:05</v>
       </c>
       <c r="H21" t="str">
-        <v>NICK JONAS</v>
+        <v>Iman Fandi</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
+        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-08</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:08</v>
+        <v>3:34</v>
       </c>
       <c r="H22" t="str">
-        <v>Charlie Puth</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
+        <v>Dylan Davidson - Escape Artist</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
+        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-08</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:03</v>
+        <v>3:15</v>
       </c>
       <c r="H23" t="str">
-        <v>Olivia Newton-John</v>
+        <v>Dylan Davidson</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
+        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
+        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-08</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:01</v>
+        <v>4:16</v>
       </c>
       <c r="H24" t="str">
-        <v>The Warning and Carin Leon</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
+        <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
+        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-08</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:05</v>
+        <v>3:53</v>
       </c>
       <c r="H25" t="str">
-        <v>Iman Fandi</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
+        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
+        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-08</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:34</v>
+        <v>2:25</v>
       </c>
       <c r="H26" t="str">
-        <v>Megan Moroney</v>
+        <v>Monsieur Periné</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Dylan Davidson - Escape Artist</v>
+        <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
+        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-08</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:15</v>
+        <v>4:09</v>
       </c>
       <c r="H27" t="str">
-        <v>Dylan Davidson</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
+        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
+        <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
+        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-08</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:16</v>
+        <v>2:45</v>
       </c>
       <c r="H28" t="str">
-        <v>Lady Gaga</v>
+        <v>Michael Aldag</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
+        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video)</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
+        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-08</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:53</v>
+        <v>4:07</v>
       </c>
       <c r="H29" t="str">
-        <v>Carlos Vives</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
+        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-08</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:25</v>
+        <v>4:34</v>
       </c>
       <c r="H30" t="str">
-        <v>Monsieur Periné</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
+        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-08</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:09</v>
+        <v>5:14</v>
       </c>
       <c r="H31" t="str">
-        <v>The Happy Fits</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>chase (lyric vid) - Michael Aldag</v>
+        <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
+        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-08</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:45</v>
+        <v>3:11</v>
       </c>
       <c r="H32" t="str">
-        <v>Michael Aldag</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
+        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
+        <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
+        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-08</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:07</v>
+        <v>3:40</v>
       </c>
       <c r="H33" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Lachie Gill</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
+        <v>Lachie Gill - Last Drive - Lachie Gill</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
+        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-08</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:34</v>
+        <v>3:45</v>
       </c>
       <c r="H34" t="str">
-        <v>Marc Anthony</v>
+        <v>Eli &amp; Fur</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
+        <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
+        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-08</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>5:14</v>
+        <v>4:19</v>
       </c>
       <c r="H35" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Freya Skye - why'd you have to call - Freya Skye</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer)</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
+        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-08</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:11</v>
+        <v>2:30</v>
       </c>
       <c r="H36" t="str">
-        <v>Michael Bolton</v>
+        <v>Jessie J</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Lachie Gill - Last Drive</v>
+        <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
+        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-08</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:40</v>
+        <v>4:24</v>
       </c>
       <c r="H37" t="str">
-        <v>Lachie Gill</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Lachie Gill - Last Drive - Lachie Gill</v>
+        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
+        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-08</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:45</v>
+        <v>2:33</v>
       </c>
       <c r="H38" t="str">
-        <v>Eli &amp; Fur</v>
+        <v>Clara Mae</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Freya Skye - why'd you have to call</v>
+        <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
+        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-08</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:19</v>
+        <v>3:25</v>
       </c>
       <c r="H39" t="str">
-        <v>Freya Skye</v>
+        <v>metricmusic</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Freya Skye - why'd you have to call - Freya Skye</v>
+        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
+        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-08</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>2:30</v>
+        <v>3:41</v>
       </c>
       <c r="H40" t="str">
-        <v>Jessie J</v>
+        <v>kesha</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
+        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-08</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:24</v>
+        <v>3:19</v>
       </c>
       <c r="H41" t="str">
-        <v>Marc Anthony</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
+        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-08</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:33</v>
+        <v>3:37</v>
       </c>
       <c r="H42" t="str">
-        <v>Clara Mae</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Metric - Victim of Luck (Official Music Video)</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
+        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-08</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:25</v>
+        <v>3:08</v>
       </c>
       <c r="H43" t="str">
-        <v>metricmusic</v>
+        <v>Bob Moses</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
+        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-08</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:41</v>
+        <v>3:28</v>
       </c>
       <c r="H44" t="str">
-        <v>kesha</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
+        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-08</v>
@@ -2088,10 +2088,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:19</v>
+        <v>5:05</v>
       </c>
       <c r="H45" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
+        <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B46" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
+        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-08</v>
@@ -2126,10 +2126,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:37</v>
+        <v>3:14</v>
       </c>
       <c r="H46" t="str">
-        <v>Vera Blue</v>
+        <v>Loreen</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
+        <v>Loreen - Feels Like Heaven - Loreen</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B47" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
+        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-08</v>
@@ -2164,10 +2164,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:08</v>
+        <v>3:36</v>
       </c>
       <c r="H47" t="str">
-        <v>Bob Moses</v>
+        <v>Take That</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B48" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
+        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-08</v>
@@ -2202,10 +2202,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:28</v>
+        <v>5:31</v>
       </c>
       <c r="H48" t="str">
-        <v>Marc Anthony</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
+        <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B49" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
+        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-08</v>
@@ -2240,10 +2240,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>5:05</v>
+        <v>3:37</v>
       </c>
       <c r="H49" t="str">
-        <v>Marc Anthony</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
+        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Loreen - Feels Like Heaven</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-08</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:14</v>
+        <v>4:58</v>
       </c>
       <c r="H50" t="str">
-        <v>Loreen</v>
+        <v>The Warning</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Loreen - Feels Like Heaven - Loreen</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B51" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-08</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:36</v>
+        <v>5:08</v>
       </c>
       <c r="H51" t="str">
-        <v>Take That</v>
+        <v>The Offspring</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B52" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-08</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>5:31</v>
+        <v>4:38</v>
       </c>
       <c r="H52" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Roxette</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio)</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
       </c>
       <c r="B53" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-08</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:37</v>
+        <v>3:50</v>
       </c>
       <c r="H53" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-08</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:58</v>
+        <v>3:10</v>
       </c>
       <c r="H54" t="str">
-        <v>The Warning</v>
+        <v>Joseph</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-08</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>5:08</v>
+        <v>2:44</v>
       </c>
       <c r="H55" t="str">
-        <v>The Offspring</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-08</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:38</v>
+        <v>2:57</v>
       </c>
       <c r="H56" t="str">
-        <v>Roxette</v>
+        <v>Take That</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-08</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:50</v>
+        <v>3:07</v>
       </c>
       <c r="H57" t="str">
-        <v>Jessie Ware</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-08</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:10</v>
+        <v>4:47</v>
       </c>
       <c r="H58" t="str">
-        <v>Joseph</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B59" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-08</v>
@@ -2620,10 +2620,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:44</v>
+        <v>3:22</v>
       </c>
       <c r="H59" t="str">
-        <v>Dean Lewis</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-08</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:57</v>
+        <v>2:48</v>
       </c>
       <c r="H60" t="str">
-        <v>Take That</v>
+        <v>only the poets</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-08</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:07</v>
+        <v>2:52</v>
       </c>
       <c r="H61" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-08</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>4:47</v>
+        <v>3:33</v>
       </c>
       <c r="H62" t="str">
-        <v>Paris Paloma</v>
+        <v>David Guetta</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-08</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:22</v>
+        <v>2:41</v>
       </c>
       <c r="H63" t="str">
-        <v>Zara Larsson</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-08</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:48</v>
+        <v>4:01</v>
       </c>
       <c r="H64" t="str">
-        <v>only the poets</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-08</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:52</v>
+        <v>3:16</v>
       </c>
       <c r="H65" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Dogpark</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-08</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:33</v>
+        <v>3:03</v>
       </c>
       <c r="H66" t="str">
-        <v>David Guetta</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-08</v>
@@ -2927,7 +2927,7 @@
         <v>2:41</v>
       </c>
       <c r="H67" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>ERNEST</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-08</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:01</v>
+        <v>3:05</v>
       </c>
       <c r="H68" t="str">
-        <v>Ella Langley</v>
+        <v>Labrinth</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-08</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:16</v>
+        <v>2:46</v>
       </c>
       <c r="H69" t="str">
-        <v>Dogpark</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-08</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:03</v>
+        <v>3:32</v>
       </c>
       <c r="H70" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-08</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:41</v>
+        <v>3:42</v>
       </c>
       <c r="H71" t="str">
-        <v>ERNEST</v>
+        <v>Cannons</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-08</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:05</v>
+        <v>2:38</v>
       </c>
       <c r="H72" t="str">
-        <v>Labrinth</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-08</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:46</v>
+        <v>3:10</v>
       </c>
       <c r="H73" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-08</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:32</v>
+        <v>3:57</v>
       </c>
       <c r="H74" t="str">
-        <v>VOILÀ</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-08</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:42</v>
+        <v>2:19</v>
       </c>
       <c r="H75" t="str">
-        <v>Cannons</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-08</v>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:38</v>
+        <v>4:04</v>
       </c>
       <c r="H76" t="str">
-        <v>Kylie Morgan</v>
+        <v>India Martínez</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-08</v>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:10</v>
+        <v>2:16</v>
       </c>
       <c r="H77" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-08</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:57</v>
+        <v>5:58</v>
       </c>
       <c r="H78" t="str">
-        <v>Willie Nelson</v>
+        <v>TINI</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-08</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:19</v>
+        <v>3:26</v>
       </c>
       <c r="H79" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Charley</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-08</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:04</v>
+        <v>4:05</v>
       </c>
       <c r="H80" t="str">
-        <v>India Martínez</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-08</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:16</v>
+        <v>3:16</v>
       </c>
       <c r="H81" t="str">
-        <v>Chelsea Cutler</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-08</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>5:58</v>
+        <v>3:14</v>
       </c>
       <c r="H82" t="str">
-        <v>TINI</v>
+        <v>Beck</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B83" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-08</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:26</v>
+        <v>2:57</v>
       </c>
       <c r="H83" t="str">
-        <v>Charley</v>
+        <v>The Offspring</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B84" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-08</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:05</v>
+        <v>4:10</v>
       </c>
       <c r="H84" t="str">
-        <v>Demi Lovato</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B85" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-08</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:16</v>
+        <v>2:10</v>
       </c>
       <c r="H85" t="str">
-        <v>Teddy Swims</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B86" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-08</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:14</v>
+        <v>3:52</v>
       </c>
       <c r="H86" t="str">
-        <v>Beck</v>
+        <v>lights</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B87" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-08</v>
@@ -3684,10 +3684,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:57</v>
+        <v>3:50</v>
       </c>
       <c r="H87" t="str">
-        <v>The Offspring</v>
+        <v>Telenova</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B88" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-08</v>
@@ -3722,10 +3722,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:10</v>
+        <v>5:32</v>
       </c>
       <c r="H88" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>Marcin</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-08</v>
@@ -3760,10 +3760,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:10</v>
+        <v>4:27</v>
       </c>
       <c r="H89" t="str">
-        <v>Jason Derulo</v>
+        <v>We Three</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-08</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:52</v>
+        <v>3:01</v>
       </c>
       <c r="H90" t="str">
-        <v>lights</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B91" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-08</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>11 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:50</v>
+        <v>3:20</v>
       </c>
       <c r="H91" t="str">
-        <v>Telenova</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-08</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
-        <v>5:32</v>
+        <v>3:34</v>
       </c>
       <c r="H92" t="str">
-        <v>Marcin</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-08</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>11 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>4:27</v>
+        <v>4:01</v>
       </c>
       <c r="H93" t="str">
-        <v>We Three</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B94" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-08</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:01</v>
+        <v>3:24</v>
       </c>
       <c r="H94" t="str">
-        <v>Timebelle Official</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-08</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:20</v>
+        <v>5:52</v>
       </c>
       <c r="H95" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-08</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:34</v>
+        <v>5:01</v>
       </c>
       <c r="H96" t="str">
-        <v>Clinton Kane</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-08</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:01</v>
+        <v>4:12</v>
       </c>
       <c r="H97" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-08</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:24</v>
+        <v>3:59</v>
       </c>
       <c r="H98" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-08</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>5:52</v>
+        <v>2:56</v>
       </c>
       <c r="H99" t="str">
-        <v>Harry Styles</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-08</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:01</v>
+        <v>3:46</v>
       </c>
       <c r="H100" t="str">
-        <v>Neal Francis</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Bella White - Dream Song (Official Audio)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-08</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:12</v>
+        <v>4:37</v>
       </c>
       <c r="H101" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Bella White</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Die For Me</v>
       </c>
       <c r="B102" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-08</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>2 weeks ago</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G102" t="str">
-        <v>3:59</v>
+        <v>3:00</v>
       </c>
       <c r="H102" t="str">
-        <v>Holly Humberstone</v>
+        <v>ZAYN</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
       </c>
       <c r="L102" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Die For Me - ZAYN</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Two Six</v>
       </c>
       <c r="B103" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://music.apple.com/us/song/two-six/1875080974</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-08</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>2 weeks ago</v>
+        <v>The Fall-Off</v>
       </c>
       <c r="G103" t="str">
-        <v>2:56</v>
+        <v>3:16</v>
       </c>
       <c r="H103" t="str">
-        <v>Cliff Richard</v>
+        <v>J. Cole</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/two-six/1875080726</v>
       </c>
       <c r="L103" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Two Six - J. Cole</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Dracula (JENNIE Remix)</v>
       </c>
       <c r="B104" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-08</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>2 weeks ago</v>
+        <v>Dracula (Remix) - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:46</v>
+        <v>3:29</v>
       </c>
       <c r="H104" t="str">
-        <v>Jessie Ware</v>
+        <v>Tame Impala</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
       </c>
       <c r="L104" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Dracula (JENNIE Remix) - Tame Impala</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Hotel California</v>
       </c>
       <c r="B105" t="str">
-        <v>2 weeks ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-08</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>2 weeks ago</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G105" t="str">
-        <v>4:37</v>
+        <v>2:08</v>
       </c>
       <c r="H105" t="str">
-        <v>Bella White</v>
+        <v>Joji</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
       </c>
       <c r="L105" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Hotel California - Joji</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Die For Me</v>
+        <v>Homewrecker</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
+        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-08</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>KONNAKOL</v>
+        <v>Homewrecker - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:00</v>
+        <v>3:29</v>
       </c>
       <c r="H106" t="str">
-        <v>ZAYN</v>
+        <v>sombr</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
+        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
       </c>
       <c r="L106" t="str">
-        <v>Die For Me - ZAYN</v>
+        <v>Homewrecker - sombr</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Two Six</v>
+        <v>Might Just</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/two-six/1875080974</v>
+        <v>https://music.apple.com/us/song/might-just/1858755211</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-08</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>The Fall-Off</v>
+        <v>Do You Still Love Me?</v>
       </c>
       <c r="G107" t="str">
-        <v>3:16</v>
+        <v>3:43</v>
       </c>
       <c r="H107" t="str">
-        <v>J. Cole</v>
+        <v>Ella Mai</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
+        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/two-six/1875080726</v>
+        <v>https://music.apple.com/us/album/might-just/1858754868</v>
       </c>
       <c r="L107" t="str">
-        <v>Two Six - J. Cole</v>
+        <v>Might Just - Ella Mai</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Dracula (JENNIE Remix)</v>
+        <v>Cloud 9</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
+        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-08</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Dracula (Remix) - Single</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G108" t="str">
-        <v>3:29</v>
+        <v>3:33</v>
       </c>
       <c r="H108" t="str">
-        <v>Tame Impala</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
+        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
       </c>
       <c r="L108" t="str">
-        <v>Dracula (JENNIE Remix) - Tame Impala</v>
+        <v>Cloud 9 - Megan Moroney</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Hotel California</v>
+        <v>Cry</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
+        <v>https://music.apple.com/us/song/cry/1845189974</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-08</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Piss In The Wind</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G109" t="str">
-        <v>2:08</v>
+        <v>3:07</v>
       </c>
       <c r="H109" t="str">
-        <v>Joji</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
+        <v>https://music.apple.com/us/album/cry/1845189970</v>
       </c>
       <c r="L109" t="str">
-        <v>Hotel California - Joji</v>
+        <v>Cry - Charlie Puth</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Homewrecker</v>
+        <v>I'll Change for You</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
+        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-08</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Homewrecker - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G110" t="str">
-        <v>3:29</v>
+        <v>3:16</v>
       </c>
       <c r="H110" t="str">
-        <v>sombr</v>
+        <v>Mitski</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
+        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
       </c>
       <c r="L110" t="str">
-        <v>Homewrecker - sombr</v>
+        <v>I'll Change for You - Mitski</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Might Just</v>
+        <v>ASSIGNMENT</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/might-just/1858755211</v>
+        <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-08</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Do You Still Love Me?</v>
+        <v>ASSIGNMENT - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:43</v>
+        <v>2:23</v>
       </c>
       <c r="H111" t="str">
-        <v>Ella Mai</v>
+        <v>Power Snatch</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
+        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/might-just/1858754868</v>
+        <v>https://music.apple.com/us/album/assignment/1872764438</v>
       </c>
       <c r="L111" t="str">
-        <v>Might Just - Ella Mai</v>
+        <v>ASSIGNMENT - Power Snatch</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Cloud 9</v>
+        <v>Como en el Idilio</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
+        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-08</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Cloud 9</v>
+        <v>Como en el Idilio - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:33</v>
+        <v>4:27</v>
       </c>
       <c r="H112" t="str">
-        <v>Megan Moroney</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
+        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
       </c>
       <c r="L112" t="str">
-        <v>Cloud 9 - Megan Moroney</v>
+        <v>Como en el Idilio - Marc Anthony</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Cry</v>
+        <v>golden boy</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/cry/1845189974</v>
+        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-08</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Whatever's Clever!</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G113" t="str">
-        <v>3:07</v>
+        <v>3:17</v>
       </c>
       <c r="H113" t="str">
-        <v>Charlie Puth</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/cry/1845189970</v>
+        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
       </c>
       <c r="L113" t="str">
-        <v>Cry - Charlie Puth</v>
+        <v>golden boy - Freya Skye</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>I'll Change for You</v>
+        <v>Penny in the Lake</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
+        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-08</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>Singin’ to an Empty Chair</v>
       </c>
       <c r="G114" t="str">
-        <v>3:16</v>
+        <v>3:51</v>
       </c>
       <c r="H114" t="str">
-        <v>Mitski</v>
+        <v>Ratboys</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
+        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
       </c>
       <c r="L114" t="str">
-        <v>I'll Change for You - Mitski</v>
+        <v>Penny in the Lake - Ratboys</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>ASSIGNMENT</v>
+        <v>Heaven</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/assignment/1872764440</v>
+        <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-08</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>ASSIGNMENT - Single</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G115" t="str">
-        <v>2:23</v>
+        <v>4:26</v>
       </c>
       <c r="H115" t="str">
-        <v>Power Snatch</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/assignment/1872764438</v>
+        <v>https://music.apple.com/us/album/heaven/1862570378</v>
       </c>
       <c r="L115" t="str">
-        <v>ASSIGNMENT - Power Snatch</v>
+        <v>Heaven - Arlo Parks</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Como en el Idilio</v>
+        <v>Adrenaline</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
+        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-08</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Como en el Idilio - Single</v>
+        <v>GOLDEN HOUR : Part.4 - EP</v>
       </c>
       <c r="G116" t="str">
-        <v>4:27</v>
+        <v>3:39</v>
       </c>
       <c r="H116" t="str">
-        <v>Marc Anthony</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
+        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
       </c>
       <c r="L116" t="str">
-        <v>Como en el Idilio - Marc Anthony</v>
+        <v>Adrenaline - ATEEZ</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>golden boy</v>
+        <v>Sweet To Me</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
+        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-08</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>stardust - EP</v>
+        <v>Sunday Best</v>
       </c>
       <c r="G117" t="str">
-        <v>3:17</v>
+        <v>4:17</v>
       </c>
       <c r="H117" t="str">
-        <v>Freya Skye</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
+        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
       </c>
       <c r="L117" t="str">
-        <v>golden boy - Freya Skye</v>
+        <v>Sweet To Me - Nick Jonas</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Penny in the Lake</v>
+        <v>Time Goes On</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
+        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-08</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Singin’ to an Empty Chair</v>
+        <v>Time Goes On - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:51</v>
+        <v>2:55</v>
       </c>
       <c r="H118" t="str">
-        <v>Ratboys</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
+        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
       </c>
       <c r="L118" t="str">
-        <v>Penny in the Lake - Ratboys</v>
+        <v>Time Goes On - Koe Wetzel</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Heaven</v>
+        <v>Drive Safe</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/heaven/1862570892</v>
+        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-08</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Drive Safe - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>4:26</v>
+        <v>3:21</v>
       </c>
       <c r="H119" t="str">
-        <v>Arlo Parks</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/heaven/1862570378</v>
+        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
       </c>
       <c r="L119" t="str">
-        <v>Heaven - Arlo Parks</v>
+        <v>Drive Safe - Myles Smith</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Adrenaline</v>
+        <v>Love To Be Loved</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
+        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-08</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>GOLDEN HOUR : Part.4 - EP</v>
+        <v>Love To Be Loved - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:39</v>
+        <v>2:50</v>
       </c>
       <c r="H120" t="str">
-        <v>ATEEZ</v>
+        <v>The Warning</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
+        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
       </c>
       <c r="L120" t="str">
-        <v>Adrenaline - ATEEZ</v>
+        <v>Love To Be Loved - The Warning</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Sweet To Me</v>
+        <v>Mi Yo de Antes</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-08</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Sunday Best</v>
+        <v>Mi Yo de Antes - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:17</v>
+        <v>3:02</v>
       </c>
       <c r="H121" t="str">
-        <v>Nick Jonas</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
       </c>
       <c r="L121" t="str">
-        <v>Sweet To Me - Nick Jonas</v>
+        <v>Mi Yo de Antes - Eden Muñoz</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Time Goes On</v>
+        <v>Omens</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
+        <v>https://music.apple.com/us/song/omens/1872546206</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-08</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Time Goes On - Single</v>
+        <v>Omens - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:55</v>
+        <v>2:00</v>
       </c>
       <c r="H122" t="str">
-        <v>Koe Wetzel</v>
+        <v>EsDeeKid</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
+        <v>https://music.apple.com/us/album/omens/1872546204</v>
       </c>
       <c r="L122" t="str">
-        <v>Time Goes On - Koe Wetzel</v>
+        <v>Omens - EsDeeKid</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Drive Safe</v>
+        <v>My Regards</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
+        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-08</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Drive Safe - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G123" t="str">
-        <v>3:21</v>
+        <v>3:11</v>
       </c>
       <c r="H123" t="str">
-        <v>Myles Smith</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
+        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
       </c>
       <c r="L123" t="str">
-        <v>Drive Safe - Myles Smith</v>
+        <v>My Regards - Maisie Peters</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Love To Be Loved</v>
+        <v>Time After Time</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
+        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-08</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Love To Be Loved - Single</v>
+        <v>Time After Time - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:50</v>
+        <v>2:48</v>
       </c>
       <c r="H124" t="str">
-        <v>The Warning</v>
+        <v>EJAE</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
+        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
       </c>
       <c r="L124" t="str">
-        <v>Love To Be Loved - The Warning</v>
+        <v>Time After Time - EJAE</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Mi Yo de Antes</v>
+        <v>Don't Want Your Love</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
+        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-08</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Mi Yo de Antes - Single</v>
+        <v>ODYSSEY</v>
       </c>
       <c r="G125" t="str">
-        <v>3:02</v>
+        <v>3:12</v>
       </c>
       <c r="H125" t="str">
-        <v>Eden Muñoz</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
+        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
       </c>
       <c r="L125" t="str">
-        <v>Mi Yo de Antes - Eden Muñoz</v>
+        <v>Don't Want Your Love - ILLENIUM</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Omens</v>
+        <v>Pa' Los Envidiosos</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/omens/1872546206</v>
+        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-08</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Omens - Single</v>
+        <v>Pa' Los Envidiosos - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:00</v>
+        <v>3:37</v>
       </c>
       <c r="H126" t="str">
-        <v>EsDeeKid</v>
+        <v>Pitbull</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/omens/1872546204</v>
+        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
       </c>
       <c r="L126" t="str">
-        <v>Omens - EsDeeKid</v>
+        <v>Pa' Los Envidiosos - Pitbull</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>My Regards</v>
+        <v>Plei</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
+        <v>https://music.apple.com/us/song/plei/1872137577</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-08</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Florescence</v>
+        <v>Plei - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:11</v>
+        <v>3:22</v>
       </c>
       <c r="H127" t="str">
-        <v>Maisie Peters</v>
+        <v>Chuwi</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
+        <v>https://music.apple.com/us/album/plei/1872137372</v>
       </c>
       <c r="L127" t="str">
-        <v>My Regards - Maisie Peters</v>
+        <v>Plei - Chuwi</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Time After Time</v>
+        <v>Flood (feat. Bon Iver)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
+        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-08</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Time After Time - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G128" t="str">
-        <v>2:48</v>
+        <v>2:59</v>
       </c>
       <c r="H128" t="str">
-        <v>EJAE</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
+        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
       </c>
       <c r="L128" t="str">
-        <v>Time After Time - EJAE</v>
+        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Don't Want Your Love</v>
+        <v>Rain</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
+        <v>https://music.apple.com/us/song/rain/1867258289</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-08</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>ODYSSEY</v>
+        <v>Rain - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:12</v>
+        <v>3:28</v>
       </c>
       <c r="H129" t="str">
-        <v>ILLENIUM</v>
+        <v>FISHER</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
+        <v>https://music.apple.com/us/album/rain/1867258288</v>
       </c>
       <c r="L129" t="str">
-        <v>Don't Want Your Love - ILLENIUM</v>
+        <v>Rain - FISHER</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Pa' Los Envidiosos</v>
+        <v>Release The Pressure</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
+        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-08</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Pa' Los Envidiosos - Single</v>
+        <v>Release The Pressure - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:37</v>
+        <v>3:23</v>
       </c>
       <c r="H130" t="str">
-        <v>Pitbull</v>
+        <v>Calvin Harris</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
+        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
       </c>
       <c r="L130" t="str">
-        <v>Pa' Los Envidiosos - Pitbull</v>
+        <v>Release The Pressure - Calvin Harris</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Plei</v>
+        <v>Sexistential (Arca’s Take)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/plei/1872137577</v>
+        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-08</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Plei - Single</v>
+        <v>Sexistential (Arca’s Take) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:22</v>
+        <v>3:44</v>
       </c>
       <c r="H131" t="str">
-        <v>Chuwi</v>
+        <v>Robyn</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/plei/1872137372</v>
+        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
       </c>
       <c r="L131" t="str">
-        <v>Plei - Chuwi</v>
+        <v>Sexistential (Arca’s Take) - Robyn</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Flood (feat. Bon Iver)</v>
+        <v>heal something</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
+        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-08</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>ACT II</v>
       </c>
       <c r="G132" t="str">
-        <v>2:59</v>
+        <v>3:01</v>
       </c>
       <c r="H132" t="str">
-        <v>Dua Saleh</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
+        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
       </c>
       <c r="L132" t="str">
-        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
+        <v>heal something - Sasha Keable</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Rain</v>
+        <v>Buenos Días</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/rain/1867258289</v>
+        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-08</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Rain - Single</v>
+        <v>Buenos Días - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:28</v>
+        <v>2:39</v>
       </c>
       <c r="H133" t="str">
-        <v>FISHER</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/rain/1867258288</v>
+        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
       </c>
       <c r="L133" t="str">
-        <v>Rain - FISHER</v>
+        <v>Buenos Días - Eladio Carrión</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Release The Pressure</v>
+        <v>COOK</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
+        <v>https://music.apple.com/us/song/cook/1872816147</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-08</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Release The Pressure - Single</v>
+        <v>COOK - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H134" t="str">
-        <v>Calvin Harris</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
+        <v>https://music.apple.com/us/album/cook/1872816146</v>
       </c>
       <c r="L134" t="str">
-        <v>Release The Pressure - Calvin Harris</v>
+        <v>COOK - SOFI TUKKER</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Sexistential (Arca’s Take)</v>
+        <v>You Got to Lose</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
+        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-08</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Sexistential (Arca’s Take) - Single</v>
+        <v>Peaches!</v>
       </c>
       <c r="G135" t="str">
-        <v>3:44</v>
+        <v>3:17</v>
       </c>
       <c r="H135" t="str">
-        <v>Robyn</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
+        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
       </c>
       <c r="L135" t="str">
-        <v>Sexistential (Arca’s Take) - Robyn</v>
+        <v>You Got to Lose - The Black Keys</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>heal something</v>
+        <v>Different Kind Of Love</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
+        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-08</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>ACT II</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G136" t="str">
-        <v>3:01</v>
+        <v>3:39</v>
       </c>
       <c r="H136" t="str">
-        <v>Sasha Keable</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
+        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
       </c>
       <c r="L136" t="str">
-        <v>heal something - Sasha Keable</v>
+        <v>Different Kind Of Love - Young the Giant</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Buenos Días</v>
+        <v>Living Water</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
+        <v>https://music.apple.com/us/song/living-water/1871565262</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-08</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Buenos Días - Single</v>
+        <v>Reconstruction: Second Story</v>
       </c>
       <c r="G137" t="str">
-        <v>2:39</v>
+        <v>2:09</v>
       </c>
       <c r="H137" t="str">
-        <v>Eladio Carrión</v>
+        <v>Lecrae</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
+        <v>https://music.apple.com/us/album/living-water/1871564892</v>
       </c>
       <c r="L137" t="str">
-        <v>Buenos Días - Eladio Carrión</v>
+        <v>Living Water - Lecrae</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>COOK</v>
+        <v>What It Feels Like</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/cook/1872816147</v>
+        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-08</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>COOK - Single</v>
+        <v>What It Feels Like - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:50</v>
+        <v>2:18</v>
       </c>
       <c r="H138" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/cook/1872816146</v>
+        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
       </c>
       <c r="L138" t="str">
-        <v>COOK - SOFI TUKKER</v>
+        <v>What It Feels Like - Dillon Francis</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>You Got to Lose</v>
+        <v>neck</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
+        <v>https://music.apple.com/us/song/neck/1866953832</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-08</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Peaches!</v>
+        <v>neck - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:17</v>
+        <v>3:40</v>
       </c>
       <c r="H139" t="str">
-        <v>The Black Keys</v>
+        <v>Mau P</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
+        <v>https://music.apple.com/us/album/neck/1866953831</v>
       </c>
       <c r="L139" t="str">
-        <v>You Got to Lose - The Black Keys</v>
+        <v>neck - Mau P</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Different Kind Of Love</v>
+        <v>Colorblind</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
+        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-08</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Victory Garden</v>
+        <v>Colorblind - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:39</v>
+        <v>2:56</v>
       </c>
       <c r="H140" t="str">
-        <v>Young the Giant</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
+        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
       </c>
       <c r="L140" t="str">
-        <v>Different Kind Of Love - Young the Giant</v>
+        <v>Colorblind - Gavin Adcock</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Living Water</v>
+        <v>Au Revoir Reservoir</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/living-water/1871565262</v>
+        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-08</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Reconstruction: Second Story</v>
+        <v>Tenterhooks</v>
       </c>
       <c r="G141" t="str">
-        <v>2:09</v>
+        <v>3:21</v>
       </c>
       <c r="H141" t="str">
-        <v>Lecrae</v>
+        <v>Silversun Pickups</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
+        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/living-water/1871564892</v>
+        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
       </c>
       <c r="L141" t="str">
-        <v>Living Water - Lecrae</v>
+        <v>Au Revoir Reservoir - Silversun Pickups</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>What It Feels Like</v>
+        <v>Flavorless</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
+        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-08</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>What It Feels Like - Single</v>
+        <v>Flavorless - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:18</v>
+        <v>3:31</v>
       </c>
       <c r="H142" t="str">
-        <v>Dillon Francis</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
+        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
       </c>
       <c r="L142" t="str">
-        <v>What It Feels Like - Dillon Francis</v>
+        <v>Flavorless - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>neck</v>
+        <v>Nunca</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/neck/1866953832</v>
+        <v>https://music.apple.com/us/song/nunca/1860691713</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-08</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>neck - Single</v>
+        <v>ESCENAS</v>
       </c>
       <c r="G143" t="str">
-        <v>3:40</v>
+        <v>3:05</v>
       </c>
       <c r="H143" t="str">
-        <v>Mau P</v>
+        <v>Sin Bandera</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
+        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/neck/1866953831</v>
+        <v>https://music.apple.com/us/album/nunca/1860691704</v>
       </c>
       <c r="L143" t="str">
-        <v>neck - Mau P</v>
+        <v>Nunca - Sin Bandera</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Colorblind</v>
+        <v>Just In Case</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
+        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-08</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Colorblind - Single</v>
+        <v>NO HArD FEELINGS (Deluxe)</v>
       </c>
       <c r="G144" t="str">
-        <v>2:56</v>
+        <v>1:45</v>
       </c>
       <c r="H144" t="str">
-        <v>Gavin Adcock</v>
+        <v>Marc E. Bassy</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
+        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
       </c>
       <c r="L144" t="str">
-        <v>Colorblind - Gavin Adcock</v>
+        <v>Just In Case - Marc E. Bassy</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Au Revoir Reservoir</v>
+        <v>Thinking of You</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
+        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-08</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Tenterhooks</v>
+        <v>Thinking of You - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:21</v>
+        <v>3:00</v>
       </c>
       <c r="H145" t="str">
-        <v>Silversun Pickups</v>
+        <v>AP Dhillon</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
+        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
+        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
       </c>
       <c r="L145" t="str">
-        <v>Au Revoir Reservoir - Silversun Pickups</v>
+        <v>Thinking of You - AP Dhillon</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Flavorless</v>
+        <v>House Of Cards</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/flavorless/1870741358</v>
+        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-08</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Flavorless - Single</v>
+        <v>House of Cards</v>
       </c>
       <c r="G146" t="str">
-        <v>3:31</v>
+        <v>3:26</v>
       </c>
       <c r="H146" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/flavorless/1870741357</v>
+        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
       </c>
       <c r="L146" t="str">
-        <v>Flavorless - Dexter and The Moonrocks</v>
+        <v>House Of Cards - The Amity Affliction</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Nunca</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/nunca/1860691713</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-08</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>ESCENAS</v>
+        <v>Stay With Me - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:05</v>
+        <v>3:21</v>
       </c>
       <c r="H147" t="str">
-        <v>Sin Bandera</v>
+        <v>Agents Of Time</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/sin-bandera/14483319</v>
+        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/nunca/1860691704</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
       </c>
       <c r="L147" t="str">
-        <v>Nunca - Sin Bandera</v>
+        <v>Stay With Me - Agents Of Time</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Just In Case</v>
+        <v>I had a dream...</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
+        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-08</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>NO HArD FEELINGS (Deluxe)</v>
+        <v>Dream inside a dream…</v>
       </c>
       <c r="G148" t="str">
-        <v>1:45</v>
+        <v>2:39</v>
       </c>
       <c r="H148" t="str">
-        <v>Marc E. Bassy</v>
+        <v>R3HAB</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/marc-e-bassy/899254194</v>
+        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/just-in-case/1867547944</v>
+        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
       </c>
       <c r="L148" t="str">
-        <v>Just In Case - Marc E. Bassy</v>
+        <v>I had a dream... - R3HAB</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Thinking of You</v>
+        <v>Back to You</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
+        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-08</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Thinking of You - Single</v>
+        <v>Satellite</v>
       </c>
       <c r="G149" t="str">
-        <v>3:00</v>
+        <v>3:10</v>
       </c>
       <c r="H149" t="str">
-        <v>AP Dhillon</v>
+        <v>Charlotte Sands</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/ap-dhillon/1484701109</v>
+        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/thinking-of-you/1874128049</v>
+        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
       </c>
       <c r="L149" t="str">
-        <v>Thinking of You - AP Dhillon</v>
+        <v>Back to You - Charlotte Sands</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>House Of Cards</v>
+        <v>rager</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
+        <v>https://music.apple.com/us/song/rager/1872808801</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-08</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>House of Cards</v>
+        <v>rager</v>
       </c>
       <c r="G150" t="str">
-        <v>3:26</v>
+        <v>2:48</v>
       </c>
       <c r="H150" t="str">
-        <v>The Amity Affliction</v>
+        <v>Blusher</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
+        <v>https://music.apple.com/us/artist/blusher/485578161</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/house-of-cards/1871562765</v>
+        <v>https://music.apple.com/us/album/rager/1872808800</v>
       </c>
       <c r="L150" t="str">
-        <v>House Of Cards - The Amity Affliction</v>
+        <v>rager - Blusher</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Stay With Me</v>
+        <v>If Only</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
+        <v>https://music.apple.com/us/song/if-only/1870281318</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-08</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Stay With Me - Single</v>
+        <v>Patchwork</v>
       </c>
       <c r="G151" t="str">
-        <v>3:21</v>
+        <v>3:28</v>
       </c>
       <c r="H151" t="str">
-        <v>Agents Of Time</v>
+        <v>Charlotte Day Wilson</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
+        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1867490492</v>
+        <v>https://music.apple.com/us/album/if-only/1870281314</v>
       </c>
       <c r="L151" t="str">
-        <v>Stay With Me - Agents Of Time</v>
+        <v>If Only - Charlotte Day Wilson</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>I had a dream...</v>
+        <v>DON'T LOVE ME</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
+        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-08</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Dream inside a dream…</v>
+        <v>DON'T LOVE ME - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:39</v>
+        <v>3:01</v>
       </c>
       <c r="H152" t="str">
-        <v>R3HAB</v>
+        <v>Omah Lay</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/r3hab/331900515</v>
+        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/i-had-a-dream/1870971550</v>
+        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
       </c>
       <c r="L152" t="str">
-        <v>I had a dream... - R3HAB</v>
+        <v>DON'T LOVE ME - Omah Lay</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Back to You</v>
+        <v>No Sikes, No Tradesies</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
+        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-08</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Satellite</v>
+        <v>Sweet Nothings</v>
       </c>
       <c r="G153" t="str">
-        <v>3:10</v>
+        <v>2:32</v>
       </c>
       <c r="H153" t="str">
-        <v>Charlotte Sands</v>
+        <v>Jaymin</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-sands/1444713487</v>
+        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/back-to-you/1855724765</v>
+        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
       </c>
       <c r="L153" t="str">
-        <v>Back to You - Charlotte Sands</v>
+        <v>No Sikes, No Tradesies - Jaymin</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>rager</v>
+        <v>you woke me up</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/rager/1872808801</v>
+        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-08</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>rager</v>
+        <v>you woke me up - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:48</v>
+        <v>3:14</v>
       </c>
       <c r="H154" t="str">
-        <v>Blusher</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/blusher/485578161</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/rager/1872808800</v>
+        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
       </c>
       <c r="L154" t="str">
-        <v>rager - Blusher</v>
+        <v>you woke me up - Kevian Kraemer</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>If Only</v>
+        <v>No One’s Business</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/if-only/1870281318</v>
+        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-08</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Patchwork</v>
+        <v>No One’s Business - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:28</v>
+        <v>3:00</v>
       </c>
       <c r="H155" t="str">
-        <v>Charlotte Day Wilson</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-day-wilson/1053594538</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/if-only/1870281314</v>
+        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
       </c>
       <c r="L155" t="str">
-        <v>If Only - Charlotte Day Wilson</v>
+        <v>No One’s Business - Alicia Creti</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>DON'T LOVE ME</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
+        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-08</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>DON'T LOVE ME - Single</v>
+        <v>GOAT (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G156" t="str">
-        <v>3:01</v>
+        <v>3:13</v>
       </c>
       <c r="H156" t="str">
-        <v>Omah Lay</v>
+        <v>Bryant Barnes</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/omah-lay/1459319359</v>
+        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/dont-love-me/1873153611</v>
+        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
       </c>
       <c r="L156" t="str">
-        <v>DON'T LOVE ME - Omah Lay</v>
+        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>No Sikes, No Tradesies</v>
+        <v>TWICE</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
+        <v>https://music.apple.com/us/song/twice/1871578107</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-08</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Sweet Nothings</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G157" t="str">
-        <v>2:32</v>
+        <v>3:44</v>
       </c>
       <c r="H157" t="str">
-        <v>Jaymin</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/jaymin/1821260030</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/no-sikes-no-tradesies/1871576102</v>
+        <v>https://music.apple.com/us/album/twice/1871578103</v>
       </c>
       <c r="L157" t="str">
-        <v>No Sikes, No Tradesies - Jaymin</v>
+        <v>TWICE - Bilmuri</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>you woke me up</v>
+        <v>ROOFTOP</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
+        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-08</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>you woke me up - Single</v>
+        <v>ROOFTOP - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H158" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Hulvey</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/you-woke-me-up/1873402690</v>
+        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
       </c>
       <c r="L158" t="str">
-        <v>you woke me up - Kevian Kraemer</v>
+        <v>ROOFTOP - Hulvey</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>No One’s Business</v>
+        <v>Louisiana Rain</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
+        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-08</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>No One’s Business - Single</v>
+        <v>Louisiana Rain - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:00</v>
+        <v>3:41</v>
       </c>
       <c r="H159" t="str">
-        <v>Alicia Creti</v>
+        <v>Hunter Plake</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
+        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/no-ones-business/1873059626</v>
+        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
       </c>
       <c r="L159" t="str">
-        <v>No One’s Business - Alicia Creti</v>
+        <v>Louisiana Rain - Hunter Plake</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Don’t Dream It’s Over (From The Movie “GOAT”)</v>
+        <v>sharing Jesus with an ex</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
+        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-08</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>GOAT (Original Motion Picture Soundtrack)</v>
+        <v>sharing Jesus with an ex - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:13</v>
+        <v>1:55</v>
       </c>
       <c r="H160" t="str">
-        <v>Bryant Barnes</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/bryant-barnes/1579668433</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/dont-dream-its-over-from-the-movie-goat/1870623290</v>
+        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
       </c>
       <c r="L160" t="str">
-        <v>Don’t Dream It’s Over (From The Movie “GOAT”) - Bryant Barnes</v>
+        <v>sharing Jesus with an ex - Zoe Levert</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>TWICE</v>
+        <v>Body Control (feat. CHILLS)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/twice/1871578107</v>
+        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-08</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>KINDA HARD</v>
+        <v>Body Control (feat. CHILLS) - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:44</v>
+        <v>3:21</v>
       </c>
       <c r="H161" t="str">
-        <v>Bilmuri</v>
+        <v>Cole Knight</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/twice/1871578103</v>
+        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
       </c>
       <c r="L161" t="str">
-        <v>TWICE - Bilmuri</v>
+        <v>Body Control (feat. CHILLS) - Cole Knight</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>ROOFTOP</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/rooftop/1872534292</v>
+        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-08</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>ROOFTOP - Single</v>
+        <v>A Prayer for the Dancefloor - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:22</v>
+        <v>6:54</v>
       </c>
       <c r="H162" t="str">
-        <v>Hulvey</v>
+        <v>Charlotte de Witte</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/rooftop/1872534291</v>
+        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
       </c>
       <c r="L162" t="str">
-        <v>ROOFTOP - Hulvey</v>
+        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Louisiana Rain</v>
+        <v>Realm of Endless Misery</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
+        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-08</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Louisiana Rain - Single</v>
+        <v>Liturgy of Death</v>
       </c>
       <c r="G163" t="str">
-        <v>3:41</v>
+        <v>4:56</v>
       </c>
       <c r="H163" t="str">
-        <v>Hunter Plake</v>
+        <v>Mayhem</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/hunter-plake/1213481439</v>
+        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/louisiana-rain/1867848936</v>
+        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
       </c>
       <c r="L163" t="str">
-        <v>Louisiana Rain - Hunter Plake</v>
+        <v>Realm of Endless Misery - Mayhem</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>sharing Jesus with an ex</v>
+        <v>BLEACH</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
+        <v>https://music.apple.com/us/song/bleach/1869795882</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-08</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>sharing Jesus with an ex - Single</v>
+        <v>BLEACH - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>1:55</v>
+        <v>2:28</v>
       </c>
       <c r="H164" t="str">
-        <v>Zoe Levert</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/sharing-jesus-with-an-ex/1870912828</v>
+        <v>https://music.apple.com/us/album/bleach/1869795874</v>
       </c>
       <c r="L164" t="str">
-        <v>sharing Jesus with an ex - Zoe Levert</v>
+        <v>BLEACH - Ecca Vandal</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Body Control (feat. CHILLS)</v>
+        <v>pretty in pink</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
+        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-08</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Body Control (feat. CHILLS) - Single</v>
+        <v>AngelPink</v>
       </c>
       <c r="G165" t="str">
-        <v>3:21</v>
+        <v>3:13</v>
       </c>
       <c r="H165" t="str">
-        <v>Cole Knight</v>
+        <v>Keni Titus</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/cole-knight/589962652</v>
+        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/body-control-feat-chills/1867947668</v>
+        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
       </c>
       <c r="L165" t="str">
-        <v>Body Control (feat. CHILLS) - Cole Knight</v>
+        <v>pretty in pink - Keni Titus</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>A Prayer for the Dancefloor (feat. Conduit)</v>
+        <v>Pickup Man</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
+        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-08</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>A Prayer for the Dancefloor - Single</v>
+        <v>Pickup Man - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>6:54</v>
+        <v>3:28</v>
       </c>
       <c r="H166" t="str">
-        <v>Charlotte de Witte</v>
+        <v>Bayker Blankenship</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-de-witte/768227318</v>
+        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/a-prayer-for-the-dancefloor-feat-conduit/1869372833</v>
+        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
       </c>
       <c r="L166" t="str">
-        <v>A Prayer for the Dancefloor (feat. Conduit) - Charlotte de Witte</v>
+        <v>Pickup Man - Bayker Blankenship</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Realm of Endless Misery</v>
+        <v>Get To Drinkin'</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
+        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-08</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Liturgy of Death</v>
+        <v>Get To Drinkin' - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:56</v>
+        <v>2:48</v>
       </c>
       <c r="H167" t="str">
-        <v>Mayhem</v>
+        <v>Zach John King</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/mayhem/48820563</v>
+        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/realm-of-endless-misery/1846578494</v>
+        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
       </c>
       <c r="L167" t="str">
-        <v>Realm of Endless Misery - Mayhem</v>
+        <v>Get To Drinkin' - Zach John King</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>BLEACH</v>
+        <v>The Roses</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/bleach/1869795882</v>
+        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-08</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>BLEACH - Single</v>
+        <v>The Roses - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:28</v>
+        <v>3:02</v>
       </c>
       <c r="H168" t="str">
-        <v>Ecca Vandal</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/bleach/1869795874</v>
+        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
       </c>
       <c r="L168" t="str">
-        <v>BLEACH - Ecca Vandal</v>
+        <v>The Roses - Russell Dickerson</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>pretty in pink</v>
+        <v>I Should Know Better</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
+        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-08</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>AngelPink</v>
+        <v>Under The Streetlights</v>
       </c>
       <c r="G169" t="str">
-        <v>3:13</v>
+        <v>3:33</v>
       </c>
       <c r="H169" t="str">
-        <v>Keni Titus</v>
+        <v>Michael Marcagi</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/keni-titus/1686236534</v>
+        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/pretty-in-pink/1847770544</v>
+        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
       </c>
       <c r="L169" t="str">
-        <v>pretty in pink - Keni Titus</v>
+        <v>I Should Know Better - Michael Marcagi</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Pickup Man</v>
+        <v>Never Do</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
+        <v>https://music.apple.com/us/song/never-do/1872842226</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-08</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Pickup Man - Single</v>
+        <v>Never Do - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:28</v>
+        <v>1:58</v>
       </c>
       <c r="H170" t="str">
-        <v>Bayker Blankenship</v>
+        <v>charlieonnafriday</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/bayker-blankenship/1700165686</v>
+        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/pickup-man/1870883994</v>
+        <v>https://music.apple.com/us/album/never-do/1872842225</v>
       </c>
       <c r="L170" t="str">
-        <v>Pickup Man - Bayker Blankenship</v>
+        <v>Never Do - charlieonnafriday</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Get To Drinkin'</v>
+        <v>Primary Colors</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
+        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-08</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Get To Drinkin' - Single</v>
+        <v>Lost on You</v>
       </c>
       <c r="G171" t="str">
-        <v>2:48</v>
+        <v>3:37</v>
       </c>
       <c r="H171" t="str">
-        <v>Zach John King</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/zach-john-king/1671037314</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/get-to-drinkin/1871609743</v>
+        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
       </c>
       <c r="L171" t="str">
-        <v>Get To Drinkin' - Zach John King</v>
+        <v>Primary Colors - Tigers Jaw</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>The Roses</v>
+        <v>Rock Bottom</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/the-roses/1861042789</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-08</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>The Roses - Single</v>
+        <v>Rock Bottom / Octopus - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:02</v>
+        <v>4:10</v>
       </c>
       <c r="H172" t="str">
-        <v>Russell Dickerson</v>
+        <v>King Krule</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
+        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/the-roses/1861042786</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
       </c>
       <c r="L172" t="str">
-        <v>The Roses - Russell Dickerson</v>
+        <v>Rock Bottom - King Krule</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>I Should Know Better</v>
+        <v>Te Dedico</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
+        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-08</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Under The Streetlights</v>
+        <v>Te Dedico - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:33</v>
+        <v>3:45</v>
       </c>
       <c r="H173" t="str">
-        <v>Michael Marcagi</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/michael-marcagi/1524265962</v>
+        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/i-should-know-better/1867929277</v>
+        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
       </c>
       <c r="L173" t="str">
-        <v>I Should Know Better - Michael Marcagi</v>
+        <v>Te Dedico - Carlos Vives</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Never Do</v>
+        <v>AUNQUE SEA EN DOS</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/never-do/1872842226</v>
+        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-08</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Never Do - Single</v>
+        <v>18</v>
       </c>
       <c r="G174" t="str">
-        <v>1:58</v>
+        <v>2:38</v>
       </c>
       <c r="H174" t="str">
-        <v>charlieonnafriday</v>
+        <v>Conexión Divina</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/charlieonnafriday/1525971355</v>
+        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/never-do/1872842225</v>
+        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
       </c>
       <c r="L174" t="str">
-        <v>Never Do - charlieonnafriday</v>
+        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Primary Colors</v>
+        <v>I Dare You</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
+        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-08</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Lost on You</v>
+        <v>I Dare You - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:37</v>
+        <v>3:25</v>
       </c>
       <c r="H175" t="str">
-        <v>Tigers Jaw</v>
+        <v>Dylan Dunlap</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
+        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/primary-colors/1858041075</v>
+        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
       </c>
       <c r="L175" t="str">
-        <v>Primary Colors - Tigers Jaw</v>
+        <v>I Dare You - Dylan Dunlap</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Rock Bottom</v>
+        <v>new irish boyfriend</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
+        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-08</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Rock Bottom / Octopus - Single</v>
+        <v>long time caller, first time listener</v>
       </c>
       <c r="G176" t="str">
-        <v>4:10</v>
+        <v>3:50</v>
       </c>
       <c r="H176" t="str">
-        <v>King Krule</v>
+        <v>vegas water taxi</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/king-krule/474544289</v>
+        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871165475</v>
+        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
       </c>
       <c r="L176" t="str">
-        <v>Rock Bottom - King Krule</v>
+        <v>new irish boyfriend - vegas water taxi</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Te Dedico</v>
+        <v>Everyone Around Me Dancing</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
+        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-08</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Te Dedico - Single</v>
+        <v>Singing</v>
       </c>
       <c r="G177" t="str">
-        <v>3:45</v>
+        <v>3:05</v>
       </c>
       <c r="H177" t="str">
-        <v>Carlos Vives</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/carlos-vives/554369</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/te-dedico/1873126777</v>
+        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
       </c>
       <c r="L177" t="str">
-        <v>Te Dedico - Carlos Vives</v>
+        <v>Everyone Around Me Dancing - Gia Margaret</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>AUNQUE SEA EN DOS</v>
+        <v>Good Enough (feat. Julie Doiron)</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
+        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-08</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>18</v>
+        <v>Big Changes</v>
       </c>
       <c r="G178" t="str">
-        <v>2:38</v>
+        <v>6:05</v>
       </c>
       <c r="H178" t="str">
-        <v>Conexión Divina</v>
+        <v>Status/Non-Status</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/conexi%C3%B3n-divina/1641945707</v>
+        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/aunque-sea-en-dos/1867536522</v>
+        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
       </c>
       <c r="L178" t="str">
-        <v>AUNQUE SEA EN DOS - Conexión Divina</v>
+        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>I Dare You</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
+        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-08</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>I Dare You - Single</v>
+        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
       </c>
       <c r="G179" t="str">
-        <v>3:25</v>
+        <v>4:09</v>
       </c>
       <c r="H179" t="str">
-        <v>Dylan Dunlap</v>
+        <v>Julian Lage</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/dylan-dunlap/366488583</v>
+        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/i-dare-you/1866987592</v>
+        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
       </c>
       <c r="L179" t="str">
-        <v>I Dare You - Dylan Dunlap</v>
+        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>new irish boyfriend</v>
+        <v>Big Deal</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
+        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-08</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>long time caller, first time listener</v>
+        <v>Big Deal - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:50</v>
+        <v>3:47</v>
       </c>
       <c r="H180" t="str">
-        <v>vegas water taxi</v>
+        <v>In Color</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/vegas-water-taxi/1717868617</v>
+        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/new-irish-boyfriend/1849476535</v>
+        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
       </c>
       <c r="L180" t="str">
-        <v>new irish boyfriend - vegas water taxi</v>
+        <v>Big Deal - In Color</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Everyone Around Me Dancing</v>
+        <v>Buy What U Want</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
+        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-08</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Singing</v>
+        <v>Road To Osshland III - EP</v>
       </c>
       <c r="G181" t="str">
-        <v>3:05</v>
+        <v>3:47</v>
       </c>
       <c r="H181" t="str">
-        <v>Gia Margaret</v>
+        <v>Black Fortune</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
+        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/everyone-around-me-dancing/1869047383</v>
+        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
       </c>
       <c r="L181" t="str">
-        <v>Everyone Around Me Dancing - Gia Margaret</v>
+        <v>Buy What U Want - Black Fortune</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Good Enough (feat. Julie Doiron)</v>
+        <v>Common Ground</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
+        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-08</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Big Changes</v>
+        <v>Common Ground - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>6:05</v>
+        <v>1:42</v>
       </c>
       <c r="H182" t="str">
-        <v>Status/Non-Status</v>
+        <v>ELIO</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/status-non-status/1205477155</v>
+        <v>https://music.apple.com/us/artist/elio/1501417625</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/good-enough-feat-julie-doiron/1867375733</v>
+        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
       </c>
       <c r="L182" t="str">
-        <v>Good Enough (feat. Julie Doiron) - Status/Non-Status</v>
+        <v>Common Ground - ELIO</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
+        <v>Cellophane</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
+        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-08</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Scenes From Above (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen)</v>
+        <v>Cellophane - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>4:09</v>
+        <v>4:21</v>
       </c>
       <c r="H183" t="str">
-        <v>Julian Lage</v>
+        <v>Maddie Zahm</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/julian-lage/6937093</v>
+        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593147</v>
+        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
       </c>
       <c r="L183" t="str">
-        <v>Opal (feat. John Medeski, Jorge Roeder &amp; Kenny Wollesen) - Julian Lage</v>
+        <v>Cellophane - Maddie Zahm</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Big Deal</v>
+        <v>96 Camry</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/big-deal/1871607668</v>
+        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-08</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Big Deal - Single</v>
+        <v>PRAY FOR ME</v>
       </c>
       <c r="G184" t="str">
-        <v>3:47</v>
+        <v>3:15</v>
       </c>
       <c r="H184" t="str">
-        <v>In Color</v>
+        <v>RAAHiiM</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/in-color/1788977129</v>
+        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/big-deal/1871607667</v>
+        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
       </c>
       <c r="L184" t="str">
-        <v>Big Deal - In Color</v>
+        <v>96 Camry - RAAHiiM</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Buy What U Want</v>
+        <v>La Allstar</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
+        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-08</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Road To Osshland III - EP</v>
+        <v>La Allstar - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:47</v>
+        <v>2:49</v>
       </c>
       <c r="H185" t="str">
-        <v>Black Fortune</v>
+        <v>ELIKAI</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
+        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/buy-what-u-want/1872511292</v>
+        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
       </c>
       <c r="L185" t="str">
-        <v>Buy What U Want - Black Fortune</v>
+        <v>La Allstar - ELIKAI</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Common Ground</v>
+        <v>Luka</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/common-ground/1852654933</v>
+        <v>https://music.apple.com/us/song/luka/1869396162</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-08</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Common Ground - Single</v>
+        <v>Luka - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>1:42</v>
+        <v>2:07</v>
       </c>
       <c r="H186" t="str">
-        <v>ELIO</v>
+        <v>Fonta</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/elio/1501417625</v>
+        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/common-ground/1852654920</v>
+        <v>https://music.apple.com/us/album/luka/1869396161</v>
       </c>
       <c r="L186" t="str">
-        <v>Common Ground - ELIO</v>
+        <v>Luka - Fonta</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Cellophane</v>
+        <v>Ganas De Tenerla</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/cellophane/1868833598</v>
+        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-08</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Cellophane - Single</v>
+        <v>Ganas De Tenerla - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>4:21</v>
+        <v>3:06</v>
       </c>
       <c r="H187" t="str">
-        <v>Maddie Zahm</v>
+        <v>Silvestre Dangond</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/maddie-zahm/1397016641</v>
+        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/cellophane/1868833594</v>
+        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
       </c>
       <c r="L187" t="str">
-        <v>Cellophane - Maddie Zahm</v>
+        <v>Ganas De Tenerla - Silvestre Dangond</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>96 Camry</v>
+        <v>In My Blue</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/96-camry/1867251408</v>
+        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-08</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>PRAY FOR ME</v>
+        <v>Doomsday...Don't Leave Me Here</v>
       </c>
       <c r="G188" t="str">
-        <v>3:15</v>
+        <v>3:26</v>
       </c>
       <c r="H188" t="str">
-        <v>RAAHiiM</v>
+        <v>Rosie Carney</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/raahiim/1539090681</v>
+        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/96-camry/1867251391</v>
+        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
       </c>
       <c r="L188" t="str">
-        <v>96 Camry - RAAHiiM</v>
+        <v>In My Blue - Rosie Carney</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>La Allstar</v>
+        <v>Living With It (feat. Feist)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
+        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-08</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>La Allstar - Single</v>
+        <v>Hurts Like Hell</v>
       </c>
       <c r="G189" t="str">
-        <v>2:49</v>
+        <v>3:20</v>
       </c>
       <c r="H189" t="str">
-        <v>ELIKAI</v>
+        <v>Charlotte Cornfield</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/elikai/1764453112</v>
+        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/la-allstar/1867796342</v>
+        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
       </c>
       <c r="L189" t="str">
-        <v>La Allstar - ELIKAI</v>
+        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Luka</v>
+        <v>Silently</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/luka/1869396162</v>
+        <v>https://music.apple.com/us/song/silently/1841629898</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-08</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Luka - Single</v>
+        <v>Croak Dream</v>
       </c>
       <c r="G190" t="str">
-        <v>2:07</v>
+        <v>3:29</v>
       </c>
       <c r="H190" t="str">
-        <v>Fonta</v>
+        <v>Puma Blue</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/fonta/1757885481</v>
+        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/luka/1869396161</v>
+        <v>https://music.apple.com/us/album/silently/1841629444</v>
       </c>
       <c r="L190" t="str">
-        <v>Luka - Fonta</v>
+        <v>Silently - Puma Blue</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Ganas De Tenerla</v>
+        <v>Ashes &amp; Smoke</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
+        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-08</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Ganas De Tenerla - Single</v>
+        <v>Ashes &amp; Smoke - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:06</v>
+        <v>3:05</v>
       </c>
       <c r="H191" t="str">
-        <v>Silvestre Dangond</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/silvestre-dangond/311205761</v>
+        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/ganas-de-tenerla/1870909219</v>
+        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
       </c>
       <c r="L191" t="str">
-        <v>Ganas De Tenerla - Silvestre Dangond</v>
+        <v>Ashes &amp; Smoke - Anna Graves</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>In My Blue</v>
+        <v>Tormentor</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
+        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-08</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Doomsday...Don't Leave Me Here</v>
+        <v>The Flowers I See You In - EP</v>
       </c>
       <c r="G192" t="str">
-        <v>3:26</v>
+        <v>2:40</v>
       </c>
       <c r="H192" t="str">
-        <v>Rosie Carney</v>
+        <v>Ninush</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/rosie-carney/1057803106</v>
+        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/in-my-blue/1838571277</v>
+        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
       </c>
       <c r="L192" t="str">
-        <v>In My Blue - Rosie Carney</v>
+        <v>Tormentor - Ninush</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Living With It (feat. Feist)</v>
+        <v>Red Rocking Chair</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
+        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-08</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Hurts Like Hell</v>
+        <v>Red Rocking Chair - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:20</v>
+        <v>6:28</v>
       </c>
       <c r="H193" t="str">
-        <v>Charlotte Cornfield</v>
+        <v>All Them Witches</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cornfield/281901047</v>
+        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/living-with-it-feat-feist/1860115035</v>
+        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
       </c>
       <c r="L193" t="str">
-        <v>Living With It (feat. Feist) - Charlotte Cornfield</v>
+        <v>Red Rocking Chair - All Them Witches</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Silently</v>
+        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/silently/1841629898</v>
+        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-08</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Croak Dream</v>
+        <v>...of Death and Fire</v>
       </c>
       <c r="G194" t="str">
-        <v>3:29</v>
+        <v>7:07</v>
       </c>
       <c r="H194" t="str">
-        <v>Puma Blue</v>
+        <v>In Aeternum</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/puma-blue/1231178386</v>
+        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/silently/1841629444</v>
+        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
       </c>
       <c r="L194" t="str">
-        <v>Silently - Puma Blue</v>
+        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Ashes &amp; Smoke</v>
+        <v>Mizantrop</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
+        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-08</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Ashes &amp; Smoke - Single</v>
+        <v>Mizantrop</v>
       </c>
       <c r="G195" t="str">
-        <v>3:05</v>
+        <v>3:42</v>
       </c>
       <c r="H195" t="str">
-        <v>Anna Graves</v>
+        <v>She Past Away</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/anna-graves/1441311957</v>
+        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/ashes-smoke/1871026507</v>
+        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
       </c>
       <c r="L195" t="str">
-        <v>Ashes &amp; Smoke - Anna Graves</v>
+        <v>Mizantrop - She Past Away</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Tormentor</v>
+        <v>In the Name of the Moth</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/tormentor/1847995443</v>
+        <v>https://music.apple.com/us/song/in-the-name-of-the-moth/1866911203</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-08</v>
@@ -7823,182 +7823,30 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>The Flowers I See You In - EP</v>
+        <v>Hidden Fires Burn Hottest</v>
       </c>
       <c r="G196" t="str">
-        <v>2:40</v>
+        <v>7:15</v>
       </c>
       <c r="H196" t="str">
-        <v>Ninush</v>
+        <v>Bosse-de-Nage</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/ninush/1794862552</v>
+        <v>https://music.apple.com/us/artist/bosse-de-nage/465123183</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/tormentor/1847995441</v>
+        <v>https://music.apple.com/us/album/in-the-name-of-the-moth/1866911198</v>
       </c>
       <c r="L196" t="str">
-        <v>Tormentor - Ninush</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Red Rocking Chair</v>
-      </c>
-      <c r="B197" t="str">
-        <v/>
-      </c>
-      <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
-      </c>
-      <c r="D197" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" t="str">
-        <v>Red Rocking Chair - Single</v>
-      </c>
-      <c r="G197" t="str">
-        <v>6:28</v>
-      </c>
-      <c r="H197" t="str">
-        <v>All Them Witches</v>
-      </c>
-      <c r="I197" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/all-them-witches/534924603</v>
-      </c>
-      <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/red-rocking-chair/1870654854</v>
-      </c>
-      <c r="L197" t="str">
-        <v>Red Rocking Chair - All Them Witches</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>To Those Who Have Rode On (feat. Erik Danielsson)</v>
-      </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
-      </c>
-      <c r="D198" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
-        <v>...of Death and Fire</v>
-      </c>
-      <c r="G198" t="str">
-        <v>7:07</v>
-      </c>
-      <c r="H198" t="str">
-        <v>In Aeternum</v>
-      </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/in-aeternum/263130305</v>
-      </c>
-      <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/to-those-who-have-rode-on-feat-erik-danielsson/1852322618</v>
-      </c>
-      <c r="L198" t="str">
-        <v>To Those Who Have Rode On (feat. Erik Danielsson) - In Aeternum</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Mizantrop</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Mizantrop</v>
-      </c>
-      <c r="G199" t="str">
-        <v>3:42</v>
-      </c>
-      <c r="H199" t="str">
-        <v>She Past Away</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/she-past-away/347750887</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/mizantrop/1870240904</v>
-      </c>
-      <c r="L199" t="str">
-        <v>Mizantrop - She Past Away</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>In the Name of the Moth</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/in-the-name-of-the-moth/1866911203</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>Hidden Fires Burn Hottest</v>
-      </c>
-      <c r="G200" t="str">
-        <v>7:15</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Bosse-de-Nage</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/bosse-de-nage/465123183</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/in-the-name-of-the-moth/1866911198</v>
-      </c>
-      <c r="L200" t="str">
         <v>In the Name of the Moth - Bosse-de-Nage</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L196"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>6:00</v>
@@ -477,7 +477,7 @@
         <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B3" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>10 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:20</v>
@@ -1275,7 +1275,7 @@
         <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>4:16</v>
@@ -3251,7 +3251,7 @@
         <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>4:04</v>
@@ -3289,7 +3289,7 @@
         <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>2:16</v>

--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -436,28 +436,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>6:00</v>
+        <v>3:04</v>
       </c>
       <c r="H2" t="str">
-        <v>Taylor Swift</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,33 +469,33 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:20</v>
+        <v>6:00</v>
       </c>
       <c r="H3" t="str">
-        <v>Michael Bolton</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,33 +507,33 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:27</v>
+        <v>4:20</v>
       </c>
       <c r="H4" t="str">
-        <v>Mariah Carey</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:26</v>
+        <v>4:27</v>
       </c>
       <c r="H5" t="str">
-        <v>Netflix</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:29</v>
+        <v>3:26</v>
       </c>
       <c r="H6" t="str">
-        <v>Michael Bolton</v>
+        <v>Netflix</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,33 +621,33 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:59</v>
+        <v>3:29</v>
       </c>
       <c r="H7" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B8" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -682,10 +682,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:51</v>
+        <v>2:59</v>
       </c>
       <c r="H8" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>mgk</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -720,10 +720,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>4:13</v>
+        <v>2:51</v>
       </c>
       <c r="H9" t="str">
-        <v>Michael Bolton</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:41</v>
+        <v>4:13</v>
       </c>
       <c r="H10" t="str">
-        <v>NICK JONAS</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>7:03</v>
+        <v>4:41</v>
       </c>
       <c r="H11" t="str">
-        <v>Take That</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:37</v>
+        <v>7:03</v>
       </c>
       <c r="H12" t="str">
-        <v>Cliff Richard</v>
+        <v>Take That</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,21 +849,21 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:54</v>
+        <v>4:37</v>
       </c>
       <c r="H13" t="str">
-        <v>Bryan Adams</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,21 +887,21 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:06</v>
+        <v>3:54</v>
       </c>
       <c r="H14" t="str">
-        <v>Anna Graves</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,21 +925,21 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H15" t="str">
-        <v>George Birge</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,21 +963,21 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:09</v>
+        <v>3:21</v>
       </c>
       <c r="H16" t="str">
-        <v>Warner Records</v>
+        <v>George Birge</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,21 +1001,21 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
+        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:18</v>
+        <v>4:09</v>
       </c>
       <c r="H17" t="str">
-        <v>NICK JONAS</v>
+        <v>Warner Records</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,21 +1039,21 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
+        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:08</v>
+        <v>4:18</v>
       </c>
       <c r="H18" t="str">
-        <v>Charlie Puth</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,21 +1077,21 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
+        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>4:03</v>
+        <v>3:08</v>
       </c>
       <c r="H19" t="str">
-        <v>Olivia Newton-John</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
+        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:01</v>
+        <v>4:03</v>
       </c>
       <c r="H20" t="str">
-        <v>The Warning and Carin Leon</v>
+        <v>Olivia Newton-John</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,21 +1153,21 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
+        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:05</v>
+        <v>3:01</v>
       </c>
       <c r="H21" t="str">
-        <v>Iman Fandi</v>
+        <v>The Warning and Carin Leon</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
+        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:34</v>
+        <v>3:05</v>
       </c>
       <c r="H22" t="str">
-        <v>Megan Moroney</v>
+        <v>Iman Fandi</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,21 +1229,21 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dylan Davidson - Escape Artist</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
+        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:15</v>
+        <v>3:34</v>
       </c>
       <c r="H23" t="str">
-        <v>Dylan Davidson</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,33 +1267,33 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
+        <v>Dylan Davidson - Escape Artist</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
+        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:16</v>
+        <v>3:15</v>
       </c>
       <c r="H24" t="str">
-        <v>Lady Gaga</v>
+        <v>Dylan Davidson</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,33 +1305,33 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
+        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video)</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
+        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:53</v>
+        <v>4:16</v>
       </c>
       <c r="H25" t="str">
-        <v>Carlos Vives</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,33 +1343,33 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
+        <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
+        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:25</v>
+        <v>3:53</v>
       </c>
       <c r="H26" t="str">
-        <v>Monsieur Periné</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
+        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio)</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
+        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:09</v>
+        <v>2:25</v>
       </c>
       <c r="H27" t="str">
-        <v>The Happy Fits</v>
+        <v>Monsieur Periné</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,21 +1419,21 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>chase (lyric vid) - Michael Aldag</v>
+        <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
+        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:45</v>
+        <v>4:09</v>
       </c>
       <c r="H28" t="str">
-        <v>Michael Aldag</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,21 +1457,21 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
+        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
+        <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
+        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:07</v>
+        <v>2:45</v>
       </c>
       <c r="H29" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Michael Aldag</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,21 +1495,21 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
+        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
+        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:34</v>
+        <v>4:07</v>
       </c>
       <c r="H30" t="str">
-        <v>Marc Anthony</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,21 +1533,21 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
+        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:14</v>
+        <v>4:34</v>
       </c>
       <c r="H31" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,21 +1571,21 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
+        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:11</v>
+        <v>5:14</v>
       </c>
       <c r="H32" t="str">
-        <v>Michael Bolton</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,21 +1609,21 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Lachie Gill - Last Drive</v>
+        <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
+        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:40</v>
+        <v>3:11</v>
       </c>
       <c r="H33" t="str">
-        <v>Lachie Gill</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,21 +1647,21 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Lachie Gill - Last Drive - Lachie Gill</v>
+        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
+        <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
+        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:45</v>
+        <v>3:40</v>
       </c>
       <c r="H34" t="str">
-        <v>Eli &amp; Fur</v>
+        <v>Lachie Gill</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
+        <v>Lachie Gill - Last Drive - Lachie Gill</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Freya Skye - why'd you have to call</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
+        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:19</v>
+        <v>3:45</v>
       </c>
       <c r="H35" t="str">
-        <v>Freya Skye</v>
+        <v>Eli &amp; Fur</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,21 +1723,21 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Freya Skye - why'd you have to call - Freya Skye</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
+        <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B36" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
+        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1746,10 +1746,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:30</v>
+        <v>4:19</v>
       </c>
       <c r="H36" t="str">
-        <v>Jessie J</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,21 +1761,21 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
+        <v>Freya Skye - why'd you have to call - Freya Skye</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer)</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
+        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1784,10 +1784,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:24</v>
+        <v>2:30</v>
       </c>
       <c r="H37" t="str">
-        <v>Marc Anthony</v>
+        <v>Jessie J</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,21 +1799,21 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
+        <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B38" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
+        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1822,10 +1822,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:33</v>
+        <v>4:24</v>
       </c>
       <c r="H38" t="str">
-        <v>Clara Mae</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,21 +1837,21 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
+        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Metric - Victim of Luck (Official Music Video)</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B39" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
+        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1860,10 +1860,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:25</v>
+        <v>2:33</v>
       </c>
       <c r="H39" t="str">
-        <v>metricmusic</v>
+        <v>Clara Mae</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,21 +1875,21 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
+        <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
+        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1898,10 +1898,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:41</v>
+        <v>3:25</v>
       </c>
       <c r="H40" t="str">
-        <v>kesha</v>
+        <v>metricmusic</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
+        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
+        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:19</v>
+        <v>3:41</v>
       </c>
       <c r="H41" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>kesha</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,21 +1951,21 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B42" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
+        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1974,10 +1974,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:37</v>
+        <v>3:19</v>
       </c>
       <c r="H42" t="str">
-        <v>Vera Blue</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,21 +1989,21 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B43" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
+        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2012,10 +2012,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:08</v>
+        <v>3:37</v>
       </c>
       <c r="H43" t="str">
-        <v>Bob Moses</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,21 +2027,21 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B44" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
+        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2050,10 +2050,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:28</v>
+        <v>3:08</v>
       </c>
       <c r="H44" t="str">
-        <v>Marc Anthony</v>
+        <v>Bob Moses</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,21 +2065,21 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
+        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2088,7 +2088,7 @@
         <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>5:05</v>
+        <v>3:28</v>
       </c>
       <c r="H45" t="str">
         <v>Marc Anthony</v>
@@ -2103,21 +2103,21 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Loreen - Feels Like Heaven</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
+        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2126,10 +2126,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:14</v>
+        <v>5:05</v>
       </c>
       <c r="H46" t="str">
-        <v>Loreen</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,21 +2141,21 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Loreen - Feels Like Heaven - Loreen</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
+        <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B47" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
+        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2164,10 +2164,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:36</v>
+        <v>3:14</v>
       </c>
       <c r="H47" t="str">
-        <v>Take That</v>
+        <v>Loreen</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,21 +2179,21 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
+        <v>Loreen - Feels Like Heaven - Loreen</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B48" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
+        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2202,10 +2202,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>5:31</v>
+        <v>3:36</v>
       </c>
       <c r="H48" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Take That</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,21 +2217,21 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio)</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B49" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
+        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2240,10 +2240,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:37</v>
+        <v>5:31</v>
       </c>
       <c r="H49" t="str">
-        <v>Nothing But Thieves</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:58</v>
+        <v>3:37</v>
       </c>
       <c r="H50" t="str">
-        <v>The Warning</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,21 +2293,21 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B51" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2316,10 +2316,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>5:08</v>
+        <v>4:58</v>
       </c>
       <c r="H51" t="str">
-        <v>The Offspring</v>
+        <v>The Warning</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,21 +2331,21 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B52" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2354,10 +2354,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:38</v>
+        <v>5:08</v>
       </c>
       <c r="H52" t="str">
-        <v>Roxette</v>
+        <v>The Offspring</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,21 +2369,21 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B53" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2392,10 +2392,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:50</v>
+        <v>4:38</v>
       </c>
       <c r="H53" t="str">
-        <v>Jessie Ware</v>
+        <v>Roxette</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:10</v>
+        <v>3:50</v>
       </c>
       <c r="H54" t="str">
-        <v>Joseph</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,21 +2445,21 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2468,10 +2468,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:44</v>
+        <v>3:10</v>
       </c>
       <c r="H55" t="str">
-        <v>Dean Lewis</v>
+        <v>Joseph</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,21 +2483,21 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2506,10 +2506,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:57</v>
+        <v>2:44</v>
       </c>
       <c r="H56" t="str">
-        <v>Take That</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,21 +2521,21 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:07</v>
+        <v>2:57</v>
       </c>
       <c r="H57" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>Take That</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,21 +2559,21 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:47</v>
+        <v>3:07</v>
       </c>
       <c r="H58" t="str">
-        <v>Paris Paloma</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,21 +2597,21 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B59" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2620,10 +2620,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:22</v>
+        <v>4:47</v>
       </c>
       <c r="H59" t="str">
-        <v>Zara Larsson</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,21 +2635,21 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:48</v>
+        <v>3:22</v>
       </c>
       <c r="H60" t="str">
-        <v>only the poets</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,21 +2673,21 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:52</v>
+        <v>2:48</v>
       </c>
       <c r="H61" t="str">
-        <v>Katelyn Tarver</v>
+        <v>only the poets</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,21 +2711,21 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:33</v>
+        <v>2:52</v>
       </c>
       <c r="H62" t="str">
-        <v>David Guetta</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,21 +2749,21 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:41</v>
+        <v>3:33</v>
       </c>
       <c r="H63" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>David Guetta</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,21 +2787,21 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:01</v>
+        <v>2:41</v>
       </c>
       <c r="H64" t="str">
-        <v>Ella Langley</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,21 +2825,21 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:16</v>
+        <v>4:01</v>
       </c>
       <c r="H65" t="str">
-        <v>Dogpark</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,21 +2863,21 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:03</v>
+        <v>3:16</v>
       </c>
       <c r="H66" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Dogpark</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,21 +2901,21 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:41</v>
+        <v>3:03</v>
       </c>
       <c r="H67" t="str">
-        <v>ERNEST</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,21 +2939,21 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:05</v>
+        <v>2:41</v>
       </c>
       <c r="H68" t="str">
-        <v>Labrinth</v>
+        <v>ERNEST</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,21 +2977,21 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:46</v>
+        <v>3:05</v>
       </c>
       <c r="H69" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Labrinth</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,21 +3015,21 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:32</v>
+        <v>2:46</v>
       </c>
       <c r="H70" t="str">
-        <v>VOILÀ</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,21 +3053,21 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:42</v>
+        <v>3:32</v>
       </c>
       <c r="H71" t="str">
-        <v>Cannons</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,21 +3091,21 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:38</v>
+        <v>3:42</v>
       </c>
       <c r="H72" t="str">
-        <v>Kylie Morgan</v>
+        <v>Cannons</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,21 +3129,21 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:10</v>
+        <v>2:38</v>
       </c>
       <c r="H73" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,21 +3167,21 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:57</v>
+        <v>3:10</v>
       </c>
       <c r="H74" t="str">
-        <v>Willie Nelson</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,21 +3205,21 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:19</v>
+        <v>3:57</v>
       </c>
       <c r="H75" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,33 +3243,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:04</v>
+        <v>2:19</v>
       </c>
       <c r="H76" t="str">
-        <v>India Martínez</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,21 +3281,21 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B77" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3304,10 +3304,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>2:16</v>
+        <v>4:04</v>
       </c>
       <c r="H77" t="str">
-        <v>Chelsea Cutler</v>
+        <v>India Martínez</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,21 +3319,21 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3342,10 +3342,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>5:58</v>
+        <v>2:16</v>
       </c>
       <c r="H78" t="str">
-        <v>TINI</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,21 +3357,21 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B79" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3380,10 +3380,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:26</v>
+        <v>5:58</v>
       </c>
       <c r="H79" t="str">
-        <v>Charley</v>
+        <v>TINI</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,21 +3395,21 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B80" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3418,10 +3418,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:05</v>
+        <v>3:26</v>
       </c>
       <c r="H80" t="str">
-        <v>Demi Lovato</v>
+        <v>Charley</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,21 +3433,21 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B81" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3456,10 +3456,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H81" t="str">
-        <v>Teddy Swims</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,21 +3471,21 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:14</v>
+        <v>3:16</v>
       </c>
       <c r="H82" t="str">
-        <v>Beck</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B83" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:57</v>
+        <v>3:14</v>
       </c>
       <c r="H83" t="str">
-        <v>The Offspring</v>
+        <v>Beck</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,21 +3547,21 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B84" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:10</v>
+        <v>2:57</v>
       </c>
       <c r="H84" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>The Offspring</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,21 +3585,21 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B85" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3608,10 +3608,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:10</v>
+        <v>4:10</v>
       </c>
       <c r="H85" t="str">
-        <v>Jason Derulo</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,21 +3623,21 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B86" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3646,10 +3646,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:52</v>
+        <v>2:10</v>
       </c>
       <c r="H86" t="str">
-        <v>lights</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,21 +3661,21 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B87" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3684,10 +3684,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:50</v>
+        <v>3:52</v>
       </c>
       <c r="H87" t="str">
-        <v>Telenova</v>
+        <v>lights</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,21 +3699,21 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B88" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3722,10 +3722,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>5:32</v>
+        <v>3:50</v>
       </c>
       <c r="H88" t="str">
-        <v>Marcin</v>
+        <v>Telenova</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,21 +3737,21 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B89" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3760,10 +3760,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:27</v>
+        <v>5:32</v>
       </c>
       <c r="H89" t="str">
-        <v>We Three</v>
+        <v>Marcin</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,33 +3775,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:01</v>
+        <v>4:27</v>
       </c>
       <c r="H90" t="str">
-        <v>Timebelle Official</v>
+        <v>We Three</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:20</v>
+        <v>3:01</v>
       </c>
       <c r="H91" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:34</v>
+        <v>3:20</v>
       </c>
       <c r="H92" t="str">
-        <v>Clinton Kane</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,21 +3889,21 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3912,10 +3912,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
-        <v>4:01</v>
+        <v>3:34</v>
       </c>
       <c r="H93" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,21 +3927,21 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:24</v>
+        <v>4:01</v>
       </c>
       <c r="H94" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,21 +3965,21 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>5:52</v>
+        <v>3:24</v>
       </c>
       <c r="H95" t="str">
-        <v>Harry Styles</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,21 +4003,21 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>5:01</v>
+        <v>5:52</v>
       </c>
       <c r="H96" t="str">
-        <v>Neal Francis</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,21 +4041,21 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:12</v>
+        <v>5:01</v>
       </c>
       <c r="H97" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,21 +4079,21 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:59</v>
+        <v>4:12</v>
       </c>
       <c r="H98" t="str">
-        <v>Holly Humberstone</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,21 +4117,21 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>2:56</v>
+        <v>3:59</v>
       </c>
       <c r="H99" t="str">
-        <v>Cliff Richard</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,21 +4155,21 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:46</v>
+        <v>2:56</v>
       </c>
       <c r="H100" t="str">
-        <v>Jessie Ware</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,21 +4193,21 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Bella White - Dream Song (Official Audio)</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=VZTuUbvwCR0</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:37</v>
+        <v>3:46</v>
       </c>
       <c r="H101" t="str">
-        <v>Bella White</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Bella White - Dream Song (Official Audio) - Bella White</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="102">
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/two-six/1875080974</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/might-just/1858755211</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/cry/1845189974</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/omens/1872546206</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/my-regards/1871502698</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/plei/1872137577</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/rain/1867258289</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/heal-something/1871463897</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/cook/1872816147</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/living-water/1871565262</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/neck/1866953832</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/colorblind/1873445412</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/flavorless/1870741358</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/nunca/1860691713</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/just-in-case/1867548367</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/thinking-of-you/1874128053</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/house-of-cards/1871562986</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/stay-with-me/1867490493</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/i-had-a-dream/1870971554</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/back-to-you/1855725165</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/rager/1872808801</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/if-only/1870281318</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/dont-love-me/1873153612</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/no-sikes-no-tradesies/1871576137</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/you-woke-me-up/1873402923</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/no-ones-business/1873059628</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/dont-dream-its-over-from-the-movie-goat/1870623627</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/twice/1871578107</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/rooftop/1872534292</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/louisiana-rain/1867848946</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/sharing-jesus-with-an-ex/1870912832</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/body-control-feat-chills/1867947671</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/a-prayer-for-the-dancefloor-feat-conduit/1869372836</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/realm-of-endless-misery/1846578506</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/bleach/1869795882</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/pretty-in-pink/1847771037</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/pickup-man/1870883995</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/get-to-drinkin/1871609753</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/the-roses/1861042789</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/i-should-know-better/1867929284</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/never-do/1872842226</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/primary-colors/1858041089</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/rock-bottom/1871165476</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/te-dedico/1873127022</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/aunque-sea-en-dos/1867536534</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/i-dare-you/1866987593</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/new-irish-boyfriend/1849476917</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/everyone-around-me-dancing/1869047384</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/good-enough-feat-julie-doiron/1867375846</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/opal-feat-john-medeski-jorge-roeder-kenny-wollesen/1849593156</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/big-deal/1871607668</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/buy-what-u-want/1872511530</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/common-ground/1852654933</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/cellophane/1868833598</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/96-camry/1867251408</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/la-allstar/1867796343</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/luka/1869396162</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/ganas-de-tenerla/1870909222</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/in-my-blue/1838571293</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/living-with-it-feat-feist/1860115264</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/silently/1841629898</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/ashes-smoke/1871026508</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/tormentor/1847995443</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/red-rocking-chair/1870654858</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/to-those-who-have-rode-on-feat-erik-danielsson/1852323086</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/mizantrop/1870241244</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/in-the-name-of-the-moth/1866911203</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E196" t="str">
         <v/>

--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B2" t="str">
-        <v>7 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:04</v>
@@ -477,7 +477,7 @@
         <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>6:00</v>
@@ -515,7 +515,7 @@
         <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B4" t="str">
-        <v>13 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>13 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>4:20</v>

--- a/data/global/2026-02-week02/titles.xlsx
+++ b/data/global/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:L197"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
+        <v>מייפל Wishing for peace</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>2026-02-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%a4%d7%9c-wishing-for-peace/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-09</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>מייפל שרה שיר בעל משקל היסטורי ורגשי עצום. “Wishing for Peace” הוא שיר פולק, שנולד מעדות משפחתית. הבחירה בבלדת פולק מיד־טמפו איננה מקרית. פולק הוא ז’אנר של סיפורים, מסורת והעברה בין דורות. הקצב האמצעי מתניע דרמה. של הליכה מתמשכת זו</v>
       </c>
       <c r="G2" t="str">
-        <v>3:04</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Olivia Dean</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
+        <v>מייפל Wishing for peace</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video)</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
+        <v>https://www.youtube.com/watch?v=S-mowvext3E</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-09</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>6:00</v>
+        <v>3:04</v>
       </c>
       <c r="H3" t="str">
-        <v>Taylor Swift</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
+        <v>Olivia Dean - Man I Need (Live) | Spotify Best New Artist - Olivia Dean</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
+        <v>Taylor Swift - Opalite (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
+        <v>https://www.youtube.com/watch?v=1FVF-9KQiPo</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-09</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:20</v>
+        <v>6:00</v>
       </c>
       <c r="H4" t="str">
-        <v>Michael Bolton</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
+        <v>Taylor Swift - Opalite (Official Music Video) - Taylor Swift</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
+        <v>https://www.youtube.com/watch?v=D5OUv26MG9w</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-09</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:27</v>
+        <v>4:20</v>
       </c>
       <c r="H5" t="str">
-        <v>Mariah Carey</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
+        <v>Michael Bolton | When A Man Loves A Woman - Live (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony)</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
+        <v>https://www.youtube.com/watch?v=i9mZIIi3tgE</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-09</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:26</v>
+        <v>4:27</v>
       </c>
       <c r="H6" t="str">
-        <v>Netflix</v>
+        <v>Mariah Carey</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
+        <v>Volare / Nothing Is Impossible Medley (Milano Cortina 2026 Olympic Winter Games Opening Ceremony) - Mariah Carey</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
+        <v>https://www.youtube.com/watch?v=fGyTN5UjnL4</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-09</v>
@@ -644,10 +644,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:29</v>
+        <v>3:26</v>
       </c>
       <c r="H7" t="str">
-        <v>Michael Bolton</v>
+        <v>Netflix</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
+        <v>‘Your Idol’ Lyric Video | KPop Demon Hunters | Netflix - Netflix</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>mgk - cliché (Official Lyric Video)</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
+        <v>https://www.youtube.com/watch?v=x0cpCw99EN0</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-09</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>2:59</v>
+        <v>3:29</v>
       </c>
       <c r="H8" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>mgk - cliché (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | We Could Be Something (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK</v>
+        <v>mgk - cliché (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
+        <v>https://www.youtube.com/watch?v=lXWn1zeWXfc</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-09</v>
@@ -720,10 +720,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>2:51</v>
+        <v>2:59</v>
       </c>
       <c r="H9" t="str">
-        <v>SOFI TUKKER and J Balvin</v>
+        <v>mgk</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
+        <v>mgk - cliché (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
+        <v>SOFI TUKKER, J Balvin - COOK</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
+        <v>https://www.youtube.com/watch?v=iJzE0AULogg</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-09</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:13</v>
+        <v>2:51</v>
       </c>
       <c r="H10" t="str">
-        <v>Michael Bolton</v>
+        <v>SOFI TUKKER and J Balvin</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
+        <v>SOFI TUKKER, J Balvin - COOK - SOFI TUKKER and J Balvin</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Nick Jonas - Gut Punch</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
+        <v>https://www.youtube.com/watch?v=qnjeveURY2w</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-09</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:41</v>
+        <v>4:13</v>
       </c>
       <c r="H11" t="str">
-        <v>NICK JONAS</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
+        <v>Michael Bolton &amp; Eva Cassidy | Fields of Gold (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Take That - Sure (Official HD Video)</v>
+        <v>Nick Jonas - Gut Punch</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
+        <v>https://www.youtube.com/watch?v=ISId7FbHjxc</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-09</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>7:03</v>
+        <v>4:41</v>
       </c>
       <c r="H12" t="str">
-        <v>Take That</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Take That - Sure (Official HD Video) - Take That</v>
+        <v>Nick Jonas - Gut Punch - NICK JONAS</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
+        <v>Take That - Sure (Official HD Video)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
+        <v>https://www.youtube.com/watch?v=ZDGr7Y9eweY</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-09</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:37</v>
+        <v>7:03</v>
       </c>
       <c r="H13" t="str">
-        <v>Cliff Richard</v>
+        <v>Take That</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
+        <v>Take That - Sure (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bryan Adams - Hey Baby</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
+        <v>https://www.youtube.com/watch?v=JZM2tHMmqck</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-09</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:54</v>
+        <v>4:37</v>
       </c>
       <c r="H14" t="str">
-        <v>Bryan Adams</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
+        <v>Cliff Richard - Golden (75th Birthday Concert, Royal Albert Hall, 14 Oct 2015) - Cliff Richard</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
+        <v>Bryan Adams - Hey Baby</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
+        <v>https://www.youtube.com/watch?v=aYcAl98fDYk</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-09</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:06</v>
+        <v>3:54</v>
       </c>
       <c r="H15" t="str">
-        <v>Anna Graves</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
+        <v>Bryan Adams - Hey Baby - Bryan Adams</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
+        <v>https://www.youtube.com/watch?v=n90qajAa6oQ</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-09</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H16" t="str">
-        <v>George Birge</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
+        <v>Anna Graves - Ashes &amp; Smoke (Official Audio) - Anna Graves</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video]</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
+        <v>https://www.youtube.com/watch?v=rWGpexrWhJE</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-09</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:09</v>
+        <v>3:21</v>
       </c>
       <c r="H17" t="str">
-        <v>Warner Records</v>
+        <v>George Birge</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
+        <v>George Birge - Ride, Ride, Ride (Feat. Luke Bryan) [Official Music Video] - George Birge</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
+        <v>https://www.youtube.com/watch?v=Q44JiUwa2Xg</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-09</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:18</v>
+        <v>4:09</v>
       </c>
       <c r="H18" t="str">
-        <v>NICK JONAS</v>
+        <v>Warner Records</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
+        <v>Morrissey - Notre-Dame (Official Lyric Video) - Warner Records</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
+        <v>https://www.youtube.com/watch?v=Jy2dqfKWY-c</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-09</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:08</v>
+        <v>4:18</v>
       </c>
       <c r="H19" t="str">
-        <v>Charlie Puth</v>
+        <v>NICK JONAS</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
+        <v>Nick Jonas - Sweet To Me (Official Lyric Video) - NICK JONAS</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio]</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
+        <v>https://www.youtube.com/watch?v=Bam3O09kLAQ</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-09</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:03</v>
+        <v>3:08</v>
       </c>
       <c r="H20" t="str">
-        <v>Olivia Newton-John</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
+        <v>Charlie Puth - Cry (with Kenny G) [Official Audio] - Charlie Puth</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
+        <v>https://www.youtube.com/watch?v=F-usO6XVXcs</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-09</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:01</v>
+        <v>4:03</v>
       </c>
       <c r="H21" t="str">
-        <v>The Warning and Carin Leon</v>
+        <v>Olivia Newton-John</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
+        <v>Olivia Newton-John - Serenity (Visualizer) (Official) - Olivia Newton-John</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
+        <v>https://www.youtube.com/watch?v=8DUQ5vPcz9o</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-09</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:05</v>
+        <v>3:01</v>
       </c>
       <c r="H22" t="str">
-        <v>Iman Fandi</v>
+        <v>The Warning and Carin Leon</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
+        <v>The Warning, Carín León - Love To Be Loved (Official Video) - The Warning and Carin Leon</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
+        <v>https://www.youtube.com/watch?v=WRvCKHSm12Y</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-09</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:34</v>
+        <v>3:05</v>
       </c>
       <c r="H23" t="str">
-        <v>Megan Moroney</v>
+        <v>Iman Fandi</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
+        <v>Iman Fandi - Tip Toes (Official Dance Visualiser) - Iman Fandi</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Dylan Davidson - Escape Artist</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
+        <v>https://www.youtube.com/watch?v=BiNIdrm9miE</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-09</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:15</v>
+        <v>3:34</v>
       </c>
       <c r="H24" t="str">
-        <v>Dylan Davidson</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
+        <v>Megan Moroney - Cloud 9 (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
+        <v>Dylan Davidson - Escape Artist</v>
       </c>
       <c r="B25" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
+        <v>https://www.youtube.com/watch?v=iKW4wCw_LoY</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-09</v>
@@ -1328,10 +1328,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>4:16</v>
+        <v>3:15</v>
       </c>
       <c r="H25" t="str">
-        <v>Lady Gaga</v>
+        <v>Dylan Davidson</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
+        <v>Dylan Davidson - Escape Artist - Dylan Davidson</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video)</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS)</v>
       </c>
       <c r="B26" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
+        <v>https://www.youtube.com/watch?v=Rn89mUndYbo</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-09</v>
@@ -1366,10 +1366,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:53</v>
+        <v>4:16</v>
       </c>
       <c r="H26" t="str">
-        <v>Carlos Vives</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
+        <v>LADY GAGA - ABRACADABRA (LIVE AT THE 2026 GRAMMYS) - Lady Gaga</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
+        <v>Carlos Vives - Te Dedico (Official Video)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
+        <v>https://www.youtube.com/watch?v=H8KW0SgW99I</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-09</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:25</v>
+        <v>3:53</v>
       </c>
       <c r="H27" t="str">
-        <v>Monsieur Periné</v>
+        <v>Carlos Vives</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
+        <v>Carlos Vives - Te Dedico (Official Video) - Carlos Vives</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio)</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
+        <v>https://www.youtube.com/watch?v=mpmrrvhLzZ0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-09</v>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:09</v>
+        <v>2:25</v>
       </c>
       <c r="H28" t="str">
-        <v>The Happy Fits</v>
+        <v>Monsieur Periné</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
+        <v>Monsieur Periné, Jossman - MUCHO CON DEMASIAO' (Video Oficial) - Monsieur Periné</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>chase (lyric vid) - Michael Aldag</v>
+        <v>The Happy Fits - Tenderly (Official Audio)</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
+        <v>https://www.youtube.com/watch?v=10hExzTW4Hc</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-09</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:45</v>
+        <v>4:09</v>
       </c>
       <c r="H29" t="str">
-        <v>Michael Aldag</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
+        <v>The Happy Fits - Tenderly (Official Audio) - The Happy Fits</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
+        <v>chase (lyric vid) - Michael Aldag</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
+        <v>https://www.youtube.com/watch?v=QASMKs97wec</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-09</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:07</v>
+        <v>2:45</v>
       </c>
       <c r="H30" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Michael Aldag</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
+        <v>chase (lyric vid) - Michael Aldag - Michael Aldag</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
+        <v>https://www.youtube.com/watch?v=RyR1xAw9edU</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-09</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:34</v>
+        <v>4:07</v>
       </c>
       <c r="H31" t="str">
-        <v>Marc Anthony</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
+        <v>Dermot Kennedy - Funeral (Live Acoustic Session) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
+        <v>https://www.youtube.com/watch?v=OYtHvS7n7ic</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-09</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>5:14</v>
+        <v>4:34</v>
       </c>
       <c r="H32" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Official Video) - Marc Anthony</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
+        <v>https://www.youtube.com/watch?v=XKvzT2CTnLE</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-09</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:11</v>
+        <v>5:14</v>
       </c>
       <c r="H33" t="str">
-        <v>Michael Bolton</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Lachie Gill - Last Drive</v>
+        <v>Michael Bolton | Cupid (Official Visualizer)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
+        <v>https://www.youtube.com/watch?v=1XDIbfJ_OGw</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-09</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:40</v>
+        <v>3:11</v>
       </c>
       <c r="H34" t="str">
-        <v>Lachie Gill</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Lachie Gill - Last Drive - Lachie Gill</v>
+        <v>Michael Bolton | Cupid (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
+        <v>Lachie Gill - Last Drive</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
+        <v>https://www.youtube.com/watch?v=y79kD37Ffic</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-09</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:45</v>
+        <v>3:40</v>
       </c>
       <c r="H35" t="str">
-        <v>Eli &amp; Fur</v>
+        <v>Lachie Gill</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
+        <v>Lachie Gill - Last Drive - Lachie Gill</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Freya Skye - why'd you have to call</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser)</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
+        <v>https://www.youtube.com/watch?v=KlgO3kKNc8o</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-09</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:19</v>
+        <v>3:45</v>
       </c>
       <c r="H36" t="str">
-        <v>Freya Skye</v>
+        <v>Eli &amp; Fur</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Freya Skye - why'd you have to call - Freya Skye</v>
+        <v>Eli &amp; Fur - Strange (Official Visualiser) - Eli &amp; Fur</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
+        <v>Freya Skye - why'd you have to call</v>
       </c>
       <c r="B37" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
+        <v>https://www.youtube.com/watch?v=75o0FuwCdaA</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-09</v>
@@ -1784,10 +1784,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:30</v>
+        <v>4:19</v>
       </c>
       <c r="H37" t="str">
-        <v>Jessie J</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
+        <v>Freya Skye - why'd you have to call - Freya Skye</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer)</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
+        <v>https://www.youtube.com/watch?v=DGmbe49F8aI</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-09</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:24</v>
+        <v>2:30</v>
       </c>
       <c r="H38" t="str">
-        <v>Marc Anthony</v>
+        <v>Jessie J</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
+        <v>Jessie J - FEEL IT ON ME (Lyric Visualiser) (Official Lyric Video) - Jessie J</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
+        <v>Marc Anthony - Make It With You (Visualizer)</v>
       </c>
       <c r="B39" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
+        <v>https://www.youtube.com/watch?v=WHnz1jDrxw8</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-09</v>
@@ -1860,10 +1860,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:33</v>
+        <v>4:24</v>
       </c>
       <c r="H39" t="str">
-        <v>Clara Mae</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
+        <v>Marc Anthony - Make It With You (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Metric - Victim of Luck (Official Music Video)</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt</v>
       </c>
       <c r="B40" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
+        <v>https://www.youtube.com/watch?v=HtVuKBlBuPg</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-09</v>
@@ -1898,10 +1898,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:25</v>
+        <v>2:33</v>
       </c>
       <c r="H40" t="str">
-        <v>metricmusic</v>
+        <v>Clara Mae</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
+        <v>Clara Mae - Never Been Yours ft. Bob John Holt - Clara Mae</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
+        <v>Metric - Victim of Luck (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
+        <v>https://www.youtube.com/watch?v=shmhTOUd8mA</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-09</v>
@@ -1936,10 +1936,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:41</v>
+        <v>3:25</v>
       </c>
       <c r="H41" t="str">
-        <v>kesha</v>
+        <v>metricmusic</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
+        <v>Metric - Victim of Luck (Official Music Video) - metricmusic</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
+        <v>https://www.youtube.com/watch?v=pvrJ5RnPAEA</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-09</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:19</v>
+        <v>3:41</v>
       </c>
       <c r="H42" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>kesha</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
+        <v>Kesha - RED FLAG. (Red Carpet) OFFICIAL MUSIC VIDEO - kesha</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio)</v>
       </c>
       <c r="B43" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
+        <v>https://www.youtube.com/watch?v=mgsdQI-GVMM</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-09</v>
@@ -2012,10 +2012,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:37</v>
+        <v>3:19</v>
       </c>
       <c r="H43" t="str">
-        <v>Vera Blue</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Studio) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour)</v>
       </c>
       <c r="B44" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
+        <v>https://www.youtube.com/watch?v=SYEwk-EZJPU</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-09</v>
@@ -2050,10 +2050,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:08</v>
+        <v>3:37</v>
       </c>
       <c r="H44" t="str">
-        <v>Bob Moses</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
+        <v>Vera Blue - Hold (Live on Sydney Harbour) - Vera Blue</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023</v>
       </c>
       <c r="B45" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
+        <v>https://www.youtube.com/watch?v=CoCqPwDIBOA</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-09</v>
@@ -2088,10 +2088,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:28</v>
+        <v>3:08</v>
       </c>
       <c r="H45" t="str">
-        <v>Marc Anthony</v>
+        <v>Bob Moses</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
+        <v>Bob Moses - Need You Tonight (INXS Cover) - Brooklyn Mirage 2023 - Bob Moses</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
+        <v>https://www.youtube.com/watch?v=18yZq5xtke4</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-09</v>
@@ -2126,7 +2126,7 @@
         <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>5:05</v>
+        <v>3:28</v>
       </c>
       <c r="H46" t="str">
         <v>Marc Anthony</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
+        <v>Marc Anthony - Un Mal Sueño (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Loreen - Feels Like Heaven</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer)</v>
       </c>
       <c r="B47" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
+        <v>https://www.youtube.com/watch?v=IGLmJ71oHhQ</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-09</v>
@@ -2164,10 +2164,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:14</v>
+        <v>5:05</v>
       </c>
       <c r="H47" t="str">
-        <v>Loreen</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Loreen - Feels Like Heaven - Loreen</v>
+        <v>Marc Anthony - Contra La Corriente (Visualizer) - Marc Anthony</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
+        <v>Loreen - Feels Like Heaven</v>
       </c>
       <c r="B48" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
+        <v>https://www.youtube.com/watch?v=BQc97moyQBg</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-09</v>
@@ -2202,10 +2202,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:36</v>
+        <v>3:14</v>
       </c>
       <c r="H48" t="str">
-        <v>Take That</v>
+        <v>Loreen</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
+        <v>Loreen - Feels Like Heaven - Loreen</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992)</v>
       </c>
       <c r="B49" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
+        <v>https://www.youtube.com/watch?v=dOeoDOueESk</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-09</v>
@@ -2240,10 +2240,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>5:31</v>
+        <v>3:36</v>
       </c>
       <c r="H49" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Take That</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
+        <v>Take That - Once You've Tasted Love (Live on Pebble Mill, 1992) - Take That</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio)</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser)</v>
       </c>
       <c r="B50" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
+        <v>https://www.youtube.com/watch?v=a4AIjUHuWpU</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-09</v>
@@ -2278,10 +2278,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:37</v>
+        <v>5:31</v>
       </c>
       <c r="H50" t="str">
-        <v>Nothing But Thieves</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
+        <v>Paul McCartney, Wings - Nineteen Hundred And Eighty Five (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
+        <v>Nothing But Thieves - Sorry (Official Audio)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
+        <v>https://www.youtube.com/watch?v=D7QfVqo5YqY</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-09</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:58</v>
+        <v>3:37</v>
       </c>
       <c r="H51" t="str">
-        <v>The Warning</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
+        <v>Nothing But Thieves - Sorry (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music</v>
       </c>
       <c r="B52" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
+        <v>https://www.youtube.com/watch?v=KdsHxyl4bE8</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-09</v>
@@ -2354,10 +2354,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>5:08</v>
+        <v>4:58</v>
       </c>
       <c r="H52" t="str">
-        <v>The Offspring</v>
+        <v>The Warning</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
+        <v>Escapism (Live) | The Warning | Honda Stage x Uforia Music - The Warning</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026)</v>
       </c>
       <c r="B53" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
+        <v>https://www.youtube.com/watch?v=Mwkl_Cz_SG8</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-09</v>
@@ -2392,10 +2392,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:38</v>
+        <v>5:08</v>
       </c>
       <c r="H53" t="str">
-        <v>Roxette</v>
+        <v>The Offspring</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
+        <v>The Offspring - Pretty Fly (for a White Guy) Live in Bakersfield, CA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
+        <v>https://www.youtube.com/watch?v=I7a-pDZFE7U</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-09</v>
@@ -2430,10 +2430,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:50</v>
+        <v>4:38</v>
       </c>
       <c r="H54" t="str">
-        <v>Jessie Ware</v>
+        <v>Roxette</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
+        <v>Roxette - Crash! Boom! Bang! (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
+        <v>https://www.youtube.com/watch?v=kGeamxRf8Gw</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-09</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:10</v>
+        <v>3:50</v>
       </c>
       <c r="H55" t="str">
-        <v>Joseph</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
+        <v>Jessie Ware - I Could Get Used To This ( Live at Graham Norton) - Jessie Ware</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
+        <v>JOSEPH - Water in the Room (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
+        <v>https://www.youtube.com/watch?v=tNmT47k6MjM</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-09</v>
@@ -2506,10 +2506,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:44</v>
+        <v>3:10</v>
       </c>
       <c r="H56" t="str">
-        <v>Dean Lewis</v>
+        <v>Joseph</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
+        <v>JOSEPH - Water in the Room (Official Music Video) - Joseph</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Take That - Take That and Party (Official HD Video)</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video)</v>
       </c>
       <c r="B57" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
+        <v>https://www.youtube.com/watch?v=6ecgOSOMWzc</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-09</v>
@@ -2544,10 +2544,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:57</v>
+        <v>2:44</v>
       </c>
       <c r="H57" t="str">
-        <v>Take That</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
+        <v>Dean Lewis - I Am Getting Well (Lyric Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
+        <v>Take That - Take That and Party (Official HD Video)</v>
       </c>
       <c r="B58" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
+        <v>https://www.youtube.com/watch?v=DAerJcerikU</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-09</v>
@@ -2582,10 +2582,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:07</v>
+        <v>2:57</v>
       </c>
       <c r="H58" t="str">
-        <v>The Kiffness and Matisyahu</v>
+        <v>Take That</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
+        <v>Take That - Take That and Party (Official HD Video) - Take That</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video]</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO]</v>
       </c>
       <c r="B59" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
+        <v>https://www.youtube.com/watch?v=buS21tVq5r0</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-09</v>
@@ -2620,10 +2620,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>4:47</v>
+        <v>3:07</v>
       </c>
       <c r="H59" t="str">
-        <v>Paris Paloma</v>
+        <v>The Kiffness and Matisyahu</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
+        <v>The Kiffness &amp; Matisyahu - ONE DAY (ft. Andel and Nalyn) [OFFICIAL VIDEO] - The Kiffness and Matisyahu</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
+        <v>Paris Paloma - Good Girl [Official Music Video]</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
+        <v>https://www.youtube.com/watch?v=qhO6VMC-nx0</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-09</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:22</v>
+        <v>4:47</v>
       </c>
       <c r="H60" t="str">
-        <v>Zara Larsson</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
+        <v>Paris Paloma - Good Girl [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Only The Poets - Monumental</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
+        <v>https://www.youtube.com/watch?v=FgAyfRnbbRs</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-09</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:48</v>
+        <v>3:22</v>
       </c>
       <c r="H61" t="str">
-        <v>only the poets</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Only The Poets - Monumental - only the poets</v>
+        <v>Zara Larsson - Lush Life (Official UGC Compilation Video) - Zara Larsson</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
+        <v>Only The Poets - Monumental</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
+        <v>https://www.youtube.com/watch?v=nwXiAjjl6NE</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-09</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>2:52</v>
+        <v>2:48</v>
       </c>
       <c r="H62" t="str">
-        <v>Katelyn Tarver</v>
+        <v>only the poets</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
+        <v>Only The Poets - Monumental - only the poets</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
+        <v>https://www.youtube.com/watch?v=MjUiVPzMQHw</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-09</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:33</v>
+        <v>2:52</v>
       </c>
       <c r="H63" t="str">
-        <v>David Guetta</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
+        <v>Katelyn Tarver - So Am I (Official Music Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer]</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
+        <v>https://www.youtube.com/watch?v=eWglDE7O5r8</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-09</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:41</v>
+        <v>3:33</v>
       </c>
       <c r="H64" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>David Guetta</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>David Guetta, TeddySwims, Tones And I - Gone Gone Gone (Unplugged) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer)</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
+        <v>https://www.youtube.com/watch?v=Cmy8CsYIUL0</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-09</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>4:01</v>
+        <v>2:41</v>
       </c>
       <c r="H65" t="str">
-        <v>Ella Langley</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
+        <v>SANTOS BRAVOS “KAWASAKI” Performance Video - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Dogpark - Dandelion (Official Music Video)</v>
+        <v>Ella Langley - Dandelion (Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
+        <v>https://www.youtube.com/watch?v=sf6eRmInk1s</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-09</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:16</v>
+        <v>4:01</v>
       </c>
       <c r="H66" t="str">
-        <v>Dogpark</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
+        <v>Ella Langley - Dandelion (Official Visualizer) - Ella Langley</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
+        <v>Dogpark - Dandelion (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
+        <v>https://www.youtube.com/watch?v=fv9prIYHHzk</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-09</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:03</v>
+        <v>3:16</v>
       </c>
       <c r="H67" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Dogpark</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
+        <v>Dogpark - Dandelion (Official Music Video) - Dogpark</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ERNEST - Lorelei (Official Music Video)</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
+        <v>https://www.youtube.com/watch?v=T9YvLA2cdZs</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-09</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:41</v>
+        <v>3:03</v>
       </c>
       <c r="H68" t="str">
-        <v>ERNEST</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
+        <v>Lauren Spencer Smith - Natural Disaster (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio)</v>
+        <v>ERNEST - Lorelei (Official Music Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
+        <v>https://www.youtube.com/watch?v=dPWc_6IdDJk</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-09</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:05</v>
+        <v>2:41</v>
       </c>
       <c r="H69" t="str">
-        <v>Labrinth</v>
+        <v>ERNEST</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
+        <v>ERNEST - Lorelei (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
+        <v>Labrinth - I Keep My Promises (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
+        <v>https://www.youtube.com/watch?v=CV5rR9JZK-0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-09</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:46</v>
+        <v>3:05</v>
       </c>
       <c r="H70" t="str">
-        <v>Grace VanderWaal</v>
+        <v>Labrinth</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
+        <v>Labrinth - I Keep My Promises (Official Audio) - Labrinth</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
+        <v>https://www.youtube.com/watch?v=9HwTj3NZ16E</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-09</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:32</v>
+        <v>2:46</v>
       </c>
       <c r="H71" t="str">
-        <v>VOILÀ</v>
+        <v>Grace VanderWaal</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
+        <v>Grace VanderWaal - Prettier (Official Lyric Video) - Grace VanderWaal</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Cannons - Starlight (Official Video)</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
+        <v>https://www.youtube.com/watch?v=Lmus-UbL1H0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-09</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:42</v>
+        <v>3:32</v>
       </c>
       <c r="H72" t="str">
-        <v>Cannons</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Cannons - Starlight (Official Video) - Cannons</v>
+        <v>VOILÀ - Frozen Lake (Official Lyric Video) - VOILÀ</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video)</v>
+        <v>Cannons - Starlight (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
+        <v>https://www.youtube.com/watch?v=bu6WSMDDPGY</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-09</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:38</v>
+        <v>3:42</v>
       </c>
       <c r="H73" t="str">
-        <v>Kylie Morgan</v>
+        <v>Cannons</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
+        <v>Cannons - Starlight (Official Video) - Cannons</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
+        <v>Kylie Morgan - Like My Own (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
+        <v>https://www.youtube.com/watch?v=zcYeoGBglC0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-09</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:10</v>
+        <v>2:38</v>
       </c>
       <c r="H74" t="str">
-        <v>Lizzy McAlpine</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
+        <v>Kylie Morgan - Like My Own (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio)</v>
       </c>
       <c r="B75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
+        <v>https://www.youtube.com/watch?v=3igYRj82EiU</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-09</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:57</v>
+        <v>3:10</v>
       </c>
       <c r="H75" t="str">
-        <v>Willie Nelson</v>
+        <v>Lizzy McAlpine</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
+        <v>Lizzy McAlpine - House of the Rising Sun (Audio) - Lizzy McAlpine</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
+        <v>https://www.youtube.com/watch?v=0bhcO4Yphuo</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-09</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:19</v>
+        <v>3:57</v>
       </c>
       <c r="H76" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
+        <v>Willie Nelson - Heart Of America (From The Gray House Original Soundtrack) - Willie Nelson</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet</v>
       </c>
       <c r="B77" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
+        <v>https://www.youtube.com/watch?v=Jjz1wFe5dMo</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-09</v>
@@ -3304,10 +3304,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:04</v>
+        <v>2:19</v>
       </c>
       <c r="H77" t="str">
-        <v>India Martínez</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
+        <v>Jeremy Camp - No Survivors (Live) ft. Skillet - JeremyCampMusic</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo</v>
       </c>
       <c r="B78" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
+        <v>https://www.youtube.com/watch?v=Vug_FPbXe9E</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-09</v>
@@ -3342,10 +3342,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:16</v>
+        <v>4:04</v>
       </c>
       <c r="H78" t="str">
-        <v>Chelsea Cutler</v>
+        <v>India Martínez</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
+        <v>India Martinez, Coro ArteSí de Olvidados - Niño Sin Miedo - India Martínez</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
+        <v>https://www.youtube.com/watch?v=ZIW2vA3Zs1U</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-09</v>
@@ -3380,10 +3380,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>5:58</v>
+        <v>2:16</v>
       </c>
       <c r="H79" t="str">
-        <v>TINI</v>
+        <v>Chelsea Cutler</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
+        <v>Chelsea Cutler - BAD (Official Lyric Video) - Chelsea Cutler</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Charley - Serial Idealist (Official Video)</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa</v>
       </c>
       <c r="B80" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
+        <v>https://www.youtube.com/watch?v=q_rrgJZAdNg</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-09</v>
@@ -3418,10 +3418,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:26</v>
+        <v>5:58</v>
       </c>
       <c r="H80" t="str">
-        <v>Charley</v>
+        <v>TINI</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Charley - Serial Idealist (Official Video) - Charley</v>
+        <v>TINI - FUTTTURA LIVE - el cielo + fresa - TINI</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Demi Lovato - Ghost (Live)</v>
+        <v>Charley - Serial Idealist (Official Video)</v>
       </c>
       <c r="B81" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
+        <v>https://www.youtube.com/watch?v=uVIuKbPJz0U</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-09</v>
@@ -3456,10 +3456,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:05</v>
+        <v>3:26</v>
       </c>
       <c r="H81" t="str">
-        <v>Demi Lovato</v>
+        <v>Charley</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
+        <v>Charley - Serial Idealist (Official Video) - Charley</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
+        <v>Demi Lovato - Ghost (Live)</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
+        <v>https://www.youtube.com/watch?v=E-ECwdRndVA</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-09</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:16</v>
+        <v>4:05</v>
       </c>
       <c r="H82" t="str">
-        <v>Teddy Swims</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
+        <v>Demi Lovato - Ghost (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Beck - Love (Audio)</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions)</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
+        <v>https://www.youtube.com/watch?v=1ugf5aaY4pY</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-09</v>
@@ -3532,10 +3532,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:14</v>
+        <v>3:16</v>
       </c>
       <c r="H83" t="str">
-        <v>Beck</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Beck - Love (Audio) - Beck</v>
+        <v>Teddy Swims - Need You More (Live - Green Room Sessions) - Teddy Swims</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
+        <v>Beck - Love (Audio)</v>
       </c>
       <c r="B84" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
+        <v>https://www.youtube.com/watch?v=ByABj3Xof1I</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-09</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:57</v>
+        <v>3:14</v>
       </c>
       <c r="H84" t="str">
-        <v>The Offspring</v>
+        <v>Beck</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
+        <v>Beck - Love (Audio) - Beck</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026)</v>
       </c>
       <c r="B85" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
+        <v>https://www.youtube.com/watch?v=2HSbo51EFNg</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-09</v>
@@ -3608,10 +3608,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:10</v>
+        <v>2:57</v>
       </c>
       <c r="H85" t="str">
-        <v>Sophie Ellis-Bextor</v>
+        <v>The Offspring</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
+        <v>The Offspring - Looking Out For #1 | Live in Spokane, WA (2026) - The Offspring</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show</v>
       </c>
       <c r="B86" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
+        <v>https://www.youtube.com/watch?v=ylifHFJWJ_c</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-09</v>
@@ -3646,10 +3646,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:10</v>
+        <v>4:10</v>
       </c>
       <c r="H86" t="str">
-        <v>Jason Derulo</v>
+        <v>Sophie Ellis-Bextor</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
+        <v>Sophie Ellis-Bextor 'Murder On The Dancefloor' - Live on Michael McIntyre's Big Show - Sophie Ellis-Bextor</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Lights - COME GET YOUR GIRL</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video]</v>
       </c>
       <c r="B87" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
+        <v>https://www.youtube.com/watch?v=9ST-eBNL0NU</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-09</v>
@@ -3684,10 +3684,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:52</v>
+        <v>2:10</v>
       </c>
       <c r="H87" t="str">
-        <v>lights</v>
+        <v>Jason Derulo</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Lights - COME GET YOUR GIRL - lights</v>
+        <v>Jason Derulo - Sexy For Me [Official Music Video] - Jason Derulo</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
+        <v>Lights - COME GET YOUR GIRL</v>
       </c>
       <c r="B88" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
+        <v>https://www.youtube.com/watch?v=EhzX2y5MpSM</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-09</v>
@@ -3722,10 +3722,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:50</v>
+        <v>3:52</v>
       </c>
       <c r="H88" t="str">
-        <v>Telenova</v>
+        <v>lights</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
+        <v>Lights - COME GET YOUR GIRL - lights</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video)</v>
       </c>
       <c r="B89" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
+        <v>https://www.youtube.com/watch?v=yUAvfo8fpuU</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-09</v>
@@ -3760,10 +3760,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>5:32</v>
+        <v>3:50</v>
       </c>
       <c r="H89" t="str">
-        <v>Marcin</v>
+        <v>Telenova</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
+        <v>Telenova - IN THE NAME OF YOUR LOVE (Official Video) - Telenova</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>We Three - Drunk Driving (Official Music Video)</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert</v>
       </c>
       <c r="B90" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
+        <v>https://www.youtube.com/watch?v=KnsBdAM3HqY</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-09</v>
@@ -3798,10 +3798,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:27</v>
+        <v>5:32</v>
       </c>
       <c r="H90" t="str">
-        <v>We Three</v>
+        <v>Marcin</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
+        <v>I Had To Explain "How Music Works" LIVE In Concert - Marcin</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Timebelle - Top of the World (Mood Video)</v>
+        <v>We Three - Drunk Driving (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
+        <v>https://www.youtube.com/watch?v=BTqRGxSX6AQ</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-09</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:01</v>
+        <v>4:27</v>
       </c>
       <c r="H91" t="str">
-        <v>Timebelle Official</v>
+        <v>We Three</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
+        <v>We Three - Drunk Driving (Official Music Video) - We Three</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
+        <v>Timebelle - Top of the World (Mood Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
+        <v>https://www.youtube.com/watch?v=r9KyYK_E34s</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-09</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:20</v>
+        <v>3:01</v>
       </c>
       <c r="H92" t="str">
-        <v>David Guetta and Tones And I</v>
+        <v>Timebelle Official</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
+        <v>Timebelle - Top of the World (Mood Video) - Timebelle Official</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
+        <v>https://www.youtube.com/watch?v=57a_OheOlDw</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-09</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:34</v>
+        <v>3:20</v>
       </c>
       <c r="H93" t="str">
-        <v>Clinton Kane</v>
+        <v>David Guetta and Tones And I</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
+        <v>David Guetta, Teddy Swims, Tones And I - Gone Gone Gone (Tones Acoustic Session - Rooftop) - David Guetta and Tones And I</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
+        <v>https://www.youtube.com/watch?v=-5Aa8NTiRqE</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-09</v>
@@ -3950,10 +3950,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
-        <v>4:01</v>
+        <v>3:34</v>
       </c>
       <c r="H94" t="str">
-        <v>Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
+        <v>Clinton Kane - this is my last love song to you (Official Lyric Video) - Clinton Kane</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
+        <v>https://www.youtube.com/watch?v=5RNy_1odv20</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-09</v>
@@ -3988,10 +3988,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:24</v>
+        <v>4:01</v>
       </c>
       <c r="H95" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
+        <v>SIENNA SPIRO - Die On This Hill (Official Music Video) - Lyrical Lemonade and SIENNA SPIRO</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Harry Styles - Aperture (Official Video)</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
+        <v>https://www.youtube.com/watch?v=stYIRyCLN4Y</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-09</v>
@@ -4026,10 +4026,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
-        <v>5:52</v>
+        <v>3:24</v>
       </c>
       <c r="H96" t="str">
-        <v>Harry Styles</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
+        <v>Amazon Music presents: Sienna Spiro - You Stole The Show - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
+        <v>Harry Styles - Aperture (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
+        <v>https://www.youtube.com/watch?v=7sxVHYZ_PnA</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-09</v>
@@ -4064,10 +4064,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
-        <v>5:01</v>
+        <v>5:52</v>
       </c>
       <c r="H97" t="str">
-        <v>Neal Francis</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
+        <v>Harry Styles - Aperture (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
+        <v>https://www.youtube.com/watch?v=46iZEdsxjC0</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-09</v>
@@ -4102,10 +4102,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:12</v>
+        <v>5:01</v>
       </c>
       <c r="H98" t="str">
-        <v>OfficiallyExtreme</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
+        <v>Neal Francis - Back It Up (Live At The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
+        <v>https://www.youtube.com/watch?v=K2nG1Uukz7E</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-09</v>
@@ -4140,10 +4140,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:59</v>
+        <v>4:12</v>
       </c>
       <c r="H99" t="str">
-        <v>Holly Humberstone</v>
+        <v>OfficiallyExtreme</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
+        <v>Extreme - Medley (More Than Words &amp; Hole Hearted) (Brit Awards, February 12, 1992) - OfficiallyExtreme</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
+        <v>https://www.youtube.com/watch?v=9hWa9w0njxE</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-09</v>
@@ -4178,10 +4178,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:56</v>
+        <v>3:59</v>
       </c>
       <c r="H100" t="str">
-        <v>Cliff Richard</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
+        <v>Holly Humberstone - To Love Somebody (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
+        <v>https://www.youtube.com/watch?v=dLqV5Z062Sk</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-09</v>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:46</v>
+        <v>2:56</v>
       </c>
       <c r="H101" t="str">
-        <v>Jessie Ware</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
+        <v>Cliff Richard - The Next Time (60th Anniversary Tour, Manchester, 12 Oct 2018) - Cliff Richard</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Die For Me</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>2 weeks ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
+        <v>https://www.youtube.com/watch?v=RV-ONO_Ok5c</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-09</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>KONNAKOL</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:00</v>
+        <v>3:46</v>
       </c>
       <c r="H102" t="str">
-        <v>ZAYN</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Die For Me - ZAYN</v>
+        <v>Jessie Ware - I Could Get Used To This (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Two Six</v>
+        <v>Die For Me</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/two-six/1875080974</v>
+        <v>https://music.apple.com/us/song/die-for-me/1872664213</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-09</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Fall-Off</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G103" t="str">
-        <v>3:16</v>
+        <v>3:00</v>
       </c>
       <c r="H103" t="str">
-        <v>J. Cole</v>
+        <v>ZAYN</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/two-six/1875080726</v>
+        <v>https://music.apple.com/us/album/die-for-me/1872663947</v>
       </c>
       <c r="L103" t="str">
-        <v>Two Six - J. Cole</v>
+        <v>Die For Me - ZAYN</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Dracula (JENNIE Remix)</v>
+        <v>Two Six</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
+        <v>https://music.apple.com/us/song/two-six/1875080974</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-09</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Dracula (Remix) - Single</v>
+        <v>The Fall-Off</v>
       </c>
       <c r="G104" t="str">
-        <v>3:29</v>
+        <v>3:16</v>
       </c>
       <c r="H104" t="str">
-        <v>Tame Impala</v>
+        <v>J. Cole</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
+        <v>https://music.apple.com/us/artist/j-cole/73705833</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
+        <v>https://music.apple.com/us/album/two-six/1875080726</v>
       </c>
       <c r="L104" t="str">
-        <v>Dracula (JENNIE Remix) - Tame Impala</v>
+        <v>Two Six - J. Cole</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Hotel California</v>
+        <v>Dracula (JENNIE Remix)</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
+        <v>https://music.apple.com/us/song/dracula-jennie-remix/1874125269</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-09</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Piss In The Wind</v>
+        <v>Dracula (Remix) - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:08</v>
+        <v>3:29</v>
       </c>
       <c r="H105" t="str">
-        <v>Joji</v>
+        <v>Tame Impala</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/tame-impala/290242959</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
+        <v>https://music.apple.com/us/album/dracula-jennie-remix/1874125260</v>
       </c>
       <c r="L105" t="str">
-        <v>Hotel California - Joji</v>
+        <v>Dracula (JENNIE Remix) - Tame Impala</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Homewrecker</v>
+        <v>Hotel California</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
+        <v>https://music.apple.com/us/song/hotel-california/1849707040</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-09</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Homewrecker - Single</v>
+        <v>Piss In The Wind</v>
       </c>
       <c r="G106" t="str">
-        <v>3:29</v>
+        <v>2:08</v>
       </c>
       <c r="H106" t="str">
-        <v>sombr</v>
+        <v>Joji</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
+        <v>https://music.apple.com/us/album/hotel-california/1849706656</v>
       </c>
       <c r="L106" t="str">
-        <v>Homewrecker - sombr</v>
+        <v>Hotel California - Joji</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Might Just</v>
+        <v>Homewrecker</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/might-just/1858755211</v>
+        <v>https://music.apple.com/us/song/homewrecker/1871595253</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-09</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Do You Still Love Me?</v>
+        <v>Homewrecker - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:43</v>
+        <v>3:29</v>
       </c>
       <c r="H107" t="str">
-        <v>Ella Mai</v>
+        <v>sombr</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/might-just/1858754868</v>
+        <v>https://music.apple.com/us/album/homewrecker/1871595252</v>
       </c>
       <c r="L107" t="str">
-        <v>Might Just - Ella Mai</v>
+        <v>Homewrecker - sombr</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Cloud 9</v>
+        <v>Might Just</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
+        <v>https://music.apple.com/us/song/might-just/1858755211</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-09</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Cloud 9</v>
+        <v>Do You Still Love Me?</v>
       </c>
       <c r="G108" t="str">
-        <v>3:33</v>
+        <v>3:43</v>
       </c>
       <c r="H108" t="str">
-        <v>Megan Moroney</v>
+        <v>Ella Mai</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/ella-mai/1160482144</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
+        <v>https://music.apple.com/us/album/might-just/1858754868</v>
       </c>
       <c r="L108" t="str">
-        <v>Cloud 9 - Megan Moroney</v>
+        <v>Might Just - Ella Mai</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Cry</v>
+        <v>Cloud 9</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/cry/1845189974</v>
+        <v>https://music.apple.com/us/song/cloud-9/1851297055</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-09</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G109" t="str">
-        <v>3:07</v>
+        <v>3:33</v>
       </c>
       <c r="H109" t="str">
-        <v>Charlie Puth</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/cry/1845189970</v>
+        <v>https://music.apple.com/us/album/cloud-9/1851296746</v>
       </c>
       <c r="L109" t="str">
-        <v>Cry - Charlie Puth</v>
+        <v>Cloud 9 - Megan Moroney</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>I'll Change for You</v>
+        <v>Cry</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
+        <v>https://music.apple.com/us/song/cry/1845189974</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-09</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G110" t="str">
-        <v>3:16</v>
+        <v>3:07</v>
       </c>
       <c r="H110" t="str">
-        <v>Mitski</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
+        <v>https://music.apple.com/us/album/cry/1845189970</v>
       </c>
       <c r="L110" t="str">
-        <v>I'll Change for You - Mitski</v>
+        <v>Cry - Charlie Puth</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>ASSIGNMENT</v>
+        <v>I'll Change for You</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/assignment/1872764440</v>
+        <v>https://music.apple.com/us/song/ill-change-for-you/1860622841</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-09</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>ASSIGNMENT - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G111" t="str">
-        <v>2:23</v>
+        <v>3:16</v>
       </c>
       <c r="H111" t="str">
-        <v>Power Snatch</v>
+        <v>Mitski</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/assignment/1872764438</v>
+        <v>https://music.apple.com/us/album/ill-change-for-you/1860622550</v>
       </c>
       <c r="L111" t="str">
-        <v>ASSIGNMENT - Power Snatch</v>
+        <v>I'll Change for You - Mitski</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Como en el Idilio</v>
+        <v>ASSIGNMENT</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
+        <v>https://music.apple.com/us/song/assignment/1872764440</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-09</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Como en el Idilio - Single</v>
+        <v>ASSIGNMENT - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>4:27</v>
+        <v>2:23</v>
       </c>
       <c r="H112" t="str">
-        <v>Marc Anthony</v>
+        <v>Power Snatch</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
+        <v>https://music.apple.com/us/artist/power-snatch/1872764439</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
+        <v>https://music.apple.com/us/album/assignment/1872764438</v>
       </c>
       <c r="L112" t="str">
-        <v>Como en el Idilio - Marc Anthony</v>
+        <v>ASSIGNMENT - Power Snatch</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>golden boy</v>
+        <v>Como en el Idilio</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
+        <v>https://music.apple.com/us/song/como-en-el-idilio/1870716613</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-09</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>stardust - EP</v>
+        <v>Como en el Idilio - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:17</v>
+        <v>4:27</v>
       </c>
       <c r="H113" t="str">
-        <v>Freya Skye</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
+        <v>https://music.apple.com/us/artist/marc-anthony/217029</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
+        <v>https://music.apple.com/us/album/como-en-el-idilio/1870716612</v>
       </c>
       <c r="L113" t="str">
-        <v>golden boy - Freya Skye</v>
+        <v>Como en el Idilio - Marc Anthony</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Penny in the Lake</v>
+        <v>golden boy</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
+        <v>https://music.apple.com/us/song/golden-boy/1872543012</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-09</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Singin’ to an Empty Chair</v>
+        <v>stardust - EP</v>
       </c>
       <c r="G114" t="str">
-        <v>3:51</v>
+        <v>3:17</v>
       </c>
       <c r="H114" t="str">
-        <v>Ratboys</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
+        <v>https://music.apple.com/us/artist/freya-skye/1541643053</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
+        <v>https://music.apple.com/us/album/golden-boy/1872542998</v>
       </c>
       <c r="L114" t="str">
-        <v>Penny in the Lake - Ratboys</v>
+        <v>golden boy - Freya Skye</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Heaven</v>
+        <v>Penny in the Lake</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/heaven/1862570892</v>
+        <v>https://music.apple.com/us/song/penny-in-the-lake/1844710053</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-09</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Singin’ to an Empty Chair</v>
       </c>
       <c r="G115" t="str">
-        <v>4:26</v>
+        <v>3:51</v>
       </c>
       <c r="H115" t="str">
-        <v>Arlo Parks</v>
+        <v>Ratboys</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/ratboys/997909855</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/heaven/1862570378</v>
+        <v>https://music.apple.com/us/album/penny-in-the-lake/1844710034</v>
       </c>
       <c r="L115" t="str">
-        <v>Heaven - Arlo Parks</v>
+        <v>Penny in the Lake - Ratboys</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Adrenaline</v>
+        <v>Heaven</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
+        <v>https://music.apple.com/us/song/heaven/1862570892</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-09</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>GOLDEN HOUR : Part.4 - EP</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G116" t="str">
-        <v>3:39</v>
+        <v>4:26</v>
       </c>
       <c r="H116" t="str">
-        <v>ATEEZ</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
+        <v>https://music.apple.com/us/album/heaven/1862570378</v>
       </c>
       <c r="L116" t="str">
-        <v>Adrenaline - ATEEZ</v>
+        <v>Heaven - Arlo Parks</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Sweet To Me</v>
+        <v>Adrenaline</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
+        <v>https://music.apple.com/us/song/adrenaline/1867153030</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-09</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Sunday Best</v>
+        <v>GOLDEN HOUR : Part.4 - EP</v>
       </c>
       <c r="G117" t="str">
-        <v>4:17</v>
+        <v>3:39</v>
       </c>
       <c r="H117" t="str">
-        <v>Nick Jonas</v>
+        <v>ATEEZ</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
+        <v>https://music.apple.com/us/artist/ateez/1439301205</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
+        <v>https://music.apple.com/us/album/adrenaline/1867153027</v>
       </c>
       <c r="L117" t="str">
-        <v>Sweet To Me - Nick Jonas</v>
+        <v>Adrenaline - ATEEZ</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Time Goes On</v>
+        <v>Sweet To Me</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
+        <v>https://music.apple.com/us/song/sweet-to-me/1856393194</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-09</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Time Goes On - Single</v>
+        <v>Sunday Best</v>
       </c>
       <c r="G118" t="str">
-        <v>2:55</v>
+        <v>4:17</v>
       </c>
       <c r="H118" t="str">
-        <v>Koe Wetzel</v>
+        <v>Nick Jonas</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/nick-jonas/286541773</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
+        <v>https://music.apple.com/us/album/sweet-to-me/1856393193</v>
       </c>
       <c r="L118" t="str">
-        <v>Time Goes On - Koe Wetzel</v>
+        <v>Sweet To Me - Nick Jonas</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Drive Safe</v>
+        <v>Time Goes On</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
+        <v>https://music.apple.com/us/song/time-goes-on/1872532339</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-09</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Drive Safe - Single</v>
+        <v>Time Goes On - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:21</v>
+        <v>2:55</v>
       </c>
       <c r="H119" t="str">
-        <v>Myles Smith</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
+        <v>https://music.apple.com/us/album/time-goes-on/1872532335</v>
       </c>
       <c r="L119" t="str">
-        <v>Drive Safe - Myles Smith</v>
+        <v>Time Goes On - Koe Wetzel</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Love To Be Loved</v>
+        <v>Drive Safe</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
+        <v>https://music.apple.com/us/song/drive-safe/1868764975</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-09</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Love To Be Loved - Single</v>
+        <v>Drive Safe - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:50</v>
+        <v>3:21</v>
       </c>
       <c r="H120" t="str">
-        <v>The Warning</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
+        <v>https://music.apple.com/us/album/drive-safe/1868764971</v>
       </c>
       <c r="L120" t="str">
-        <v>Love To Be Loved - The Warning</v>
+        <v>Drive Safe - Myles Smith</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Mi Yo de Antes</v>
+        <v>Love To Be Loved</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
+        <v>https://music.apple.com/us/song/love-to-be-loved/1873043629</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-09</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Mi Yo de Antes - Single</v>
+        <v>Love To Be Loved - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:02</v>
+        <v>2:50</v>
       </c>
       <c r="H121" t="str">
-        <v>Eden Muñoz</v>
+        <v>The Warning</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
+        <v>https://music.apple.com/us/album/love-to-be-loved/1873043478</v>
       </c>
       <c r="L121" t="str">
-        <v>Mi Yo de Antes - Eden Muñoz</v>
+        <v>Love To Be Loved - The Warning</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Omens</v>
+        <v>Mi Yo de Antes</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/omens/1872546206</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/1871552001</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-09</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Omens - Single</v>
+        <v>Mi Yo de Antes - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:00</v>
+        <v>3:02</v>
       </c>
       <c r="H122" t="str">
-        <v>EsDeeKid</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/omens/1872546204</v>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/1871552000</v>
       </c>
       <c r="L122" t="str">
-        <v>Omens - EsDeeKid</v>
+        <v>Mi Yo de Antes - Eden Muñoz</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>My Regards</v>
+        <v>Omens</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
+        <v>https://music.apple.com/us/song/omens/1872546206</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-09</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Florescence</v>
+        <v>Omens - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:11</v>
+        <v>2:00</v>
       </c>
       <c r="H123" t="str">
-        <v>Maisie Peters</v>
+        <v>EsDeeKid</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/esdeekid/1754179834</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
+        <v>https://music.apple.com/us/album/omens/1872546204</v>
       </c>
       <c r="L123" t="str">
-        <v>My Regards - Maisie Peters</v>
+        <v>Omens - EsDeeKid</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Time After Time</v>
+        <v>My Regards</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
+        <v>https://music.apple.com/us/song/my-regards/1871502698</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-09</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Time After Time - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G124" t="str">
-        <v>2:48</v>
+        <v>3:11</v>
       </c>
       <c r="H124" t="str">
-        <v>EJAE</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
+        <v>https://music.apple.com/us/album/my-regards/1871502372</v>
       </c>
       <c r="L124" t="str">
-        <v>Time After Time - EJAE</v>
+        <v>My Regards - Maisie Peters</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Don't Want Your Love</v>
+        <v>Time After Time</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
+        <v>https://music.apple.com/us/song/time-after-time/1869014152</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-09</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>ODYSSEY</v>
+        <v>Time After Time - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:12</v>
+        <v>2:48</v>
       </c>
       <c r="H125" t="str">
-        <v>ILLENIUM</v>
+        <v>EJAE</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/illenium/645420096</v>
+        <v>https://music.apple.com/us/artist/ejae/1118367711</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
+        <v>https://music.apple.com/us/album/time-after-time/1869014148</v>
       </c>
       <c r="L125" t="str">
-        <v>Don't Want Your Love - ILLENIUM</v>
+        <v>Time After Time - EJAE</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Pa' Los Envidiosos</v>
+        <v>Don't Want Your Love</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
+        <v>https://music.apple.com/us/song/dont-want-your-love/1851368163</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-09</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Pa' Los Envidiosos - Single</v>
+        <v>ODYSSEY</v>
       </c>
       <c r="G126" t="str">
-        <v>3:37</v>
+        <v>3:12</v>
       </c>
       <c r="H126" t="str">
-        <v>Pitbull</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
+        <v>https://music.apple.com/us/album/dont-want-your-love/1851368154</v>
       </c>
       <c r="L126" t="str">
-        <v>Pa' Los Envidiosos - Pitbull</v>
+        <v>Don't Want Your Love - ILLENIUM</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Plei</v>
+        <v>Pa' Los Envidiosos</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/plei/1872137577</v>
+        <v>https://music.apple.com/us/song/pa-los-envidiosos/1867022002</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-09</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Plei - Single</v>
+        <v>Pa' Los Envidiosos - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:22</v>
+        <v>3:37</v>
       </c>
       <c r="H127" t="str">
-        <v>Chuwi</v>
+        <v>Pitbull</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/plei/1872137372</v>
+        <v>https://music.apple.com/us/album/pa-los-envidiosos/1867021988</v>
       </c>
       <c r="L127" t="str">
-        <v>Plei - Chuwi</v>
+        <v>Pa' Los Envidiosos - Pitbull</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Flood (feat. Bon Iver)</v>
+        <v>Plei</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
+        <v>https://music.apple.com/us/song/plei/1872137577</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-09</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Plei - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:59</v>
+        <v>3:22</v>
       </c>
       <c r="H128" t="str">
-        <v>Dua Saleh</v>
+        <v>Chuwi</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/chuwi/1493658688</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
+        <v>https://music.apple.com/us/album/plei/1872137372</v>
       </c>
       <c r="L128" t="str">
-        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
+        <v>Plei - Chuwi</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Rain</v>
+        <v>Flood (feat. Bon Iver)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/rain/1867258289</v>
+        <v>https://music.apple.com/us/song/flood-feat-bon-iver/1868826992</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-09</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Rain - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G129" t="str">
-        <v>3:28</v>
+        <v>2:59</v>
       </c>
       <c r="H129" t="str">
-        <v>FISHER</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/rain/1867258288</v>
+        <v>https://music.apple.com/us/album/flood-feat-bon-iver/1868826829</v>
       </c>
       <c r="L129" t="str">
-        <v>Rain - FISHER</v>
+        <v>Flood (feat. Bon Iver) - Dua Saleh</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Release The Pressure</v>
+        <v>Rain</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
+        <v>https://music.apple.com/us/song/rain/1867258289</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-09</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Release The Pressure - Single</v>
+        <v>Rain - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:23</v>
+        <v>3:28</v>
       </c>
       <c r="H130" t="str">
-        <v>Calvin Harris</v>
+        <v>FISHER</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
+        <v>https://music.apple.com/us/artist/fisher/1256012920</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
+        <v>https://music.apple.com/us/album/rain/1867258288</v>
       </c>
       <c r="L130" t="str">
-        <v>Release The Pressure - Calvin Harris</v>
+        <v>Rain - FISHER</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Sexistential (Arca’s Take)</v>
+        <v>Release The Pressure</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
+        <v>https://music.apple.com/us/song/release-the-pressure/1869050189</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-09</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Sexistential (Arca’s Take) - Single</v>
+        <v>Release The Pressure - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:44</v>
+        <v>3:23</v>
       </c>
       <c r="H131" t="str">
-        <v>Robyn</v>
+        <v>Calvin Harris</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
+        <v>https://music.apple.com/us/album/release-the-pressure/1869050188</v>
       </c>
       <c r="L131" t="str">
-        <v>Sexistential (Arca’s Take) - Robyn</v>
+        <v>Release The Pressure - Calvin Harris</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>heal something</v>
+        <v>Sexistential (Arca’s Take)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
+        <v>https://music.apple.com/us/song/sexistential-arcas-take/1871222137</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-09</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>ACT II</v>
+        <v>Sexistential (Arca’s Take) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:01</v>
+        <v>3:44</v>
       </c>
       <c r="H132" t="str">
-        <v>Sasha Keable</v>
+        <v>Robyn</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
+        <v>https://music.apple.com/us/album/sexistential-arcas-take/1871222136</v>
       </c>
       <c r="L132" t="str">
-        <v>heal something - Sasha Keable</v>
+        <v>Sexistential (Arca’s Take) - Robyn</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Buenos Días</v>
+        <v>heal something</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
+        <v>https://music.apple.com/us/song/heal-something/1871463897</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-09</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Buenos Días - Single</v>
+        <v>ACT II</v>
       </c>
       <c r="G133" t="str">
-        <v>2:39</v>
+        <v>3:01</v>
       </c>
       <c r="H133" t="str">
-        <v>Eladio Carrión</v>
+        <v>Sasha Keable</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
+        <v>https://music.apple.com/us/artist/sasha-keable/325850892</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
+        <v>https://music.apple.com/us/album/heal-something/1871463550</v>
       </c>
       <c r="L133" t="str">
-        <v>Buenos Días - Eladio Carrión</v>
+        <v>heal something - Sasha Keable</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>COOK</v>
+        <v>Buenos Días</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/cook/1872816147</v>
+        <v>https://music.apple.com/us/song/buenos-d%C3%ADas/1872144122</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-09</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>COOK - Single</v>
+        <v>Buenos Días - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:50</v>
+        <v>2:39</v>
       </c>
       <c r="H134" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Eladio Carrión</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/eladio-carri%C3%B3n/1024801206</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/cook/1872816146</v>
+        <v>https://music.apple.com/us/album/buenos-d%C3%ADas/1872144118</v>
       </c>
       <c r="L134" t="str">
-        <v>COOK - SOFI TUKKER</v>
+        <v>Buenos Días - Eladio Carrión</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>You Got to Lose</v>
+        <v>COOK</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
+        <v>https://music.apple.com/us/song/cook/1872816147</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-09</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Peaches!</v>
+        <v>COOK - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:17</v>
+        <v>2:50</v>
       </c>
       <c r="H135" t="str">
-        <v>The Black Keys</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
+        <v>https://music.apple.com/us/album/cook/1872816146</v>
       </c>
       <c r="L135" t="str">
-        <v>You Got to Lose - The Black Keys</v>
+        <v>COOK - SOFI TUKKER</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Different Kind Of Love</v>
+        <v>You Got to Lose</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
+        <v>https://music.apple.com/us/song/you-got-to-lose/1873477955</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-09</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Victory Garden</v>
+        <v>Peaches!</v>
       </c>
       <c r="G136" t="str">
-        <v>3:39</v>
+        <v>3:17</v>
       </c>
       <c r="H136" t="str">
-        <v>Young the Giant</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
+        <v>https://music.apple.com/us/album/you-got-to-lose/1873477948</v>
       </c>
       <c r="L136" t="str">
-        <v>Different Kind Of Love - Young the Giant</v>
+        <v>You Got to Lose - The Black Keys</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Living Water</v>
+        <v>Different Kind Of Love</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/living-water/1871565262</v>
+        <v>https://music.apple.com/us/song/different-kind-of-love/1866700768</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-09</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Reconstruction: Second Story</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G137" t="str">
-        <v>2:09</v>
+        <v>3:39</v>
       </c>
       <c r="H137" t="str">
-        <v>Lecrae</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/living-water/1871564892</v>
+        <v>https://music.apple.com/us/album/different-kind-of-love/1866700309</v>
       </c>
       <c r="L137" t="str">
-        <v>Living Water - Lecrae</v>
+        <v>Different Kind Of Love - Young the Giant</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>What It Feels Like</v>
+        <v>Living Water</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
+        <v>https://music.apple.com/us/song/living-water/1871565262</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-09</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>What It Feels Like - Single</v>
+        <v>Reconstruction: Second Story</v>
       </c>
       <c r="G138" t="str">
-        <v>2:18</v>
+        <v>2:09</v>
       </c>
       <c r="H138" t="str">
-        <v>Dillon Francis</v>
+        <v>Lecrae</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/lecrae/130043072</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
+        <v>https://music.apple.com/us/album/living-water/1871564892</v>
       </c>
       <c r="L138" t="str">
-        <v>What It Feels Like - Dillon Francis</v>
+        <v>Living Water - Lecrae</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>neck</v>
+        <v>What It Feels Like</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/neck/1866953832</v>
+        <v>https://music.apple.com/us/song/what-it-feels-like/1870886919</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-09</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>neck - Single</v>
+        <v>What It Feels Like - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:40</v>
+        <v>2:18</v>
       </c>
       <c r="H139" t="str">
-        <v>Mau P</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/neck/1866953831</v>
+        <v>https://music.apple.com/us/album/what-it-feels-like/1870886918</v>
       </c>
       <c r="L139" t="str">
-        <v>neck - Mau P</v>
+        <v>What It Feels Like - Dillon Francis</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Colorblind</v>
+        <v>neck</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
+        <v>https://music.apple.com/us/song/neck/1866953832</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-09</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Colorblind - Single</v>
+        <v>neck - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:56</v>
+        <v>3:40</v>
       </c>
       <c r="H140" t="str">
-        <v>Gavin Adcock</v>
+        <v>Mau P</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
+        <v>https://music.apple.com/us/artist/mau-p/1636676418</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
+        <v>https://music.apple.com/us/album/neck/1866953831</v>
       </c>
       <c r="L140" t="str">
-        <v>Colorblind - Gavin Adcock</v>
+        <v>neck - Mau P</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Au Revoir Reservoir</v>
+        <v>Colorblind</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/au-revoir-reservoir/1847573922</v>
+        <v>https://music.apple.com/us/song/colorblind/1873445412</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-09</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Tenterhooks</v>
+        <v>Colorblind - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:21</v>
+        <v>2:56</v>
       </c>
       <c r="H141" t="str">
-        <v>Silversun Pickups</v>
+        <v>Gavin Adcock</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/silversun-pickups/74752665</v>
+        <v>https://music.apple.com/us/artist/gavin-adcock/1580645019</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/au-revoir-reservoir/1847573918</v>
+        <v>https://music.apple.com/us/album/colorblind/1873445402</v>
       </c>
       <c r="L141" t="str">
-        <v>Au Revoir Reservoir - Silversun Pickups</v>
+        <v>Colorblind - Gavin Adcock</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Flavorless</v>
+        <v>Au Revoir Reservoir</v>
       </c>
       <c r="B142" t="str">
         <v/